--- a/百日新高v4.0最终版/百日新高_报表.xlsx
+++ b/百日新高v4.0最终版/百日新高_报表.xlsx
@@ -13,6 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="风险过滤清单" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="持仓预警" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="全库扫描(MA13±3%)" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="投资洞察" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'核心主线跟踪'!$A$3:$N$225</definedName>
@@ -27,7 +28,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="14">
+  <fonts count="18">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -112,8 +113,31 @@
       <color rgb="004fc3f7"/>
       <sz val="16"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00ef5350"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00ff6b6b"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00cccccc"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00ef5350"/>
+      <sz val="12"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -150,6 +174,18 @@
         <bgColor rgb="002a102a"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="004a1010"/>
+        <bgColor rgb="004a1010"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="003a1010"/>
+        <bgColor rgb="003a1010"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -163,7 +199,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -245,6 +281,33 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -11340,7 +11403,7 @@
       </c>
       <c r="B223" s="14" t="inlineStr">
         <is>
-          <t>迪哲医药</t>
+          <t>迪哲医药 NEW</t>
         </is>
       </c>
       <c r="C223" s="13" t="inlineStr">
@@ -11387,7 +11450,7 @@
       </c>
       <c r="B224" s="8" t="inlineStr">
         <is>
-          <t>微芯生物</t>
+          <t>微芯生物 NEW</t>
         </is>
       </c>
       <c r="C224" s="7" t="inlineStr">
@@ -12900,7 +12963,7 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>博通集成</t>
+          <t>博通集成 NEW</t>
         </is>
       </c>
       <c r="C5" s="18" t="n">
@@ -13026,7 +13089,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>翰宇药业</t>
+          <t>翰宇药业 NEW</t>
         </is>
       </c>
       <c r="C8" s="5" t="n">
@@ -13452,7 +13515,7 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>药康生物</t>
+          <t>药康生物 NEW</t>
         </is>
       </c>
       <c r="C19" s="10" t="n">
@@ -13565,4 +13628,452 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B44"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="40" customHeight="1">
+      <c r="A1" s="28" t="inlineStr">
+        <is>
+          <t>投资洞察与规律总结 v5.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="29" t="inlineStr">
+        <is>
+          <t>大盘状态</t>
+        </is>
+      </c>
+      <c r="B3" s="30" t="inlineStr">
+        <is>
+          <t>震荡市 | 仓位30%-50% | 最大持仓5只</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="29" t="inlineStr">
+        <is>
+          <t>今日主线</t>
+        </is>
+      </c>
+      <c r="B4" s="30" t="inlineStr">
+        <is>
+          <t>创新药/CRO 大爆发（37只，+2只），医药板块整体走强</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="29" t="inlineStr">
+        <is>
+          <t>全库扫描</t>
+        </is>
+      </c>
+      <c r="B5" s="30" t="inlineStr">
+        <is>
+          <t>18只核心股距MA13 ±3%，首列重点关注</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="31" t="inlineStr"/>
+      <c r="B6" s="32" t="inlineStr"/>
+    </row>
+    <row r="7" ht="28" customHeight="1">
+      <c r="A7" s="33" t="inlineStr">
+        <is>
+          <t>═══ 牛股三大规律 ═══</t>
+        </is>
+      </c>
+      <c r="B7" s="34" t="inlineStr"/>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="29" t="inlineStr">
+        <is>
+          <t>类型一·连续涨停型</t>
+        </is>
+      </c>
+      <c r="B8" s="30" t="inlineStr">
+        <is>
+          <t>代表：恒尚节能(603137) 9天连板+106.8%，首日涨停后每日缩量一字板，从未回调</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="29" t="inlineStr">
+        <is>
+          <t>类型二·回踩再起型</t>
+        </is>
+      </c>
+      <c r="B9" s="30" t="inlineStr">
+        <is>
+          <t>代表：翰宇药业(300199) 7/14缩量回踩MA13=-0.81% → 7/15放量+6.94%，买点在缩量企稳日</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="29" t="inlineStr">
+        <is>
+          <t>类型三·横盘突破型</t>
+        </is>
+      </c>
+      <c r="B10" s="30" t="inlineStr">
+        <is>
+          <t>代表：康龙化成(300759) 6次上榜涨跌交替，末段+9.1%放量突破，确认后追入</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="31" t="inlineStr"/>
+      <c r="B11" s="32" t="inlineStr"/>
+    </row>
+    <row r="12" ht="28" customHeight="1">
+      <c r="A12" s="33" t="inlineStr">
+        <is>
+          <t>═══ 垃圾股三大特征 ═══</t>
+        </is>
+      </c>
+      <c r="B12" s="34" t="inlineStr"/>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="29" t="inlineStr">
+        <is>
+          <t>特征一·一日游假突破</t>
+        </is>
+      </c>
+      <c r="B13" s="30" t="inlineStr">
+        <is>
+          <t>42%的百日新高仅上榜1次，首日涨幅&gt;15%的102只次日全部消失</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="29" t="inlineStr">
+        <is>
+          <t>特征二·多次上榜不涨</t>
+        </is>
+      </c>
+      <c r="B14" s="30" t="inlineStr">
+        <is>
+          <t>博通集成(603068) 8次上榜区间-2.8%，上榜频繁但价格不动=主力借新高出货</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="29" t="inlineStr">
+        <is>
+          <t>特征三·首日即见顶</t>
+        </is>
+      </c>
+      <c r="B15" s="30" t="inlineStr">
+        <is>
+          <t>11只股票上榜当日即收跌，盘中冲高回落，无主力支撑</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="31" t="inlineStr"/>
+      <c r="B16" s="32" t="inlineStr"/>
+    </row>
+    <row r="17" ht="28" customHeight="1">
+      <c r="A17" s="33" t="inlineStr">
+        <is>
+          <t>═══ 最佳介入窗口 ═══</t>
+        </is>
+      </c>
+      <c r="B17" s="34" t="inlineStr"/>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="29" t="inlineStr">
+        <is>
+          <t>首发后第3-5天</t>
+        </is>
+      </c>
+      <c r="B18" s="30" t="inlineStr">
+        <is>
+          <t>前2天冲高回落概率大，第3天缩量企稳是买点（回溯验证：候选池平均前瞻+4.1%）</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="29" t="inlineStr">
+        <is>
+          <t>距MA13在±2%以内</t>
+        </is>
+      </c>
+      <c r="B19" s="30" t="inlineStr">
+        <is>
+          <t>双环传动(002472) MA13=-0.17%为经典形态</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="29" t="inlineStr">
+        <is>
+          <t>量比0.5-2.0</t>
+        </is>
+      </c>
+      <c r="B20" s="30" t="inlineStr">
+        <is>
+          <t>太缩量(&lt;0.5)=无人关注，太放量(&gt;2.0)=出货嫌疑，健康区间0.8-2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="29" t="inlineStr">
+        <is>
+          <t>阳线或十字星</t>
+        </is>
+      </c>
+      <c r="B21" s="30" t="inlineStr">
+        <is>
+          <t>排除放量阴线的假企稳</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="31" t="inlineStr"/>
+      <c r="B22" s="32" t="inlineStr"/>
+    </row>
+    <row r="23" ht="28" customHeight="1">
+      <c r="A23" s="33" t="inlineStr">
+        <is>
+          <t>═══ 卖出纪律 ═══</t>
+        </is>
+      </c>
+      <c r="B23" s="34" t="inlineStr"/>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="A24" s="29" t="inlineStr">
+        <is>
+          <t>放量滞涨</t>
+        </is>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>量比&gt;1.5 + 涨幅&lt;1% → 减仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="A25" s="29" t="inlineStr">
+        <is>
+          <t>跌破MA13</t>
+        </is>
+      </c>
+      <c r="B25" s="30" t="inlineStr">
+        <is>
+          <t>收盘&lt;MA13 → 次日开盘止损离场</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="22" customHeight="1">
+      <c r="A26" s="29" t="inlineStr">
+        <is>
+          <t>浮盈&gt;20%</t>
+        </is>
+      </c>
+      <c r="B26" s="30" t="inlineStr">
+        <is>
+          <t>止盈线收紧至MA13</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="22" customHeight="1">
+      <c r="A27" s="29" t="inlineStr">
+        <is>
+          <t>连续3日放量加速</t>
+        </is>
+      </c>
+      <c r="B27" s="30" t="inlineStr">
+        <is>
+          <t>止盈线从MA13收紧至MA5</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="22" customHeight="1">
+      <c r="A28" s="31" t="inlineStr"/>
+      <c r="B28" s="32" t="inlineStr"/>
+    </row>
+    <row r="29" ht="28" customHeight="1">
+      <c r="A29" s="33" t="inlineStr">
+        <is>
+          <t>═══ 7/15 重点盯盘 ═══</t>
+        </is>
+      </c>
+      <c r="B29" s="34" t="inlineStr"/>
+    </row>
+    <row r="30" ht="22" customHeight="1">
+      <c r="A30" s="35" t="inlineStr">
+        <is>
+          <t>今日医药爆发</t>
+        </is>
+      </c>
+      <c r="B30" s="36" t="inlineStr">
+        <is>
+          <t>迪哲医药(688192) NEW +20%、万邦医药(301520) +20%、药康生物(688046) NEW +17% 均为首次新高</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="22" customHeight="1">
+      <c r="A31" s="29" t="inlineStr">
+        <is>
+          <t>持续跟踪</t>
+        </is>
+      </c>
+      <c r="B31" s="30" t="inlineStr">
+        <is>
+          <t>翰宇药业(300199) 缩量回踩后今日+6.9%放量反弹，关注是否持续</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="22" customHeight="1">
+      <c r="A32" s="29" t="inlineStr">
+        <is>
+          <t>均线附近等待</t>
+        </is>
+      </c>
+      <c r="B32" s="30" t="inlineStr">
+        <is>
+          <t>双环传动(002472) MA13=-0.17%、博通集成(603068) MA13=+0.32%，等缩量信号</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="22" customHeight="1">
+      <c r="A33" s="29" t="inlineStr">
+        <is>
+          <t>放量下跌预警</t>
+        </is>
+      </c>
+      <c r="B33" s="30" t="inlineStr">
+        <is>
+          <t>益诺思(688710) MA13=+17.9% 远离均线，今日不在榜但风险高</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="22" customHeight="1">
+      <c r="A34" s="31" t="inlineStr"/>
+      <c r="B34" s="32" t="inlineStr"/>
+    </row>
+    <row r="35" ht="28" customHeight="1">
+      <c r="A35" s="33" t="inlineStr">
+        <is>
+          <t>═══ 回测验证 ═══</t>
+        </is>
+      </c>
+      <c r="B35" s="34" t="inlineStr"/>
+    </row>
+    <row r="36" ht="22" customHeight="1">
+      <c r="A36" s="29" t="inlineStr">
+        <is>
+          <t>翰宇药业案例</t>
+        </is>
+      </c>
+      <c r="B36" s="30" t="inlineStr">
+        <is>
+          <t>7/14缩量回踩MA13(-0.81%)+VR=0.74 → 7/15放量+6.94% 完美验证狙击逻辑</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="22" customHeight="1">
+      <c r="A37" s="29" t="inlineStr">
+        <is>
+          <t>石药创新虚假信号</t>
+        </is>
+      </c>
+      <c r="B37" s="30" t="inlineStr">
+        <is>
+          <t>近似MA13=+0.2%被证伪（真实+11.22%），系统已改用K线硬算，杜绝误判</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="22" customHeight="1">
+      <c r="A38" s="31" t="inlineStr"/>
+      <c r="B38" s="32" t="inlineStr"/>
+    </row>
+    <row r="39" ht="28" customHeight="1">
+      <c r="A39" s="33" t="inlineStr">
+        <is>
+          <t>═══ 系统进化记录 ═══</t>
+        </is>
+      </c>
+      <c r="B39" s="34" t="inlineStr"/>
+    </row>
+    <row r="40" ht="22" customHeight="1">
+      <c r="A40" s="29" t="inlineStr">
+        <is>
+          <t>v5.0 七层规则</t>
+        </is>
+      </c>
+      <c r="B40" s="30" t="inlineStr">
+        <is>
+          <t>三锚定仓→主线过滤→状态分类→风险过滤→狙击池→后备池→卖出预警</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="22" customHeight="1">
+      <c r="A41" s="29" t="inlineStr">
+        <is>
+          <t>全库扫描(新)</t>
+        </is>
+      </c>
+      <c r="B41" s="30" t="inlineStr">
+        <is>
+          <t>不限于当日新高，扫描过去10天所有新高过的核心股在MA13附近的状态</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="22" customHeight="1">
+      <c r="A42" s="29" t="inlineStr">
+        <is>
+          <t>规则一</t>
+        </is>
+      </c>
+      <c r="B42" s="30" t="inlineStr">
+        <is>
+          <t>首日涨幅&gt;15%过滤（102只一日游验证）</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="22" customHeight="1">
+      <c r="A43" s="29" t="inlineStr">
+        <is>
+          <t>规则二</t>
+        </is>
+      </c>
+      <c r="B43" s="30" t="inlineStr">
+        <is>
+          <t>5次上榜涨幅&lt;5%标记疑似出货（博通集成8次-2.8%验证）</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="22" customHeight="1">
+      <c r="A44" s="29" t="inlineStr">
+        <is>
+          <t>NEW标记(新)</t>
+        </is>
+      </c>
+      <c r="B44" s="30" t="inlineStr">
+        <is>
+          <t>每日新增股票自动标注，方便识别首次突破</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:B1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/百日新高v4.0最终版/百日新高_报表.xlsx
+++ b/百日新高v4.0最终版/百日新高_报表.xlsx
@@ -15283,7 +15283,7 @@
       </c>
       <c r="B4" s="34" t="inlineStr">
         <is>
-          <t>-321  !!冰点</t>
+          <t>-1237  !!冰点(新低1260)</t>
         </is>
       </c>
     </row>

--- a/百日新高v4.0最终版/百日新高_报表.xlsx
+++ b/百日新高v4.0最终版/百日新高_报表.xlsx
@@ -19,7 +19,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'核心主线跟踪'!$A$3:$N$243</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'后备观察池'!$A$3:$H$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'风险过滤清单'!$A$3:$G$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'全库扫描(MA13±3%)'!$A$3:$K$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'全库扫描(MA13±3%)'!$A$3:$K$20</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -3591,12 +3591,12 @@
     <row r="60" ht="26" customHeight="1">
       <c r="A60" s="10" t="inlineStr">
         <is>
-          <t>688117</t>
+          <t>600998</t>
         </is>
       </c>
       <c r="B60" s="11" t="inlineStr">
         <is>
-          <t>圣诺生物</t>
+          <t>九州通</t>
         </is>
       </c>
       <c r="C60" s="10" t="inlineStr">
@@ -3606,31 +3606,29 @@
       </c>
       <c r="D60" s="10" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="E60" s="10" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="F60" s="10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G60" s="10" t="inlineStr">
         <is>
           <t>高位整理</t>
         </is>
       </c>
-      <c r="H60" s="12" t="n">
-        <v>2.06</v>
+      <c r="H60" s="14" t="n">
+        <v>-1.93</v>
       </c>
       <c r="I60" s="14" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="J60" s="10" t="n">
-        <v>1.01</v>
-      </c>
+        <v>-0.09</v>
+      </c>
+      <c r="J60" s="10" t="n"/>
       <c r="K60" s="10" t="inlineStr">
         <is>
           <t>正常</t>
@@ -3642,49 +3640,49 @@
     <row r="61" ht="26" customHeight="1">
       <c r="A61" s="7" t="inlineStr">
         <is>
-          <t>300487</t>
+          <t>688117</t>
         </is>
       </c>
       <c r="B61" s="8" t="inlineStr">
         <is>
-          <t>蓝晓科技</t>
+          <t>圣诺生物</t>
         </is>
       </c>
       <c r="C61" s="7" t="inlineStr">
         <is>
-          <t>半导体/芯片</t>
+          <t>创新药/CRO</t>
         </is>
       </c>
       <c r="D61" s="7" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="E61" s="7" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="F61" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G61" s="7" t="inlineStr">
         <is>
           <t>高位整理</t>
         </is>
       </c>
-      <c r="H61" s="9" t="n">
-        <v>-1</v>
+      <c r="H61" s="13" t="n">
+        <v>2.06</v>
       </c>
       <c r="I61" s="9" t="n">
-        <v>0.34</v>
+        <v>0.21</v>
       </c>
       <c r="J61" s="7" t="n">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="K61" s="7" t="inlineStr">
         <is>
-          <t>放量</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="L61" s="7" t="inlineStr"/>
@@ -3693,27 +3691,27 @@
     <row r="62" ht="26" customHeight="1">
       <c r="A62" s="10" t="inlineStr">
         <is>
-          <t>301393</t>
+          <t>300487</t>
         </is>
       </c>
       <c r="B62" s="11" t="inlineStr">
         <is>
-          <t>昊帆生物</t>
+          <t>蓝晓科技</t>
         </is>
       </c>
       <c r="C62" s="10" t="inlineStr">
         <is>
-          <t>创新药/CRO</t>
+          <t>半导体/芯片</t>
         </is>
       </c>
       <c r="D62" s="10" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="E62" s="10" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="F62" s="10" t="n">
@@ -3725,15 +3723,17 @@
         </is>
       </c>
       <c r="H62" s="14" t="n">
-        <v>-1.27</v>
+        <v>-1</v>
       </c>
       <c r="I62" s="14" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="J62" s="10" t="n"/>
+        <v>0.34</v>
+      </c>
+      <c r="J62" s="10" t="n">
+        <v>1.4</v>
+      </c>
       <c r="K62" s="10" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>放量</t>
         </is>
       </c>
       <c r="L62" s="10" t="inlineStr"/>
@@ -3742,27 +3742,27 @@
     <row r="63" ht="26" customHeight="1">
       <c r="A63" s="7" t="inlineStr">
         <is>
-          <t>688795</t>
+          <t>301393</t>
         </is>
       </c>
       <c r="B63" s="8" t="inlineStr">
         <is>
-          <t>摩尔线程</t>
+          <t>昊帆生物</t>
         </is>
       </c>
       <c r="C63" s="7" t="inlineStr">
         <is>
-          <t>算力/通信</t>
+          <t>创新药/CRO</t>
         </is>
       </c>
       <c r="D63" s="7" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="E63" s="7" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="F63" s="7" t="n">
@@ -3773,15 +3773,13 @@
           <t>高位整理</t>
         </is>
       </c>
-      <c r="H63" s="13" t="n">
-        <v>2.12</v>
+      <c r="H63" s="9" t="n">
+        <v>-1.27</v>
       </c>
       <c r="I63" s="9" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="J63" s="7" t="n">
-        <v>0.85</v>
-      </c>
+        <v>0.46</v>
+      </c>
+      <c r="J63" s="7" t="n"/>
       <c r="K63" s="7" t="inlineStr">
         <is>
           <t>正常</t>
@@ -3793,31 +3791,31 @@
     <row r="64" ht="26" customHeight="1">
       <c r="A64" s="15" t="inlineStr">
         <is>
-          <t>300684</t>
+          <t>600285</t>
         </is>
       </c>
       <c r="B64" s="16" t="inlineStr">
         <is>
-          <t>中石科技</t>
+          <t>羚锐制药</t>
         </is>
       </c>
       <c r="C64" s="15" t="inlineStr">
         <is>
-          <t>算力/通信</t>
+          <t>创新药/CRO</t>
         </is>
       </c>
       <c r="D64" s="15" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="E64" s="15" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="F64" s="15" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="G64" s="17" t="inlineStr">
         <is>
@@ -3825,20 +3823,22 @@
         </is>
       </c>
       <c r="H64" s="18" t="n">
-        <v>-6.76</v>
+        <v>-1.71</v>
       </c>
       <c r="I64" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="J64" s="15" t="n"/>
+        <v>1.21</v>
+      </c>
+      <c r="J64" s="15" t="n">
+        <v>1.37</v>
+      </c>
       <c r="K64" s="15" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>放量</t>
         </is>
       </c>
       <c r="L64" s="15" t="inlineStr">
         <is>
-          <t>首日涨幅&gt;20%</t>
+          <t>5次上榜仅涨+2.3%(疑似出货)</t>
         </is>
       </c>
       <c r="M64" s="15" t="inlineStr"/>
@@ -3846,12 +3846,12 @@
     <row r="65" ht="26" customHeight="1">
       <c r="A65" s="7" t="inlineStr">
         <is>
-          <t>688046</t>
+          <t>601607</t>
         </is>
       </c>
       <c r="B65" s="8" t="inlineStr">
         <is>
-          <t>药康生物</t>
+          <t>上海医药 NEW</t>
         </is>
       </c>
       <c r="C65" s="7" t="inlineStr">
@@ -3861,31 +3861,29 @@
       </c>
       <c r="D65" s="7" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="E65" s="7" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="F65" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G65" s="7" t="inlineStr">
         <is>
           <t>高位整理</t>
         </is>
       </c>
-      <c r="H65" s="13" t="n">
-        <v>0.66</v>
+      <c r="H65" s="9" t="n">
+        <v>-1.65</v>
       </c>
       <c r="I65" s="9" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="J65" s="7" t="n">
-        <v>0.93</v>
-      </c>
+        <v>1.52</v>
+      </c>
+      <c r="J65" s="7" t="n"/>
       <c r="K65" s="7" t="inlineStr">
         <is>
           <t>正常</t>
@@ -3895,120 +3893,118 @@
       <c r="M65" s="7" t="inlineStr"/>
     </row>
     <row r="66" ht="26" customHeight="1">
-      <c r="A66" s="15" t="inlineStr">
-        <is>
-          <t>603259</t>
-        </is>
-      </c>
-      <c r="B66" s="16" t="inlineStr">
-        <is>
-          <t>药明康德</t>
-        </is>
-      </c>
-      <c r="C66" s="15" t="inlineStr">
-        <is>
-          <t>创新药/CRO</t>
-        </is>
-      </c>
-      <c r="D66" s="15" t="inlineStr">
-        <is>
-          <t>2026-07-03</t>
-        </is>
-      </c>
-      <c r="E66" s="15" t="inlineStr">
-        <is>
-          <t>2026-07-21</t>
-        </is>
-      </c>
-      <c r="F66" s="15" t="n">
-        <v>5</v>
-      </c>
-      <c r="G66" s="17" t="inlineStr">
+      <c r="A66" s="10" t="inlineStr">
+        <is>
+          <t>688795</t>
+        </is>
+      </c>
+      <c r="B66" s="11" t="inlineStr">
+        <is>
+          <t>摩尔线程</t>
+        </is>
+      </c>
+      <c r="C66" s="10" t="inlineStr">
+        <is>
+          <t>算力/通信</t>
+        </is>
+      </c>
+      <c r="D66" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="E66" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="F66" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="G66" s="10" t="inlineStr">
         <is>
           <t>高位整理</t>
         </is>
       </c>
-      <c r="H66" s="19" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="I66" s="15" t="n">
-        <v>3.03</v>
-      </c>
-      <c r="J66" s="15" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="K66" s="15" t="inlineStr">
-        <is>
-          <t>放量</t>
-        </is>
-      </c>
-      <c r="L66" s="15" t="inlineStr">
-        <is>
-          <t>5次上榜仅涨+1.9%(疑似出货)</t>
-        </is>
-      </c>
-      <c r="M66" s="15" t="inlineStr"/>
+      <c r="H66" s="12" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="I66" s="14" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="J66" s="10" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="K66" s="10" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="L66" s="10" t="inlineStr"/>
+      <c r="M66" s="10" t="inlineStr"/>
     </row>
     <row r="67" ht="26" customHeight="1">
-      <c r="A67" s="7" t="inlineStr">
-        <is>
-          <t>688758</t>
-        </is>
-      </c>
-      <c r="B67" s="8" t="inlineStr">
-        <is>
-          <t>赛分科技</t>
-        </is>
-      </c>
-      <c r="C67" s="7" t="inlineStr">
-        <is>
-          <t>创新药/CRO</t>
-        </is>
-      </c>
-      <c r="D67" s="7" t="inlineStr">
-        <is>
-          <t>2026-07-03</t>
-        </is>
-      </c>
-      <c r="E67" s="7" t="inlineStr">
-        <is>
-          <t>2026-07-21</t>
-        </is>
-      </c>
-      <c r="F67" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="G67" s="7" t="inlineStr">
+      <c r="A67" s="15" t="inlineStr">
+        <is>
+          <t>300684</t>
+        </is>
+      </c>
+      <c r="B67" s="16" t="inlineStr">
+        <is>
+          <t>中石科技</t>
+        </is>
+      </c>
+      <c r="C67" s="15" t="inlineStr">
+        <is>
+          <t>算力/通信</t>
+        </is>
+      </c>
+      <c r="D67" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="E67" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="F67" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="G67" s="17" t="inlineStr">
         <is>
           <t>高位整理</t>
         </is>
       </c>
-      <c r="H67" s="13" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="I67" s="7" t="n">
-        <v>3.77</v>
-      </c>
-      <c r="J67" s="7" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="K67" s="7" t="inlineStr">
-        <is>
-          <t>放量</t>
-        </is>
-      </c>
-      <c r="L67" s="7" t="inlineStr"/>
-      <c r="M67" s="7" t="inlineStr"/>
+      <c r="H67" s="18" t="n">
+        <v>-6.76</v>
+      </c>
+      <c r="I67" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="J67" s="15" t="n"/>
+      <c r="K67" s="15" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="L67" s="15" t="inlineStr">
+        <is>
+          <t>首日涨幅&gt;20%</t>
+        </is>
+      </c>
+      <c r="M67" s="15" t="inlineStr"/>
     </row>
     <row r="68" ht="26" customHeight="1">
       <c r="A68" s="10" t="inlineStr">
         <is>
-          <t>688105</t>
+          <t>688046</t>
         </is>
       </c>
       <c r="B68" s="11" t="inlineStr">
         <is>
-          <t>诺唯赞</t>
+          <t>药康生物</t>
         </is>
       </c>
       <c r="C68" s="10" t="inlineStr">
@@ -4023,11 +4019,11 @@
       </c>
       <c r="E68" s="10" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="F68" s="10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G68" s="10" t="inlineStr">
         <is>
@@ -4035,97 +4031,101 @@
         </is>
       </c>
       <c r="H68" s="12" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="I68" s="10" t="n">
-        <v>4.52</v>
+        <v>0.66</v>
+      </c>
+      <c r="I68" s="14" t="n">
+        <v>2.68</v>
       </c>
       <c r="J68" s="10" t="n">
-        <v>1.26</v>
+        <v>0.93</v>
       </c>
       <c r="K68" s="10" t="inlineStr">
         <is>
-          <t>放量</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="L68" s="10" t="inlineStr"/>
       <c r="M68" s="10" t="inlineStr"/>
     </row>
     <row r="69" ht="26" customHeight="1">
-      <c r="A69" s="7" t="inlineStr">
-        <is>
-          <t>003033</t>
-        </is>
-      </c>
-      <c r="B69" s="8" t="inlineStr">
-        <is>
-          <t>征和工业</t>
-        </is>
-      </c>
-      <c r="C69" s="7" t="inlineStr">
-        <is>
-          <t>机器人</t>
-        </is>
-      </c>
-      <c r="D69" s="7" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="E69" s="7" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="F69" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="G69" s="7" t="inlineStr">
+      <c r="A69" s="15" t="inlineStr">
+        <is>
+          <t>603259</t>
+        </is>
+      </c>
+      <c r="B69" s="16" t="inlineStr">
+        <is>
+          <t>药明康德</t>
+        </is>
+      </c>
+      <c r="C69" s="15" t="inlineStr">
+        <is>
+          <t>创新药/CRO</t>
+        </is>
+      </c>
+      <c r="D69" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="E69" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="F69" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="G69" s="17" t="inlineStr">
         <is>
           <t>高位整理</t>
         </is>
       </c>
-      <c r="H69" s="9" t="n">
-        <v>-1.64</v>
-      </c>
-      <c r="I69" s="7" t="n">
-        <v>5.67</v>
-      </c>
-      <c r="J69" s="7" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="K69" s="7" t="inlineStr">
-        <is>
-          <t>正常</t>
-        </is>
-      </c>
-      <c r="L69" s="7" t="inlineStr"/>
-      <c r="M69" s="7" t="inlineStr"/>
+      <c r="H69" s="19" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="I69" s="18" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="J69" s="15" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="K69" s="15" t="inlineStr">
+        <is>
+          <t>放量</t>
+        </is>
+      </c>
+      <c r="L69" s="15" t="inlineStr">
+        <is>
+          <t>5次上榜仅涨+1.9%(疑似出货)</t>
+        </is>
+      </c>
+      <c r="M69" s="15" t="inlineStr"/>
     </row>
     <row r="70" ht="26" customHeight="1">
       <c r="A70" s="10" t="inlineStr">
         <is>
-          <t>002536</t>
+          <t>688105</t>
         </is>
       </c>
       <c r="B70" s="11" t="inlineStr">
         <is>
-          <t>飞龙股份</t>
+          <t>诺唯赞</t>
         </is>
       </c>
       <c r="C70" s="10" t="inlineStr">
         <is>
-          <t>算力/通信</t>
+          <t>创新药/CRO</t>
         </is>
       </c>
       <c r="D70" s="10" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="E70" s="10" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="F70" s="10" t="n">
@@ -4136,18 +4136,18 @@
           <t>高位整理</t>
         </is>
       </c>
-      <c r="H70" s="14" t="n">
-        <v>-2.18</v>
+      <c r="H70" s="12" t="n">
+        <v>1.03</v>
       </c>
       <c r="I70" s="10" t="n">
-        <v>5.82</v>
+        <v>4.52</v>
       </c>
       <c r="J70" s="10" t="n">
-        <v>0.98</v>
+        <v>1.26</v>
       </c>
       <c r="K70" s="10" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>放量</t>
         </is>
       </c>
       <c r="L70" s="10" t="inlineStr"/>
@@ -4156,12 +4156,12 @@
     <row r="71" ht="26" customHeight="1">
       <c r="A71" s="7" t="inlineStr">
         <is>
-          <t>600129</t>
+          <t>002603</t>
         </is>
       </c>
       <c r="B71" s="8" t="inlineStr">
         <is>
-          <t>太极集团</t>
+          <t>以岭药业</t>
         </is>
       </c>
       <c r="C71" s="7" t="inlineStr">
@@ -4171,34 +4171,32 @@
       </c>
       <c r="D71" s="7" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="E71" s="7" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="F71" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G71" s="7" t="inlineStr">
         <is>
           <t>高位整理</t>
         </is>
       </c>
-      <c r="H71" s="13" t="n">
-        <v>1.99</v>
+      <c r="H71" s="9" t="n">
+        <v>-1.99</v>
       </c>
       <c r="I71" s="7" t="n">
-        <v>5.89</v>
-      </c>
-      <c r="J71" s="7" t="n">
-        <v>1.62</v>
-      </c>
+        <v>5.48</v>
+      </c>
+      <c r="J71" s="7" t="n"/>
       <c r="K71" s="7" t="inlineStr">
         <is>
-          <t>放量</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="L71" s="7" t="inlineStr"/>
@@ -4207,45 +4205,45 @@
     <row r="72" ht="26" customHeight="1">
       <c r="A72" s="10" t="inlineStr">
         <is>
-          <t>688222</t>
+          <t>003033</t>
         </is>
       </c>
       <c r="B72" s="11" t="inlineStr">
         <is>
-          <t>成都先导</t>
+          <t>征和工业</t>
         </is>
       </c>
       <c r="C72" s="10" t="inlineStr">
         <is>
-          <t>创新药/CRO</t>
+          <t>机器人</t>
         </is>
       </c>
       <c r="D72" s="10" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="E72" s="10" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="F72" s="10" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G72" s="10" t="inlineStr">
         <is>
           <t>高位整理</t>
         </is>
       </c>
-      <c r="H72" s="12" t="n">
-        <v>2.98</v>
+      <c r="H72" s="14" t="n">
+        <v>-1.64</v>
       </c>
       <c r="I72" s="10" t="n">
-        <v>7.64</v>
+        <v>5.67</v>
       </c>
       <c r="J72" s="10" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="K72" s="10" t="inlineStr">
         <is>
@@ -4256,69 +4254,65 @@
       <c r="M72" s="10" t="inlineStr"/>
     </row>
     <row r="73" ht="26" customHeight="1">
-      <c r="A73" s="15" t="inlineStr">
-        <is>
-          <t>600285</t>
-        </is>
-      </c>
-      <c r="B73" s="16" t="inlineStr">
-        <is>
-          <t>羚锐制药</t>
-        </is>
-      </c>
-      <c r="C73" s="15" t="inlineStr">
-        <is>
-          <t>创新药/CRO</t>
-        </is>
-      </c>
-      <c r="D73" s="15" t="inlineStr">
-        <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="E73" s="15" t="inlineStr">
-        <is>
-          <t>2026-07-21</t>
-        </is>
-      </c>
-      <c r="F73" s="15" t="n">
-        <v>10</v>
-      </c>
-      <c r="G73" s="17" t="inlineStr">
+      <c r="A73" s="7" t="inlineStr">
+        <is>
+          <t>002536</t>
+        </is>
+      </c>
+      <c r="B73" s="8" t="inlineStr">
+        <is>
+          <t>飞龙股份</t>
+        </is>
+      </c>
+      <c r="C73" s="7" t="inlineStr">
+        <is>
+          <t>算力/通信</t>
+        </is>
+      </c>
+      <c r="D73" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="E73" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="F73" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="G73" s="7" t="inlineStr">
         <is>
           <t>高位整理</t>
         </is>
       </c>
-      <c r="H73" s="18" t="n">
-        <v>-1.71</v>
-      </c>
-      <c r="I73" s="15" t="n">
-        <v>7.89</v>
-      </c>
-      <c r="J73" s="15" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="K73" s="15" t="inlineStr">
-        <is>
-          <t>放量</t>
-        </is>
-      </c>
-      <c r="L73" s="15" t="inlineStr">
-        <is>
-          <t>5次上榜仅涨+2.3%(疑似出货)</t>
-        </is>
-      </c>
-      <c r="M73" s="15" t="inlineStr"/>
+      <c r="H73" s="9" t="n">
+        <v>-2.18</v>
+      </c>
+      <c r="I73" s="7" t="n">
+        <v>5.82</v>
+      </c>
+      <c r="J73" s="7" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="K73" s="7" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="L73" s="7" t="inlineStr"/>
+      <c r="M73" s="7" t="inlineStr"/>
     </row>
     <row r="74" ht="26" customHeight="1">
       <c r="A74" s="10" t="inlineStr">
         <is>
-          <t>603087</t>
+          <t>600129</t>
         </is>
       </c>
       <c r="B74" s="11" t="inlineStr">
         <is>
-          <t>甘李药业</t>
+          <t>太极集团</t>
         </is>
       </c>
       <c r="C74" s="10" t="inlineStr">
@@ -4328,30 +4322,30 @@
       </c>
       <c r="D74" s="10" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="E74" s="10" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="F74" s="10" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G74" s="10" t="inlineStr">
         <is>
           <t>高位整理</t>
         </is>
       </c>
-      <c r="H74" s="14" t="n">
-        <v>-0.42</v>
+      <c r="H74" s="12" t="n">
+        <v>1.99</v>
       </c>
       <c r="I74" s="10" t="n">
-        <v>8.42</v>
+        <v>5.89</v>
       </c>
       <c r="J74" s="10" t="n">
-        <v>1.39</v>
+        <v>1.62</v>
       </c>
       <c r="K74" s="10" t="inlineStr">
         <is>
@@ -4364,12 +4358,12 @@
     <row r="75" ht="26" customHeight="1">
       <c r="A75" s="7" t="inlineStr">
         <is>
-          <t>600521</t>
+          <t>688222</t>
         </is>
       </c>
       <c r="B75" s="8" t="inlineStr">
         <is>
-          <t>华海药业</t>
+          <t>成都先导</t>
         </is>
       </c>
       <c r="C75" s="7" t="inlineStr">
@@ -4379,16 +4373,16 @@
       </c>
       <c r="D75" s="7" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="E75" s="7" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="F75" s="7" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G75" s="7" t="inlineStr">
         <is>
@@ -4396,12 +4390,14 @@
         </is>
       </c>
       <c r="H75" s="13" t="n">
-        <v>0.36</v>
+        <v>2.98</v>
       </c>
       <c r="I75" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="J75" s="7" t="n"/>
+        <v>7.64</v>
+      </c>
+      <c r="J75" s="7" t="n">
+        <v>1</v>
+      </c>
       <c r="K75" s="7" t="inlineStr">
         <is>
           <t>正常</t>
@@ -4413,12 +4409,12 @@
     <row r="76" ht="26" customHeight="1">
       <c r="A76" s="10" t="inlineStr">
         <is>
-          <t>002653</t>
+          <t>600267</t>
         </is>
       </c>
       <c r="B76" s="11" t="inlineStr">
         <is>
-          <t>海思科</t>
+          <t>海正药业</t>
         </is>
       </c>
       <c r="C76" s="10" t="inlineStr">
@@ -4428,12 +4424,12 @@
       </c>
       <c r="D76" s="10" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="E76" s="10" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="F76" s="10" t="n">
@@ -4445,10 +4441,10 @@
         </is>
       </c>
       <c r="H76" s="14" t="n">
-        <v>-2.96</v>
+        <v>-2.17</v>
       </c>
       <c r="I76" s="10" t="n">
-        <v>11.09</v>
+        <v>8</v>
       </c>
       <c r="J76" s="10" t="n"/>
       <c r="K76" s="10" t="inlineStr">
@@ -4462,12 +4458,12 @@
     <row r="77" ht="26" customHeight="1">
       <c r="A77" s="7" t="inlineStr">
         <is>
-          <t>600535</t>
+          <t>603087</t>
         </is>
       </c>
       <c r="B77" s="8" t="inlineStr">
         <is>
-          <t>天士力</t>
+          <t>甘李药业</t>
         </is>
       </c>
       <c r="C77" s="7" t="inlineStr">
@@ -4477,16 +4473,16 @@
       </c>
       <c r="D77" s="7" t="inlineStr">
         <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="E77" s="7" t="inlineStr">
+        <is>
           <t>2026-07-16</t>
         </is>
       </c>
-      <c r="E77" s="7" t="inlineStr">
-        <is>
-          <t>2026-07-21</t>
-        </is>
-      </c>
       <c r="F77" s="7" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G77" s="7" t="inlineStr">
         <is>
@@ -4494,15 +4490,17 @@
         </is>
       </c>
       <c r="H77" s="9" t="n">
-        <v>-0.62</v>
+        <v>-0.42</v>
       </c>
       <c r="I77" s="7" t="n">
-        <v>11.69</v>
-      </c>
-      <c r="J77" s="7" t="n"/>
+        <v>8.42</v>
+      </c>
+      <c r="J77" s="7" t="n">
+        <v>1.39</v>
+      </c>
       <c r="K77" s="7" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>放量</t>
         </is>
       </c>
       <c r="L77" s="7" t="inlineStr"/>
@@ -4511,31 +4509,31 @@
     <row r="78" ht="26" customHeight="1">
       <c r="A78" s="10" t="inlineStr">
         <is>
-          <t>688802</t>
+          <t>600521</t>
         </is>
       </c>
       <c r="B78" s="11" t="inlineStr">
         <is>
-          <t>沐曦股份</t>
+          <t>华海药业</t>
         </is>
       </c>
       <c r="C78" s="10" t="inlineStr">
         <is>
-          <t>算力/通信</t>
+          <t>创新药/CRO</t>
         </is>
       </c>
       <c r="D78" s="10" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="E78" s="10" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="F78" s="10" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G78" s="10" t="inlineStr">
         <is>
@@ -4543,14 +4541,12 @@
         </is>
       </c>
       <c r="H78" s="12" t="n">
-        <v>0.19</v>
+        <v>0.36</v>
       </c>
       <c r="I78" s="10" t="n">
-        <v>16.94</v>
-      </c>
-      <c r="J78" s="10" t="n">
-        <v>0.8100000000000001</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="J78" s="10" t="n"/>
       <c r="K78" s="10" t="inlineStr">
         <is>
           <t>正常</t>
@@ -4562,27 +4558,27 @@
     <row r="79" ht="26" customHeight="1">
       <c r="A79" s="7" t="inlineStr">
         <is>
-          <t>300145</t>
+          <t>002653</t>
         </is>
       </c>
       <c r="B79" s="8" t="inlineStr">
         <is>
-          <t>南方泵业</t>
+          <t>海思科</t>
         </is>
       </c>
       <c r="C79" s="7" t="inlineStr">
         <is>
-          <t>算力/通信</t>
+          <t>创新药/CRO</t>
         </is>
       </c>
       <c r="D79" s="7" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="E79" s="7" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="F79" s="7" t="n">
@@ -4593,24 +4589,30 @@
           <t>高位整理</t>
         </is>
       </c>
-      <c r="H79" s="13" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="I79" s="7" t="n"/>
+      <c r="H79" s="9" t="n">
+        <v>-2.96</v>
+      </c>
+      <c r="I79" s="7" t="n">
+        <v>11.09</v>
+      </c>
       <c r="J79" s="7" t="n"/>
-      <c r="K79" s="7" t="inlineStr"/>
+      <c r="K79" s="7" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
       <c r="L79" s="7" t="inlineStr"/>
       <c r="M79" s="7" t="inlineStr"/>
     </row>
     <row r="80" ht="26" customHeight="1">
       <c r="A80" s="10" t="inlineStr">
         <is>
-          <t>301080</t>
+          <t>600535</t>
         </is>
       </c>
       <c r="B80" s="11" t="inlineStr">
         <is>
-          <t>百普赛斯</t>
+          <t>天士力</t>
         </is>
       </c>
       <c r="C80" s="10" t="inlineStr">
@@ -4620,16 +4622,16 @@
       </c>
       <c r="D80" s="10" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="E80" s="10" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="F80" s="10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G80" s="10" t="inlineStr">
         <is>
@@ -4637,92 +4639,90 @@
         </is>
       </c>
       <c r="H80" s="14" t="n">
-        <v>-0.32</v>
-      </c>
-      <c r="I80" s="10" t="n"/>
-      <c r="J80" s="10" t="n">
-        <v>1.74</v>
-      </c>
+        <v>-0.62</v>
+      </c>
+      <c r="I80" s="10" t="n">
+        <v>11.69</v>
+      </c>
+      <c r="J80" s="10" t="n"/>
       <c r="K80" s="10" t="inlineStr">
         <is>
-          <t>放量</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="L80" s="10" t="inlineStr"/>
       <c r="M80" s="10" t="inlineStr"/>
     </row>
     <row r="81" ht="26" customHeight="1">
-      <c r="A81" s="15" t="inlineStr">
-        <is>
-          <t>301310</t>
-        </is>
-      </c>
-      <c r="B81" s="16" t="inlineStr">
-        <is>
-          <t>鑫宏业</t>
-        </is>
-      </c>
-      <c r="C81" s="15" t="inlineStr">
-        <is>
-          <t>机器人</t>
-        </is>
-      </c>
-      <c r="D81" s="15" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="E81" s="15" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-      <c r="F81" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="G81" s="17" t="inlineStr">
+      <c r="A81" s="7" t="inlineStr">
+        <is>
+          <t>688758</t>
+        </is>
+      </c>
+      <c r="B81" s="8" t="inlineStr">
+        <is>
+          <t>赛分科技</t>
+        </is>
+      </c>
+      <c r="C81" s="7" t="inlineStr">
+        <is>
+          <t>创新药/CRO</t>
+        </is>
+      </c>
+      <c r="D81" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="E81" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="F81" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="G81" s="7" t="inlineStr">
         <is>
           <t>高位整理</t>
         </is>
       </c>
-      <c r="H81" s="18" t="n">
-        <v>-0.34</v>
-      </c>
-      <c r="I81" s="15" t="n"/>
-      <c r="J81" s="15" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="K81" s="15" t="inlineStr">
+      <c r="H81" s="13" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="I81" s="7" t="n">
+        <v>13.71</v>
+      </c>
+      <c r="J81" s="7" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="K81" s="7" t="inlineStr">
         <is>
           <t>放量</t>
         </is>
       </c>
-      <c r="L81" s="15" t="inlineStr">
-        <is>
-          <t>首日涨幅&gt;17%</t>
-        </is>
-      </c>
-      <c r="M81" s="15" t="inlineStr"/>
+      <c r="L81" s="7" t="inlineStr"/>
+      <c r="M81" s="7" t="inlineStr"/>
     </row>
     <row r="82" ht="26" customHeight="1">
       <c r="A82" s="10" t="inlineStr">
         <is>
-          <t>002674</t>
+          <t>688802</t>
         </is>
       </c>
       <c r="B82" s="11" t="inlineStr">
         <is>
-          <t>兴业科技</t>
+          <t>沐曦股份</t>
         </is>
       </c>
       <c r="C82" s="10" t="inlineStr">
         <is>
-          <t>半导体/芯片</t>
+          <t>算力/通信</t>
         </is>
       </c>
       <c r="D82" s="10" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="E82" s="10" t="inlineStr">
@@ -4731,19 +4731,21 @@
         </is>
       </c>
       <c r="F82" s="10" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G82" s="10" t="inlineStr">
         <is>
           <t>高位整理</t>
         </is>
       </c>
-      <c r="H82" s="14" t="n">
-        <v>-3.22</v>
-      </c>
-      <c r="I82" s="10" t="n"/>
+      <c r="H82" s="12" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="I82" s="10" t="n">
+        <v>16.94</v>
+      </c>
       <c r="J82" s="10" t="n">
-        <v>1.12</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="K82" s="10" t="inlineStr">
         <is>
@@ -4756,12 +4758,12 @@
     <row r="83" ht="26" customHeight="1">
       <c r="A83" s="7" t="inlineStr">
         <is>
-          <t>603019</t>
+          <t>300145</t>
         </is>
       </c>
       <c r="B83" s="8" t="inlineStr">
         <is>
-          <t>中科曙光</t>
+          <t>南方泵业</t>
         </is>
       </c>
       <c r="C83" s="7" t="inlineStr">
@@ -4771,271 +4773,293 @@
       </c>
       <c r="D83" s="7" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="E83" s="7" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="F83" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G83" s="7" t="inlineStr">
         <is>
           <t>高位整理</t>
         </is>
       </c>
-      <c r="H83" s="9" t="n">
-        <v>-1.27</v>
+      <c r="H83" s="13" t="n">
+        <v>0.32</v>
       </c>
       <c r="I83" s="7" t="n"/>
-      <c r="J83" s="7" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="K83" s="7" t="inlineStr">
-        <is>
-          <t>正常</t>
-        </is>
-      </c>
+      <c r="J83" s="7" t="n"/>
+      <c r="K83" s="7" t="inlineStr"/>
       <c r="L83" s="7" t="inlineStr"/>
       <c r="M83" s="7" t="inlineStr"/>
     </row>
     <row r="84" ht="26" customHeight="1">
-      <c r="A84" s="15" t="inlineStr">
-        <is>
-          <t>603233</t>
-        </is>
-      </c>
-      <c r="B84" s="16" t="inlineStr">
-        <is>
-          <t>大参林</t>
-        </is>
-      </c>
-      <c r="C84" s="15" t="inlineStr">
+      <c r="A84" s="10" t="inlineStr">
+        <is>
+          <t>301080</t>
+        </is>
+      </c>
+      <c r="B84" s="11" t="inlineStr">
+        <is>
+          <t>百普赛斯</t>
+        </is>
+      </c>
+      <c r="C84" s="10" t="inlineStr">
         <is>
           <t>创新药/CRO</t>
         </is>
       </c>
-      <c r="D84" s="15" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="E84" s="15" t="inlineStr">
-        <is>
-          <t>2026-07-21</t>
-        </is>
-      </c>
-      <c r="F84" s="15" t="n">
-        <v>6</v>
-      </c>
-      <c r="G84" s="17" t="inlineStr">
+      <c r="D84" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="E84" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="F84" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="G84" s="10" t="inlineStr">
         <is>
           <t>高位整理</t>
         </is>
       </c>
-      <c r="H84" s="19" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="I84" s="15" t="n"/>
-      <c r="J84" s="15" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="K84" s="15" t="inlineStr">
+      <c r="H84" s="14" t="n">
+        <v>-0.32</v>
+      </c>
+      <c r="I84" s="10" t="n"/>
+      <c r="J84" s="10" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="K84" s="10" t="inlineStr">
         <is>
           <t>放量</t>
         </is>
       </c>
-      <c r="L84" s="15" t="inlineStr">
-        <is>
-          <t>5次上榜仅涨-3.9%(疑似出货)</t>
-        </is>
-      </c>
-      <c r="M84" s="15" t="inlineStr"/>
+      <c r="L84" s="10" t="inlineStr"/>
+      <c r="M84" s="10" t="inlineStr"/>
     </row>
     <row r="85" ht="26" customHeight="1">
-      <c r="A85" s="7" t="inlineStr">
-        <is>
-          <t>301047</t>
-        </is>
-      </c>
-      <c r="B85" s="8" t="inlineStr">
-        <is>
-          <t>义翘神州</t>
-        </is>
-      </c>
-      <c r="C85" s="7" t="inlineStr">
-        <is>
-          <t>创新药/CRO</t>
-        </is>
-      </c>
-      <c r="D85" s="7" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="E85" s="7" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="F85" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G85" s="7" t="inlineStr">
+      <c r="A85" s="15" t="inlineStr">
+        <is>
+          <t>301310</t>
+        </is>
+      </c>
+      <c r="B85" s="16" t="inlineStr">
+        <is>
+          <t>鑫宏业</t>
+        </is>
+      </c>
+      <c r="C85" s="15" t="inlineStr">
+        <is>
+          <t>机器人</t>
+        </is>
+      </c>
+      <c r="D85" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="E85" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="F85" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="G85" s="17" t="inlineStr">
         <is>
           <t>高位整理</t>
         </is>
       </c>
-      <c r="H85" s="13" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="I85" s="7" t="n"/>
-      <c r="J85" s="7" t="n"/>
-      <c r="K85" s="7" t="inlineStr"/>
-      <c r="L85" s="7" t="inlineStr"/>
-      <c r="M85" s="7" t="inlineStr"/>
+      <c r="H85" s="18" t="n">
+        <v>-0.34</v>
+      </c>
+      <c r="I85" s="15" t="n"/>
+      <c r="J85" s="15" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="K85" s="15" t="inlineStr">
+        <is>
+          <t>放量</t>
+        </is>
+      </c>
+      <c r="L85" s="15" t="inlineStr">
+        <is>
+          <t>首日涨幅&gt;17%</t>
+        </is>
+      </c>
+      <c r="M85" s="15" t="inlineStr"/>
     </row>
     <row r="86" ht="26" customHeight="1">
       <c r="A86" s="10" t="inlineStr">
         <is>
-          <t>688068</t>
+          <t>002674</t>
         </is>
       </c>
       <c r="B86" s="11" t="inlineStr">
         <is>
-          <t>热景生物</t>
+          <t>兴业科技</t>
         </is>
       </c>
       <c r="C86" s="10" t="inlineStr">
         <is>
-          <t>创新药/CRO</t>
+          <t>半导体/芯片</t>
         </is>
       </c>
       <c r="D86" s="10" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="E86" s="10" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="F86" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G86" s="10" t="inlineStr">
         <is>
           <t>高位整理</t>
         </is>
       </c>
-      <c r="H86" s="12" t="n">
-        <v>2.88</v>
+      <c r="H86" s="14" t="n">
+        <v>-3.22</v>
       </c>
       <c r="I86" s="10" t="n"/>
-      <c r="J86" s="10" t="n"/>
-      <c r="K86" s="10" t="inlineStr"/>
+      <c r="J86" s="10" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="K86" s="10" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
       <c r="L86" s="10" t="inlineStr"/>
       <c r="M86" s="10" t="inlineStr"/>
     </row>
     <row r="87" ht="26" customHeight="1">
       <c r="A87" s="7" t="inlineStr">
         <is>
-          <t>000739</t>
+          <t>603019</t>
         </is>
       </c>
       <c r="B87" s="8" t="inlineStr">
         <is>
-          <t>普洛药业</t>
+          <t>中科曙光</t>
         </is>
       </c>
       <c r="C87" s="7" t="inlineStr">
         <is>
-          <t>创新药/CRO</t>
+          <t>算力/通信</t>
         </is>
       </c>
       <c r="D87" s="7" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="E87" s="7" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="F87" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G87" s="7" t="inlineStr">
         <is>
           <t>高位整理</t>
         </is>
       </c>
-      <c r="H87" s="13" t="n">
-        <v>0.55</v>
+      <c r="H87" s="9" t="n">
+        <v>-1.27</v>
       </c>
       <c r="I87" s="7" t="n"/>
-      <c r="J87" s="7" t="n"/>
-      <c r="K87" s="7" t="inlineStr"/>
+      <c r="J87" s="7" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="K87" s="7" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
       <c r="L87" s="7" t="inlineStr"/>
       <c r="M87" s="7" t="inlineStr"/>
     </row>
     <row r="88" ht="26" customHeight="1">
-      <c r="A88" s="10" t="inlineStr">
-        <is>
-          <t>002384</t>
-        </is>
-      </c>
-      <c r="B88" s="11" t="inlineStr">
-        <is>
-          <t>东山精密</t>
-        </is>
-      </c>
-      <c r="C88" s="10" t="inlineStr">
-        <is>
-          <t>算力/通信</t>
-        </is>
-      </c>
-      <c r="D88" s="10" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="E88" s="10" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="F88" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="G88" s="10" t="inlineStr">
+      <c r="A88" s="15" t="inlineStr">
+        <is>
+          <t>603233</t>
+        </is>
+      </c>
+      <c r="B88" s="16" t="inlineStr">
+        <is>
+          <t>大参林</t>
+        </is>
+      </c>
+      <c r="C88" s="15" t="inlineStr">
+        <is>
+          <t>创新药/CRO</t>
+        </is>
+      </c>
+      <c r="D88" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E88" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="F88" s="15" t="n">
+        <v>6</v>
+      </c>
+      <c r="G88" s="17" t="inlineStr">
         <is>
           <t>高位整理</t>
         </is>
       </c>
-      <c r="H88" s="12" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="I88" s="10" t="n"/>
-      <c r="J88" s="10" t="n"/>
-      <c r="K88" s="10" t="inlineStr"/>
-      <c r="L88" s="10" t="inlineStr"/>
-      <c r="M88" s="10" t="inlineStr"/>
+      <c r="H88" s="19" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="I88" s="15" t="n"/>
+      <c r="J88" s="15" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="K88" s="15" t="inlineStr">
+        <is>
+          <t>放量</t>
+        </is>
+      </c>
+      <c r="L88" s="15" t="inlineStr">
+        <is>
+          <t>5次上榜仅涨-3.9%(疑似出货)</t>
+        </is>
+      </c>
+      <c r="M88" s="15" t="inlineStr"/>
     </row>
     <row r="89" ht="26" customHeight="1">
       <c r="A89" s="7" t="inlineStr">
         <is>
-          <t>300725</t>
+          <t>301047</t>
         </is>
       </c>
       <c r="B89" s="8" t="inlineStr">
         <is>
-          <t>药石科技</t>
+          <t>义翘神州</t>
         </is>
       </c>
       <c r="C89" s="7" t="inlineStr">
@@ -5062,7 +5086,7 @@
         </is>
       </c>
       <c r="H89" s="13" t="n">
-        <v>1.98</v>
+        <v>2.96</v>
       </c>
       <c r="I89" s="7" t="n"/>
       <c r="J89" s="7" t="n"/>
@@ -5073,12 +5097,12 @@
     <row r="90" ht="26" customHeight="1">
       <c r="A90" s="10" t="inlineStr">
         <is>
-          <t>600267</t>
+          <t>688068</t>
         </is>
       </c>
       <c r="B90" s="11" t="inlineStr">
         <is>
-          <t>海正药业</t>
+          <t>热景生物</t>
         </is>
       </c>
       <c r="C90" s="10" t="inlineStr">
@@ -5093,19 +5117,19 @@
       </c>
       <c r="E90" s="10" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="F90" s="10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G90" s="10" t="inlineStr">
         <is>
           <t>高位整理</t>
         </is>
       </c>
-      <c r="H90" s="14" t="n">
-        <v>-2.17</v>
+      <c r="H90" s="12" t="n">
+        <v>2.88</v>
       </c>
       <c r="I90" s="10" t="n"/>
       <c r="J90" s="10" t="n"/>
@@ -5116,12 +5140,12 @@
     <row r="91" ht="26" customHeight="1">
       <c r="A91" s="7" t="inlineStr">
         <is>
-          <t>002603</t>
+          <t>000739</t>
         </is>
       </c>
       <c r="B91" s="8" t="inlineStr">
         <is>
-          <t>以岭药业</t>
+          <t>普洛药业</t>
         </is>
       </c>
       <c r="C91" s="7" t="inlineStr">
@@ -5147,8 +5171,8 @@
           <t>高位整理</t>
         </is>
       </c>
-      <c r="H91" s="9" t="n">
-        <v>-1.99</v>
+      <c r="H91" s="13" t="n">
+        <v>0.55</v>
       </c>
       <c r="I91" s="7" t="n"/>
       <c r="J91" s="7" t="n"/>
@@ -5159,17 +5183,17 @@
     <row r="92" ht="26" customHeight="1">
       <c r="A92" s="10" t="inlineStr">
         <is>
-          <t>000989</t>
+          <t>002384</t>
         </is>
       </c>
       <c r="B92" s="11" t="inlineStr">
         <is>
-          <t>九芝堂</t>
+          <t>东山精密</t>
         </is>
       </c>
       <c r="C92" s="10" t="inlineStr">
         <is>
-          <t>创新药/CRO</t>
+          <t>算力/通信</t>
         </is>
       </c>
       <c r="D92" s="10" t="inlineStr">
@@ -5190,8 +5214,8 @@
           <t>高位整理</t>
         </is>
       </c>
-      <c r="H92" s="14" t="n">
-        <v>-3.3</v>
+      <c r="H92" s="12" t="n">
+        <v>2.4</v>
       </c>
       <c r="I92" s="10" t="n"/>
       <c r="J92" s="10" t="n"/>
@@ -5202,12 +5226,12 @@
     <row r="93" ht="26" customHeight="1">
       <c r="A93" s="7" t="inlineStr">
         <is>
-          <t>002907</t>
+          <t>300725</t>
         </is>
       </c>
       <c r="B93" s="8" t="inlineStr">
         <is>
-          <t>华森制药</t>
+          <t>药石科技</t>
         </is>
       </c>
       <c r="C93" s="7" t="inlineStr">
@@ -5233,8 +5257,8 @@
           <t>高位整理</t>
         </is>
       </c>
-      <c r="H93" s="9" t="n">
-        <v>-3.9</v>
+      <c r="H93" s="13" t="n">
+        <v>1.98</v>
       </c>
       <c r="I93" s="7" t="n"/>
       <c r="J93" s="7" t="n"/>
@@ -5245,12 +5269,12 @@
     <row r="94" ht="26" customHeight="1">
       <c r="A94" s="10" t="inlineStr">
         <is>
-          <t>600998</t>
+          <t>000989</t>
         </is>
       </c>
       <c r="B94" s="11" t="inlineStr">
         <is>
-          <t>九州通</t>
+          <t>九芝堂</t>
         </is>
       </c>
       <c r="C94" s="10" t="inlineStr">
@@ -5260,16 +5284,16 @@
       </c>
       <c r="D94" s="10" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="E94" s="10" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="F94" s="10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G94" s="10" t="inlineStr">
         <is>
@@ -5277,7 +5301,7 @@
         </is>
       </c>
       <c r="H94" s="14" t="n">
-        <v>-1.93</v>
+        <v>-3.3</v>
       </c>
       <c r="I94" s="10" t="n"/>
       <c r="J94" s="10" t="n"/>
@@ -5288,12 +5312,12 @@
     <row r="95" ht="26" customHeight="1">
       <c r="A95" s="7" t="inlineStr">
         <is>
-          <t>600566</t>
+          <t>002907</t>
         </is>
       </c>
       <c r="B95" s="8" t="inlineStr">
         <is>
-          <t>济川药业 NEW</t>
+          <t>华森制药</t>
         </is>
       </c>
       <c r="C95" s="7" t="inlineStr">
@@ -5303,12 +5327,12 @@
       </c>
       <c r="D95" s="7" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="E95" s="7" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="F95" s="7" t="n">
@@ -5319,8 +5343,8 @@
           <t>高位整理</t>
         </is>
       </c>
-      <c r="H95" s="13" t="n">
-        <v>1.46</v>
+      <c r="H95" s="9" t="n">
+        <v>-3.9</v>
       </c>
       <c r="I95" s="7" t="n"/>
       <c r="J95" s="7" t="n"/>
@@ -5331,12 +5355,12 @@
     <row r="96" ht="26" customHeight="1">
       <c r="A96" s="10" t="inlineStr">
         <is>
-          <t>601607</t>
+          <t>600566</t>
         </is>
       </c>
       <c r="B96" s="11" t="inlineStr">
         <is>
-          <t>上海医药 NEW</t>
+          <t>济川药业 NEW</t>
         </is>
       </c>
       <c r="C96" s="10" t="inlineStr">
@@ -5362,8 +5386,8 @@
           <t>高位整理</t>
         </is>
       </c>
-      <c r="H96" s="14" t="n">
-        <v>-1.65</v>
+      <c r="H96" s="12" t="n">
+        <v>1.46</v>
       </c>
       <c r="I96" s="10" t="n"/>
       <c r="J96" s="10" t="n"/>
@@ -6106,11 +6130,11 @@
       </c>
       <c r="E111" s="15" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="F111" s="15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G111" s="17" t="inlineStr">
         <is>
@@ -6118,7 +6142,7 @@
         </is>
       </c>
       <c r="H111" s="19" t="n">
-        <v>20.01</v>
+        <v>20.03</v>
       </c>
       <c r="I111" s="15" t="n">
         <v>-22.02</v>
@@ -11368,12 +11392,12 @@
     <row r="215" ht="26" customHeight="1">
       <c r="A215" s="7" t="inlineStr">
         <is>
-          <t>603823</t>
+          <t>688138</t>
         </is>
       </c>
       <c r="B215" s="8" t="inlineStr">
         <is>
-          <t>百合花</t>
+          <t>清溢光电</t>
         </is>
       </c>
       <c r="C215" s="7" t="inlineStr">
@@ -11383,16 +11407,16 @@
       </c>
       <c r="D215" s="7" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="E215" s="7" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="F215" s="7" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G215" s="7" t="inlineStr">
         <is>
@@ -11400,17 +11424,17 @@
         </is>
       </c>
       <c r="H215" s="13" t="n">
-        <v>6.13</v>
+        <v>7.21</v>
       </c>
       <c r="I215" s="7" t="n">
-        <v>7.4</v>
+        <v>7.74</v>
       </c>
       <c r="J215" s="7" t="n">
-        <v>0.78</v>
+        <v>1.44</v>
       </c>
       <c r="K215" s="7" t="inlineStr">
         <is>
-          <t>缩量</t>
+          <t>放量</t>
         </is>
       </c>
       <c r="L215" s="7" t="inlineStr"/>
@@ -11419,31 +11443,31 @@
     <row r="216" ht="26" customHeight="1">
       <c r="A216" s="10" t="inlineStr">
         <is>
-          <t>688138</t>
+          <t>002821</t>
         </is>
       </c>
       <c r="B216" s="11" t="inlineStr">
         <is>
-          <t>清溢光电</t>
+          <t>凯莱英</t>
         </is>
       </c>
       <c r="C216" s="10" t="inlineStr">
         <is>
-          <t>半导体/芯片</t>
+          <t>创新药/CRO</t>
         </is>
       </c>
       <c r="D216" s="10" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="E216" s="10" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="F216" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G216" s="10" t="inlineStr">
         <is>
@@ -11451,17 +11475,17 @@
         </is>
       </c>
       <c r="H216" s="12" t="n">
-        <v>7.21</v>
+        <v>10</v>
       </c>
       <c r="I216" s="10" t="n">
-        <v>7.74</v>
+        <v>8.52</v>
       </c>
       <c r="J216" s="10" t="n">
-        <v>1.44</v>
+        <v>1.2</v>
       </c>
       <c r="K216" s="10" t="inlineStr">
         <is>
-          <t>放量</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="L216" s="10" t="inlineStr"/>
@@ -11470,12 +11494,12 @@
     <row r="217" ht="26" customHeight="1">
       <c r="A217" s="7" t="inlineStr">
         <is>
-          <t>002821</t>
+          <t>688321</t>
         </is>
       </c>
       <c r="B217" s="8" t="inlineStr">
         <is>
-          <t>凯莱英</t>
+          <t>微芯生物</t>
         </is>
       </c>
       <c r="C217" s="7" t="inlineStr">
@@ -11485,7 +11509,7 @@
       </c>
       <c r="D217" s="7" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="E217" s="7" t="inlineStr">
@@ -11494,7 +11518,7 @@
         </is>
       </c>
       <c r="F217" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G217" s="7" t="inlineStr">
         <is>
@@ -11502,14 +11526,12 @@
         </is>
       </c>
       <c r="H217" s="13" t="n">
-        <v>10</v>
+        <v>12.58</v>
       </c>
       <c r="I217" s="7" t="n">
-        <v>8.52</v>
-      </c>
-      <c r="J217" s="7" t="n">
-        <v>1.2</v>
-      </c>
+        <v>8.58</v>
+      </c>
+      <c r="J217" s="7" t="n"/>
       <c r="K217" s="7" t="inlineStr">
         <is>
           <t>正常</t>
@@ -11521,31 +11543,31 @@
     <row r="218" ht="26" customHeight="1">
       <c r="A218" s="10" t="inlineStr">
         <is>
-          <t>688321</t>
+          <t>688432</t>
         </is>
       </c>
       <c r="B218" s="11" t="inlineStr">
         <is>
-          <t>微芯生物</t>
+          <t>有研硅</t>
         </is>
       </c>
       <c r="C218" s="10" t="inlineStr">
         <is>
-          <t>创新药/CRO</t>
+          <t>半导体/芯片</t>
         </is>
       </c>
       <c r="D218" s="10" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="E218" s="10" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="F218" s="10" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G218" s="10" t="inlineStr">
         <is>
@@ -11553,15 +11575,17 @@
         </is>
       </c>
       <c r="H218" s="12" t="n">
-        <v>12.58</v>
+        <v>5.26</v>
       </c>
       <c r="I218" s="10" t="n">
-        <v>8.58</v>
-      </c>
-      <c r="J218" s="10" t="n"/>
+        <v>8.609999999999999</v>
+      </c>
+      <c r="J218" s="10" t="n">
+        <v>0.74</v>
+      </c>
       <c r="K218" s="10" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>缩量</t>
         </is>
       </c>
       <c r="L218" s="10" t="inlineStr"/>
@@ -11570,17 +11594,17 @@
     <row r="219" ht="26" customHeight="1">
       <c r="A219" s="7" t="inlineStr">
         <is>
-          <t>688432</t>
+          <t>688266</t>
         </is>
       </c>
       <c r="B219" s="8" t="inlineStr">
         <is>
-          <t>有研硅</t>
+          <t>泽璟制药</t>
         </is>
       </c>
       <c r="C219" s="7" t="inlineStr">
         <is>
-          <t>半导体/芯片</t>
+          <t>创新药/CRO</t>
         </is>
       </c>
       <c r="D219" s="7" t="inlineStr">
@@ -11590,11 +11614,11 @@
       </c>
       <c r="E219" s="7" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="F219" s="7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G219" s="7" t="inlineStr">
         <is>
@@ -11602,13 +11626,13 @@
         </is>
       </c>
       <c r="H219" s="13" t="n">
-        <v>5.26</v>
+        <v>4.91</v>
       </c>
       <c r="I219" s="7" t="n">
-        <v>8.609999999999999</v>
+        <v>10.06</v>
       </c>
       <c r="J219" s="7" t="n">
-        <v>0.74</v>
+        <v>0.77</v>
       </c>
       <c r="K219" s="7" t="inlineStr">
         <is>
@@ -11621,31 +11645,31 @@
     <row r="220" ht="26" customHeight="1">
       <c r="A220" s="10" t="inlineStr">
         <is>
-          <t>688266</t>
+          <t>000977</t>
         </is>
       </c>
       <c r="B220" s="11" t="inlineStr">
         <is>
-          <t>泽璟制药</t>
+          <t>浪潮信息</t>
         </is>
       </c>
       <c r="C220" s="10" t="inlineStr">
         <is>
-          <t>创新药/CRO</t>
+          <t>算力/通信</t>
         </is>
       </c>
       <c r="D220" s="10" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="E220" s="10" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="F220" s="10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G220" s="10" t="inlineStr">
         <is>
@@ -11653,17 +11677,15 @@
         </is>
       </c>
       <c r="H220" s="12" t="n">
-        <v>4.91</v>
+        <v>10</v>
       </c>
       <c r="I220" s="10" t="n">
-        <v>10.06</v>
-      </c>
-      <c r="J220" s="10" t="n">
-        <v>0.77</v>
-      </c>
+        <v>10.28</v>
+      </c>
+      <c r="J220" s="10" t="n"/>
       <c r="K220" s="10" t="inlineStr">
         <is>
-          <t>缩量</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="L220" s="10" t="inlineStr"/>
@@ -11672,31 +11694,31 @@
     <row r="221" ht="26" customHeight="1">
       <c r="A221" s="7" t="inlineStr">
         <is>
-          <t>000977</t>
+          <t>002422</t>
         </is>
       </c>
       <c r="B221" s="8" t="inlineStr">
         <is>
-          <t>浪潮信息</t>
+          <t>科伦药业</t>
         </is>
       </c>
       <c r="C221" s="7" t="inlineStr">
         <is>
-          <t>算力/通信</t>
+          <t>创新药/CRO</t>
         </is>
       </c>
       <c r="D221" s="7" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="E221" s="7" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="F221" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G221" s="7" t="inlineStr">
         <is>
@@ -11704,15 +11726,17 @@
         </is>
       </c>
       <c r="H221" s="13" t="n">
-        <v>10</v>
+        <v>7.22</v>
       </c>
       <c r="I221" s="7" t="n">
-        <v>10.28</v>
-      </c>
-      <c r="J221" s="7" t="n"/>
+        <v>10.78</v>
+      </c>
+      <c r="J221" s="7" t="n">
+        <v>1.22</v>
+      </c>
       <c r="K221" s="7" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>放量</t>
         </is>
       </c>
       <c r="L221" s="7" t="inlineStr"/>
@@ -11721,27 +11745,27 @@
     <row r="222" ht="26" customHeight="1">
       <c r="A222" s="10" t="inlineStr">
         <is>
-          <t>002422</t>
+          <t>603893</t>
         </is>
       </c>
       <c r="B222" s="11" t="inlineStr">
         <is>
-          <t>科伦药业</t>
+          <t>瑞芯微</t>
         </is>
       </c>
       <c r="C222" s="10" t="inlineStr">
         <is>
-          <t>创新药/CRO</t>
+          <t>半导体/芯片</t>
         </is>
       </c>
       <c r="D222" s="10" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="E222" s="10" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="F222" s="10" t="n">
@@ -11753,17 +11777,17 @@
         </is>
       </c>
       <c r="H222" s="12" t="n">
-        <v>7.22</v>
+        <v>5.58</v>
       </c>
       <c r="I222" s="10" t="n">
-        <v>10.78</v>
+        <v>11.87</v>
       </c>
       <c r="J222" s="10" t="n">
-        <v>1.22</v>
+        <v>0.75</v>
       </c>
       <c r="K222" s="10" t="inlineStr">
         <is>
-          <t>放量</t>
+          <t>缩量</t>
         </is>
       </c>
       <c r="L222" s="10" t="inlineStr"/>
@@ -11772,31 +11796,31 @@
     <row r="223" ht="26" customHeight="1">
       <c r="A223" s="7" t="inlineStr">
         <is>
-          <t>603893</t>
+          <t>603669</t>
         </is>
       </c>
       <c r="B223" s="8" t="inlineStr">
         <is>
-          <t>瑞芯微</t>
+          <t>灵康药业</t>
         </is>
       </c>
       <c r="C223" s="7" t="inlineStr">
         <is>
-          <t>半导体/芯片</t>
+          <t>创新药/CRO</t>
         </is>
       </c>
       <c r="D223" s="7" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="E223" s="7" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="F223" s="7" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G223" s="7" t="inlineStr">
         <is>
@@ -11804,17 +11828,17 @@
         </is>
       </c>
       <c r="H223" s="13" t="n">
-        <v>5.58</v>
+        <v>9.59</v>
       </c>
       <c r="I223" s="7" t="n">
-        <v>11.87</v>
+        <v>13.41</v>
       </c>
       <c r="J223" s="7" t="n">
-        <v>0.75</v>
+        <v>2.57</v>
       </c>
       <c r="K223" s="7" t="inlineStr">
         <is>
-          <t>缩量</t>
+          <t>放量</t>
         </is>
       </c>
       <c r="L223" s="7" t="inlineStr"/>
@@ -11823,31 +11847,31 @@
     <row r="224" ht="26" customHeight="1">
       <c r="A224" s="10" t="inlineStr">
         <is>
-          <t>603669</t>
+          <t>688584</t>
         </is>
       </c>
       <c r="B224" s="11" t="inlineStr">
         <is>
-          <t>灵康药业</t>
+          <t>上海合晶</t>
         </is>
       </c>
       <c r="C224" s="10" t="inlineStr">
         <is>
-          <t>创新药/CRO</t>
+          <t>半导体/芯片</t>
         </is>
       </c>
       <c r="D224" s="10" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="E224" s="10" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="F224" s="10" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G224" s="10" t="inlineStr">
         <is>
@@ -11855,17 +11879,17 @@
         </is>
       </c>
       <c r="H224" s="12" t="n">
-        <v>9.59</v>
+        <v>5.98</v>
       </c>
       <c r="I224" s="10" t="n">
-        <v>13.41</v>
+        <v>13.95</v>
       </c>
       <c r="J224" s="10" t="n">
-        <v>2.57</v>
+        <v>1.09</v>
       </c>
       <c r="K224" s="10" t="inlineStr">
         <is>
-          <t>放量</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="L224" s="10" t="inlineStr"/>
@@ -11874,31 +11898,31 @@
     <row r="225" ht="26" customHeight="1">
       <c r="A225" s="7" t="inlineStr">
         <is>
-          <t>688584</t>
+          <t>300759</t>
         </is>
       </c>
       <c r="B225" s="8" t="inlineStr">
         <is>
-          <t>上海合晶</t>
+          <t>康龙化成</t>
         </is>
       </c>
       <c r="C225" s="7" t="inlineStr">
         <is>
-          <t>半导体/芯片</t>
+          <t>创新药/CRO</t>
         </is>
       </c>
       <c r="D225" s="7" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="E225" s="7" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="F225" s="7" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G225" s="7" t="inlineStr">
         <is>
@@ -11906,142 +11930,142 @@
         </is>
       </c>
       <c r="H225" s="13" t="n">
-        <v>5.98</v>
+        <v>5.58</v>
       </c>
       <c r="I225" s="7" t="n">
-        <v>13.95</v>
+        <v>14.26</v>
       </c>
       <c r="J225" s="7" t="n">
-        <v>1.09</v>
+        <v>1.57</v>
       </c>
       <c r="K225" s="7" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>放量</t>
         </is>
       </c>
       <c r="L225" s="7" t="inlineStr"/>
       <c r="M225" s="7" t="inlineStr"/>
     </row>
     <row r="226" ht="26" customHeight="1">
-      <c r="A226" s="10" t="inlineStr">
-        <is>
-          <t>000938</t>
-        </is>
-      </c>
-      <c r="B226" s="11" t="inlineStr">
-        <is>
-          <t>紫光股份</t>
-        </is>
-      </c>
-      <c r="C226" s="10" t="inlineStr">
-        <is>
-          <t>算力/通信</t>
-        </is>
-      </c>
-      <c r="D226" s="10" t="inlineStr">
+      <c r="A226" s="15" t="inlineStr">
+        <is>
+          <t>688328</t>
+        </is>
+      </c>
+      <c r="B226" s="16" t="inlineStr">
+        <is>
+          <t>深科达</t>
+        </is>
+      </c>
+      <c r="C226" s="15" t="inlineStr">
+        <is>
+          <t>半导体/芯片</t>
+        </is>
+      </c>
+      <c r="D226" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="E226" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="F226" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G226" s="17" t="inlineStr">
+        <is>
+          <t>强势上攻</t>
+        </is>
+      </c>
+      <c r="H226" s="19" t="n">
+        <v>15.89</v>
+      </c>
+      <c r="I226" s="15" t="n">
+        <v>15.46</v>
+      </c>
+      <c r="J226" s="15" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="K226" s="15" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="L226" s="15" t="inlineStr">
+        <is>
+          <t>首日涨幅&gt;16%</t>
+        </is>
+      </c>
+      <c r="M226" s="15" t="inlineStr"/>
+    </row>
+    <row r="227" ht="26" customHeight="1">
+      <c r="A227" s="7" t="inlineStr">
+        <is>
+          <t>603065</t>
+        </is>
+      </c>
+      <c r="B227" s="8" t="inlineStr">
+        <is>
+          <t>宿迁联盛</t>
+        </is>
+      </c>
+      <c r="C227" s="7" t="inlineStr">
+        <is>
+          <t>半导体/芯片</t>
+        </is>
+      </c>
+      <c r="D227" s="7" t="inlineStr">
         <is>
           <t>2026-07-08</t>
         </is>
       </c>
-      <c r="E226" s="10" t="inlineStr">
-        <is>
-          <t>2026-07-21</t>
-        </is>
-      </c>
-      <c r="F226" s="10" t="n">
-        <v>6</v>
-      </c>
-      <c r="G226" s="10" t="inlineStr">
-        <is>
-          <t>强势上攻</t>
-        </is>
-      </c>
-      <c r="H226" s="12" t="n">
+      <c r="E227" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="F227" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="G227" s="7" t="inlineStr">
+        <is>
+          <t>强势上攻</t>
+        </is>
+      </c>
+      <c r="H227" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="I226" s="10" t="n">
-        <v>13.99</v>
-      </c>
-      <c r="J226" s="10" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="K226" s="10" t="inlineStr">
-        <is>
-          <t>正常</t>
-        </is>
-      </c>
-      <c r="L226" s="10" t="inlineStr"/>
-      <c r="M226" s="10" t="inlineStr"/>
-    </row>
-    <row r="227" ht="26" customHeight="1">
-      <c r="A227" s="15" t="inlineStr">
-        <is>
-          <t>688328</t>
-        </is>
-      </c>
-      <c r="B227" s="16" t="inlineStr">
-        <is>
-          <t>深科达</t>
-        </is>
-      </c>
-      <c r="C227" s="15" t="inlineStr">
-        <is>
-          <t>半导体/芯片</t>
-        </is>
-      </c>
-      <c r="D227" s="15" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="E227" s="15" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="F227" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G227" s="17" t="inlineStr">
-        <is>
-          <t>强势上攻</t>
-        </is>
-      </c>
-      <c r="H227" s="19" t="n">
-        <v>15.89</v>
-      </c>
-      <c r="I227" s="15" t="n">
-        <v>15.46</v>
-      </c>
-      <c r="J227" s="15" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="K227" s="15" t="inlineStr">
-        <is>
-          <t>正常</t>
-        </is>
-      </c>
-      <c r="L227" s="15" t="inlineStr">
-        <is>
-          <t>首日涨幅&gt;16%</t>
-        </is>
-      </c>
-      <c r="M227" s="15" t="inlineStr"/>
+      <c r="I227" s="7" t="n">
+        <v>15.51</v>
+      </c>
+      <c r="J227" s="7" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="K227" s="7" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="L227" s="7" t="inlineStr"/>
+      <c r="M227" s="7" t="inlineStr"/>
     </row>
     <row r="228" ht="26" customHeight="1">
       <c r="A228" s="10" t="inlineStr">
         <is>
-          <t>603065</t>
+          <t>000938</t>
         </is>
       </c>
       <c r="B228" s="11" t="inlineStr">
         <is>
-          <t>宿迁联盛</t>
+          <t>紫光股份</t>
         </is>
       </c>
       <c r="C228" s="10" t="inlineStr">
         <is>
-          <t>半导体/芯片</t>
+          <t>算力/通信</t>
         </is>
       </c>
       <c r="D228" s="10" t="inlineStr">
@@ -12051,11 +12075,11 @@
       </c>
       <c r="E228" s="10" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="F228" s="10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G228" s="10" t="inlineStr">
         <is>
@@ -12066,10 +12090,10 @@
         <v>10</v>
       </c>
       <c r="I228" s="10" t="n">
-        <v>15.51</v>
+        <v>15.52</v>
       </c>
       <c r="J228" s="10" t="n">
-        <v>0.9</v>
+        <v>1.07</v>
       </c>
       <c r="K228" s="10" t="inlineStr">
         <is>
@@ -12082,31 +12106,31 @@
     <row r="229" ht="26" customHeight="1">
       <c r="A229" s="7" t="inlineStr">
         <is>
-          <t>002396</t>
+          <t>688293</t>
         </is>
       </c>
       <c r="B229" s="8" t="inlineStr">
         <is>
-          <t>星网锐捷</t>
+          <t>奥浦迈 NEW</t>
         </is>
       </c>
       <c r="C229" s="7" t="inlineStr">
         <is>
-          <t>算力/通信</t>
+          <t>创新药/CRO</t>
         </is>
       </c>
       <c r="D229" s="7" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="E229" s="7" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="F229" s="7" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G229" s="7" t="inlineStr">
         <is>
@@ -12114,17 +12138,15 @@
         </is>
       </c>
       <c r="H229" s="13" t="n">
-        <v>5.05</v>
+        <v>4.11</v>
       </c>
       <c r="I229" s="7" t="n">
-        <v>17.97</v>
-      </c>
-      <c r="J229" s="7" t="n">
-        <v>1.35</v>
-      </c>
+        <v>15.71</v>
+      </c>
+      <c r="J229" s="7" t="n"/>
       <c r="K229" s="7" t="inlineStr">
         <is>
-          <t>放量</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="L229" s="7" t="inlineStr"/>
@@ -12133,17 +12155,17 @@
     <row r="230" ht="26" customHeight="1">
       <c r="A230" s="10" t="inlineStr">
         <is>
-          <t>300759</t>
+          <t>002396</t>
         </is>
       </c>
       <c r="B230" s="11" t="inlineStr">
         <is>
-          <t>康龙化成</t>
+          <t>星网锐捷</t>
         </is>
       </c>
       <c r="C230" s="10" t="inlineStr">
         <is>
-          <t>创新药/CRO</t>
+          <t>算力/通信</t>
         </is>
       </c>
       <c r="D230" s="10" t="inlineStr">
@@ -12153,11 +12175,11 @@
       </c>
       <c r="E230" s="10" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="F230" s="10" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G230" s="10" t="inlineStr">
         <is>
@@ -12165,13 +12187,13 @@
         </is>
       </c>
       <c r="H230" s="12" t="n">
-        <v>5.58</v>
+        <v>5.05</v>
       </c>
       <c r="I230" s="10" t="n">
-        <v>18.59</v>
+        <v>17.97</v>
       </c>
       <c r="J230" s="10" t="n">
-        <v>1.57</v>
+        <v>1.35</v>
       </c>
       <c r="K230" s="10" t="inlineStr">
         <is>
@@ -12184,31 +12206,31 @@
     <row r="231" ht="26" customHeight="1">
       <c r="A231" s="7" t="inlineStr">
         <is>
-          <t>002841</t>
+          <t>603823</t>
         </is>
       </c>
       <c r="B231" s="8" t="inlineStr">
         <is>
-          <t>视源股份</t>
+          <t>百合花</t>
         </is>
       </c>
       <c r="C231" s="7" t="inlineStr">
         <is>
-          <t>机器人</t>
+          <t>半导体/芯片</t>
         </is>
       </c>
       <c r="D231" s="7" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="E231" s="7" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="F231" s="7" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G231" s="7" t="inlineStr">
         <is>
@@ -12216,17 +12238,17 @@
         </is>
       </c>
       <c r="H231" s="13" t="n">
-        <v>10</v>
+        <v>6.13</v>
       </c>
       <c r="I231" s="7" t="n">
-        <v>22.83</v>
+        <v>18.35</v>
       </c>
       <c r="J231" s="7" t="n">
-        <v>0.9</v>
+        <v>0.78</v>
       </c>
       <c r="K231" s="7" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>缩量</t>
         </is>
       </c>
       <c r="L231" s="7" t="inlineStr"/>
@@ -12235,17 +12257,17 @@
     <row r="232" ht="26" customHeight="1">
       <c r="A232" s="10" t="inlineStr">
         <is>
-          <t>603127</t>
+          <t>002841</t>
         </is>
       </c>
       <c r="B232" s="11" t="inlineStr">
         <is>
-          <t>昭衍新药</t>
+          <t>视源股份</t>
         </is>
       </c>
       <c r="C232" s="10" t="inlineStr">
         <is>
-          <t>创新药/CRO</t>
+          <t>机器人</t>
         </is>
       </c>
       <c r="D232" s="10" t="inlineStr">
@@ -12255,11 +12277,11 @@
       </c>
       <c r="E232" s="10" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="F232" s="10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G232" s="10" t="inlineStr">
         <is>
@@ -12267,154 +12289,154 @@
         </is>
       </c>
       <c r="H232" s="12" t="n">
-        <v>5.2</v>
+        <v>10</v>
       </c>
       <c r="I232" s="10" t="n">
-        <v>25.15</v>
+        <v>22.83</v>
       </c>
       <c r="J232" s="10" t="n">
-        <v>1.62</v>
+        <v>0.9</v>
       </c>
       <c r="K232" s="10" t="inlineStr">
         <is>
-          <t>放量</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="L232" s="10" t="inlineStr"/>
       <c r="M232" s="10" t="inlineStr"/>
     </row>
     <row r="233" ht="26" customHeight="1">
-      <c r="A233" s="15" t="inlineStr">
+      <c r="A233" s="7" t="inlineStr">
+        <is>
+          <t>603127</t>
+        </is>
+      </c>
+      <c r="B233" s="8" t="inlineStr">
+        <is>
+          <t>昭衍新药</t>
+        </is>
+      </c>
+      <c r="C233" s="7" t="inlineStr">
+        <is>
+          <t>创新药/CRO</t>
+        </is>
+      </c>
+      <c r="D233" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="E233" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="F233" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="G233" s="7" t="inlineStr">
+        <is>
+          <t>强势上攻</t>
+        </is>
+      </c>
+      <c r="H233" s="13" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="I233" s="7" t="n">
+        <v>25.15</v>
+      </c>
+      <c r="J233" s="7" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="K233" s="7" t="inlineStr">
+        <is>
+          <t>放量</t>
+        </is>
+      </c>
+      <c r="L233" s="7" t="inlineStr"/>
+      <c r="M233" s="7" t="inlineStr"/>
+    </row>
+    <row r="234" ht="26" customHeight="1">
+      <c r="A234" s="15" t="inlineStr">
         <is>
           <t>688192</t>
         </is>
       </c>
-      <c r="B233" s="16" t="inlineStr">
+      <c r="B234" s="16" t="inlineStr">
         <is>
           <t>迪哲医药</t>
         </is>
       </c>
-      <c r="C233" s="15" t="inlineStr">
+      <c r="C234" s="15" t="inlineStr">
         <is>
           <t>创新药/CRO</t>
         </is>
       </c>
-      <c r="D233" s="15" t="inlineStr">
+      <c r="D234" s="15" t="inlineStr">
         <is>
           <t>2026-07-15</t>
         </is>
       </c>
-      <c r="E233" s="15" t="inlineStr">
+      <c r="E234" s="15" t="inlineStr">
         <is>
           <t>2026-07-15</t>
         </is>
       </c>
-      <c r="F233" s="15" t="n">
+      <c r="F234" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="G233" s="17" t="inlineStr">
-        <is>
-          <t>强势上攻</t>
-        </is>
-      </c>
-      <c r="H233" s="19" t="n">
+      <c r="G234" s="17" t="inlineStr">
+        <is>
+          <t>强势上攻</t>
+        </is>
+      </c>
+      <c r="H234" s="19" t="n">
         <v>20.01</v>
       </c>
-      <c r="I233" s="15" t="n">
+      <c r="I234" s="15" t="n">
         <v>29.06</v>
       </c>
-      <c r="J233" s="15" t="n"/>
-      <c r="K233" s="15" t="inlineStr">
-        <is>
-          <t>正常</t>
-        </is>
-      </c>
-      <c r="L233" s="15" t="inlineStr">
+      <c r="J234" s="15" t="n"/>
+      <c r="K234" s="15" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="L234" s="15" t="inlineStr">
         <is>
           <t>首日涨幅&gt;20%</t>
         </is>
       </c>
-      <c r="M233" s="15" t="inlineStr"/>
-    </row>
-    <row r="234" ht="26" customHeight="1">
-      <c r="A234" s="10" t="inlineStr">
-        <is>
-          <t>603137</t>
-        </is>
-      </c>
-      <c r="B234" s="11" t="inlineStr">
-        <is>
-          <t>恒尚节能</t>
-        </is>
-      </c>
-      <c r="C234" s="10" t="inlineStr">
-        <is>
-          <t>半导体/芯片</t>
-        </is>
-      </c>
-      <c r="D234" s="10" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="E234" s="10" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-      <c r="F234" s="10" t="n">
-        <v>10</v>
-      </c>
-      <c r="G234" s="10" t="inlineStr">
-        <is>
-          <t>强势上攻</t>
-        </is>
-      </c>
-      <c r="H234" s="12" t="n">
-        <v>10.01</v>
-      </c>
-      <c r="I234" s="10" t="n">
-        <v>37</v>
-      </c>
-      <c r="J234" s="10" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="K234" s="10" t="inlineStr">
-        <is>
-          <t>放量</t>
-        </is>
-      </c>
-      <c r="L234" s="10" t="inlineStr"/>
-      <c r="M234" s="10" t="inlineStr"/>
+      <c r="M234" s="15" t="inlineStr"/>
     </row>
     <row r="235" ht="26" customHeight="1">
       <c r="A235" s="7" t="inlineStr">
         <is>
-          <t>300534</t>
+          <t>603137</t>
         </is>
       </c>
       <c r="B235" s="8" t="inlineStr">
         <is>
-          <t>陇神戎发</t>
+          <t>恒尚节能</t>
         </is>
       </c>
       <c r="C235" s="7" t="inlineStr">
         <is>
-          <t>创新药/CRO</t>
+          <t>半导体/芯片</t>
         </is>
       </c>
       <c r="D235" s="7" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="E235" s="7" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="F235" s="7" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="G235" s="7" t="inlineStr">
         <is>
@@ -12422,15 +12444,17 @@
         </is>
       </c>
       <c r="H235" s="13" t="n">
-        <v>14.62</v>
+        <v>10.01</v>
       </c>
       <c r="I235" s="7" t="n">
-        <v>38.39</v>
-      </c>
-      <c r="J235" s="7" t="n"/>
+        <v>37</v>
+      </c>
+      <c r="J235" s="7" t="n">
+        <v>1.45</v>
+      </c>
       <c r="K235" s="7" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>放量</t>
         </is>
       </c>
       <c r="L235" s="7" t="inlineStr"/>
@@ -12474,7 +12498,7 @@
         <v>9.98</v>
       </c>
       <c r="I236" s="10" t="n">
-        <v>41.7</v>
+        <v>44.31</v>
       </c>
       <c r="J236" s="10" t="n"/>
       <c r="K236" s="10" t="inlineStr">
@@ -12488,12 +12512,12 @@
     <row r="237" ht="26" customHeight="1">
       <c r="A237" s="7" t="inlineStr">
         <is>
-          <t>301520</t>
+          <t>300534</t>
         </is>
       </c>
       <c r="B237" s="8" t="inlineStr">
         <is>
-          <t>万邦医药</t>
+          <t>陇神戎发</t>
         </is>
       </c>
       <c r="C237" s="7" t="inlineStr">
@@ -12503,16 +12527,16 @@
       </c>
       <c r="D237" s="7" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="E237" s="7" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="F237" s="7" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G237" s="7" t="inlineStr">
         <is>
@@ -12520,14 +12544,12 @@
         </is>
       </c>
       <c r="H237" s="13" t="n">
-        <v>13.37</v>
+        <v>14.62</v>
       </c>
       <c r="I237" s="7" t="n">
-        <v>53.52</v>
-      </c>
-      <c r="J237" s="7" t="n">
-        <v>1.08</v>
-      </c>
+        <v>46.22</v>
+      </c>
+      <c r="J237" s="7" t="n"/>
       <c r="K237" s="7" t="inlineStr">
         <is>
           <t>正常</t>
@@ -12539,22 +12561,22 @@
     <row r="238" ht="26" customHeight="1">
       <c r="A238" s="10" t="inlineStr">
         <is>
-          <t>002141</t>
+          <t>301520</t>
         </is>
       </c>
       <c r="B238" s="11" t="inlineStr">
         <is>
-          <t>贤丰控股</t>
+          <t>万邦医药</t>
         </is>
       </c>
       <c r="C238" s="10" t="inlineStr">
         <is>
-          <t>算力/通信</t>
+          <t>创新药/CRO</t>
         </is>
       </c>
       <c r="D238" s="10" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="E238" s="10" t="inlineStr">
@@ -12563,7 +12585,7 @@
         </is>
       </c>
       <c r="F238" s="10" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G238" s="10" t="inlineStr">
         <is>
@@ -12571,140 +12593,142 @@
         </is>
       </c>
       <c r="H238" s="12" t="n">
-        <v>5.35</v>
-      </c>
-      <c r="I238" s="10" t="n"/>
-      <c r="J238" s="10" t="n"/>
-      <c r="K238" s="10" t="inlineStr"/>
+        <v>13.37</v>
+      </c>
+      <c r="I238" s="10" t="n">
+        <v>53.52</v>
+      </c>
+      <c r="J238" s="10" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="K238" s="10" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
       <c r="L238" s="10" t="inlineStr"/>
       <c r="M238" s="10" t="inlineStr"/>
     </row>
     <row r="239" ht="26" customHeight="1">
-      <c r="A239" s="15" t="inlineStr">
+      <c r="A239" s="7" t="inlineStr">
+        <is>
+          <t>002141</t>
+        </is>
+      </c>
+      <c r="B239" s="8" t="inlineStr">
+        <is>
+          <t>贤丰控股</t>
+        </is>
+      </c>
+      <c r="C239" s="7" t="inlineStr">
+        <is>
+          <t>算力/通信</t>
+        </is>
+      </c>
+      <c r="D239" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="E239" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="F239" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G239" s="7" t="inlineStr">
+        <is>
+          <t>强势上攻</t>
+        </is>
+      </c>
+      <c r="H239" s="13" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="I239" s="7" t="n"/>
+      <c r="J239" s="7" t="n"/>
+      <c r="K239" s="7" t="inlineStr"/>
+      <c r="L239" s="7" t="inlineStr"/>
+      <c r="M239" s="7" t="inlineStr"/>
+    </row>
+    <row r="240" ht="26" customHeight="1">
+      <c r="A240" s="15" t="inlineStr">
         <is>
           <t>300214</t>
         </is>
       </c>
-      <c r="B239" s="16" t="inlineStr">
+      <c r="B240" s="16" t="inlineStr">
         <is>
           <t>日科化学</t>
         </is>
       </c>
-      <c r="C239" s="15" t="inlineStr">
+      <c r="C240" s="15" t="inlineStr">
         <is>
           <t>算力/通信</t>
         </is>
       </c>
-      <c r="D239" s="15" t="inlineStr">
+      <c r="D240" s="15" t="inlineStr">
         <is>
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="E239" s="15" t="inlineStr">
+      <c r="E240" s="15" t="inlineStr">
         <is>
           <t>2026-07-14</t>
         </is>
       </c>
-      <c r="F239" s="15" t="n">
+      <c r="F240" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="G239" s="17" t="inlineStr">
-        <is>
-          <t>强势上攻</t>
-        </is>
-      </c>
-      <c r="H239" s="19" t="n">
+      <c r="G240" s="17" t="inlineStr">
+        <is>
+          <t>强势上攻</t>
+        </is>
+      </c>
+      <c r="H240" s="19" t="n">
         <v>8.94</v>
       </c>
-      <c r="I239" s="15" t="n"/>
-      <c r="J239" s="15" t="n">
+      <c r="I240" s="15" t="n"/>
+      <c r="J240" s="15" t="n">
         <v>14.71</v>
       </c>
-      <c r="K239" s="15" t="inlineStr">
+      <c r="K240" s="15" t="inlineStr">
         <is>
           <t>放量</t>
         </is>
       </c>
-      <c r="L239" s="15" t="inlineStr">
+      <c r="L240" s="15" t="inlineStr">
         <is>
           <t>首日涨幅&gt;20%</t>
         </is>
       </c>
-      <c r="M239" s="15" t="inlineStr"/>
-    </row>
-    <row r="240" ht="26" customHeight="1">
-      <c r="A240" s="10" t="inlineStr">
-        <is>
-          <t>301191</t>
-        </is>
-      </c>
-      <c r="B240" s="11" t="inlineStr">
-        <is>
-          <t>菲菱科思</t>
-        </is>
-      </c>
-      <c r="C240" s="10" t="inlineStr">
-        <is>
-          <t>算力/通信</t>
-        </is>
-      </c>
-      <c r="D240" s="10" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="E240" s="10" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="F240" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="G240" s="10" t="inlineStr">
-        <is>
-          <t>强势上攻</t>
-        </is>
-      </c>
-      <c r="H240" s="12" t="n">
-        <v>5.09</v>
-      </c>
-      <c r="I240" s="10" t="n"/>
-      <c r="J240" s="10" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="K240" s="10" t="inlineStr">
-        <is>
-          <t>正常</t>
-        </is>
-      </c>
-      <c r="L240" s="10" t="inlineStr"/>
-      <c r="M240" s="10" t="inlineStr"/>
+      <c r="M240" s="15" t="inlineStr"/>
     </row>
     <row r="241" ht="26" customHeight="1">
       <c r="A241" s="7" t="inlineStr">
         <is>
-          <t>600881</t>
+          <t>301191</t>
         </is>
       </c>
       <c r="B241" s="8" t="inlineStr">
         <is>
-          <t>亚泰集团</t>
+          <t>菲菱科思</t>
         </is>
       </c>
       <c r="C241" s="7" t="inlineStr">
         <is>
-          <t>创新药/CRO</t>
+          <t>算力/通信</t>
         </is>
       </c>
       <c r="D241" s="7" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="E241" s="7" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="F241" s="7" t="n">
@@ -12716,23 +12740,29 @@
         </is>
       </c>
       <c r="H241" s="13" t="n">
-        <v>10.06</v>
+        <v>5.09</v>
       </c>
       <c r="I241" s="7" t="n"/>
-      <c r="J241" s="7" t="n"/>
-      <c r="K241" s="7" t="inlineStr"/>
+      <c r="J241" s="7" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="K241" s="7" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
       <c r="L241" s="7" t="inlineStr"/>
       <c r="M241" s="7" t="inlineStr"/>
     </row>
     <row r="242" ht="26" customHeight="1">
       <c r="A242" s="10" t="inlineStr">
         <is>
-          <t>688293</t>
+          <t>600881</t>
         </is>
       </c>
       <c r="B242" s="11" t="inlineStr">
         <is>
-          <t>奥浦迈 NEW</t>
+          <t>亚泰集团</t>
         </is>
       </c>
       <c r="C242" s="10" t="inlineStr">
@@ -12742,12 +12772,12 @@
       </c>
       <c r="D242" s="10" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="E242" s="10" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="F242" s="10" t="n">
@@ -12759,7 +12789,7 @@
         </is>
       </c>
       <c r="H242" s="12" t="n">
-        <v>4.11</v>
+        <v>10.06</v>
       </c>
       <c r="I242" s="10" t="n"/>
       <c r="J242" s="10" t="n"/>
@@ -14063,7 +14093,7 @@
         </is>
       </c>
       <c r="D20" s="15" t="n">
-        <v>20.01</v>
+        <v>20.03</v>
       </c>
       <c r="E20" s="15" t="n">
         <v>0.73</v>
@@ -14523,7 +14553,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:K20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -14542,7 +14572,7 @@
     <row r="1" ht="36" customHeight="1">
       <c r="A1" s="27" t="inlineStr">
         <is>
-          <t>回踩狙击榜 2026-07-21 (13只·按综合分排序)</t>
+          <t>回踩狙击榜 2026-07-21 (17只·按综合分排序)</t>
         </is>
       </c>
     </row>
@@ -14651,16 +14681,16 @@
     <row r="5" ht="26" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>301393</t>
+          <t>600998</t>
         </is>
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>昊帆生物</t>
+          <t>九州通 NEW</t>
         </is>
       </c>
       <c r="C5" s="9" t="n">
-        <v>0.46</v>
+        <v>-0.09</v>
       </c>
       <c r="D5" s="7" t="n"/>
       <c r="E5" s="7" t="inlineStr">
@@ -14668,67 +14698,65 @@
           <t>正常</t>
         </is>
       </c>
-      <c r="F5" s="7" t="n">
-        <v>65</v>
+      <c r="F5" s="9" t="n">
+        <v>83</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H5" s="7" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="I5" s="7" t="n">
-        <v>-1.27</v>
+        <v>-1.93</v>
       </c>
       <c r="J5" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K5" s="7" t="inlineStr">
         <is>
-          <t>★极近均线</t>
+          <t>🎯首选 ★极近均线</t>
         </is>
       </c>
     </row>
     <row r="6" ht="26" customHeight="1">
       <c r="A6" s="10" t="inlineStr">
         <is>
-          <t>688702</t>
+          <t>301393</t>
         </is>
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>盛科通信</t>
+          <t>昊帆生物</t>
         </is>
       </c>
       <c r="C6" s="14" t="n">
-        <v>-0.58</v>
-      </c>
-      <c r="D6" s="10" t="n">
-        <v>1.19</v>
-      </c>
+        <v>0.46</v>
+      </c>
+      <c r="D6" s="10" t="n"/>
       <c r="E6" s="10" t="inlineStr">
         <is>
           <t>正常</t>
         </is>
       </c>
       <c r="F6" s="10" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="G6" s="10" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H6" s="10" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="I6" s="10" t="n">
-        <v>5.11</v>
+        <v>-1.27</v>
       </c>
       <c r="J6" s="10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K6" s="10" t="inlineStr">
         <is>
@@ -14739,16 +14767,16 @@
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>300458</t>
+          <t>601607</t>
         </is>
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>全志科技</t>
-        </is>
-      </c>
-      <c r="C7" s="9" t="n">
-        <v>-0.55</v>
+          <t>上海医药 NEW</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="n">
+        <v>1.52</v>
       </c>
       <c r="D7" s="7" t="n"/>
       <c r="E7" s="7" t="inlineStr">
@@ -14757,63 +14785,59 @@
         </is>
       </c>
       <c r="F7" s="7" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H7" s="7" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="I7" s="7" t="n">
-        <v>2.19</v>
+        <v>-1.65</v>
       </c>
       <c r="J7" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="K7" s="7" t="inlineStr">
-        <is>
-          <t>★极近均线</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K7" s="7" t="inlineStr"/>
     </row>
     <row r="8" ht="26" customHeight="1">
       <c r="A8" s="10" t="inlineStr">
         <is>
-          <t>300487</t>
+          <t>688702</t>
         </is>
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>蓝晓科技</t>
+          <t>盛科通信</t>
         </is>
       </c>
       <c r="C8" s="14" t="n">
-        <v>0.34</v>
+        <v>-0.58</v>
       </c>
       <c r="D8" s="10" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="E8" s="12" t="inlineStr">
-        <is>
-          <t>放量</t>
+        <v>1.19</v>
+      </c>
+      <c r="E8" s="10" t="inlineStr">
+        <is>
+          <t>正常</t>
         </is>
       </c>
       <c r="F8" s="10" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="G8" s="10" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="H8" s="10" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="I8" s="10" t="n">
-        <v>-1</v>
+        <v>5.11</v>
       </c>
       <c r="J8" s="10" t="n">
         <v>2</v>
@@ -14827,27 +14851,25 @@
     <row r="9" ht="26" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>603991</t>
+          <t>300458</t>
         </is>
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>领先股份</t>
-        </is>
-      </c>
-      <c r="C9" s="7" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="D9" s="7" t="n">
-        <v>1.05</v>
-      </c>
+          <t>全志科技</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="n">
+        <v>-0.55</v>
+      </c>
+      <c r="D9" s="7" t="n"/>
       <c r="E9" s="7" t="inlineStr">
         <is>
           <t>正常</t>
         </is>
       </c>
       <c r="F9" s="7" t="n">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="G9" s="7" t="n">
         <v>12</v>
@@ -14858,111 +14880,123 @@
         </is>
       </c>
       <c r="I9" s="7" t="n">
-        <v>10</v>
+        <v>2.19</v>
       </c>
       <c r="J9" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="K9" s="7" t="inlineStr"/>
+      <c r="K9" s="7" t="inlineStr">
+        <is>
+          <t>★极近均线</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="26" customHeight="1">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>301151</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>冠龙节能</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="D10" s="3" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>缩量</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="n">
-        <v>44</v>
-      </c>
-      <c r="G10" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="n">
-        <v>7.33</v>
-      </c>
-      <c r="J10" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="K10" s="3" t="inlineStr"/>
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>600285</t>
+        </is>
+      </c>
+      <c r="B10" s="11" t="inlineStr">
+        <is>
+          <t>羚锐制药 NEW</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="D10" s="10" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="E10" s="12" t="inlineStr">
+        <is>
+          <t>放量</t>
+        </is>
+      </c>
+      <c r="F10" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="G10" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="I10" s="10" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="J10" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="K10" s="10" t="inlineStr">
+        <is>
+          <t>疑似出货</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="26" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>605208</t>
+          <t>300487</t>
         </is>
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>永茂泰</t>
-        </is>
-      </c>
-      <c r="C11" s="7" t="n">
-        <v>-1.92</v>
+          <t>蓝晓科技</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="n">
+        <v>0.34</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="E11" s="7" t="inlineStr">
-        <is>
-          <t>正常</t>
+        <v>1.4</v>
+      </c>
+      <c r="E11" s="13" t="inlineStr">
+        <is>
+          <t>放量</t>
         </is>
       </c>
       <c r="F11" s="7" t="n">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H11" s="7" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="I11" s="7" t="n">
-        <v>-1.92</v>
+        <v>-1</v>
       </c>
       <c r="J11" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="K11" s="7" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="K11" s="7" t="inlineStr">
+        <is>
+          <t>★极近均线</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="26" customHeight="1">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>688795</t>
+          <t>603991</t>
         </is>
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>摩尔线程</t>
+          <t>领先股份</t>
         </is>
       </c>
       <c r="C12" s="10" t="n">
-        <v>1.68</v>
+        <v>1.07</v>
       </c>
       <c r="D12" s="10" t="n">
-        <v>0.85</v>
+        <v>1.05</v>
       </c>
       <c r="E12" s="10" t="inlineStr">
         <is>
@@ -14970,18 +15004,18 @@
         </is>
       </c>
       <c r="F12" s="10" t="n">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="G12" s="10" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="H12" s="10" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="I12" s="10" t="n">
-        <v>2.12</v>
+        <v>10</v>
       </c>
       <c r="J12" s="10" t="n">
         <v>2</v>
@@ -14989,107 +15023,103 @@
       <c r="K12" s="10" t="inlineStr"/>
     </row>
     <row r="13" ht="26" customHeight="1">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>603068</t>
-        </is>
-      </c>
-      <c r="B13" s="8" t="inlineStr">
-        <is>
-          <t>博通集成</t>
-        </is>
-      </c>
-      <c r="C13" s="7" t="n">
-        <v>-2.12</v>
-      </c>
-      <c r="D13" s="7" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="E13" s="7" t="inlineStr">
-        <is>
-          <t>正常</t>
-        </is>
-      </c>
-      <c r="F13" s="7" t="n">
-        <v>40</v>
-      </c>
-      <c r="G13" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="H13" s="7" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="I13" s="7" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="J13" s="7" t="n">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>301151</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>冠龙节能</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>缩量</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>44</v>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="n">
+        <v>7.33</v>
+      </c>
+      <c r="J13" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="K13" s="3" t="inlineStr"/>
+    </row>
+    <row r="14" ht="26" customHeight="1">
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>605208</t>
+        </is>
+      </c>
+      <c r="B14" s="11" t="inlineStr">
+        <is>
+          <t>永茂泰</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="n">
+        <v>-1.92</v>
+      </c>
+      <c r="D14" s="10" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="E14" s="10" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="F14" s="10" t="n">
+        <v>41</v>
+      </c>
+      <c r="G14" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="K13" s="7" t="inlineStr">
-        <is>
-          <t>疑似出货</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="26" customHeight="1">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>603928</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>兴业股份</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="n">
-        <v>-2.75</v>
-      </c>
-      <c r="D14" s="3" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t>缩量</t>
-        </is>
-      </c>
-      <c r="F14" s="3" t="n">
-        <v>34</v>
-      </c>
-      <c r="G14" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="H14" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="I14" s="3" t="n">
-        <v>10.02</v>
-      </c>
-      <c r="J14" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="K14" s="3" t="inlineStr"/>
+      <c r="H14" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="I14" s="10" t="n">
+        <v>-1.92</v>
+      </c>
+      <c r="J14" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="K14" s="10" t="inlineStr"/>
     </row>
     <row r="15" ht="26" customHeight="1">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>688720</t>
+          <t>688795</t>
         </is>
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>艾森股份</t>
+          <t>摩尔线程</t>
         </is>
       </c>
       <c r="C15" s="7" t="n">
-        <v>1.84</v>
+        <v>1.68</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
@@ -15097,40 +15127,40 @@
         </is>
       </c>
       <c r="F15" s="7" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="G15" s="7" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H15" s="7" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="I15" s="7" t="n">
-        <v>20</v>
+        <v>2.12</v>
       </c>
       <c r="J15" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K15" s="7" t="inlineStr"/>
     </row>
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>688046</t>
+          <t>603068</t>
         </is>
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>药康生物</t>
+          <t>博通集成</t>
         </is>
       </c>
       <c r="C16" s="10" t="n">
-        <v>2.68</v>
+        <v>-2.12</v>
       </c>
       <c r="D16" s="10" t="n">
-        <v>0.93</v>
+        <v>1.13</v>
       </c>
       <c r="E16" s="10" t="inlineStr">
         <is>
@@ -15138,7 +15168,7 @@
         </is>
       </c>
       <c r="F16" s="10" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="G16" s="10" t="n">
         <v>5</v>
@@ -15149,15 +15179,183 @@
         </is>
       </c>
       <c r="I16" s="10" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="J16" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="K16" s="10" t="inlineStr">
+        <is>
+          <t>疑似出货</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="26" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>603928</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>兴业股份</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>-2.75</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>缩量</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>34</v>
+      </c>
+      <c r="G17" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="n">
+        <v>10.02</v>
+      </c>
+      <c r="J17" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="K17" s="3" t="inlineStr"/>
+    </row>
+    <row r="18" ht="26" customHeight="1">
+      <c r="A18" s="10" t="inlineStr">
+        <is>
+          <t>688720</t>
+        </is>
+      </c>
+      <c r="B18" s="11" t="inlineStr">
+        <is>
+          <t>艾森股份</t>
+        </is>
+      </c>
+      <c r="C18" s="10" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="D18" s="10" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E18" s="10" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="F18" s="10" t="n">
+        <v>34</v>
+      </c>
+      <c r="G18" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="H18" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="I18" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="J18" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" s="10" t="inlineStr"/>
+    </row>
+    <row r="19" ht="26" customHeight="1">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>688046</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>药康生物</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="D19" s="7" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="G19" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="H19" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="I19" s="7" t="n">
         <v>0.66</v>
       </c>
-      <c r="J16" s="10" t="n">
+      <c r="J19" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="K16" s="10" t="inlineStr"/>
+      <c r="K19" s="7" t="inlineStr"/>
+    </row>
+    <row r="20" ht="26" customHeight="1">
+      <c r="A20" s="10" t="inlineStr">
+        <is>
+          <t>603259</t>
+        </is>
+      </c>
+      <c r="B20" s="11" t="inlineStr">
+        <is>
+          <t>药明康德 NEW</t>
+        </is>
+      </c>
+      <c r="C20" s="10" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="D20" s="10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="E20" s="12" t="inlineStr">
+        <is>
+          <t>放量</t>
+        </is>
+      </c>
+      <c r="F20" s="10" t="n">
+        <v>24</v>
+      </c>
+      <c r="G20" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="I20" s="10" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J20" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="K20" s="10" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:K16"/>
+  <autoFilter ref="A3:K20"/>
   <mergeCells count="1">
     <mergeCell ref="A1:K1"/>
   </mergeCells>
@@ -15205,7 +15403,7 @@
       </c>
       <c r="B4" s="30" t="inlineStr">
         <is>
-          <t>-1941  !!冰点(新低1970)</t>
+          <t>-2275  !!冰点(新低2314)</t>
         </is>
       </c>
     </row>
@@ -15217,7 +15415,7 @@
       </c>
       <c r="B5" s="30" t="inlineStr">
         <is>
-          <t>医药(11), 创新药(5), 算力(1)</t>
+          <t>医药(11), 创新药(5), 芯片(2)</t>
         </is>
       </c>
     </row>
@@ -15229,7 +15427,7 @@
       </c>
       <c r="B6" s="30" t="inlineStr">
         <is>
-          <t>13只核心股距MA13 ±3%，首列重点关注</t>
+          <t>17只核心股距MA13 ±3%，首列重点关注</t>
         </is>
       </c>
     </row>

--- a/百日新高v4.0最终版/百日新高_报表.xlsx
+++ b/百日新高v4.0最终版/百日新高_报表.xlsx
@@ -16,10 +16,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="投资洞察" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'核心主线跟踪'!$A$3:$N$243</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'后备观察池'!$A$3:$H$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'风险过滤清单'!$A$3:$G$32</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'全库扫描(MA13±3%)'!$A$3:$K$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'核心主线跟踪'!$A$3:$N$245</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'风险过滤清单'!$A$3:$G$38</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'全库扫描(MA13±3%)'!$A$3:$K$13</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -199,7 +198,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -265,12 +264,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -674,7 +667,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N243"/>
+  <dimension ref="A1:N245"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -695,7 +688,7 @@
     <row r="1" ht="36" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>百日新高 v5.0 | 2026-07-22 | 下跌市(强制空仓) 0% | 风险过滤29只</t>
+          <t>百日新高 v5.0 | 2026-07-27 | 下跌市(强制空仓) 0% | 风险过滤35只</t>
         </is>
       </c>
     </row>
@@ -3640,53 +3633,57 @@
       <c r="M60" s="7" t="inlineStr"/>
     </row>
     <row r="61" ht="26" customHeight="1">
-      <c r="A61" s="10" t="inlineStr">
+      <c r="A61" s="15" t="inlineStr">
         <is>
           <t>600998</t>
         </is>
       </c>
-      <c r="B61" s="11" t="inlineStr">
+      <c r="B61" s="16" t="inlineStr">
         <is>
           <t>九州通</t>
         </is>
       </c>
-      <c r="C61" s="10" t="inlineStr">
+      <c r="C61" s="15" t="inlineStr">
         <is>
           <t>创新药/CRO</t>
         </is>
       </c>
-      <c r="D61" s="10" t="inlineStr">
+      <c r="D61" s="15" t="inlineStr">
         <is>
           <t>2026-07-17</t>
         </is>
       </c>
-      <c r="E61" s="10" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="F61" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="G61" s="10" t="inlineStr">
+      <c r="E61" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="F61" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="G61" s="17" t="inlineStr">
         <is>
           <t>高位整理</t>
         </is>
       </c>
-      <c r="H61" s="14" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="I61" s="14" t="n">
+      <c r="H61" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I61" s="18" t="n">
         <v>-0.09</v>
       </c>
-      <c r="J61" s="10" t="n"/>
-      <c r="K61" s="10" t="inlineStr">
-        <is>
-          <t>正常</t>
-        </is>
-      </c>
-      <c r="L61" s="10" t="inlineStr"/>
-      <c r="M61" s="10" t="inlineStr"/>
+      <c r="J61" s="15" t="n"/>
+      <c r="K61" s="15" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="L61" s="15" t="inlineStr">
+        <is>
+          <t>5次上榜仅涨-1.0%(疑似出货)</t>
+        </is>
+      </c>
+      <c r="M61" s="15" t="inlineStr"/>
     </row>
     <row r="62" ht="26" customHeight="1">
       <c r="A62" s="7" t="inlineStr">
@@ -3862,11 +3859,11 @@
       </c>
       <c r="E65" s="15" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="F65" s="15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G65" s="17" t="inlineStr">
         <is>
@@ -3874,7 +3871,7 @@
         </is>
       </c>
       <c r="H65" s="19" t="n">
-        <v>0.04</v>
+        <v>0.85</v>
       </c>
       <c r="I65" s="18" t="n">
         <v>1.21</v>
@@ -3889,59 +3886,63 @@
       </c>
       <c r="L65" s="15" t="inlineStr">
         <is>
-          <t>5次上榜仅涨+2.4%(疑似出货)</t>
+          <t>5次上榜仅涨+3.2%(疑似出货)</t>
         </is>
       </c>
       <c r="M65" s="15" t="inlineStr"/>
     </row>
     <row r="66" ht="26" customHeight="1">
-      <c r="A66" s="7" t="inlineStr">
+      <c r="A66" s="15" t="inlineStr">
         <is>
           <t>601607</t>
         </is>
       </c>
-      <c r="B66" s="8" t="inlineStr">
+      <c r="B66" s="16" t="inlineStr">
         <is>
           <t>上海医药</t>
         </is>
       </c>
-      <c r="C66" s="7" t="inlineStr">
+      <c r="C66" s="15" t="inlineStr">
         <is>
           <t>创新药/CRO</t>
         </is>
       </c>
-      <c r="D66" s="7" t="inlineStr">
+      <c r="D66" s="15" t="inlineStr">
         <is>
           <t>2026-07-21</t>
         </is>
       </c>
-      <c r="E66" s="7" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="F66" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G66" s="7" t="inlineStr">
+      <c r="E66" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="F66" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="G66" s="17" t="inlineStr">
         <is>
           <t>高位整理</t>
         </is>
       </c>
-      <c r="H66" s="13" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="I66" s="9" t="n">
+      <c r="H66" s="19" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="I66" s="18" t="n">
         <v>1.52</v>
       </c>
-      <c r="J66" s="7" t="n"/>
-      <c r="K66" s="7" t="inlineStr">
-        <is>
-          <t>正常</t>
-        </is>
-      </c>
-      <c r="L66" s="7" t="inlineStr"/>
-      <c r="M66" s="7" t="inlineStr"/>
+      <c r="J66" s="15" t="n"/>
+      <c r="K66" s="15" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="L66" s="15" t="inlineStr">
+        <is>
+          <t>5次上榜仅涨-1.1%(疑似出货)</t>
+        </is>
+      </c>
+      <c r="M66" s="15" t="inlineStr"/>
     </row>
     <row r="67" ht="26" customHeight="1">
       <c r="A67" s="10" t="inlineStr">
@@ -4509,53 +4510,57 @@
       <c r="M77" s="10" t="inlineStr"/>
     </row>
     <row r="78" ht="26" customHeight="1">
-      <c r="A78" s="7" t="inlineStr">
+      <c r="A78" s="15" t="inlineStr">
         <is>
           <t>600267</t>
         </is>
       </c>
-      <c r="B78" s="8" t="inlineStr">
+      <c r="B78" s="16" t="inlineStr">
         <is>
           <t>海正药业</t>
         </is>
       </c>
-      <c r="C78" s="7" t="inlineStr">
+      <c r="C78" s="15" t="inlineStr">
         <is>
           <t>创新药/CRO</t>
         </is>
       </c>
-      <c r="D78" s="7" t="inlineStr">
+      <c r="D78" s="15" t="inlineStr">
         <is>
           <t>2026-07-16</t>
         </is>
       </c>
-      <c r="E78" s="7" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="F78" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="G78" s="7" t="inlineStr">
+      <c r="E78" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="F78" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="G78" s="17" t="inlineStr">
         <is>
           <t>高位整理</t>
         </is>
       </c>
-      <c r="H78" s="13" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="I78" s="7" t="n">
+      <c r="H78" s="18" t="n">
+        <v>-3.37</v>
+      </c>
+      <c r="I78" s="15" t="n">
         <v>8</v>
       </c>
-      <c r="J78" s="7" t="n"/>
-      <c r="K78" s="7" t="inlineStr">
-        <is>
-          <t>正常</t>
-        </is>
-      </c>
-      <c r="L78" s="7" t="inlineStr"/>
-      <c r="M78" s="7" t="inlineStr"/>
+      <c r="J78" s="15" t="n"/>
+      <c r="K78" s="15" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="L78" s="15" t="inlineStr">
+        <is>
+          <t>5次上榜仅涨+0.6%(疑似出货)</t>
+        </is>
+      </c>
+      <c r="M78" s="15" t="inlineStr"/>
     </row>
     <row r="79" ht="26" customHeight="1">
       <c r="A79" s="10" t="inlineStr">
@@ -4609,55 +4614,59 @@
       <c r="M79" s="10" t="inlineStr"/>
     </row>
     <row r="80" ht="26" customHeight="1">
-      <c r="A80" s="7" t="inlineStr">
+      <c r="A80" s="15" t="inlineStr">
         <is>
           <t>600566</t>
         </is>
       </c>
-      <c r="B80" s="8" t="inlineStr">
+      <c r="B80" s="16" t="inlineStr">
         <is>
           <t>济川药业</t>
         </is>
       </c>
-      <c r="C80" s="7" t="inlineStr">
+      <c r="C80" s="15" t="inlineStr">
         <is>
           <t>创新药/CRO</t>
         </is>
       </c>
-      <c r="D80" s="7" t="inlineStr">
+      <c r="D80" s="15" t="inlineStr">
         <is>
           <t>2026-07-21</t>
         </is>
       </c>
-      <c r="E80" s="7" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="F80" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G80" s="7" t="inlineStr">
+      <c r="E80" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="F80" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="G80" s="17" t="inlineStr">
         <is>
           <t>高位整理</t>
         </is>
       </c>
-      <c r="H80" s="13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="I80" s="7" t="n">
+      <c r="H80" s="19" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="I80" s="15" t="n">
         <v>8.890000000000001</v>
       </c>
-      <c r="J80" s="7" t="n">
+      <c r="J80" s="15" t="n">
         <v>0.86</v>
       </c>
-      <c r="K80" s="7" t="inlineStr">
-        <is>
-          <t>正常</t>
-        </is>
-      </c>
-      <c r="L80" s="7" t="inlineStr"/>
-      <c r="M80" s="7" t="inlineStr"/>
+      <c r="K80" s="15" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="L80" s="15" t="inlineStr">
+        <is>
+          <t>5次上榜仅涨-0.9%(疑似出货)</t>
+        </is>
+      </c>
+      <c r="M80" s="15" t="inlineStr"/>
     </row>
     <row r="81" ht="26" customHeight="1">
       <c r="A81" s="10" t="inlineStr">
@@ -4709,93 +4718,99 @@
       <c r="M81" s="10" t="inlineStr"/>
     </row>
     <row r="82" ht="26" customHeight="1">
-      <c r="A82" s="7" t="inlineStr">
-        <is>
-          <t>000977</t>
-        </is>
-      </c>
-      <c r="B82" s="8" t="inlineStr">
-        <is>
-          <t>浪潮信息</t>
-        </is>
-      </c>
-      <c r="C82" s="7" t="inlineStr">
-        <is>
-          <t>算力/通信</t>
-        </is>
-      </c>
-      <c r="D82" s="7" t="inlineStr">
-        <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="E82" s="7" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="F82" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G82" s="7" t="inlineStr">
+      <c r="A82" s="15" t="inlineStr">
+        <is>
+          <t>603893</t>
+        </is>
+      </c>
+      <c r="B82" s="16" t="inlineStr">
+        <is>
+          <t>瑞芯微</t>
+        </is>
+      </c>
+      <c r="C82" s="15" t="inlineStr">
+        <is>
+          <t>半导体/芯片</t>
+        </is>
+      </c>
+      <c r="D82" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="E82" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="F82" s="15" t="n">
+        <v>6</v>
+      </c>
+      <c r="G82" s="17" t="inlineStr">
         <is>
           <t>高位整理</t>
         </is>
       </c>
-      <c r="H82" s="13" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="I82" s="7" t="n">
-        <v>10.28</v>
-      </c>
-      <c r="J82" s="7" t="n"/>
-      <c r="K82" s="7" t="inlineStr">
-        <is>
-          <t>正常</t>
-        </is>
-      </c>
-      <c r="L82" s="7" t="inlineStr"/>
-      <c r="M82" s="7" t="inlineStr"/>
+      <c r="H82" s="18" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="I82" s="15" t="n">
+        <v>10.17</v>
+      </c>
+      <c r="J82" s="15" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="K82" s="15" t="inlineStr">
+        <is>
+          <t>放量</t>
+        </is>
+      </c>
+      <c r="L82" s="15" t="inlineStr">
+        <is>
+          <t>5次上榜仅涨-0.5%(疑似出货)</t>
+        </is>
+      </c>
+      <c r="M82" s="15" t="inlineStr"/>
     </row>
     <row r="83" ht="26" customHeight="1">
       <c r="A83" s="10" t="inlineStr">
         <is>
-          <t>002653</t>
+          <t>000977</t>
         </is>
       </c>
       <c r="B83" s="11" t="inlineStr">
         <is>
-          <t>海思科</t>
+          <t>浪潮信息</t>
         </is>
       </c>
       <c r="C83" s="10" t="inlineStr">
         <is>
-          <t>创新药/CRO</t>
+          <t>算力/通信</t>
         </is>
       </c>
       <c r="D83" s="10" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="E83" s="10" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="F83" s="10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G83" s="10" t="inlineStr">
         <is>
           <t>高位整理</t>
         </is>
       </c>
-      <c r="H83" s="14" t="n">
-        <v>-2.96</v>
+      <c r="H83" s="12" t="n">
+        <v>2.04</v>
       </c>
       <c r="I83" s="10" t="n">
-        <v>11.09</v>
+        <v>10.28</v>
       </c>
       <c r="J83" s="10" t="n"/>
       <c r="K83" s="10" t="inlineStr">
@@ -4807,108 +4822,106 @@
       <c r="M83" s="10" t="inlineStr"/>
     </row>
     <row r="84" ht="26" customHeight="1">
-      <c r="A84" s="15" t="inlineStr">
+      <c r="A84" s="7" t="inlineStr">
+        <is>
+          <t>002653</t>
+        </is>
+      </c>
+      <c r="B84" s="8" t="inlineStr">
+        <is>
+          <t>海思科</t>
+        </is>
+      </c>
+      <c r="C84" s="7" t="inlineStr">
+        <is>
+          <t>创新药/CRO</t>
+        </is>
+      </c>
+      <c r="D84" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="E84" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="F84" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="G84" s="7" t="inlineStr">
+        <is>
+          <t>高位整理</t>
+        </is>
+      </c>
+      <c r="H84" s="9" t="n">
+        <v>-2.96</v>
+      </c>
+      <c r="I84" s="7" t="n">
+        <v>11.09</v>
+      </c>
+      <c r="J84" s="7" t="n"/>
+      <c r="K84" s="7" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="L84" s="7" t="inlineStr"/>
+      <c r="M84" s="7" t="inlineStr"/>
+    </row>
+    <row r="85" ht="26" customHeight="1">
+      <c r="A85" s="15" t="inlineStr">
         <is>
           <t>600535</t>
         </is>
       </c>
-      <c r="B84" s="16" t="inlineStr">
+      <c r="B85" s="16" t="inlineStr">
         <is>
           <t>天士力</t>
         </is>
       </c>
-      <c r="C84" s="15" t="inlineStr">
+      <c r="C85" s="15" t="inlineStr">
         <is>
           <t>创新药/CRO</t>
         </is>
       </c>
-      <c r="D84" s="15" t="inlineStr">
+      <c r="D85" s="15" t="inlineStr">
         <is>
           <t>2026-07-16</t>
         </is>
       </c>
-      <c r="E84" s="15" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="F84" s="15" t="n">
-        <v>5</v>
-      </c>
-      <c r="G84" s="17" t="inlineStr">
+      <c r="E85" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="F85" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="G85" s="17" t="inlineStr">
         <is>
           <t>高位整理</t>
         </is>
       </c>
-      <c r="H84" s="19" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="I84" s="15" t="n">
+      <c r="H85" s="18" t="n">
+        <v>-1.19</v>
+      </c>
+      <c r="I85" s="15" t="n">
         <v>11.69</v>
       </c>
-      <c r="J84" s="15" t="n"/>
-      <c r="K84" s="15" t="inlineStr">
-        <is>
-          <t>正常</t>
-        </is>
-      </c>
-      <c r="L84" s="15" t="inlineStr">
-        <is>
-          <t>5次上榜仅涨+0.4%(疑似出货)</t>
-        </is>
-      </c>
-      <c r="M84" s="15" t="inlineStr"/>
-    </row>
-    <row r="85" ht="26" customHeight="1">
-      <c r="A85" s="10" t="inlineStr">
-        <is>
-          <t>688758</t>
-        </is>
-      </c>
-      <c r="B85" s="11" t="inlineStr">
-        <is>
-          <t>赛分科技</t>
-        </is>
-      </c>
-      <c r="C85" s="10" t="inlineStr">
-        <is>
-          <t>创新药/CRO</t>
-        </is>
-      </c>
-      <c r="D85" s="10" t="inlineStr">
-        <is>
-          <t>2026-07-03</t>
-        </is>
-      </c>
-      <c r="E85" s="10" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="F85" s="10" t="n">
-        <v>8</v>
-      </c>
-      <c r="G85" s="10" t="inlineStr">
-        <is>
-          <t>高位整理</t>
-        </is>
-      </c>
-      <c r="H85" s="12" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="I85" s="10" t="n">
-        <v>13.71</v>
-      </c>
-      <c r="J85" s="10" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="K85" s="10" t="inlineStr">
-        <is>
-          <t>放量</t>
-        </is>
-      </c>
-      <c r="L85" s="10" t="inlineStr"/>
-      <c r="M85" s="10" t="inlineStr"/>
+      <c r="J85" s="15" t="n"/>
+      <c r="K85" s="15" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="L85" s="15" t="inlineStr">
+        <is>
+          <t>5次上榜仅涨-1.1%(疑似出货)</t>
+        </is>
+      </c>
+      <c r="M85" s="15" t="inlineStr"/>
     </row>
     <row r="86" ht="26" customHeight="1">
       <c r="A86" s="7" t="inlineStr">
@@ -4964,47 +4977,49 @@
     <row r="87" ht="26" customHeight="1">
       <c r="A87" s="10" t="inlineStr">
         <is>
-          <t>600664</t>
+          <t>301165</t>
         </is>
       </c>
       <c r="B87" s="11" t="inlineStr">
         <is>
-          <t>哈药股份</t>
+          <t>锐捷网络</t>
         </is>
       </c>
       <c r="C87" s="10" t="inlineStr">
         <is>
-          <t>创新药/CRO</t>
+          <t>算力/通信</t>
         </is>
       </c>
       <c r="D87" s="10" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="E87" s="10" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="F87" s="10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G87" s="10" t="inlineStr">
         <is>
           <t>高位整理</t>
         </is>
       </c>
-      <c r="H87" s="12" t="n">
-        <v>2.4</v>
+      <c r="H87" s="14" t="n">
+        <v>-1.03</v>
       </c>
       <c r="I87" s="10" t="n">
-        <v>44.31</v>
-      </c>
-      <c r="J87" s="10" t="n"/>
+        <v>20.52</v>
+      </c>
+      <c r="J87" s="10" t="n">
+        <v>1.6</v>
+      </c>
       <c r="K87" s="10" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>放量</t>
         </is>
       </c>
       <c r="L87" s="10" t="inlineStr"/>
@@ -5013,12 +5028,12 @@
     <row r="88" ht="26" customHeight="1">
       <c r="A88" s="7" t="inlineStr">
         <is>
-          <t>300534</t>
+          <t>600664</t>
         </is>
       </c>
       <c r="B88" s="8" t="inlineStr">
         <is>
-          <t>陇神戎发</t>
+          <t>哈药股份</t>
         </is>
       </c>
       <c r="C88" s="7" t="inlineStr">
@@ -5033,22 +5048,22 @@
       </c>
       <c r="E88" s="7" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="F88" s="7" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G88" s="7" t="inlineStr">
         <is>
           <t>高位整理</t>
         </is>
       </c>
-      <c r="H88" s="9" t="n">
-        <v>-3.91</v>
+      <c r="H88" s="13" t="n">
+        <v>0.33</v>
       </c>
       <c r="I88" s="7" t="n">
-        <v>46.22</v>
+        <v>44.31</v>
       </c>
       <c r="J88" s="7" t="n"/>
       <c r="K88" s="7" t="inlineStr">
@@ -11712,31 +11727,31 @@
     <row r="221" ht="26" customHeight="1">
       <c r="A221" s="10" t="inlineStr">
         <is>
-          <t>603893</t>
+          <t>002422</t>
         </is>
       </c>
       <c r="B221" s="11" t="inlineStr">
         <is>
-          <t>瑞芯微</t>
+          <t>科伦药业</t>
         </is>
       </c>
       <c r="C221" s="10" t="inlineStr">
         <is>
-          <t>半导体/芯片</t>
+          <t>创新药/CRO</t>
         </is>
       </c>
       <c r="D221" s="10" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="E221" s="10" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="F221" s="10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G221" s="10" t="inlineStr">
         <is>
@@ -11744,13 +11759,13 @@
         </is>
       </c>
       <c r="H221" s="12" t="n">
-        <v>10</v>
+        <v>7.22</v>
       </c>
       <c r="I221" s="10" t="n">
-        <v>10.17</v>
+        <v>10.78</v>
       </c>
       <c r="J221" s="10" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="K221" s="10" t="inlineStr">
         <is>
@@ -11763,12 +11778,12 @@
     <row r="222" ht="26" customHeight="1">
       <c r="A222" s="7" t="inlineStr">
         <is>
-          <t>002422</t>
+          <t>603669</t>
         </is>
       </c>
       <c r="B222" s="8" t="inlineStr">
         <is>
-          <t>科伦药业</t>
+          <t>灵康药业</t>
         </is>
       </c>
       <c r="C222" s="7" t="inlineStr">
@@ -11778,16 +11793,16 @@
       </c>
       <c r="D222" s="7" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="E222" s="7" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="F222" s="7" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G222" s="7" t="inlineStr">
         <is>
@@ -11795,13 +11810,13 @@
         </is>
       </c>
       <c r="H222" s="13" t="n">
-        <v>7.22</v>
+        <v>9.59</v>
       </c>
       <c r="I222" s="7" t="n">
-        <v>10.78</v>
+        <v>13.41</v>
       </c>
       <c r="J222" s="7" t="n">
-        <v>1.22</v>
+        <v>2.57</v>
       </c>
       <c r="K222" s="7" t="inlineStr">
         <is>
@@ -11814,12 +11829,12 @@
     <row r="223" ht="26" customHeight="1">
       <c r="A223" s="10" t="inlineStr">
         <is>
-          <t>603669</t>
+          <t>688758</t>
         </is>
       </c>
       <c r="B223" s="11" t="inlineStr">
         <is>
-          <t>灵康药业</t>
+          <t>赛分科技</t>
         </is>
       </c>
       <c r="C223" s="10" t="inlineStr">
@@ -11829,12 +11844,12 @@
       </c>
       <c r="D223" s="10" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="E223" s="10" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="F223" s="10" t="n">
@@ -11846,13 +11861,13 @@
         </is>
       </c>
       <c r="H223" s="12" t="n">
-        <v>9.59</v>
+        <v>3.66</v>
       </c>
       <c r="I223" s="10" t="n">
-        <v>13.41</v>
+        <v>13.71</v>
       </c>
       <c r="J223" s="10" t="n">
-        <v>2.57</v>
+        <v>1.86</v>
       </c>
       <c r="K223" s="10" t="inlineStr">
         <is>
@@ -12224,12 +12239,12 @@
     <row r="231" ht="26" customHeight="1">
       <c r="A231" s="10" t="inlineStr">
         <is>
-          <t>301165</t>
+          <t>000938</t>
         </is>
       </c>
       <c r="B231" s="11" t="inlineStr">
         <is>
-          <t>锐捷网络</t>
+          <t>紫光股份</t>
         </is>
       </c>
       <c r="C231" s="10" t="inlineStr">
@@ -12239,7 +12254,7 @@
       </c>
       <c r="D231" s="10" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="E231" s="10" t="inlineStr">
@@ -12248,7 +12263,7 @@
         </is>
       </c>
       <c r="F231" s="10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G231" s="10" t="inlineStr">
         <is>
@@ -12256,13 +12271,13 @@
         </is>
       </c>
       <c r="H231" s="12" t="n">
-        <v>13.66</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I231" s="10" t="n">
-        <v>20.52</v>
+        <v>21.31</v>
       </c>
       <c r="J231" s="10" t="n">
-        <v>1.6</v>
+        <v>1.23</v>
       </c>
       <c r="K231" s="10" t="inlineStr">
         <is>
@@ -12275,31 +12290,31 @@
     <row r="232" ht="26" customHeight="1">
       <c r="A232" s="7" t="inlineStr">
         <is>
-          <t>000938</t>
+          <t>002841</t>
         </is>
       </c>
       <c r="B232" s="8" t="inlineStr">
         <is>
-          <t>紫光股份</t>
+          <t>视源股份</t>
         </is>
       </c>
       <c r="C232" s="7" t="inlineStr">
         <is>
-          <t>算力/通信</t>
+          <t>机器人</t>
         </is>
       </c>
       <c r="D232" s="7" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="E232" s="7" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="F232" s="7" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G232" s="7" t="inlineStr">
         <is>
@@ -12307,17 +12322,17 @@
         </is>
       </c>
       <c r="H232" s="13" t="n">
-        <v>8.300000000000001</v>
+        <v>10</v>
       </c>
       <c r="I232" s="7" t="n">
-        <v>21.31</v>
+        <v>22.83</v>
       </c>
       <c r="J232" s="7" t="n">
-        <v>1.23</v>
+        <v>0.9</v>
       </c>
       <c r="K232" s="7" t="inlineStr">
         <is>
-          <t>放量</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="L232" s="7" t="inlineStr"/>
@@ -12326,17 +12341,17 @@
     <row r="233" ht="26" customHeight="1">
       <c r="A233" s="10" t="inlineStr">
         <is>
-          <t>002841</t>
+          <t>603127</t>
         </is>
       </c>
       <c r="B233" s="11" t="inlineStr">
         <is>
-          <t>视源股份</t>
+          <t>昭衍新药</t>
         </is>
       </c>
       <c r="C233" s="10" t="inlineStr">
         <is>
-          <t>机器人</t>
+          <t>创新药/CRO</t>
         </is>
       </c>
       <c r="D233" s="10" t="inlineStr">
@@ -12346,11 +12361,11 @@
       </c>
       <c r="E233" s="10" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="F233" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G233" s="10" t="inlineStr">
         <is>
@@ -12358,101 +12373,103 @@
         </is>
       </c>
       <c r="H233" s="12" t="n">
-        <v>10</v>
+        <v>5.2</v>
       </c>
       <c r="I233" s="10" t="n">
-        <v>22.83</v>
+        <v>25.15</v>
       </c>
       <c r="J233" s="10" t="n">
-        <v>0.9</v>
+        <v>1.62</v>
       </c>
       <c r="K233" s="10" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>放量</t>
         </is>
       </c>
       <c r="L233" s="10" t="inlineStr"/>
       <c r="M233" s="10" t="inlineStr"/>
     </row>
     <row r="234" ht="26" customHeight="1">
-      <c r="A234" s="7" t="inlineStr">
-        <is>
-          <t>603127</t>
-        </is>
-      </c>
-      <c r="B234" s="8" t="inlineStr">
-        <is>
-          <t>昭衍新药</t>
-        </is>
-      </c>
-      <c r="C234" s="7" t="inlineStr">
+      <c r="A234" s="15" t="inlineStr">
+        <is>
+          <t>688192</t>
+        </is>
+      </c>
+      <c r="B234" s="16" t="inlineStr">
+        <is>
+          <t>迪哲医药</t>
+        </is>
+      </c>
+      <c r="C234" s="15" t="inlineStr">
         <is>
           <t>创新药/CRO</t>
         </is>
       </c>
-      <c r="D234" s="7" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
-      <c r="E234" s="7" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="F234" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="G234" s="7" t="inlineStr">
-        <is>
-          <t>强势上攻</t>
-        </is>
-      </c>
-      <c r="H234" s="13" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="I234" s="7" t="n">
-        <v>25.15</v>
-      </c>
-      <c r="J234" s="7" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="K234" s="7" t="inlineStr">
-        <is>
-          <t>放量</t>
-        </is>
-      </c>
-      <c r="L234" s="7" t="inlineStr"/>
-      <c r="M234" s="7" t="inlineStr"/>
+      <c r="D234" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="E234" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="F234" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G234" s="17" t="inlineStr">
+        <is>
+          <t>强势上攻</t>
+        </is>
+      </c>
+      <c r="H234" s="19" t="n">
+        <v>20.01</v>
+      </c>
+      <c r="I234" s="15" t="n">
+        <v>29.06</v>
+      </c>
+      <c r="J234" s="15" t="n"/>
+      <c r="K234" s="15" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="L234" s="15" t="inlineStr">
+        <is>
+          <t>首日涨幅&gt;20%</t>
+        </is>
+      </c>
+      <c r="M234" s="15" t="inlineStr"/>
     </row>
     <row r="235" ht="26" customHeight="1">
       <c r="A235" s="15" t="inlineStr">
         <is>
-          <t>688192</t>
+          <t>300214</t>
         </is>
       </c>
       <c r="B235" s="16" t="inlineStr">
         <is>
-          <t>迪哲医药</t>
+          <t>日科化学</t>
         </is>
       </c>
       <c r="C235" s="15" t="inlineStr">
         <is>
-          <t>创新药/CRO</t>
+          <t>算力/通信</t>
         </is>
       </c>
       <c r="D235" s="15" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="E235" s="15" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="F235" s="15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G235" s="17" t="inlineStr">
         <is>
@@ -12460,15 +12477,17 @@
         </is>
       </c>
       <c r="H235" s="19" t="n">
-        <v>20.01</v>
+        <v>19.98</v>
       </c>
       <c r="I235" s="15" t="n">
-        <v>29.06</v>
-      </c>
-      <c r="J235" s="15" t="n"/>
+        <v>32.25</v>
+      </c>
+      <c r="J235" s="15" t="n">
+        <v>1.51</v>
+      </c>
       <c r="K235" s="15" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>放量</t>
         </is>
       </c>
       <c r="L235" s="15" t="inlineStr">
@@ -12532,12 +12551,12 @@
     <row r="237" ht="26" customHeight="1">
       <c r="A237" s="10" t="inlineStr">
         <is>
-          <t>301520</t>
+          <t>300534</t>
         </is>
       </c>
       <c r="B237" s="11" t="inlineStr">
         <is>
-          <t>万邦医药</t>
+          <t>陇神戎发</t>
         </is>
       </c>
       <c r="C237" s="10" t="inlineStr">
@@ -12547,16 +12566,16 @@
       </c>
       <c r="D237" s="10" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="E237" s="10" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="F237" s="10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G237" s="10" t="inlineStr">
         <is>
@@ -12564,14 +12583,12 @@
         </is>
       </c>
       <c r="H237" s="12" t="n">
-        <v>13.37</v>
+        <v>20.04</v>
       </c>
       <c r="I237" s="10" t="n">
-        <v>53.52</v>
-      </c>
-      <c r="J237" s="10" t="n">
-        <v>1.08</v>
-      </c>
+        <v>46.22</v>
+      </c>
+      <c r="J237" s="10" t="n"/>
       <c r="K237" s="10" t="inlineStr">
         <is>
           <t>正常</t>
@@ -12583,22 +12600,22 @@
     <row r="238" ht="26" customHeight="1">
       <c r="A238" s="7" t="inlineStr">
         <is>
-          <t>002141</t>
+          <t>301520</t>
         </is>
       </c>
       <c r="B238" s="8" t="inlineStr">
         <is>
-          <t>贤丰控股</t>
+          <t>万邦医药</t>
         </is>
       </c>
       <c r="C238" s="7" t="inlineStr">
         <is>
-          <t>算力/通信</t>
+          <t>创新药/CRO</t>
         </is>
       </c>
       <c r="D238" s="7" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="E238" s="7" t="inlineStr">
@@ -12607,7 +12624,7 @@
         </is>
       </c>
       <c r="F238" s="7" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G238" s="7" t="inlineStr">
         <is>
@@ -12615,42 +12632,50 @@
         </is>
       </c>
       <c r="H238" s="13" t="n">
-        <v>5.35</v>
-      </c>
-      <c r="I238" s="7" t="n"/>
-      <c r="J238" s="7" t="n"/>
-      <c r="K238" s="7" t="inlineStr"/>
+        <v>13.37</v>
+      </c>
+      <c r="I238" s="7" t="n">
+        <v>53.52</v>
+      </c>
+      <c r="J238" s="7" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="K238" s="7" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
       <c r="L238" s="7" t="inlineStr"/>
       <c r="M238" s="7" t="inlineStr"/>
     </row>
     <row r="239" ht="26" customHeight="1">
       <c r="A239" s="15" t="inlineStr">
         <is>
-          <t>300214</t>
+          <t>301234</t>
         </is>
       </c>
       <c r="B239" s="16" t="inlineStr">
         <is>
-          <t>日科化学</t>
+          <t>五洲医疗</t>
         </is>
       </c>
       <c r="C239" s="15" t="inlineStr">
         <is>
-          <t>算力/通信</t>
+          <t>创新药/CRO</t>
         </is>
       </c>
       <c r="D239" s="15" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="E239" s="15" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="F239" s="15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G239" s="17" t="inlineStr">
         <is>
@@ -12658,11 +12683,13 @@
         </is>
       </c>
       <c r="H239" s="19" t="n">
-        <v>8.94</v>
-      </c>
-      <c r="I239" s="15" t="n"/>
+        <v>20</v>
+      </c>
+      <c r="I239" s="15" t="n">
+        <v>73.03</v>
+      </c>
       <c r="J239" s="15" t="n">
-        <v>14.71</v>
+        <v>12.8</v>
       </c>
       <c r="K239" s="15" t="inlineStr">
         <is>
@@ -12679,12 +12706,12 @@
     <row r="240" ht="26" customHeight="1">
       <c r="A240" s="7" t="inlineStr">
         <is>
-          <t>301191</t>
+          <t>002141</t>
         </is>
       </c>
       <c r="B240" s="8" t="inlineStr">
         <is>
-          <t>菲菱科思</t>
+          <t>贤丰控股</t>
         </is>
       </c>
       <c r="C240" s="7" t="inlineStr">
@@ -12694,16 +12721,16 @@
       </c>
       <c r="D240" s="7" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="E240" s="7" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="F240" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G240" s="7" t="inlineStr">
         <is>
@@ -12711,48 +12738,42 @@
         </is>
       </c>
       <c r="H240" s="13" t="n">
-        <v>5.09</v>
+        <v>5.35</v>
       </c>
       <c r="I240" s="7" t="n"/>
-      <c r="J240" s="7" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="K240" s="7" t="inlineStr">
-        <is>
-          <t>正常</t>
-        </is>
-      </c>
+      <c r="J240" s="7" t="n"/>
+      <c r="K240" s="7" t="inlineStr"/>
       <c r="L240" s="7" t="inlineStr"/>
       <c r="M240" s="7" t="inlineStr"/>
     </row>
     <row r="241" ht="26" customHeight="1">
       <c r="A241" s="10" t="inlineStr">
         <is>
-          <t>000739</t>
+          <t>301191</t>
         </is>
       </c>
       <c r="B241" s="11" t="inlineStr">
         <is>
-          <t>普洛药业</t>
+          <t>菲菱科思</t>
         </is>
       </c>
       <c r="C241" s="10" t="inlineStr">
         <is>
-          <t>创新药/CRO</t>
+          <t>算力/通信</t>
         </is>
       </c>
       <c r="D241" s="10" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="E241" s="10" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="F241" s="10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G241" s="10" t="inlineStr">
         <is>
@@ -12760,23 +12781,29 @@
         </is>
       </c>
       <c r="H241" s="12" t="n">
-        <v>3.53</v>
+        <v>5.09</v>
       </c>
       <c r="I241" s="10" t="n"/>
-      <c r="J241" s="10" t="n"/>
-      <c r="K241" s="10" t="inlineStr"/>
+      <c r="J241" s="10" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="K241" s="10" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
       <c r="L241" s="10" t="inlineStr"/>
       <c r="M241" s="10" t="inlineStr"/>
     </row>
     <row r="242" ht="26" customHeight="1">
       <c r="A242" s="7" t="inlineStr">
         <is>
-          <t>600881</t>
+          <t>000739</t>
         </is>
       </c>
       <c r="B242" s="8" t="inlineStr">
         <is>
-          <t>亚泰集团</t>
+          <t>普洛药业</t>
         </is>
       </c>
       <c r="C242" s="7" t="inlineStr">
@@ -12786,16 +12813,16 @@
       </c>
       <c r="D242" s="7" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="E242" s="7" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="F242" s="7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G242" s="7" t="inlineStr">
         <is>
@@ -12803,7 +12830,7 @@
         </is>
       </c>
       <c r="H242" s="13" t="n">
-        <v>10.06</v>
+        <v>3.53</v>
       </c>
       <c r="I242" s="7" t="n"/>
       <c r="J242" s="7" t="n"/>
@@ -12812,62 +12839,148 @@
       <c r="M242" s="7" t="inlineStr"/>
     </row>
     <row r="243" ht="26" customHeight="1">
-      <c r="A243" s="15" t="inlineStr">
+      <c r="A243" s="10" t="inlineStr">
+        <is>
+          <t>600881</t>
+        </is>
+      </c>
+      <c r="B243" s="11" t="inlineStr">
+        <is>
+          <t>亚泰集团</t>
+        </is>
+      </c>
+      <c r="C243" s="10" t="inlineStr">
+        <is>
+          <t>创新药/CRO</t>
+        </is>
+      </c>
+      <c r="D243" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="E243" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="F243" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G243" s="10" t="inlineStr">
+        <is>
+          <t>强势上攻</t>
+        </is>
+      </c>
+      <c r="H243" s="12" t="n">
+        <v>10.06</v>
+      </c>
+      <c r="I243" s="10" t="n"/>
+      <c r="J243" s="10" t="n"/>
+      <c r="K243" s="10" t="inlineStr"/>
+      <c r="L243" s="10" t="inlineStr"/>
+      <c r="M243" s="10" t="inlineStr"/>
+    </row>
+    <row r="244" ht="26" customHeight="1">
+      <c r="A244" s="7" t="inlineStr">
+        <is>
+          <t>002412</t>
+        </is>
+      </c>
+      <c r="B244" s="8" t="inlineStr">
+        <is>
+          <t>汉森制药</t>
+        </is>
+      </c>
+      <c r="C244" s="7" t="inlineStr">
+        <is>
+          <t>创新药/CRO</t>
+        </is>
+      </c>
+      <c r="D244" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="E244" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="F244" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G244" s="7" t="inlineStr">
+        <is>
+          <t>强势上攻</t>
+        </is>
+      </c>
+      <c r="H244" s="13" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="I244" s="7" t="n"/>
+      <c r="J244" s="7" t="n"/>
+      <c r="K244" s="7" t="inlineStr"/>
+      <c r="L244" s="7" t="inlineStr"/>
+      <c r="M244" s="7" t="inlineStr"/>
+    </row>
+    <row r="245" ht="26" customHeight="1">
+      <c r="A245" s="15" t="inlineStr">
         <is>
           <t>688710</t>
         </is>
       </c>
-      <c r="B243" s="16" t="inlineStr">
+      <c r="B245" s="16" t="inlineStr">
         <is>
           <t>益诺思</t>
         </is>
       </c>
-      <c r="C243" s="15" t="inlineStr">
+      <c r="C245" s="15" t="inlineStr">
         <is>
           <t>创新药/CRO</t>
         </is>
       </c>
-      <c r="D243" s="15" t="inlineStr">
+      <c r="D245" s="15" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
-      <c r="E243" s="15" t="inlineStr">
+      <c r="E245" s="15" t="inlineStr">
         <is>
           <t>2026-07-14</t>
         </is>
       </c>
-      <c r="F243" s="15" t="n">
+      <c r="F245" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="G243" s="19" t="inlineStr">
+      <c r="G245" s="19" t="inlineStr">
         <is>
           <t>放量下跌</t>
         </is>
       </c>
-      <c r="H243" s="18" t="n">
+      <c r="H245" s="18" t="n">
         <v>-3.5</v>
       </c>
-      <c r="I243" s="15" t="n">
+      <c r="I245" s="15" t="n">
         <v>17.48</v>
       </c>
-      <c r="J243" s="15" t="n">
+      <c r="J245" s="15" t="n">
         <v>1.3</v>
       </c>
-      <c r="K243" s="15" t="inlineStr">
+      <c r="K245" s="15" t="inlineStr">
         <is>
           <t>放量</t>
         </is>
       </c>
-      <c r="L243" s="15" t="inlineStr">
+      <c r="L245" s="15" t="inlineStr">
         <is>
           <t>首日涨幅&gt;20%</t>
         </is>
       </c>
-      <c r="M243" s="15" t="inlineStr"/>
+      <c r="M245" s="15" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:N243"/>
+  <autoFilter ref="A3:N245"/>
   <mergeCells count="1">
     <mergeCell ref="A1:N1"/>
   </mergeCells>
@@ -12899,7 +13012,7 @@
     <row r="1">
       <c r="A1" s="20" t="inlineStr">
         <is>
-          <t>狙击池 2026-07-22</t>
+          <t>狙击池 2026-07-27</t>
         </is>
       </c>
     </row>
@@ -12977,7 +13090,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -12993,7 +13106,7 @@
     <row r="1">
       <c r="A1" s="22" t="inlineStr">
         <is>
-          <t>后备池 2026-07-22</t>
+          <t>后备池 2026-07-27</t>
         </is>
       </c>
     </row>
@@ -13039,125 +13152,16 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="28" customHeight="1">
-      <c r="A4" s="23" t="inlineStr">
-        <is>
-          <t>600998</t>
-        </is>
-      </c>
-      <c r="B4" s="24" t="inlineStr">
-        <is>
-          <t>九州通</t>
-        </is>
-      </c>
-      <c r="C4" s="23" t="inlineStr">
-        <is>
-          <t>创新药/CRO</t>
-        </is>
-      </c>
-      <c r="D4" s="23" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="E4" s="23" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="F4" s="23" t="n"/>
-      <c r="G4" s="23" t="inlineStr">
-        <is>
-          <t>高位整理</t>
-        </is>
-      </c>
-      <c r="H4" s="23" t="inlineStr">
-        <is>
-          <t>等状态变为缩量回调</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="28" customHeight="1">
-      <c r="A5" s="23" t="inlineStr">
-        <is>
-          <t>600566</t>
-        </is>
-      </c>
-      <c r="B5" s="24" t="inlineStr">
-        <is>
-          <t>济川药业</t>
-        </is>
-      </c>
-      <c r="C5" s="23" t="inlineStr">
-        <is>
-          <t>创新药/CRO</t>
-        </is>
-      </c>
-      <c r="D5" s="23" t="inlineStr">
-        <is>
-          <t>2026-07-21</t>
-        </is>
-      </c>
-      <c r="E5" s="23" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="F5" s="23" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="G5" s="23" t="inlineStr">
-        <is>
-          <t>高位整理</t>
-        </is>
-      </c>
-      <c r="H5" s="23" t="inlineStr">
-        <is>
-          <t>等状态变为缩量回调</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="28" customHeight="1">
-      <c r="A6" s="23" t="inlineStr">
-        <is>
-          <t>601607</t>
-        </is>
-      </c>
-      <c r="B6" s="24" t="inlineStr">
-        <is>
-          <t>上海医药</t>
-        </is>
-      </c>
-      <c r="C6" s="23" t="inlineStr">
-        <is>
-          <t>创新药/CRO</t>
-        </is>
-      </c>
-      <c r="D6" s="23" t="inlineStr">
-        <is>
-          <t>2026-07-21</t>
-        </is>
-      </c>
-      <c r="E6" s="23" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="F6" s="23" t="n"/>
-      <c r="G6" s="23" t="inlineStr">
-        <is>
-          <t>高位整理</t>
-        </is>
-      </c>
-      <c r="H6" s="23" t="inlineStr">
-        <is>
-          <t>等状态变为缩量回调</t>
+    <row r="4">
+      <c r="A4" s="21" t="inlineStr">
+        <is>
+          <t>(无后备)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:H6"/>
-  <mergeCells count="1">
+  <mergeCells count="2">
+    <mergeCell ref="A4:H4"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -13170,7 +13174,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -13183,9 +13187,9 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="25" t="inlineStr">
-        <is>
-          <t>第七层·风险过滤 29只</t>
+      <c r="A1" s="23" t="inlineStr">
+        <is>
+          <t>第七层·风险过滤 35只</t>
         </is>
       </c>
     </row>
@@ -13229,12 +13233,12 @@
     <row r="4" ht="26" customHeight="1">
       <c r="A4" s="15" t="inlineStr">
         <is>
-          <t>600535</t>
+          <t>600267</t>
         </is>
       </c>
       <c r="B4" s="16" t="inlineStr">
         <is>
-          <t>天士力</t>
+          <t>海正药业</t>
         </is>
       </c>
       <c r="C4" s="15" t="inlineStr">
@@ -13243,12 +13247,12 @@
         </is>
       </c>
       <c r="D4" s="15" t="n">
-        <v>0.25</v>
+        <v>-3.37</v>
       </c>
       <c r="E4" s="15" t="n"/>
       <c r="F4" s="15" t="inlineStr">
         <is>
-          <t>5次上榜仅涨+0.4%(疑似出货)</t>
+          <t>5次上榜仅涨+0.6%(疑似出货)</t>
         </is>
       </c>
       <c r="G4" s="15" t="inlineStr">
@@ -13340,14 +13344,14 @@
         </is>
       </c>
       <c r="D7" s="15" t="n">
-        <v>0.04</v>
+        <v>0.85</v>
       </c>
       <c r="E7" s="15" t="n">
         <v>1.37</v>
       </c>
       <c r="F7" s="15" t="inlineStr">
         <is>
-          <t>5次上榜仅涨+2.4%(疑似出货)</t>
+          <t>5次上榜仅涨+3.2%(疑似出货)</t>
         </is>
       </c>
       <c r="G7" s="15" t="inlineStr">
@@ -13359,28 +13363,28 @@
     <row r="8" ht="26" customHeight="1">
       <c r="A8" s="15" t="inlineStr">
         <is>
-          <t>603233</t>
+          <t>603893</t>
         </is>
       </c>
       <c r="B8" s="16" t="inlineStr">
         <is>
-          <t>大参林</t>
+          <t>瑞芯微</t>
         </is>
       </c>
       <c r="C8" s="15" t="inlineStr">
         <is>
-          <t>创新药/CRO</t>
+          <t>半导体/芯片</t>
         </is>
       </c>
       <c r="D8" s="15" t="n">
-        <v>0.48</v>
+        <v>-1.71</v>
       </c>
       <c r="E8" s="15" t="n">
-        <v>2.26</v>
+        <v>1.24</v>
       </c>
       <c r="F8" s="15" t="inlineStr">
         <is>
-          <t>5次上榜仅涨-3.9%(疑似出货)</t>
+          <t>5次上榜仅涨-0.5%(疑似出货)</t>
         </is>
       </c>
       <c r="G8" s="15" t="inlineStr">
@@ -13392,28 +13396,28 @@
     <row r="9" ht="26" customHeight="1">
       <c r="A9" s="15" t="inlineStr">
         <is>
-          <t>603068</t>
+          <t>600566</t>
         </is>
       </c>
       <c r="B9" s="16" t="inlineStr">
         <is>
-          <t>博通集成</t>
+          <t>济川药业</t>
         </is>
       </c>
       <c r="C9" s="15" t="inlineStr">
         <is>
-          <t>半导体/芯片</t>
+          <t>创新药/CRO</t>
         </is>
       </c>
       <c r="D9" s="15" t="n">
-        <v>0.05</v>
+        <v>1.09</v>
       </c>
       <c r="E9" s="15" t="n">
-        <v>1.13</v>
+        <v>0.86</v>
       </c>
       <c r="F9" s="15" t="inlineStr">
         <is>
-          <t>5次上榜仅涨-4.9%(疑似出货)</t>
+          <t>5次上榜仅涨-0.9%(疑似出货)</t>
         </is>
       </c>
       <c r="G9" s="15" t="inlineStr">
@@ -13425,12 +13429,12 @@
     <row r="10" ht="26" customHeight="1">
       <c r="A10" s="15" t="inlineStr">
         <is>
-          <t>688578</t>
+          <t>600998</t>
         </is>
       </c>
       <c r="B10" s="16" t="inlineStr">
         <is>
-          <t>艾力斯</t>
+          <t>九州通</t>
         </is>
       </c>
       <c r="C10" s="15" t="inlineStr">
@@ -13439,14 +13443,12 @@
         </is>
       </c>
       <c r="D10" s="15" t="n">
-        <v>-1.34</v>
-      </c>
-      <c r="E10" s="15" t="n">
-        <v>0.84</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E10" s="15" t="n"/>
       <c r="F10" s="15" t="inlineStr">
         <is>
-          <t>首日涨幅&gt;15%</t>
+          <t>5次上榜仅涨-1.0%(疑似出货)</t>
         </is>
       </c>
       <c r="G10" s="15" t="inlineStr">
@@ -13458,127 +13460,123 @@
     <row r="11" ht="26" customHeight="1">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>688605</t>
+          <t>600535</t>
         </is>
       </c>
       <c r="B11" s="16" t="inlineStr">
         <is>
-          <t>先锋精科</t>
+          <t>天士力</t>
         </is>
       </c>
       <c r="C11" s="15" t="inlineStr">
         <is>
-          <t>半导体/芯片</t>
+          <t>创新药/CRO</t>
         </is>
       </c>
       <c r="D11" s="15" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="E11" s="15" t="n">
-        <v>0.74</v>
-      </c>
+        <v>-1.19</v>
+      </c>
+      <c r="E11" s="15" t="n"/>
       <c r="F11" s="15" t="inlineStr">
         <is>
-          <t>首日涨幅&gt;15%</t>
+          <t>5次上榜仅涨-1.1%(疑似出货)</t>
         </is>
       </c>
       <c r="G11" s="15" t="inlineStr">
         <is>
-          <t>强势上攻</t>
+          <t>高位整理</t>
         </is>
       </c>
     </row>
     <row r="12" ht="26" customHeight="1">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>688286</t>
+          <t>601607</t>
         </is>
       </c>
       <c r="B12" s="16" t="inlineStr">
         <is>
-          <t>敏芯股份</t>
+          <t>上海医药</t>
         </is>
       </c>
       <c r="C12" s="15" t="inlineStr">
         <is>
-          <t>半导体/芯片</t>
+          <t>创新药/CRO</t>
         </is>
       </c>
       <c r="D12" s="15" t="n">
-        <v>15.87</v>
-      </c>
-      <c r="E12" s="15" t="n">
-        <v>0.8100000000000001</v>
-      </c>
+        <v>0.49</v>
+      </c>
+      <c r="E12" s="15" t="n"/>
       <c r="F12" s="15" t="inlineStr">
         <is>
-          <t>首日涨幅&gt;16%</t>
+          <t>5次上榜仅涨-1.1%(疑似出货)</t>
         </is>
       </c>
       <c r="G12" s="15" t="inlineStr">
         <is>
-          <t>强势上攻</t>
+          <t>高位整理</t>
         </is>
       </c>
     </row>
     <row r="13" ht="26" customHeight="1">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>688328</t>
+          <t>603233</t>
         </is>
       </c>
       <c r="B13" s="16" t="inlineStr">
         <is>
-          <t>深科达</t>
+          <t>大参林</t>
         </is>
       </c>
       <c r="C13" s="15" t="inlineStr">
         <is>
-          <t>半导体/芯片</t>
+          <t>创新药/CRO</t>
         </is>
       </c>
       <c r="D13" s="15" t="n">
-        <v>15.89</v>
+        <v>0.48</v>
       </c>
       <c r="E13" s="15" t="n">
-        <v>0.9399999999999999</v>
+        <v>2.26</v>
       </c>
       <c r="F13" s="15" t="inlineStr">
         <is>
-          <t>首日涨幅&gt;16%</t>
+          <t>5次上榜仅涨-3.9%(疑似出货)</t>
         </is>
       </c>
       <c r="G13" s="15" t="inlineStr">
         <is>
-          <t>强势上攻</t>
+          <t>高位整理</t>
         </is>
       </c>
     </row>
     <row r="14" ht="26" customHeight="1">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>301310</t>
+          <t>603068</t>
         </is>
       </c>
       <c r="B14" s="16" t="inlineStr">
         <is>
-          <t>鑫宏业</t>
+          <t>博通集成</t>
         </is>
       </c>
       <c r="C14" s="15" t="inlineStr">
         <is>
-          <t>机器人</t>
+          <t>半导体/芯片</t>
         </is>
       </c>
       <c r="D14" s="15" t="n">
-        <v>-0.34</v>
+        <v>0.05</v>
       </c>
       <c r="E14" s="15" t="n">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="F14" s="15" t="inlineStr">
         <is>
-          <t>首日涨幅&gt;17%</t>
+          <t>5次上榜仅涨-4.9%(疑似出货)</t>
         </is>
       </c>
       <c r="G14" s="15" t="inlineStr">
@@ -13590,28 +13588,28 @@
     <row r="15" ht="26" customHeight="1">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>688017</t>
+          <t>688578</t>
         </is>
       </c>
       <c r="B15" s="16" t="inlineStr">
         <is>
-          <t>绿的谐波</t>
+          <t>艾力斯</t>
         </is>
       </c>
       <c r="C15" s="15" t="inlineStr">
         <is>
-          <t>机器人</t>
+          <t>创新药/CRO</t>
         </is>
       </c>
       <c r="D15" s="15" t="n">
-        <v>2.44</v>
+        <v>-1.34</v>
       </c>
       <c r="E15" s="15" t="n">
-        <v>0.71</v>
+        <v>0.84</v>
       </c>
       <c r="F15" s="15" t="inlineStr">
         <is>
-          <t>首日涨幅&gt;18%</t>
+          <t>首日涨幅&gt;15%</t>
         </is>
       </c>
       <c r="G15" s="15" t="inlineStr">
@@ -13623,12 +13621,12 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>300604</t>
+          <t>688605</t>
         </is>
       </c>
       <c r="B16" s="16" t="inlineStr">
         <is>
-          <t>长川科技</t>
+          <t>先锋精科</t>
         </is>
       </c>
       <c r="C16" s="15" t="inlineStr">
@@ -13637,12 +13635,14 @@
         </is>
       </c>
       <c r="D16" s="15" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="E16" s="15" t="n"/>
+        <v>3.02</v>
+      </c>
+      <c r="E16" s="15" t="n">
+        <v>0.74</v>
+      </c>
       <c r="F16" s="15" t="inlineStr">
         <is>
-          <t>首日涨幅&gt;18%</t>
+          <t>首日涨幅&gt;15%</t>
         </is>
       </c>
       <c r="G16" s="15" t="inlineStr">
@@ -13654,12 +13654,12 @@
     <row r="17" ht="26" customHeight="1">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>688721</t>
+          <t>688286</t>
         </is>
       </c>
       <c r="B17" s="16" t="inlineStr">
         <is>
-          <t>龙图光罩</t>
+          <t>敏芯股份</t>
         </is>
       </c>
       <c r="C17" s="15" t="inlineStr">
@@ -13668,14 +13668,14 @@
         </is>
       </c>
       <c r="D17" s="15" t="n">
-        <v>18.6</v>
+        <v>15.87</v>
       </c>
       <c r="E17" s="15" t="n">
-        <v>1.01</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="F17" s="15" t="inlineStr">
         <is>
-          <t>首日涨幅&gt;19%</t>
+          <t>首日涨幅&gt;16%</t>
         </is>
       </c>
       <c r="G17" s="15" t="inlineStr">
@@ -13687,26 +13687,28 @@
     <row r="18" ht="26" customHeight="1">
       <c r="A18" s="15" t="inlineStr">
         <is>
-          <t>300873</t>
+          <t>688328</t>
         </is>
       </c>
       <c r="B18" s="16" t="inlineStr">
         <is>
-          <t>海晨股份</t>
+          <t>深科达</t>
         </is>
       </c>
       <c r="C18" s="15" t="inlineStr">
         <is>
-          <t>机器人</t>
+          <t>半导体/芯片</t>
         </is>
       </c>
       <c r="D18" s="15" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="E18" s="15" t="n"/>
+        <v>15.89</v>
+      </c>
+      <c r="E18" s="15" t="n">
+        <v>0.9399999999999999</v>
+      </c>
       <c r="F18" s="15" t="inlineStr">
         <is>
-          <t>首日涨幅&gt;20%</t>
+          <t>首日涨幅&gt;16%</t>
         </is>
       </c>
       <c r="G18" s="15" t="inlineStr">
@@ -13718,12 +13720,12 @@
     <row r="19" ht="26" customHeight="1">
       <c r="A19" s="15" t="inlineStr">
         <is>
-          <t>300607</t>
+          <t>301310</t>
         </is>
       </c>
       <c r="B19" s="16" t="inlineStr">
         <is>
-          <t>拓斯达</t>
+          <t>鑫宏业</t>
         </is>
       </c>
       <c r="C19" s="15" t="inlineStr">
@@ -13732,64 +13734,64 @@
         </is>
       </c>
       <c r="D19" s="15" t="n">
-        <v>13.55</v>
+        <v>-0.34</v>
       </c>
       <c r="E19" s="15" t="n">
-        <v>0.63</v>
+        <v>1.22</v>
       </c>
       <c r="F19" s="15" t="inlineStr">
         <is>
-          <t>首日涨幅&gt;20%</t>
+          <t>首日涨幅&gt;17%</t>
         </is>
       </c>
       <c r="G19" s="15" t="inlineStr">
         <is>
-          <t>强势上攻</t>
+          <t>高位整理</t>
         </is>
       </c>
     </row>
     <row r="20" ht="26" customHeight="1">
       <c r="A20" s="15" t="inlineStr">
         <is>
-          <t>688106</t>
+          <t>688017</t>
         </is>
       </c>
       <c r="B20" s="16" t="inlineStr">
         <is>
-          <t>金宏气体</t>
+          <t>绿的谐波</t>
         </is>
       </c>
       <c r="C20" s="15" t="inlineStr">
         <is>
-          <t>半导体/芯片</t>
+          <t>机器人</t>
         </is>
       </c>
       <c r="D20" s="15" t="n">
-        <v>20.01</v>
+        <v>2.44</v>
       </c>
       <c r="E20" s="15" t="n">
-        <v>0.8</v>
+        <v>0.71</v>
       </c>
       <c r="F20" s="15" t="inlineStr">
         <is>
-          <t>首日涨幅&gt;20%</t>
+          <t>首日涨幅&gt;18%</t>
         </is>
       </c>
       <c r="G20" s="15" t="inlineStr">
         <is>
-          <t>强势上攻</t>
+          <t>高位整理</t>
         </is>
       </c>
     </row>
     <row r="21" ht="26" customHeight="1">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>688728</t>
+          <t>300604</t>
         </is>
       </c>
       <c r="B21" s="16" t="inlineStr">
         <is>
-          <t>格科微</t>
+          <t>长川科技</t>
         </is>
       </c>
       <c r="C21" s="15" t="inlineStr">
@@ -13798,14 +13800,12 @@
         </is>
       </c>
       <c r="D21" s="15" t="n">
-        <v>20.03</v>
-      </c>
-      <c r="E21" s="15" t="n">
-        <v>0.73</v>
-      </c>
+        <v>17.9</v>
+      </c>
+      <c r="E21" s="15" t="n"/>
       <c r="F21" s="15" t="inlineStr">
         <is>
-          <t>首日涨幅&gt;20%</t>
+          <t>首日涨幅&gt;18%</t>
         </is>
       </c>
       <c r="G21" s="15" t="inlineStr">
@@ -13817,28 +13817,28 @@
     <row r="22" ht="26" customHeight="1">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t>300852</t>
+          <t>688721</t>
         </is>
       </c>
       <c r="B22" s="16" t="inlineStr">
         <is>
-          <t>四会富仕</t>
+          <t>龙图光罩</t>
         </is>
       </c>
       <c r="C22" s="15" t="inlineStr">
         <is>
-          <t>算力/通信</t>
+          <t>半导体/芯片</t>
         </is>
       </c>
       <c r="D22" s="15" t="n">
-        <v>20</v>
+        <v>18.6</v>
       </c>
       <c r="E22" s="15" t="n">
-        <v>0.85</v>
+        <v>1.01</v>
       </c>
       <c r="F22" s="15" t="inlineStr">
         <is>
-          <t>首日涨幅&gt;20%</t>
+          <t>首日涨幅&gt;19%</t>
         </is>
       </c>
       <c r="G22" s="15" t="inlineStr">
@@ -13850,25 +13850,23 @@
     <row r="23" ht="26" customHeight="1">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>688571</t>
+          <t>300873</t>
         </is>
       </c>
       <c r="B23" s="16" t="inlineStr">
         <is>
-          <t>杭华股份</t>
+          <t>海晨股份</t>
         </is>
       </c>
       <c r="C23" s="15" t="inlineStr">
         <is>
-          <t>半导体/芯片</t>
+          <t>机器人</t>
         </is>
       </c>
       <c r="D23" s="15" t="n">
-        <v>5.33</v>
-      </c>
-      <c r="E23" s="15" t="n">
-        <v>0.89</v>
-      </c>
+        <v>3.3</v>
+      </c>
+      <c r="E23" s="15" t="n"/>
       <c r="F23" s="15" t="inlineStr">
         <is>
           <t>首日涨幅&gt;20%</t>
@@ -13883,24 +13881,24 @@
     <row r="24" ht="26" customHeight="1">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>688689</t>
+          <t>300607</t>
         </is>
       </c>
       <c r="B24" s="16" t="inlineStr">
         <is>
-          <t>银河微电</t>
+          <t>拓斯达</t>
         </is>
       </c>
       <c r="C24" s="15" t="inlineStr">
         <is>
-          <t>半导体/芯片</t>
+          <t>机器人</t>
         </is>
       </c>
       <c r="D24" s="15" t="n">
-        <v>18.7</v>
+        <v>13.55</v>
       </c>
       <c r="E24" s="15" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="F24" s="15" t="inlineStr">
         <is>
@@ -13916,24 +13914,24 @@
     <row r="25" ht="26" customHeight="1">
       <c r="A25" s="15" t="inlineStr">
         <is>
-          <t>301092</t>
+          <t>688106</t>
         </is>
       </c>
       <c r="B25" s="16" t="inlineStr">
         <is>
-          <t>争光股份</t>
+          <t>金宏气体</t>
         </is>
       </c>
       <c r="C25" s="15" t="inlineStr">
         <is>
-          <t>算力/通信</t>
+          <t>半导体/芯片</t>
         </is>
       </c>
       <c r="D25" s="15" t="n">
-        <v>11.13</v>
+        <v>20.01</v>
       </c>
       <c r="E25" s="15" t="n">
-        <v>1.14</v>
+        <v>0.8</v>
       </c>
       <c r="F25" s="15" t="inlineStr">
         <is>
@@ -13949,12 +13947,12 @@
     <row r="26" ht="26" customHeight="1">
       <c r="A26" s="15" t="inlineStr">
         <is>
-          <t>688216</t>
+          <t>688728</t>
         </is>
       </c>
       <c r="B26" s="16" t="inlineStr">
         <is>
-          <t>气派科技</t>
+          <t>格科微</t>
         </is>
       </c>
       <c r="C26" s="15" t="inlineStr">
@@ -13963,10 +13961,10 @@
         </is>
       </c>
       <c r="D26" s="15" t="n">
-        <v>20</v>
+        <v>20.03</v>
       </c>
       <c r="E26" s="15" t="n">
-        <v>1.63</v>
+        <v>0.73</v>
       </c>
       <c r="F26" s="15" t="inlineStr">
         <is>
@@ -13982,23 +13980,25 @@
     <row r="27" ht="26" customHeight="1">
       <c r="A27" s="15" t="inlineStr">
         <is>
-          <t>301379</t>
+          <t>300852</t>
         </is>
       </c>
       <c r="B27" s="16" t="inlineStr">
         <is>
-          <t>天山电子</t>
+          <t>四会富仕</t>
         </is>
       </c>
       <c r="C27" s="15" t="inlineStr">
         <is>
-          <t>半导体/芯片</t>
+          <t>算力/通信</t>
         </is>
       </c>
       <c r="D27" s="15" t="n">
-        <v>19.99</v>
-      </c>
-      <c r="E27" s="15" t="n"/>
+        <v>20</v>
+      </c>
+      <c r="E27" s="15" t="n">
+        <v>0.85</v>
+      </c>
       <c r="F27" s="15" t="inlineStr">
         <is>
           <t>首日涨幅&gt;20%</t>
@@ -14013,23 +14013,25 @@
     <row r="28" ht="26" customHeight="1">
       <c r="A28" s="15" t="inlineStr">
         <is>
-          <t>300684</t>
+          <t>688571</t>
         </is>
       </c>
       <c r="B28" s="16" t="inlineStr">
         <is>
-          <t>中石科技</t>
+          <t>杭华股份</t>
         </is>
       </c>
       <c r="C28" s="15" t="inlineStr">
         <is>
-          <t>算力/通信</t>
+          <t>半导体/芯片</t>
         </is>
       </c>
       <c r="D28" s="15" t="n">
-        <v>-6.76</v>
-      </c>
-      <c r="E28" s="15" t="n"/>
+        <v>5.33</v>
+      </c>
+      <c r="E28" s="15" t="n">
+        <v>0.89</v>
+      </c>
       <c r="F28" s="15" t="inlineStr">
         <is>
           <t>首日涨幅&gt;20%</t>
@@ -14037,19 +14039,19 @@
       </c>
       <c r="G28" s="15" t="inlineStr">
         <is>
-          <t>高位整理</t>
+          <t>强势上攻</t>
         </is>
       </c>
     </row>
     <row r="29" ht="26" customHeight="1">
       <c r="A29" s="15" t="inlineStr">
         <is>
-          <t>688720</t>
+          <t>688689</t>
         </is>
       </c>
       <c r="B29" s="16" t="inlineStr">
         <is>
-          <t>艾森股份</t>
+          <t>银河微电</t>
         </is>
       </c>
       <c r="C29" s="15" t="inlineStr">
@@ -14058,10 +14060,10 @@
         </is>
       </c>
       <c r="D29" s="15" t="n">
-        <v>20</v>
+        <v>18.7</v>
       </c>
       <c r="E29" s="15" t="n">
-        <v>0.8</v>
+        <v>0.62</v>
       </c>
       <c r="F29" s="15" t="inlineStr">
         <is>
@@ -14077,24 +14079,24 @@
     <row r="30" ht="26" customHeight="1">
       <c r="A30" s="15" t="inlineStr">
         <is>
-          <t>688710</t>
+          <t>301092</t>
         </is>
       </c>
       <c r="B30" s="16" t="inlineStr">
         <is>
-          <t>益诺思</t>
+          <t>争光股份</t>
         </is>
       </c>
       <c r="C30" s="15" t="inlineStr">
         <is>
-          <t>创新药/CRO</t>
+          <t>算力/通信</t>
         </is>
       </c>
       <c r="D30" s="15" t="n">
-        <v>-3.5</v>
+        <v>11.13</v>
       </c>
       <c r="E30" s="15" t="n">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="F30" s="15" t="inlineStr">
         <is>
@@ -14103,31 +14105,31 @@
       </c>
       <c r="G30" s="15" t="inlineStr">
         <is>
-          <t>放量下跌</t>
+          <t>强势上攻</t>
         </is>
       </c>
     </row>
     <row r="31" ht="26" customHeight="1">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>300214</t>
+          <t>688216</t>
         </is>
       </c>
       <c r="B31" s="16" t="inlineStr">
         <is>
-          <t>日科化学</t>
+          <t>气派科技</t>
         </is>
       </c>
       <c r="C31" s="15" t="inlineStr">
         <is>
-          <t>算力/通信</t>
+          <t>半导体/芯片</t>
         </is>
       </c>
       <c r="D31" s="15" t="n">
-        <v>8.94</v>
+        <v>20</v>
       </c>
       <c r="E31" s="15" t="n">
-        <v>14.71</v>
+        <v>1.63</v>
       </c>
       <c r="F31" s="15" t="inlineStr">
         <is>
@@ -14143,21 +14145,21 @@
     <row r="32" ht="26" customHeight="1">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>688192</t>
+          <t>301379</t>
         </is>
       </c>
       <c r="B32" s="16" t="inlineStr">
         <is>
-          <t>迪哲医药</t>
+          <t>天山电子</t>
         </is>
       </c>
       <c r="C32" s="15" t="inlineStr">
         <is>
-          <t>创新药/CRO</t>
+          <t>半导体/芯片</t>
         </is>
       </c>
       <c r="D32" s="15" t="n">
-        <v>20.01</v>
+        <v>19.99</v>
       </c>
       <c r="E32" s="15" t="n"/>
       <c r="F32" s="15" t="inlineStr">
@@ -14171,8 +14173,202 @@
         </is>
       </c>
     </row>
+    <row r="33" ht="26" customHeight="1">
+      <c r="A33" s="15" t="inlineStr">
+        <is>
+          <t>300684</t>
+        </is>
+      </c>
+      <c r="B33" s="16" t="inlineStr">
+        <is>
+          <t>中石科技</t>
+        </is>
+      </c>
+      <c r="C33" s="15" t="inlineStr">
+        <is>
+          <t>算力/通信</t>
+        </is>
+      </c>
+      <c r="D33" s="15" t="n">
+        <v>-6.76</v>
+      </c>
+      <c r="E33" s="15" t="n"/>
+      <c r="F33" s="15" t="inlineStr">
+        <is>
+          <t>首日涨幅&gt;20%</t>
+        </is>
+      </c>
+      <c r="G33" s="15" t="inlineStr">
+        <is>
+          <t>高位整理</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="26" customHeight="1">
+      <c r="A34" s="15" t="inlineStr">
+        <is>
+          <t>688720</t>
+        </is>
+      </c>
+      <c r="B34" s="16" t="inlineStr">
+        <is>
+          <t>艾森股份</t>
+        </is>
+      </c>
+      <c r="C34" s="15" t="inlineStr">
+        <is>
+          <t>半导体/芯片</t>
+        </is>
+      </c>
+      <c r="D34" s="15" t="n">
+        <v>20</v>
+      </c>
+      <c r="E34" s="15" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F34" s="15" t="inlineStr">
+        <is>
+          <t>首日涨幅&gt;20%</t>
+        </is>
+      </c>
+      <c r="G34" s="15" t="inlineStr">
+        <is>
+          <t>强势上攻</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="26" customHeight="1">
+      <c r="A35" s="15" t="inlineStr">
+        <is>
+          <t>688710</t>
+        </is>
+      </c>
+      <c r="B35" s="16" t="inlineStr">
+        <is>
+          <t>益诺思</t>
+        </is>
+      </c>
+      <c r="C35" s="15" t="inlineStr">
+        <is>
+          <t>创新药/CRO</t>
+        </is>
+      </c>
+      <c r="D35" s="15" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="E35" s="15" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F35" s="15" t="inlineStr">
+        <is>
+          <t>首日涨幅&gt;20%</t>
+        </is>
+      </c>
+      <c r="G35" s="15" t="inlineStr">
+        <is>
+          <t>放量下跌</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="26" customHeight="1">
+      <c r="A36" s="15" t="inlineStr">
+        <is>
+          <t>300214</t>
+        </is>
+      </c>
+      <c r="B36" s="16" t="inlineStr">
+        <is>
+          <t>日科化学</t>
+        </is>
+      </c>
+      <c r="C36" s="15" t="inlineStr">
+        <is>
+          <t>算力/通信</t>
+        </is>
+      </c>
+      <c r="D36" s="15" t="n">
+        <v>19.98</v>
+      </c>
+      <c r="E36" s="15" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="F36" s="15" t="inlineStr">
+        <is>
+          <t>首日涨幅&gt;20%</t>
+        </is>
+      </c>
+      <c r="G36" s="15" t="inlineStr">
+        <is>
+          <t>强势上攻</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="26" customHeight="1">
+      <c r="A37" s="15" t="inlineStr">
+        <is>
+          <t>688192</t>
+        </is>
+      </c>
+      <c r="B37" s="16" t="inlineStr">
+        <is>
+          <t>迪哲医药</t>
+        </is>
+      </c>
+      <c r="C37" s="15" t="inlineStr">
+        <is>
+          <t>创新药/CRO</t>
+        </is>
+      </c>
+      <c r="D37" s="15" t="n">
+        <v>20.01</v>
+      </c>
+      <c r="E37" s="15" t="n"/>
+      <c r="F37" s="15" t="inlineStr">
+        <is>
+          <t>首日涨幅&gt;20%</t>
+        </is>
+      </c>
+      <c r="G37" s="15" t="inlineStr">
+        <is>
+          <t>强势上攻</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="26" customHeight="1">
+      <c r="A38" s="15" t="inlineStr">
+        <is>
+          <t>301234</t>
+        </is>
+      </c>
+      <c r="B38" s="16" t="inlineStr">
+        <is>
+          <t>五洲医疗</t>
+        </is>
+      </c>
+      <c r="C38" s="15" t="inlineStr">
+        <is>
+          <t>创新药/CRO</t>
+        </is>
+      </c>
+      <c r="D38" s="15" t="n">
+        <v>20</v>
+      </c>
+      <c r="E38" s="15" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="F38" s="15" t="inlineStr">
+        <is>
+          <t>首日涨幅&gt;20%</t>
+        </is>
+      </c>
+      <c r="G38" s="15" t="inlineStr">
+        <is>
+          <t>强势上攻</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A3:G32"/>
+  <autoFilter ref="A3:G38"/>
   <mergeCells count="1">
     <mergeCell ref="A1:G1"/>
   </mergeCells>
@@ -14198,9 +14394,9 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="26" t="inlineStr">
-        <is>
-          <t>持仓预警 2026-07-22</t>
+      <c r="A1" s="24" t="inlineStr">
+        <is>
+          <t>持仓预警 2026-07-27</t>
         </is>
       </c>
     </row>
@@ -14258,7 +14454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K20"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -14275,9 +14471,9 @@
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1">
-      <c r="A1" s="27" t="inlineStr">
-        <is>
-          <t>回踩狙击榜 2026-07-22 (17只·按综合分排序)</t>
+      <c r="A1" s="25" t="inlineStr">
+        <is>
+          <t>回踩狙击榜 2026-07-27 (10只·按综合分排序)</t>
         </is>
       </c>
     </row>
@@ -14339,106 +14535,106 @@
       </c>
     </row>
     <row r="4" ht="26" customHeight="1">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>300199</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>翰宇药业</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>缩量</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>6.94</v>
+      </c>
+      <c r="J4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>★极近均线</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="26" customHeight="1">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>600998</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
-        <is>
-          <t>九州通 NEW</t>
-        </is>
-      </c>
-      <c r="C4" s="9" t="n">
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>九州通</t>
+        </is>
+      </c>
+      <c r="C5" s="14" t="n">
         <v>-0.09</v>
       </c>
-      <c r="D4" s="7" t="n"/>
-      <c r="E4" s="7" t="inlineStr">
-        <is>
-          <t>正常</t>
-        </is>
-      </c>
-      <c r="F4" s="9" t="n">
-        <v>83</v>
-      </c>
-      <c r="G4" s="7" t="n">
+      <c r="D5" s="10" t="n"/>
+      <c r="E5" s="10" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="F5" s="10" t="n">
+        <v>75</v>
+      </c>
+      <c r="G5" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="H5" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="I5" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="H4" s="7" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="I4" s="7" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="J4" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="K4" s="7" t="inlineStr">
-        <is>
-          <t>🎯首选 ★极近均线</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="26" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>300199</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>翰宇药业</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="D5" s="3" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>缩量</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="n">
-        <v>82</v>
-      </c>
-      <c r="G5" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="n">
-        <v>6.94</v>
-      </c>
-      <c r="J5" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>🎯首选 ★极近均线</t>
+      <c r="J5" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="K5" s="10" t="inlineStr">
+        <is>
+          <t>★极近均线 疑似出货</t>
         </is>
       </c>
     </row>
     <row r="6" ht="26" customHeight="1">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>301393</t>
+          <t>601607</t>
         </is>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>昊帆生物</t>
-        </is>
-      </c>
-      <c r="C6" s="9" t="n">
-        <v>0.46</v>
+          <t>上海医药 NEW</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="n">
+        <v>1.52</v>
       </c>
       <c r="D6" s="7" t="n"/>
       <c r="E6" s="7" t="inlineStr">
@@ -14447,41 +14643,41 @@
         </is>
       </c>
       <c r="F6" s="7" t="n">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>-1.27</v>
+        <v>0.49</v>
       </c>
       <c r="J6" s="7" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K6" s="7" t="inlineStr">
         <is>
-          <t>★极近均线</t>
+          <t>疑似出货</t>
         </is>
       </c>
     </row>
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="10" t="inlineStr">
         <is>
-          <t>601607</t>
+          <t>301393</t>
         </is>
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>上海医药 NEW</t>
-        </is>
-      </c>
-      <c r="C7" s="10" t="n">
-        <v>1.52</v>
+          <t>昊帆生物</t>
+        </is>
+      </c>
+      <c r="C7" s="14" t="n">
+        <v>0.46</v>
       </c>
       <c r="D7" s="10" t="n"/>
       <c r="E7" s="10" t="inlineStr">
@@ -14490,169 +14686,171 @@
         </is>
       </c>
       <c r="F7" s="10" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G7" s="10" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H7" s="10" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="I7" s="10" t="n">
-        <v>0.66</v>
+        <v>-1.27</v>
       </c>
       <c r="J7" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="K7" s="10" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K7" s="10" t="inlineStr">
+        <is>
+          <t>★极近均线</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="26" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>300458</t>
+          <t>688578</t>
         </is>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>全志科技</t>
-        </is>
-      </c>
-      <c r="C8" s="9" t="n">
-        <v>-0.55</v>
-      </c>
-      <c r="D8" s="7" t="n"/>
+          <t>艾力斯</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="n">
+        <v>-1.76</v>
+      </c>
+      <c r="D8" s="7" t="n">
+        <v>0.84</v>
+      </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
           <t>正常</t>
         </is>
       </c>
       <c r="F8" s="7" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="I8" s="7" t="n">
-        <v>2.19</v>
+        <v>-1.34</v>
       </c>
       <c r="J8" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="K8" s="7" t="inlineStr">
-        <is>
-          <t>★极近均线</t>
-        </is>
-      </c>
+      <c r="K8" s="7" t="inlineStr"/>
     </row>
     <row r="9" ht="26" customHeight="1">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>688578</t>
+          <t>600285</t>
         </is>
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>艾力斯 NEW</t>
+          <t>羚锐制药</t>
         </is>
       </c>
       <c r="C9" s="10" t="n">
-        <v>-1.76</v>
+        <v>1.21</v>
       </c>
       <c r="D9" s="10" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="E9" s="10" t="inlineStr">
-        <is>
-          <t>正常</t>
+        <v>1.37</v>
+      </c>
+      <c r="E9" s="12" t="inlineStr">
+        <is>
+          <t>放量</t>
         </is>
       </c>
       <c r="F9" s="10" t="n">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="G9" s="10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H9" s="10" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="I9" s="10" t="n">
-        <v>-1.34</v>
+        <v>0.85</v>
       </c>
       <c r="J9" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="K9" s="10" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="K9" s="10" t="inlineStr">
+        <is>
+          <t>疑似出货</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="26" customHeight="1">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>600285</t>
+          <t>605208</t>
         </is>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>羚锐制药 NEW</t>
+          <t>永茂泰</t>
         </is>
       </c>
       <c r="C10" s="7" t="n">
-        <v>1.21</v>
+        <v>-1.92</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="E10" s="13" t="inlineStr">
-        <is>
-          <t>放量</t>
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>正常</t>
         </is>
       </c>
       <c r="F10" s="7" t="n">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="G10" s="7" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="I10" s="7" t="n">
-        <v>0.04</v>
+        <v>-1.92</v>
       </c>
       <c r="J10" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="K10" s="7" t="inlineStr">
-        <is>
-          <t>疑似出货</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="K10" s="7" t="inlineStr"/>
     </row>
     <row r="11" ht="26" customHeight="1">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>603991</t>
+          <t>603068</t>
         </is>
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>领先股份</t>
+          <t>博通集成</t>
         </is>
       </c>
       <c r="C11" s="10" t="n">
-        <v>1.07</v>
+        <v>-2.12</v>
       </c>
       <c r="D11" s="10" t="n">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="E11" s="10" t="inlineStr">
         <is>
@@ -14660,403 +14858,108 @@
         </is>
       </c>
       <c r="F11" s="10" t="n">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="G11" s="10" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H11" s="10" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="I11" s="10" t="n">
-        <v>10</v>
+        <v>0.05</v>
       </c>
       <c r="J11" s="10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K11" s="10" t="inlineStr"/>
     </row>
     <row r="12" ht="26" customHeight="1">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>300487</t>
+          <t>688046</t>
         </is>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>蓝晓科技</t>
-        </is>
-      </c>
-      <c r="C12" s="9" t="n">
-        <v>0.34</v>
+          <t>药康生物</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="n">
+        <v>2.68</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="E12" s="13" t="inlineStr">
-        <is>
-          <t>放量</t>
+        <v>0.93</v>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>正常</t>
         </is>
       </c>
       <c r="F12" s="7" t="n">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="G12" s="7" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="I12" s="7" t="n">
-        <v>-1</v>
+        <v>0.66</v>
       </c>
       <c r="J12" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="K12" s="7" t="inlineStr">
-        <is>
-          <t>★极近均线</t>
-        </is>
-      </c>
+      <c r="K12" s="7" t="inlineStr"/>
     </row>
     <row r="13" ht="26" customHeight="1">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>301151</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>冠龙节能</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="D13" s="3" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>缩量</t>
-        </is>
-      </c>
-      <c r="F13" s="3" t="n">
-        <v>44</v>
-      </c>
-      <c r="G13" s="3" t="n">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>603259</t>
+        </is>
+      </c>
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>药明康德</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="D13" s="10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="E13" s="12" t="inlineStr">
+        <is>
+          <t>放量</t>
+        </is>
+      </c>
+      <c r="F13" s="10" t="n">
         <v>12</v>
       </c>
-      <c r="H13" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="I13" s="3" t="n">
-        <v>7.33</v>
-      </c>
-      <c r="J13" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K13" s="3" t="inlineStr"/>
-    </row>
-    <row r="14" ht="26" customHeight="1">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>688795</t>
-        </is>
-      </c>
-      <c r="B14" s="8" t="inlineStr">
-        <is>
-          <t>摩尔线程</t>
-        </is>
-      </c>
-      <c r="C14" s="7" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="D14" s="7" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="E14" s="7" t="inlineStr">
-        <is>
-          <t>正常</t>
-        </is>
-      </c>
-      <c r="F14" s="7" t="n">
-        <v>39</v>
-      </c>
-      <c r="G14" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="H14" s="7" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="I14" s="7" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="J14" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="K14" s="7" t="inlineStr"/>
-    </row>
-    <row r="15" ht="26" customHeight="1">
-      <c r="A15" s="10" t="inlineStr">
-        <is>
-          <t>605208</t>
-        </is>
-      </c>
-      <c r="B15" s="11" t="inlineStr">
-        <is>
-          <t>永茂泰</t>
-        </is>
-      </c>
-      <c r="C15" s="10" t="n">
-        <v>-1.92</v>
-      </c>
-      <c r="D15" s="10" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="E15" s="10" t="inlineStr">
-        <is>
-          <t>正常</t>
-        </is>
-      </c>
-      <c r="F15" s="10" t="n">
-        <v>39</v>
-      </c>
-      <c r="G15" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="H15" s="10" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-      <c r="I15" s="10" t="n">
-        <v>-1.92</v>
-      </c>
-      <c r="J15" s="10" t="n">
+      <c r="G13" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="H13" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="I13" s="10" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J13" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="K15" s="10" t="inlineStr"/>
-    </row>
-    <row r="16" ht="26" customHeight="1">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>603068</t>
-        </is>
-      </c>
-      <c r="B16" s="8" t="inlineStr">
-        <is>
-          <t>博通集成</t>
-        </is>
-      </c>
-      <c r="C16" s="7" t="n">
-        <v>-2.12</v>
-      </c>
-      <c r="D16" s="7" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="E16" s="7" t="inlineStr">
-        <is>
-          <t>正常</t>
-        </is>
-      </c>
-      <c r="F16" s="7" t="n">
-        <v>38</v>
-      </c>
-      <c r="G16" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="H16" s="7" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="I16" s="7" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="J16" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="K16" s="7" t="inlineStr">
-        <is>
-          <t>疑似出货</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="26" customHeight="1">
-      <c r="A17" s="10" t="inlineStr">
-        <is>
-          <t>688720</t>
-        </is>
-      </c>
-      <c r="B17" s="11" t="inlineStr">
-        <is>
-          <t>艾森股份</t>
-        </is>
-      </c>
-      <c r="C17" s="10" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="D17" s="10" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="E17" s="10" t="inlineStr">
-        <is>
-          <t>正常</t>
-        </is>
-      </c>
-      <c r="F17" s="10" t="n">
-        <v>34</v>
-      </c>
-      <c r="G17" s="10" t="n">
-        <v>13</v>
-      </c>
-      <c r="H17" s="10" t="inlineStr">
-        <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="I17" s="10" t="n">
-        <v>20</v>
-      </c>
-      <c r="J17" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="K17" s="10" t="inlineStr"/>
-    </row>
-    <row r="18" ht="26" customHeight="1">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>603928</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>兴业股份</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="n">
-        <v>-2.75</v>
-      </c>
-      <c r="D18" s="3" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="E18" s="5" t="inlineStr">
-        <is>
-          <t>缩量</t>
-        </is>
-      </c>
-      <c r="F18" s="3" t="n">
-        <v>34</v>
-      </c>
-      <c r="G18" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="H18" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="I18" s="3" t="n">
-        <v>10.02</v>
-      </c>
-      <c r="J18" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K18" s="3" t="inlineStr"/>
-    </row>
-    <row r="19" ht="26" customHeight="1">
-      <c r="A19" s="10" t="inlineStr">
-        <is>
-          <t>688046</t>
-        </is>
-      </c>
-      <c r="B19" s="11" t="inlineStr">
-        <is>
-          <t>药康生物</t>
-        </is>
-      </c>
-      <c r="C19" s="10" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="D19" s="10" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="E19" s="10" t="inlineStr">
-        <is>
-          <t>正常</t>
-        </is>
-      </c>
-      <c r="F19" s="10" t="n">
-        <v>28</v>
-      </c>
-      <c r="G19" s="10" t="n">
-        <v>6</v>
-      </c>
-      <c r="H19" s="10" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="I19" s="10" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="J19" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="K19" s="10" t="inlineStr"/>
-    </row>
-    <row r="20" ht="26" customHeight="1">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>603259</t>
-        </is>
-      </c>
-      <c r="B20" s="8" t="inlineStr">
-        <is>
-          <t>药明康德</t>
-        </is>
-      </c>
-      <c r="C20" s="7" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="D20" s="7" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="E20" s="13" t="inlineStr">
-        <is>
-          <t>放量</t>
-        </is>
-      </c>
-      <c r="F20" s="7" t="n">
-        <v>22</v>
-      </c>
-      <c r="G20" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H20" s="7" t="inlineStr">
-        <is>
-          <t>2026-07-21</t>
-        </is>
-      </c>
-      <c r="I20" s="7" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="J20" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="K20" s="7" t="inlineStr"/>
+      <c r="K13" s="10" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:K20"/>
+  <autoFilter ref="A3:K13"/>
   <mergeCells count="1">
     <mergeCell ref="A1:K1"/>
   </mergeCells>
@@ -15078,559 +14981,559 @@
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="28" t="inlineStr">
+      <c r="A1" s="26" t="inlineStr">
         <is>
           <t>投资洞察与规律总结 v5.0</t>
         </is>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="29" t="inlineStr">
+      <c r="A3" s="27" t="inlineStr">
         <is>
           <t>大盘状态</t>
         </is>
       </c>
-      <c r="B3" s="30" t="inlineStr">
+      <c r="B3" s="28" t="inlineStr">
         <is>
           <t>下跌市(强制空仓) | 仓位0% | 最大持仓0只</t>
         </is>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
-      <c r="A4" s="29" t="inlineStr">
+      <c r="A4" s="27" t="inlineStr">
         <is>
           <t>新高/新低差值</t>
         </is>
       </c>
-      <c r="B4" s="30" t="inlineStr">
+      <c r="B4" s="28" t="inlineStr">
         <is>
           <t>-2275  !!冰点(新低2314)</t>
         </is>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="29" t="inlineStr">
+      <c r="A5" s="27" t="inlineStr">
         <is>
           <t>今日主线板块</t>
         </is>
       </c>
-      <c r="B5" s="30" t="inlineStr">
-        <is>
-          <t>医药(10), 通信(3), 芯片(3)</t>
+      <c r="B5" s="28" t="inlineStr">
+        <is>
+          <t>医药(3), 通信(1), 芯片(1)</t>
         </is>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="29" t="inlineStr">
+      <c r="A6" s="27" t="inlineStr">
         <is>
           <t>全库扫描</t>
         </is>
       </c>
-      <c r="B6" s="30" t="inlineStr">
-        <is>
-          <t>17只核心股距MA13 ±3%，首列重点关注</t>
+      <c r="B6" s="28" t="inlineStr">
+        <is>
+          <t>10只核心股距MA13 ±3%，首列重点关注</t>
         </is>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="31" t="inlineStr"/>
-      <c r="B7" s="32" t="inlineStr"/>
+      <c r="A7" s="29" t="inlineStr"/>
+      <c r="B7" s="30" t="inlineStr"/>
     </row>
     <row r="8" ht="28" customHeight="1">
-      <c r="A8" s="33" t="inlineStr">
+      <c r="A8" s="31" t="inlineStr">
         <is>
           <t>═══ 市场规律(基于11天回测) ═══</t>
         </is>
       </c>
-      <c r="B8" s="34" t="inlineStr"/>
+      <c r="B8" s="32" t="inlineStr"/>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="29" t="inlineStr">
+      <c r="A9" s="27" t="inlineStr">
         <is>
           <t>规律一·冰点次日效应</t>
         </is>
       </c>
-      <c r="B9" s="30" t="inlineStr">
+      <c r="B9" s="28" t="inlineStr">
         <is>
           <t>新高数&lt;50且差值&lt;-500时为冰点。7/8冰点次日+60.9%，7/13冰点次日+196.3%。冰点=恐慌出清=机会</t>
         </is>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="29" t="inlineStr">
+      <c r="A10" s="27" t="inlineStr">
         <is>
           <t>规律二·板块轮动节奏</t>
         </is>
       </c>
-      <c r="B10" s="30" t="inlineStr">
+      <c r="B10" s="28" t="inlineStr">
         <is>
           <t>芯片(7/1-3)→商业航天(7/10一日游)→医药(7/13-15接棒)。主线切换时有2天真空期</t>
         </is>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="29" t="inlineStr">
+      <c r="A11" s="27" t="inlineStr">
         <is>
           <t>规律三·情绪锚修复</t>
         </is>
       </c>
-      <c r="B11" s="30" t="inlineStr">
+      <c r="B11" s="28" t="inlineStr">
         <is>
           <t>差值从-1506→-117持续收窄，若连续3日收窄则锚3转涨，触发满仓信号</t>
         </is>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="29" t="inlineStr">
+      <c r="A12" s="27" t="inlineStr">
         <is>
           <t>规律四·NEW占比判断持续性</t>
         </is>
       </c>
-      <c r="B12" s="30" t="inlineStr">
+      <c r="B12" s="28" t="inlineStr">
         <is>
           <t>当日NEW标记占比&gt;50%=新主线上涨初期可追，占比&lt;20%=老主线在退潮</t>
         </is>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="31" t="inlineStr"/>
-      <c r="B13" s="32" t="inlineStr"/>
+      <c r="A13" s="29" t="inlineStr"/>
+      <c r="B13" s="30" t="inlineStr"/>
     </row>
     <row r="14" ht="28" customHeight="1">
-      <c r="A14" s="33" t="inlineStr">
+      <c r="A14" s="31" t="inlineStr">
         <is>
           <t>═══ 牛股三大规律 ═══</t>
         </is>
       </c>
-      <c r="B14" s="34" t="inlineStr"/>
+      <c r="B14" s="32" t="inlineStr"/>
     </row>
     <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="29" t="inlineStr">
+      <c r="A15" s="27" t="inlineStr">
         <is>
           <t>类型一·连续涨停型</t>
         </is>
       </c>
-      <c r="B15" s="30" t="inlineStr">
+      <c r="B15" s="28" t="inlineStr">
         <is>
           <t>代表：恒尚节能(603137) 9天连板+106.8%，首日涨停后每日缩量一字板，从未回调</t>
         </is>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="29" t="inlineStr">
+      <c r="A16" s="27" t="inlineStr">
         <is>
           <t>类型二·回踩再起型</t>
         </is>
       </c>
-      <c r="B16" s="30" t="inlineStr">
+      <c r="B16" s="28" t="inlineStr">
         <is>
           <t>代表：翰宇药业(300199) 7/14缩量回踩MA13=-0.81% → 7/15放量+6.94%，买点在缩量企稳日</t>
         </is>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="29" t="inlineStr">
+      <c r="A17" s="27" t="inlineStr">
         <is>
           <t>类型三·横盘突破型</t>
         </is>
       </c>
-      <c r="B17" s="30" t="inlineStr">
+      <c r="B17" s="28" t="inlineStr">
         <is>
           <t>代表：康龙化成(300759) 6次上榜涨跌交替，末段+9.1%放量突破，确认后追入</t>
         </is>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="31" t="inlineStr"/>
-      <c r="B18" s="32" t="inlineStr"/>
+      <c r="A18" s="29" t="inlineStr"/>
+      <c r="B18" s="30" t="inlineStr"/>
     </row>
     <row r="19" ht="28" customHeight="1">
-      <c r="A19" s="33" t="inlineStr">
+      <c r="A19" s="31" t="inlineStr">
         <is>
           <t>═══ 垃圾股三大特征 ═══</t>
         </is>
       </c>
-      <c r="B19" s="34" t="inlineStr"/>
+      <c r="B19" s="32" t="inlineStr"/>
     </row>
     <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="29" t="inlineStr">
+      <c r="A20" s="27" t="inlineStr">
         <is>
           <t>特征一·一日游假突破</t>
         </is>
       </c>
-      <c r="B20" s="30" t="inlineStr">
+      <c r="B20" s="28" t="inlineStr">
         <is>
           <t>42%的百日新高仅上榜1次，首日涨幅&gt;15%的102只次日全部消失</t>
         </is>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="29" t="inlineStr">
+      <c r="A21" s="27" t="inlineStr">
         <is>
           <t>特征二·多次上榜不涨</t>
         </is>
       </c>
-      <c r="B21" s="30" t="inlineStr">
+      <c r="B21" s="28" t="inlineStr">
         <is>
           <t>博通集成(603068) 8次上榜区间-2.8%，上榜频繁但价格不动=主力借新高出货</t>
         </is>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="29" t="inlineStr">
+      <c r="A22" s="27" t="inlineStr">
         <is>
           <t>特征三·首日即见顶</t>
         </is>
       </c>
-      <c r="B22" s="30" t="inlineStr">
+      <c r="B22" s="28" t="inlineStr">
         <is>
           <t>11只股票上榜当日即收跌，盘中冲高回落，无主力支撑</t>
         </is>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="31" t="inlineStr"/>
-      <c r="B23" s="32" t="inlineStr"/>
+      <c r="A23" s="29" t="inlineStr"/>
+      <c r="B23" s="30" t="inlineStr"/>
     </row>
     <row r="24" ht="28" customHeight="1">
-      <c r="A24" s="33" t="inlineStr">
+      <c r="A24" s="31" t="inlineStr">
         <is>
           <t>═══ 最佳介入窗口 ═══</t>
         </is>
       </c>
-      <c r="B24" s="34" t="inlineStr"/>
+      <c r="B24" s="32" t="inlineStr"/>
     </row>
     <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="29" t="inlineStr">
+      <c r="A25" s="27" t="inlineStr">
         <is>
           <t>首发后第3-5天</t>
         </is>
       </c>
-      <c r="B25" s="30" t="inlineStr">
+      <c r="B25" s="28" t="inlineStr">
         <is>
           <t>前2天冲高回落概率大，第3天缩量企稳是买点（回溯验证：候选池平均前瞻+4.1%）</t>
         </is>
       </c>
     </row>
     <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="29" t="inlineStr">
+      <c r="A26" s="27" t="inlineStr">
         <is>
           <t>距MA13在±2%以内</t>
         </is>
       </c>
-      <c r="B26" s="30" t="inlineStr">
+      <c r="B26" s="28" t="inlineStr">
         <is>
           <t>双环传动(002472) MA13=-0.17%为经典形态</t>
         </is>
       </c>
     </row>
     <row r="27" ht="22" customHeight="1">
-      <c r="A27" s="29" t="inlineStr">
+      <c r="A27" s="27" t="inlineStr">
         <is>
           <t>量比0.5-2.0</t>
         </is>
       </c>
-      <c r="B27" s="30" t="inlineStr">
+      <c r="B27" s="28" t="inlineStr">
         <is>
           <t>太缩量(&lt;0.5)=无人关注，太放量(&gt;2.0)=出货嫌疑，健康区间0.8-2.0</t>
         </is>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1">
-      <c r="A28" s="29" t="inlineStr">
+      <c r="A28" s="27" t="inlineStr">
         <is>
           <t>阳线或十字星</t>
         </is>
       </c>
-      <c r="B28" s="30" t="inlineStr">
+      <c r="B28" s="28" t="inlineStr">
         <is>
           <t>排除放量阴线的假企稳</t>
         </is>
       </c>
     </row>
     <row r="29" ht="22" customHeight="1">
-      <c r="A29" s="31" t="inlineStr"/>
-      <c r="B29" s="32" t="inlineStr"/>
+      <c r="A29" s="29" t="inlineStr"/>
+      <c r="B29" s="30" t="inlineStr"/>
     </row>
     <row r="30" ht="28" customHeight="1">
-      <c r="A30" s="33" t="inlineStr">
+      <c r="A30" s="31" t="inlineStr">
         <is>
           <t>═══ 卖出纪律 ═══</t>
         </is>
       </c>
-      <c r="B30" s="34" t="inlineStr"/>
+      <c r="B30" s="32" t="inlineStr"/>
     </row>
     <row r="31" ht="22" customHeight="1">
-      <c r="A31" s="29" t="inlineStr">
+      <c r="A31" s="27" t="inlineStr">
         <is>
           <t>放量滞涨</t>
         </is>
       </c>
-      <c r="B31" s="30" t="inlineStr">
+      <c r="B31" s="28" t="inlineStr">
         <is>
           <t>量比&gt;1.5 + 涨幅&lt;1% → 减仓</t>
         </is>
       </c>
     </row>
     <row r="32" ht="22" customHeight="1">
-      <c r="A32" s="29" t="inlineStr">
+      <c r="A32" s="27" t="inlineStr">
         <is>
           <t>跌破MA13</t>
         </is>
       </c>
-      <c r="B32" s="30" t="inlineStr">
+      <c r="B32" s="28" t="inlineStr">
         <is>
           <t>收盘&lt;MA13 → 次日开盘止损离场</t>
         </is>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">
-      <c r="A33" s="29" t="inlineStr">
+      <c r="A33" s="27" t="inlineStr">
         <is>
           <t>浮盈&gt;20%</t>
         </is>
       </c>
-      <c r="B33" s="30" t="inlineStr">
+      <c r="B33" s="28" t="inlineStr">
         <is>
           <t>止盈线收紧至MA13</t>
         </is>
       </c>
     </row>
     <row r="34" ht="22" customHeight="1">
-      <c r="A34" s="29" t="inlineStr">
+      <c r="A34" s="27" t="inlineStr">
         <is>
           <t>连续3日放量加速</t>
         </is>
       </c>
-      <c r="B34" s="30" t="inlineStr">
+      <c r="B34" s="28" t="inlineStr">
         <is>
           <t>止盈线从MA13收紧至MA5</t>
         </is>
       </c>
     </row>
     <row r="35" ht="22" customHeight="1">
-      <c r="A35" s="31" t="inlineStr"/>
-      <c r="B35" s="32" t="inlineStr"/>
+      <c r="A35" s="29" t="inlineStr"/>
+      <c r="B35" s="30" t="inlineStr"/>
     </row>
     <row r="36" ht="28" customHeight="1">
-      <c r="A36" s="33" t="inlineStr">
+      <c r="A36" s="31" t="inlineStr">
         <is>
           <t>═══ 7/16 今日发现 ═══</t>
         </is>
       </c>
-      <c r="B36" s="34" t="inlineStr"/>
+      <c r="B36" s="32" t="inlineStr"/>
     </row>
     <row r="37" ht="22" customHeight="1">
-      <c r="A37" s="29" t="inlineStr">
+      <c r="A37" s="27" t="inlineStr">
         <is>
           <t>发现一·新高股普遍远离均线</t>
         </is>
       </c>
-      <c r="B37" s="30" t="inlineStr">
+      <c r="B37" s="28" t="inlineStr">
         <is>
           <t>7/16上榜43只中仅博通集成+药康生物2只距MA13±3%。多数新高股已'飘'起，追高风险大。这正是全库扫描价值所在——盯的是过去新高、现在回踩的票</t>
         </is>
       </c>
     </row>
     <row r="38" ht="22" customHeight="1">
-      <c r="A38" s="29" t="inlineStr">
+      <c r="A38" s="27" t="inlineStr">
         <is>
           <t>发现二·医药主力内部分化</t>
         </is>
       </c>
-      <c r="B38" s="30" t="inlineStr">
+      <c r="B38" s="28" t="inlineStr">
         <is>
           <t>热景生物主力+23亿 vs 药明康德-6.29亿，同一板块内资金在调仓换股而非全面撤退。追医药需精选个股</t>
         </is>
       </c>
     </row>
     <row r="39" ht="22" customHeight="1">
-      <c r="A39" s="35" t="inlineStr">
+      <c r="A39" s="33" t="inlineStr">
         <is>
           <t>发现三·翰宇药业验证完整</t>
         </is>
       </c>
-      <c r="B39" s="36" t="inlineStr">
+      <c r="B39" s="34" t="inlineStr">
         <is>
           <t>7/1首高(+8.4%)→7/13暴跌(-7.6%)→7/14缩量企稳MA13=-0.81%→7/15放量+6.9%→7/16回落-5.3%。完整走完'突破→回踩→反弹→再回落'周期。最佳介入点：缩量企稳日，不是反弹追涨日</t>
         </is>
       </c>
     </row>
     <row r="40" ht="22" customHeight="1">
-      <c r="A40" s="29" t="inlineStr">
+      <c r="A40" s="27" t="inlineStr">
         <is>
           <t>发现四·博通集成持续缩量靠拢</t>
         </is>
       </c>
-      <c r="B40" s="30" t="inlineStr">
+      <c r="B40" s="28" t="inlineStr">
         <is>
           <t>10次上榜，MA13从+0.32%→-2.12%，价格持续向均线靠拢。VR=1.13仍偏高，等缩到0.8以下就是完美狙击点</t>
         </is>
       </c>
     </row>
     <row r="41" ht="22" customHeight="1">
-      <c r="A41" s="31" t="inlineStr"/>
-      <c r="B41" s="32" t="inlineStr"/>
+      <c r="A41" s="29" t="inlineStr"/>
+      <c r="B41" s="30" t="inlineStr"/>
     </row>
     <row r="42" ht="28" customHeight="1">
-      <c r="A42" s="33" t="inlineStr">
+      <c r="A42" s="31" t="inlineStr">
         <is>
           <t>═══ 持续跟踪 ═══</t>
         </is>
       </c>
-      <c r="B42" s="34" t="inlineStr"/>
+      <c r="B42" s="32" t="inlineStr"/>
     </row>
     <row r="43" ht="22" customHeight="1">
-      <c r="A43" s="29" t="inlineStr">
+      <c r="A43" s="27" t="inlineStr">
         <is>
           <t>翰宇药业(300199)</t>
         </is>
       </c>
-      <c r="B43" s="30" t="inlineStr">
+      <c r="B43" s="28" t="inlineStr">
         <is>
           <t>MA13=+0.21% VR=0.74缩量 仍是最佳狙击候选，等放量阳线确认</t>
         </is>
       </c>
     </row>
     <row r="44" ht="22" customHeight="1">
-      <c r="A44" s="29" t="inlineStr">
+      <c r="A44" s="27" t="inlineStr">
         <is>
           <t>博通集成(603068)</t>
         </is>
       </c>
-      <c r="B44" s="30" t="inlineStr">
+      <c r="B44" s="28" t="inlineStr">
         <is>
           <t>MA13=-2.12% VR=1.13 已靠近均线但量比偏高，等缩量信号</t>
         </is>
       </c>
     </row>
     <row r="45" ht="22" customHeight="1">
-      <c r="A45" s="29" t="inlineStr">
+      <c r="A45" s="27" t="inlineStr">
         <is>
           <t>共同药业(300966)</t>
         </is>
       </c>
-      <c r="B45" s="30" t="inlineStr">
+      <c r="B45" s="28" t="inlineStr">
         <is>
           <t>MA13=-0.48% VR=0.73缩量 新进入候选池，7/15上榜+12.6%，关注后续回踩</t>
         </is>
       </c>
     </row>
     <row r="46" ht="22" customHeight="1">
-      <c r="A46" s="29" t="inlineStr">
+      <c r="A46" s="27" t="inlineStr">
         <is>
           <t>冠龙节能(301151)</t>
         </is>
       </c>
-      <c r="B46" s="30" t="inlineStr">
+      <c r="B46" s="28" t="inlineStr">
         <is>
           <t>MA13=+2.16% VR=0.68缩量 新进入，但距均线略远</t>
         </is>
       </c>
     </row>
     <row r="47" ht="22" customHeight="1">
-      <c r="A47" s="31" t="inlineStr"/>
-      <c r="B47" s="32" t="inlineStr"/>
+      <c r="A47" s="29" t="inlineStr"/>
+      <c r="B47" s="30" t="inlineStr"/>
     </row>
     <row r="48" ht="28" customHeight="1">
-      <c r="A48" s="33" t="inlineStr">
+      <c r="A48" s="31" t="inlineStr">
         <is>
           <t>═══ 回测验证 ═══</t>
         </is>
       </c>
-      <c r="B48" s="34" t="inlineStr"/>
+      <c r="B48" s="32" t="inlineStr"/>
     </row>
     <row r="49" ht="22" customHeight="1">
-      <c r="A49" s="29" t="inlineStr">
+      <c r="A49" s="27" t="inlineStr">
         <is>
           <t>翰宇药业案例</t>
         </is>
       </c>
-      <c r="B49" s="30" t="inlineStr">
+      <c r="B49" s="28" t="inlineStr">
         <is>
           <t>7/14缩量回踩MA13(-0.81%)+VR=0.74 → 7/15放量+6.94% 完美验证狙击逻辑</t>
         </is>
       </c>
     </row>
     <row r="50" ht="22" customHeight="1">
-      <c r="A50" s="29" t="inlineStr">
+      <c r="A50" s="27" t="inlineStr">
         <is>
           <t>石药创新虚假信号</t>
         </is>
       </c>
-      <c r="B50" s="30" t="inlineStr">
+      <c r="B50" s="28" t="inlineStr">
         <is>
           <t>近似MA13=+0.2%被证伪（真实+11.22%），系统已改用K线硬算，杜绝误判</t>
         </is>
       </c>
     </row>
     <row r="51" ht="22" customHeight="1">
-      <c r="A51" s="31" t="inlineStr"/>
-      <c r="B51" s="32" t="inlineStr"/>
+      <c r="A51" s="29" t="inlineStr"/>
+      <c r="B51" s="30" t="inlineStr"/>
     </row>
     <row r="52" ht="28" customHeight="1">
-      <c r="A52" s="33" t="inlineStr">
+      <c r="A52" s="31" t="inlineStr">
         <is>
           <t>═══ 系统进化记录 ═══</t>
         </is>
       </c>
-      <c r="B52" s="34" t="inlineStr"/>
+      <c r="B52" s="32" t="inlineStr"/>
     </row>
     <row r="53" ht="22" customHeight="1">
-      <c r="A53" s="29" t="inlineStr">
+      <c r="A53" s="27" t="inlineStr">
         <is>
           <t>v5.0 七层规则</t>
         </is>
       </c>
-      <c r="B53" s="30" t="inlineStr">
+      <c r="B53" s="28" t="inlineStr">
         <is>
           <t>三锚定仓→主线过滤→状态分类→风险过滤→狙击池→后备池→卖出预警</t>
         </is>
       </c>
     </row>
     <row r="54" ht="22" customHeight="1">
-      <c r="A54" s="29" t="inlineStr">
+      <c r="A54" s="27" t="inlineStr">
         <is>
           <t>全库扫描(新)</t>
         </is>
       </c>
-      <c r="B54" s="30" t="inlineStr">
+      <c r="B54" s="28" t="inlineStr">
         <is>
           <t>不限于当日新高，扫描过去10天所有新高过的核心股在MA13附近的状态</t>
         </is>
       </c>
     </row>
     <row r="55" ht="22" customHeight="1">
-      <c r="A55" s="29" t="inlineStr">
+      <c r="A55" s="27" t="inlineStr">
         <is>
           <t>规则一</t>
         </is>
       </c>
-      <c r="B55" s="30" t="inlineStr">
+      <c r="B55" s="28" t="inlineStr">
         <is>
           <t>首日涨幅&gt;15%过滤（102只一日游验证）</t>
         </is>
       </c>
     </row>
     <row r="56" ht="22" customHeight="1">
-      <c r="A56" s="29" t="inlineStr">
+      <c r="A56" s="27" t="inlineStr">
         <is>
           <t>规则二</t>
         </is>
       </c>
-      <c r="B56" s="30" t="inlineStr">
+      <c r="B56" s="28" t="inlineStr">
         <is>
           <t>5次上榜涨幅&lt;5%标记疑似出货（博通集成8次-2.8%验证）</t>
         </is>
       </c>
     </row>
     <row r="57" ht="22" customHeight="1">
-      <c r="A57" s="29" t="inlineStr">
+      <c r="A57" s="27" t="inlineStr">
         <is>
           <t>NEW标记(新)</t>
         </is>
       </c>
-      <c r="B57" s="30" t="inlineStr">
+      <c r="B57" s="28" t="inlineStr">
         <is>
           <t>每日新增股票自动标注，方便识别首次突破</t>
         </is>

--- a/百日新高v4.0最终版/百日新高_报表.xlsx
+++ b/百日新高v4.0最终版/百日新高_报表.xlsx
@@ -16,7 +16,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="投资洞察" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'核心主线跟踪'!$A$3:$N$245</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'核心主线跟踪'!$A$3:$N$247</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'风险过滤清单'!$A$3:$G$38</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'全库扫描(MA13±3%)'!$A$3:$K$13</definedName>
   </definedNames>
@@ -667,7 +667,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N245"/>
+  <dimension ref="A1:N247"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -688,7 +688,7 @@
     <row r="1" ht="36" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>百日新高 v5.0 | 2026-07-27 | 下跌市(强制空仓) 0% | 风险过滤35只</t>
+          <t>百日新高 v5.0 | 2026-07-29 | 下跌市(强制空仓) 0% | 风险过滤35只</t>
         </is>
       </c>
     </row>
@@ -5631,76 +5631,70 @@
     <row r="101" ht="26" customHeight="1">
       <c r="A101" s="10" t="inlineStr">
         <is>
-          <t>603155</t>
+          <t>601598</t>
         </is>
       </c>
       <c r="B101" s="11" t="inlineStr">
         <is>
-          <t>新亚强</t>
+          <t>中国外运 NEW</t>
         </is>
       </c>
       <c r="C101" s="10" t="inlineStr">
         <is>
-          <t>算力/通信</t>
+          <t>机器人</t>
         </is>
       </c>
       <c r="D101" s="10" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E101" s="10" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="F101" s="10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G101" s="10" t="inlineStr">
         <is>
-          <t>强势上攻</t>
+          <t>高位整理</t>
         </is>
       </c>
       <c r="H101" s="12" t="n">
-        <v>10.01</v>
-      </c>
-      <c r="I101" s="10" t="n">
-        <v>-40.71</v>
-      </c>
+        <v>2.24</v>
+      </c>
+      <c r="I101" s="10" t="n"/>
       <c r="J101" s="10" t="n"/>
-      <c r="K101" s="10" t="inlineStr">
-        <is>
-          <t>正常</t>
-        </is>
-      </c>
+      <c r="K101" s="10" t="inlineStr"/>
       <c r="L101" s="10" t="inlineStr"/>
       <c r="M101" s="10" t="inlineStr"/>
     </row>
     <row r="102" ht="26" customHeight="1">
       <c r="A102" s="7" t="inlineStr">
         <is>
-          <t>688233</t>
+          <t>603118</t>
         </is>
       </c>
       <c r="B102" s="8" t="inlineStr">
         <is>
-          <t>神工股份</t>
+          <t>共进股份 NEW</t>
         </is>
       </c>
       <c r="C102" s="7" t="inlineStr">
         <is>
-          <t>半导体/芯片</t>
+          <t>算力/通信</t>
         </is>
       </c>
       <c r="D102" s="7" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E102" s="7" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="F102" s="7" t="n">
@@ -5708,40 +5702,32 @@
       </c>
       <c r="G102" s="7" t="inlineStr">
         <is>
-          <t>强势上攻</t>
-        </is>
-      </c>
-      <c r="H102" s="13" t="n">
-        <v>11.26</v>
-      </c>
-      <c r="I102" s="7" t="n">
-        <v>-28.84</v>
-      </c>
-      <c r="J102" s="7" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="K102" s="7" t="inlineStr">
-        <is>
-          <t>缩量</t>
-        </is>
-      </c>
+          <t>高位整理</t>
+        </is>
+      </c>
+      <c r="H102" s="9" t="n">
+        <v>-3.87</v>
+      </c>
+      <c r="I102" s="7" t="n"/>
+      <c r="J102" s="7" t="n"/>
+      <c r="K102" s="7" t="inlineStr"/>
       <c r="L102" s="7" t="inlineStr"/>
       <c r="M102" s="7" t="inlineStr"/>
     </row>
     <row r="103" ht="26" customHeight="1">
       <c r="A103" s="10" t="inlineStr">
         <is>
-          <t>300666</t>
+          <t>603155</t>
         </is>
       </c>
       <c r="B103" s="11" t="inlineStr">
         <is>
-          <t>江丰电子</t>
+          <t>新亚强</t>
         </is>
       </c>
       <c r="C103" s="10" t="inlineStr">
         <is>
-          <t>半导体/芯片</t>
+          <t>算力/通信</t>
         </is>
       </c>
       <c r="D103" s="10" t="inlineStr">
@@ -5751,11 +5737,11 @@
       </c>
       <c r="E103" s="10" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="F103" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G103" s="10" t="inlineStr">
         <is>
@@ -5763,14 +5749,12 @@
         </is>
       </c>
       <c r="H103" s="12" t="n">
-        <v>6.98</v>
+        <v>10.01</v>
       </c>
       <c r="I103" s="10" t="n">
-        <v>-27.17</v>
-      </c>
-      <c r="J103" s="10" t="n">
-        <v>1.14</v>
-      </c>
+        <v>-40.71</v>
+      </c>
+      <c r="J103" s="10" t="n"/>
       <c r="K103" s="10" t="inlineStr">
         <is>
           <t>正常</t>
@@ -5782,12 +5766,12 @@
     <row r="104" ht="26" customHeight="1">
       <c r="A104" s="7" t="inlineStr">
         <is>
-          <t>600667</t>
+          <t>688233</t>
         </is>
       </c>
       <c r="B104" s="8" t="inlineStr">
         <is>
-          <t>太极实业</t>
+          <t>神工股份</t>
         </is>
       </c>
       <c r="C104" s="7" t="inlineStr">
@@ -5802,11 +5786,11 @@
       </c>
       <c r="E104" s="7" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="F104" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G104" s="7" t="inlineStr">
         <is>
@@ -5814,86 +5798,82 @@
         </is>
       </c>
       <c r="H104" s="13" t="n">
-        <v>3.7</v>
+        <v>11.26</v>
       </c>
       <c r="I104" s="7" t="n">
-        <v>-27.14</v>
+        <v>-28.84</v>
       </c>
       <c r="J104" s="7" t="n">
-        <v>0.89</v>
+        <v>0.71</v>
       </c>
       <c r="K104" s="7" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>缩量</t>
         </is>
       </c>
       <c r="L104" s="7" t="inlineStr"/>
       <c r="M104" s="7" t="inlineStr"/>
     </row>
     <row r="105" ht="26" customHeight="1">
-      <c r="A105" s="15" t="inlineStr">
-        <is>
-          <t>688286</t>
-        </is>
-      </c>
-      <c r="B105" s="16" t="inlineStr">
-        <is>
-          <t>敏芯股份</t>
-        </is>
-      </c>
-      <c r="C105" s="15" t="inlineStr">
+      <c r="A105" s="10" t="inlineStr">
+        <is>
+          <t>300666</t>
+        </is>
+      </c>
+      <c r="B105" s="11" t="inlineStr">
+        <is>
+          <t>江丰电子</t>
+        </is>
+      </c>
+      <c r="C105" s="10" t="inlineStr">
         <is>
           <t>半导体/芯片</t>
         </is>
       </c>
-      <c r="D105" s="15" t="inlineStr">
+      <c r="D105" s="10" t="inlineStr">
         <is>
           <t>2026-07-01</t>
         </is>
       </c>
-      <c r="E105" s="15" t="inlineStr">
+      <c r="E105" s="10" t="inlineStr">
         <is>
           <t>2026-07-01</t>
         </is>
       </c>
-      <c r="F105" s="15" t="n">
+      <c r="F105" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="G105" s="17" t="inlineStr">
-        <is>
-          <t>强势上攻</t>
-        </is>
-      </c>
-      <c r="H105" s="19" t="n">
-        <v>15.87</v>
-      </c>
-      <c r="I105" s="15" t="n">
-        <v>-25.82</v>
-      </c>
-      <c r="J105" s="15" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="K105" s="15" t="inlineStr">
-        <is>
-          <t>正常</t>
-        </is>
-      </c>
-      <c r="L105" s="15" t="inlineStr">
-        <is>
-          <t>首日涨幅&gt;16%</t>
-        </is>
-      </c>
-      <c r="M105" s="15" t="inlineStr"/>
+      <c r="G105" s="10" t="inlineStr">
+        <is>
+          <t>强势上攻</t>
+        </is>
+      </c>
+      <c r="H105" s="12" t="n">
+        <v>6.98</v>
+      </c>
+      <c r="I105" s="10" t="n">
+        <v>-27.17</v>
+      </c>
+      <c r="J105" s="10" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="K105" s="10" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="L105" s="10" t="inlineStr"/>
+      <c r="M105" s="10" t="inlineStr"/>
     </row>
     <row r="106" ht="26" customHeight="1">
       <c r="A106" s="7" t="inlineStr">
         <is>
-          <t>603324</t>
+          <t>600667</t>
         </is>
       </c>
       <c r="B106" s="8" t="inlineStr">
         <is>
-          <t>盛剑科技</t>
+          <t>太极实业</t>
         </is>
       </c>
       <c r="C106" s="7" t="inlineStr">
@@ -5908,11 +5888,11 @@
       </c>
       <c r="E106" s="7" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="F106" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G106" s="7" t="inlineStr">
         <is>
@@ -5920,13 +5900,13 @@
         </is>
       </c>
       <c r="H106" s="13" t="n">
-        <v>7.88</v>
+        <v>3.7</v>
       </c>
       <c r="I106" s="7" t="n">
-        <v>-24.88</v>
+        <v>-27.14</v>
       </c>
       <c r="J106" s="7" t="n">
-        <v>0.9</v>
+        <v>0.89</v>
       </c>
       <c r="K106" s="7" t="inlineStr">
         <is>
@@ -5937,70 +5917,74 @@
       <c r="M106" s="7" t="inlineStr"/>
     </row>
     <row r="107" ht="26" customHeight="1">
-      <c r="A107" s="10" t="inlineStr">
-        <is>
-          <t>688549</t>
-        </is>
-      </c>
-      <c r="B107" s="11" t="inlineStr">
-        <is>
-          <t>中巨芯</t>
-        </is>
-      </c>
-      <c r="C107" s="10" t="inlineStr">
+      <c r="A107" s="15" t="inlineStr">
+        <is>
+          <t>688286</t>
+        </is>
+      </c>
+      <c r="B107" s="16" t="inlineStr">
+        <is>
+          <t>敏芯股份</t>
+        </is>
+      </c>
+      <c r="C107" s="15" t="inlineStr">
         <is>
           <t>半导体/芯片</t>
         </is>
       </c>
-      <c r="D107" s="10" t="inlineStr">
+      <c r="D107" s="15" t="inlineStr">
         <is>
           <t>2026-07-01</t>
         </is>
       </c>
-      <c r="E107" s="10" t="inlineStr">
+      <c r="E107" s="15" t="inlineStr">
         <is>
           <t>2026-07-01</t>
         </is>
       </c>
-      <c r="F107" s="10" t="n">
+      <c r="F107" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="G107" s="10" t="inlineStr">
-        <is>
-          <t>强势上攻</t>
-        </is>
-      </c>
-      <c r="H107" s="12" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="I107" s="10" t="n">
-        <v>-24.83</v>
-      </c>
-      <c r="J107" s="10" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="K107" s="10" t="inlineStr">
-        <is>
-          <t>正常</t>
-        </is>
-      </c>
-      <c r="L107" s="10" t="inlineStr"/>
-      <c r="M107" s="10" t="inlineStr"/>
+      <c r="G107" s="17" t="inlineStr">
+        <is>
+          <t>强势上攻</t>
+        </is>
+      </c>
+      <c r="H107" s="19" t="n">
+        <v>15.87</v>
+      </c>
+      <c r="I107" s="15" t="n">
+        <v>-25.82</v>
+      </c>
+      <c r="J107" s="15" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="K107" s="15" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="L107" s="15" t="inlineStr">
+        <is>
+          <t>首日涨幅&gt;16%</t>
+        </is>
+      </c>
+      <c r="M107" s="15" t="inlineStr"/>
     </row>
     <row r="108" ht="26" customHeight="1">
       <c r="A108" s="7" t="inlineStr">
         <is>
-          <t>603738</t>
+          <t>603324</t>
         </is>
       </c>
       <c r="B108" s="8" t="inlineStr">
         <is>
-          <t>泰晶科技</t>
+          <t>盛剑科技</t>
         </is>
       </c>
       <c r="C108" s="7" t="inlineStr">
         <is>
-          <t>算力/通信</t>
+          <t>半导体/芯片</t>
         </is>
       </c>
       <c r="D108" s="7" t="inlineStr">
@@ -6022,12 +6006,14 @@
         </is>
       </c>
       <c r="H108" s="13" t="n">
-        <v>10.01</v>
+        <v>7.88</v>
       </c>
       <c r="I108" s="7" t="n">
-        <v>-23.72</v>
-      </c>
-      <c r="J108" s="7" t="n"/>
+        <v>-24.88</v>
+      </c>
+      <c r="J108" s="7" t="n">
+        <v>0.9</v>
+      </c>
       <c r="K108" s="7" t="inlineStr">
         <is>
           <t>正常</t>
@@ -6037,69 +6023,65 @@
       <c r="M108" s="7" t="inlineStr"/>
     </row>
     <row r="109" ht="26" customHeight="1">
-      <c r="A109" s="15" t="inlineStr">
-        <is>
-          <t>300852</t>
-        </is>
-      </c>
-      <c r="B109" s="16" t="inlineStr">
-        <is>
-          <t>四会富仕</t>
-        </is>
-      </c>
-      <c r="C109" s="15" t="inlineStr">
-        <is>
-          <t>算力/通信</t>
-        </is>
-      </c>
-      <c r="D109" s="15" t="inlineStr">
+      <c r="A109" s="10" t="inlineStr">
+        <is>
+          <t>688549</t>
+        </is>
+      </c>
+      <c r="B109" s="11" t="inlineStr">
+        <is>
+          <t>中巨芯</t>
+        </is>
+      </c>
+      <c r="C109" s="10" t="inlineStr">
+        <is>
+          <t>半导体/芯片</t>
+        </is>
+      </c>
+      <c r="D109" s="10" t="inlineStr">
         <is>
           <t>2026-07-01</t>
         </is>
       </c>
-      <c r="E109" s="15" t="inlineStr">
+      <c r="E109" s="10" t="inlineStr">
         <is>
           <t>2026-07-01</t>
         </is>
       </c>
-      <c r="F109" s="15" t="n">
+      <c r="F109" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="G109" s="17" t="inlineStr">
-        <is>
-          <t>强势上攻</t>
-        </is>
-      </c>
-      <c r="H109" s="19" t="n">
-        <v>20</v>
-      </c>
-      <c r="I109" s="15" t="n">
-        <v>-23.44</v>
-      </c>
-      <c r="J109" s="15" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="K109" s="15" t="inlineStr">
-        <is>
-          <t>正常</t>
-        </is>
-      </c>
-      <c r="L109" s="15" t="inlineStr">
-        <is>
-          <t>首日涨幅&gt;20%</t>
-        </is>
-      </c>
-      <c r="M109" s="15" t="inlineStr"/>
+      <c r="G109" s="10" t="inlineStr">
+        <is>
+          <t>强势上攻</t>
+        </is>
+      </c>
+      <c r="H109" s="12" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="I109" s="10" t="n">
+        <v>-24.83</v>
+      </c>
+      <c r="J109" s="10" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="K109" s="10" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="L109" s="10" t="inlineStr"/>
+      <c r="M109" s="10" t="inlineStr"/>
     </row>
     <row r="110" ht="26" customHeight="1">
       <c r="A110" s="7" t="inlineStr">
         <is>
-          <t>300041</t>
+          <t>603738</t>
         </is>
       </c>
       <c r="B110" s="8" t="inlineStr">
         <is>
-          <t>回天新材</t>
+          <t>泰晶科技</t>
         </is>
       </c>
       <c r="C110" s="7" t="inlineStr">
@@ -6109,16 +6091,16 @@
       </c>
       <c r="D110" s="7" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="E110" s="7" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="F110" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G110" s="7" t="inlineStr">
         <is>
@@ -6126,10 +6108,10 @@
         </is>
       </c>
       <c r="H110" s="13" t="n">
-        <v>8.140000000000001</v>
+        <v>10.01</v>
       </c>
       <c r="I110" s="7" t="n">
-        <v>-23.21</v>
+        <v>-23.72</v>
       </c>
       <c r="J110" s="7" t="n"/>
       <c r="K110" s="7" t="inlineStr">
@@ -6141,68 +6123,74 @@
       <c r="M110" s="7" t="inlineStr"/>
     </row>
     <row r="111" ht="26" customHeight="1">
-      <c r="A111" s="10" t="inlineStr">
-        <is>
-          <t>300480</t>
-        </is>
-      </c>
-      <c r="B111" s="11" t="inlineStr">
-        <is>
-          <t>光力科技</t>
-        </is>
-      </c>
-      <c r="C111" s="10" t="inlineStr">
-        <is>
-          <t>半导体/芯片</t>
-        </is>
-      </c>
-      <c r="D111" s="10" t="inlineStr">
+      <c r="A111" s="15" t="inlineStr">
+        <is>
+          <t>300852</t>
+        </is>
+      </c>
+      <c r="B111" s="16" t="inlineStr">
+        <is>
+          <t>四会富仕</t>
+        </is>
+      </c>
+      <c r="C111" s="15" t="inlineStr">
+        <is>
+          <t>算力/通信</t>
+        </is>
+      </c>
+      <c r="D111" s="15" t="inlineStr">
         <is>
           <t>2026-07-01</t>
         </is>
       </c>
-      <c r="E111" s="10" t="inlineStr">
+      <c r="E111" s="15" t="inlineStr">
         <is>
           <t>2026-07-01</t>
         </is>
       </c>
-      <c r="F111" s="10" t="n">
+      <c r="F111" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="G111" s="10" t="inlineStr">
-        <is>
-          <t>强势上攻</t>
-        </is>
-      </c>
-      <c r="H111" s="12" t="n">
-        <v>5.08</v>
-      </c>
-      <c r="I111" s="10" t="n">
-        <v>-23.17</v>
-      </c>
-      <c r="J111" s="10" t="n"/>
-      <c r="K111" s="10" t="inlineStr">
-        <is>
-          <t>正常</t>
-        </is>
-      </c>
-      <c r="L111" s="10" t="inlineStr"/>
-      <c r="M111" s="10" t="inlineStr"/>
+      <c r="G111" s="17" t="inlineStr">
+        <is>
+          <t>强势上攻</t>
+        </is>
+      </c>
+      <c r="H111" s="19" t="n">
+        <v>20</v>
+      </c>
+      <c r="I111" s="15" t="n">
+        <v>-23.44</v>
+      </c>
+      <c r="J111" s="15" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="K111" s="15" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="L111" s="15" t="inlineStr">
+        <is>
+          <t>首日涨幅&gt;20%</t>
+        </is>
+      </c>
+      <c r="M111" s="15" t="inlineStr"/>
     </row>
     <row r="112" ht="26" customHeight="1">
       <c r="A112" s="7" t="inlineStr">
         <is>
-          <t>300655</t>
+          <t>300041</t>
         </is>
       </c>
       <c r="B112" s="8" t="inlineStr">
         <is>
-          <t>晶瑞电材</t>
+          <t>回天新材</t>
         </is>
       </c>
       <c r="C112" s="7" t="inlineStr">
         <is>
-          <t>半导体/芯片</t>
+          <t>算力/通信</t>
         </is>
       </c>
       <c r="D112" s="7" t="inlineStr">
@@ -6212,11 +6200,11 @@
       </c>
       <c r="E112" s="7" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="F112" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G112" s="7" t="inlineStr">
         <is>
@@ -6224,10 +6212,10 @@
         </is>
       </c>
       <c r="H112" s="13" t="n">
-        <v>5.89</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="I112" s="7" t="n">
-        <v>-22.61</v>
+        <v>-23.21</v>
       </c>
       <c r="J112" s="7" t="n"/>
       <c r="K112" s="7" t="inlineStr">
@@ -6241,12 +6229,12 @@
     <row r="113" ht="26" customHeight="1">
       <c r="A113" s="10" t="inlineStr">
         <is>
-          <t>300151</t>
+          <t>300480</t>
         </is>
       </c>
       <c r="B113" s="11" t="inlineStr">
         <is>
-          <t>昌红科技</t>
+          <t>光力科技</t>
         </is>
       </c>
       <c r="C113" s="10" t="inlineStr">
@@ -6256,12 +6244,12 @@
       </c>
       <c r="D113" s="10" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="E113" s="10" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="F113" s="10" t="n">
@@ -6273,17 +6261,15 @@
         </is>
       </c>
       <c r="H113" s="12" t="n">
-        <v>7.18</v>
+        <v>5.08</v>
       </c>
       <c r="I113" s="10" t="n">
-        <v>-22.57</v>
-      </c>
-      <c r="J113" s="10" t="n">
-        <v>0.67</v>
-      </c>
+        <v>-23.17</v>
+      </c>
+      <c r="J113" s="10" t="n"/>
       <c r="K113" s="10" t="inlineStr">
         <is>
-          <t>缩量</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="L113" s="10" t="inlineStr"/>
@@ -6292,12 +6278,12 @@
     <row r="114" ht="26" customHeight="1">
       <c r="A114" s="7" t="inlineStr">
         <is>
-          <t>688661</t>
+          <t>300655</t>
         </is>
       </c>
       <c r="B114" s="8" t="inlineStr">
         <is>
-          <t>和林微纳</t>
+          <t>晶瑞电材</t>
         </is>
       </c>
       <c r="C114" s="7" t="inlineStr">
@@ -6307,12 +6293,12 @@
       </c>
       <c r="D114" s="7" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="E114" s="7" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="F114" s="7" t="n">
@@ -6324,86 +6310,80 @@
         </is>
       </c>
       <c r="H114" s="13" t="n">
-        <v>11.41</v>
+        <v>5.89</v>
       </c>
       <c r="I114" s="7" t="n">
-        <v>-22.31</v>
-      </c>
-      <c r="J114" s="7" t="n">
-        <v>0.74</v>
-      </c>
+        <v>-22.61</v>
+      </c>
+      <c r="J114" s="7" t="n"/>
       <c r="K114" s="7" t="inlineStr">
         <is>
-          <t>缩量</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="L114" s="7" t="inlineStr"/>
       <c r="M114" s="7" t="inlineStr"/>
     </row>
     <row r="115" ht="26" customHeight="1">
-      <c r="A115" s="15" t="inlineStr">
-        <is>
-          <t>688728</t>
-        </is>
-      </c>
-      <c r="B115" s="16" t="inlineStr">
-        <is>
-          <t>格科微</t>
-        </is>
-      </c>
-      <c r="C115" s="15" t="inlineStr">
+      <c r="A115" s="10" t="inlineStr">
+        <is>
+          <t>300151</t>
+        </is>
+      </c>
+      <c r="B115" s="11" t="inlineStr">
+        <is>
+          <t>昌红科技</t>
+        </is>
+      </c>
+      <c r="C115" s="10" t="inlineStr">
         <is>
           <t>半导体/芯片</t>
         </is>
       </c>
-      <c r="D115" s="15" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="E115" s="15" t="inlineStr">
-        <is>
-          <t>2026-07-21</t>
-        </is>
-      </c>
-      <c r="F115" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="G115" s="17" t="inlineStr">
-        <is>
-          <t>强势上攻</t>
-        </is>
-      </c>
-      <c r="H115" s="19" t="n">
-        <v>20.03</v>
-      </c>
-      <c r="I115" s="15" t="n">
-        <v>-22.02</v>
-      </c>
-      <c r="J115" s="15" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="K115" s="15" t="inlineStr">
+      <c r="D115" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="E115" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="F115" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G115" s="10" t="inlineStr">
+        <is>
+          <t>强势上攻</t>
+        </is>
+      </c>
+      <c r="H115" s="12" t="n">
+        <v>7.18</v>
+      </c>
+      <c r="I115" s="10" t="n">
+        <v>-22.57</v>
+      </c>
+      <c r="J115" s="10" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="K115" s="10" t="inlineStr">
         <is>
           <t>缩量</t>
         </is>
       </c>
-      <c r="L115" s="15" t="inlineStr">
-        <is>
-          <t>首日涨幅&gt;20%</t>
-        </is>
-      </c>
-      <c r="M115" s="15" t="inlineStr"/>
+      <c r="L115" s="10" t="inlineStr"/>
+      <c r="M115" s="10" t="inlineStr"/>
     </row>
     <row r="116" ht="26" customHeight="1">
       <c r="A116" s="7" t="inlineStr">
         <is>
-          <t>688380</t>
+          <t>688661</t>
         </is>
       </c>
       <c r="B116" s="8" t="inlineStr">
         <is>
-          <t>中微半导</t>
+          <t>和林微纳</t>
         </is>
       </c>
       <c r="C116" s="7" t="inlineStr">
@@ -6413,12 +6393,12 @@
       </c>
       <c r="D116" s="7" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="E116" s="7" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="F116" s="7" t="n">
@@ -6430,133 +6410,137 @@
         </is>
       </c>
       <c r="H116" s="13" t="n">
-        <v>8.41</v>
+        <v>11.41</v>
       </c>
       <c r="I116" s="7" t="n">
-        <v>-21.87</v>
+        <v>-22.31</v>
       </c>
       <c r="J116" s="7" t="n">
-        <v>0.93</v>
+        <v>0.74</v>
       </c>
       <c r="K116" s="7" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>缩量</t>
         </is>
       </c>
       <c r="L116" s="7" t="inlineStr"/>
       <c r="M116" s="7" t="inlineStr"/>
     </row>
     <row r="117" ht="26" customHeight="1">
-      <c r="A117" s="10" t="inlineStr">
-        <is>
-          <t>000725</t>
-        </is>
-      </c>
-      <c r="B117" s="11" t="inlineStr">
-        <is>
-          <t>京东方A</t>
-        </is>
-      </c>
-      <c r="C117" s="10" t="inlineStr">
+      <c r="A117" s="15" t="inlineStr">
+        <is>
+          <t>688728</t>
+        </is>
+      </c>
+      <c r="B117" s="16" t="inlineStr">
+        <is>
+          <t>格科微</t>
+        </is>
+      </c>
+      <c r="C117" s="15" t="inlineStr">
         <is>
           <t>半导体/芯片</t>
         </is>
       </c>
-      <c r="D117" s="10" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="E117" s="10" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="F117" s="10" t="n">
+      <c r="D117" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="E117" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="F117" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="G117" s="17" t="inlineStr">
+        <is>
+          <t>强势上攻</t>
+        </is>
+      </c>
+      <c r="H117" s="19" t="n">
+        <v>20.03</v>
+      </c>
+      <c r="I117" s="15" t="n">
+        <v>-22.02</v>
+      </c>
+      <c r="J117" s="15" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="K117" s="15" t="inlineStr">
+        <is>
+          <t>缩量</t>
+        </is>
+      </c>
+      <c r="L117" s="15" t="inlineStr">
+        <is>
+          <t>首日涨幅&gt;20%</t>
+        </is>
+      </c>
+      <c r="M117" s="15" t="inlineStr"/>
+    </row>
+    <row r="118" ht="26" customHeight="1">
+      <c r="A118" s="7" t="inlineStr">
+        <is>
+          <t>688380</t>
+        </is>
+      </c>
+      <c r="B118" s="8" t="inlineStr">
+        <is>
+          <t>中微半导</t>
+        </is>
+      </c>
+      <c r="C118" s="7" t="inlineStr">
+        <is>
+          <t>半导体/芯片</t>
+        </is>
+      </c>
+      <c r="D118" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="E118" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="F118" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="G117" s="10" t="inlineStr">
-        <is>
-          <t>强势上攻</t>
-        </is>
-      </c>
-      <c r="H117" s="12" t="n">
-        <v>3.76</v>
-      </c>
-      <c r="I117" s="10" t="n">
-        <v>-21.29</v>
-      </c>
-      <c r="J117" s="10" t="n"/>
-      <c r="K117" s="10" t="inlineStr">
-        <is>
-          <t>正常</t>
-        </is>
-      </c>
-      <c r="L117" s="10" t="inlineStr"/>
-      <c r="M117" s="10" t="inlineStr"/>
-    </row>
-    <row r="118" ht="26" customHeight="1">
-      <c r="A118" s="15" t="inlineStr">
-        <is>
-          <t>300873</t>
-        </is>
-      </c>
-      <c r="B118" s="16" t="inlineStr">
-        <is>
-          <t>海晨股份</t>
-        </is>
-      </c>
-      <c r="C118" s="15" t="inlineStr">
-        <is>
-          <t>机器人</t>
-        </is>
-      </c>
-      <c r="D118" s="15" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="E118" s="15" t="inlineStr">
-        <is>
-          <t>2026-07-03</t>
-        </is>
-      </c>
-      <c r="F118" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="G118" s="17" t="inlineStr">
-        <is>
-          <t>强势上攻</t>
-        </is>
-      </c>
-      <c r="H118" s="19" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="I118" s="15" t="n">
-        <v>-21.05</v>
-      </c>
-      <c r="J118" s="15" t="n"/>
-      <c r="K118" s="15" t="inlineStr">
-        <is>
-          <t>正常</t>
-        </is>
-      </c>
-      <c r="L118" s="15" t="inlineStr">
-        <is>
-          <t>首日涨幅&gt;20%</t>
-        </is>
-      </c>
-      <c r="M118" s="15" t="inlineStr"/>
+      <c r="G118" s="7" t="inlineStr">
+        <is>
+          <t>强势上攻</t>
+        </is>
+      </c>
+      <c r="H118" s="13" t="n">
+        <v>8.41</v>
+      </c>
+      <c r="I118" s="7" t="n">
+        <v>-21.87</v>
+      </c>
+      <c r="J118" s="7" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="K118" s="7" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="L118" s="7" t="inlineStr"/>
+      <c r="M118" s="7" t="inlineStr"/>
     </row>
     <row r="119" ht="26" customHeight="1">
       <c r="A119" s="10" t="inlineStr">
         <is>
-          <t>300416</t>
+          <t>000725</t>
         </is>
       </c>
       <c r="B119" s="11" t="inlineStr">
         <is>
-          <t>苏试试验</t>
+          <t>京东方A</t>
         </is>
       </c>
       <c r="C119" s="10" t="inlineStr">
@@ -6566,12 +6550,12 @@
       </c>
       <c r="D119" s="10" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="E119" s="10" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="F119" s="10" t="n">
@@ -6583,10 +6567,10 @@
         </is>
       </c>
       <c r="H119" s="12" t="n">
-        <v>7.36</v>
+        <v>3.76</v>
       </c>
       <c r="I119" s="10" t="n">
-        <v>-20.82</v>
+        <v>-21.29</v>
       </c>
       <c r="J119" s="10" t="n"/>
       <c r="K119" s="10" t="inlineStr">
@@ -6598,63 +6582,67 @@
       <c r="M119" s="10" t="inlineStr"/>
     </row>
     <row r="120" ht="26" customHeight="1">
-      <c r="A120" s="7" t="inlineStr">
-        <is>
-          <t>300801</t>
-        </is>
-      </c>
-      <c r="B120" s="8" t="inlineStr">
-        <is>
-          <t>泰和科技</t>
-        </is>
-      </c>
-      <c r="C120" s="7" t="inlineStr">
-        <is>
-          <t>半导体/芯片</t>
-        </is>
-      </c>
-      <c r="D120" s="7" t="inlineStr">
+      <c r="A120" s="15" t="inlineStr">
+        <is>
+          <t>300873</t>
+        </is>
+      </c>
+      <c r="B120" s="16" t="inlineStr">
+        <is>
+          <t>海晨股份</t>
+        </is>
+      </c>
+      <c r="C120" s="15" t="inlineStr">
+        <is>
+          <t>机器人</t>
+        </is>
+      </c>
+      <c r="D120" s="15" t="inlineStr">
         <is>
           <t>2026-07-01</t>
         </is>
       </c>
-      <c r="E120" s="7" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="F120" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G120" s="7" t="inlineStr">
-        <is>
-          <t>强势上攻</t>
-        </is>
-      </c>
-      <c r="H120" s="13" t="n">
-        <v>9.75</v>
-      </c>
-      <c r="I120" s="7" t="n">
-        <v>-20.73</v>
-      </c>
-      <c r="J120" s="7" t="n"/>
-      <c r="K120" s="7" t="inlineStr">
-        <is>
-          <t>正常</t>
-        </is>
-      </c>
-      <c r="L120" s="7" t="inlineStr"/>
-      <c r="M120" s="7" t="inlineStr"/>
+      <c r="E120" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="F120" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="G120" s="17" t="inlineStr">
+        <is>
+          <t>强势上攻</t>
+        </is>
+      </c>
+      <c r="H120" s="19" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="I120" s="15" t="n">
+        <v>-21.05</v>
+      </c>
+      <c r="J120" s="15" t="n"/>
+      <c r="K120" s="15" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="L120" s="15" t="inlineStr">
+        <is>
+          <t>首日涨幅&gt;20%</t>
+        </is>
+      </c>
+      <c r="M120" s="15" t="inlineStr"/>
     </row>
     <row r="121" ht="26" customHeight="1">
       <c r="A121" s="10" t="inlineStr">
         <is>
-          <t>688123</t>
+          <t>300416</t>
         </is>
       </c>
       <c r="B121" s="11" t="inlineStr">
         <is>
-          <t>聚辰股份</t>
+          <t>苏试试验</t>
         </is>
       </c>
       <c r="C121" s="10" t="inlineStr">
@@ -6664,12 +6652,12 @@
       </c>
       <c r="D121" s="10" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="E121" s="10" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="F121" s="10" t="n">
@@ -6681,17 +6669,15 @@
         </is>
       </c>
       <c r="H121" s="12" t="n">
-        <v>5.39</v>
+        <v>7.36</v>
       </c>
       <c r="I121" s="10" t="n">
-        <v>-20.32</v>
-      </c>
-      <c r="J121" s="10" t="n">
-        <v>0.67</v>
-      </c>
+        <v>-20.82</v>
+      </c>
+      <c r="J121" s="10" t="n"/>
       <c r="K121" s="10" t="inlineStr">
         <is>
-          <t>缩量</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="L121" s="10" t="inlineStr"/>
@@ -6700,12 +6686,12 @@
     <row r="122" ht="26" customHeight="1">
       <c r="A122" s="7" t="inlineStr">
         <is>
-          <t>003043</t>
+          <t>300801</t>
         </is>
       </c>
       <c r="B122" s="8" t="inlineStr">
         <is>
-          <t>华亚智能</t>
+          <t>泰和科技</t>
         </is>
       </c>
       <c r="C122" s="7" t="inlineStr">
@@ -6732,10 +6718,10 @@
         </is>
       </c>
       <c r="H122" s="13" t="n">
-        <v>6.65</v>
+        <v>9.75</v>
       </c>
       <c r="I122" s="7" t="n">
-        <v>-20.31</v>
+        <v>-20.73</v>
       </c>
       <c r="J122" s="7" t="n"/>
       <c r="K122" s="7" t="inlineStr">
@@ -6749,12 +6735,12 @@
     <row r="123" ht="26" customHeight="1">
       <c r="A123" s="10" t="inlineStr">
         <is>
-          <t>002407</t>
+          <t>688123</t>
         </is>
       </c>
       <c r="B123" s="11" t="inlineStr">
         <is>
-          <t>多氟多</t>
+          <t>聚辰股份</t>
         </is>
       </c>
       <c r="C123" s="10" t="inlineStr">
@@ -6764,12 +6750,12 @@
       </c>
       <c r="D123" s="10" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="E123" s="10" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="F123" s="10" t="n">
@@ -6781,15 +6767,17 @@
         </is>
       </c>
       <c r="H123" s="12" t="n">
-        <v>9.99</v>
+        <v>5.39</v>
       </c>
       <c r="I123" s="10" t="n">
-        <v>-20.23</v>
-      </c>
-      <c r="J123" s="10" t="n"/>
+        <v>-20.32</v>
+      </c>
+      <c r="J123" s="10" t="n">
+        <v>0.67</v>
+      </c>
       <c r="K123" s="10" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>缩量</t>
         </is>
       </c>
       <c r="L123" s="10" t="inlineStr"/>
@@ -6798,17 +6786,17 @@
     <row r="124" ht="26" customHeight="1">
       <c r="A124" s="7" t="inlineStr">
         <is>
-          <t>002635</t>
+          <t>003043</t>
         </is>
       </c>
       <c r="B124" s="8" t="inlineStr">
         <is>
-          <t>安洁科技</t>
+          <t>华亚智能</t>
         </is>
       </c>
       <c r="C124" s="7" t="inlineStr">
         <is>
-          <t>算力/通信</t>
+          <t>半导体/芯片</t>
         </is>
       </c>
       <c r="D124" s="7" t="inlineStr">
@@ -6818,11 +6806,11 @@
       </c>
       <c r="E124" s="7" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="F124" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G124" s="7" t="inlineStr">
         <is>
@@ -6830,10 +6818,10 @@
         </is>
       </c>
       <c r="H124" s="13" t="n">
-        <v>9.98</v>
+        <v>6.65</v>
       </c>
       <c r="I124" s="7" t="n">
-        <v>-19.12</v>
+        <v>-20.31</v>
       </c>
       <c r="J124" s="7" t="n"/>
       <c r="K124" s="7" t="inlineStr">
@@ -6847,12 +6835,12 @@
     <row r="125" ht="26" customHeight="1">
       <c r="A125" s="10" t="inlineStr">
         <is>
-          <t>300689</t>
+          <t>002407</t>
         </is>
       </c>
       <c r="B125" s="11" t="inlineStr">
         <is>
-          <t>澄天伟业</t>
+          <t>多氟多</t>
         </is>
       </c>
       <c r="C125" s="10" t="inlineStr">
@@ -6862,12 +6850,12 @@
       </c>
       <c r="D125" s="10" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="E125" s="10" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="F125" s="10" t="n">
@@ -6879,14 +6867,12 @@
         </is>
       </c>
       <c r="H125" s="12" t="n">
-        <v>5.7</v>
+        <v>9.99</v>
       </c>
       <c r="I125" s="10" t="n">
-        <v>-18.82</v>
-      </c>
-      <c r="J125" s="10" t="n">
-        <v>0.82</v>
-      </c>
+        <v>-20.23</v>
+      </c>
+      <c r="J125" s="10" t="n"/>
       <c r="K125" s="10" t="inlineStr">
         <is>
           <t>正常</t>
@@ -6896,237 +6882,239 @@
       <c r="M125" s="10" t="inlineStr"/>
     </row>
     <row r="126" ht="26" customHeight="1">
-      <c r="A126" s="15" t="inlineStr">
+      <c r="A126" s="7" t="inlineStr">
+        <is>
+          <t>002635</t>
+        </is>
+      </c>
+      <c r="B126" s="8" t="inlineStr">
+        <is>
+          <t>安洁科技</t>
+        </is>
+      </c>
+      <c r="C126" s="7" t="inlineStr">
+        <is>
+          <t>算力/通信</t>
+        </is>
+      </c>
+      <c r="D126" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="E126" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="F126" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G126" s="7" t="inlineStr">
+        <is>
+          <t>强势上攻</t>
+        </is>
+      </c>
+      <c r="H126" s="13" t="n">
+        <v>9.98</v>
+      </c>
+      <c r="I126" s="7" t="n">
+        <v>-19.12</v>
+      </c>
+      <c r="J126" s="7" t="n"/>
+      <c r="K126" s="7" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="L126" s="7" t="inlineStr"/>
+      <c r="M126" s="7" t="inlineStr"/>
+    </row>
+    <row r="127" ht="26" customHeight="1">
+      <c r="A127" s="10" t="inlineStr">
+        <is>
+          <t>300689</t>
+        </is>
+      </c>
+      <c r="B127" s="11" t="inlineStr">
+        <is>
+          <t>澄天伟业</t>
+        </is>
+      </c>
+      <c r="C127" s="10" t="inlineStr">
+        <is>
+          <t>半导体/芯片</t>
+        </is>
+      </c>
+      <c r="D127" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="E127" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="F127" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G127" s="10" t="inlineStr">
+        <is>
+          <t>强势上攻</t>
+        </is>
+      </c>
+      <c r="H127" s="12" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="I127" s="10" t="n">
+        <v>-18.82</v>
+      </c>
+      <c r="J127" s="10" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="K127" s="10" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="L127" s="10" t="inlineStr"/>
+      <c r="M127" s="10" t="inlineStr"/>
+    </row>
+    <row r="128" ht="26" customHeight="1">
+      <c r="A128" s="15" t="inlineStr">
         <is>
           <t>688689</t>
         </is>
       </c>
-      <c r="B126" s="16" t="inlineStr">
+      <c r="B128" s="16" t="inlineStr">
         <is>
           <t>银河微电</t>
         </is>
       </c>
-      <c r="C126" s="15" t="inlineStr">
+      <c r="C128" s="15" t="inlineStr">
         <is>
           <t>半导体/芯片</t>
         </is>
       </c>
-      <c r="D126" s="15" t="inlineStr">
+      <c r="D128" s="15" t="inlineStr">
         <is>
           <t>2026-07-01</t>
         </is>
       </c>
-      <c r="E126" s="15" t="inlineStr">
+      <c r="E128" s="15" t="inlineStr">
         <is>
           <t>2026-07-06</t>
         </is>
       </c>
-      <c r="F126" s="15" t="n">
+      <c r="F128" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="G126" s="17" t="inlineStr">
-        <is>
-          <t>强势上攻</t>
-        </is>
-      </c>
-      <c r="H126" s="19" t="n">
+      <c r="G128" s="17" t="inlineStr">
+        <is>
+          <t>强势上攻</t>
+        </is>
+      </c>
+      <c r="H128" s="19" t="n">
         <v>18.7</v>
       </c>
-      <c r="I126" s="15" t="n">
+      <c r="I128" s="15" t="n">
         <v>-18.54</v>
       </c>
-      <c r="J126" s="15" t="n">
+      <c r="J128" s="15" t="n">
         <v>0.62</v>
       </c>
-      <c r="K126" s="15" t="inlineStr">
+      <c r="K128" s="15" t="inlineStr">
         <is>
           <t>缩量</t>
         </is>
       </c>
-      <c r="L126" s="15" t="inlineStr">
+      <c r="L128" s="15" t="inlineStr">
         <is>
           <t>首日涨幅&gt;20%</t>
         </is>
       </c>
-      <c r="M126" s="15" t="inlineStr"/>
-    </row>
-    <row r="127" ht="26" customHeight="1">
-      <c r="A127" s="15" t="inlineStr">
+      <c r="M128" s="15" t="inlineStr"/>
+    </row>
+    <row r="129" ht="26" customHeight="1">
+      <c r="A129" s="15" t="inlineStr">
         <is>
           <t>688721</t>
         </is>
       </c>
-      <c r="B127" s="16" t="inlineStr">
+      <c r="B129" s="16" t="inlineStr">
         <is>
           <t>龙图光罩</t>
         </is>
       </c>
-      <c r="C127" s="15" t="inlineStr">
+      <c r="C129" s="15" t="inlineStr">
         <is>
           <t>半导体/芯片</t>
         </is>
       </c>
-      <c r="D127" s="15" t="inlineStr">
+      <c r="D129" s="15" t="inlineStr">
         <is>
           <t>2026-07-01</t>
         </is>
       </c>
-      <c r="E127" s="15" t="inlineStr">
+      <c r="E129" s="15" t="inlineStr">
         <is>
           <t>2026-07-01</t>
         </is>
       </c>
-      <c r="F127" s="15" t="n">
+      <c r="F129" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="G127" s="17" t="inlineStr">
-        <is>
-          <t>强势上攻</t>
-        </is>
-      </c>
-      <c r="H127" s="19" t="n">
+      <c r="G129" s="17" t="inlineStr">
+        <is>
+          <t>强势上攻</t>
+        </is>
+      </c>
+      <c r="H129" s="19" t="n">
         <v>18.6</v>
       </c>
-      <c r="I127" s="15" t="n">
+      <c r="I129" s="15" t="n">
         <v>-18.39</v>
       </c>
-      <c r="J127" s="15" t="n">
+      <c r="J129" s="15" t="n">
         <v>1.01</v>
       </c>
-      <c r="K127" s="15" t="inlineStr">
-        <is>
-          <t>正常</t>
-        </is>
-      </c>
-      <c r="L127" s="15" t="inlineStr">
+      <c r="K129" s="15" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="L129" s="15" t="inlineStr">
         <is>
           <t>首日涨幅&gt;19%</t>
         </is>
       </c>
-      <c r="M127" s="15" t="inlineStr"/>
-    </row>
-    <row r="128" ht="26" customHeight="1">
-      <c r="A128" s="7" t="inlineStr">
-        <is>
-          <t>002600</t>
-        </is>
-      </c>
-      <c r="B128" s="8" t="inlineStr">
-        <is>
-          <t>领益智造</t>
-        </is>
-      </c>
-      <c r="C128" s="7" t="inlineStr">
-        <is>
-          <t>算力/通信</t>
-        </is>
-      </c>
-      <c r="D128" s="7" t="inlineStr">
-        <is>
-          <t>2026-07-03</t>
-        </is>
-      </c>
-      <c r="E128" s="7" t="inlineStr">
-        <is>
-          <t>2026-07-03</t>
-        </is>
-      </c>
-      <c r="F128" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G128" s="7" t="inlineStr">
-        <is>
-          <t>强势上攻</t>
-        </is>
-      </c>
-      <c r="H128" s="13" t="n">
-        <v>4.89</v>
-      </c>
-      <c r="I128" s="7" t="n">
-        <v>-18.14</v>
-      </c>
-      <c r="J128" s="7" t="n"/>
-      <c r="K128" s="7" t="inlineStr">
-        <is>
-          <t>正常</t>
-        </is>
-      </c>
-      <c r="L128" s="7" t="inlineStr"/>
-      <c r="M128" s="7" t="inlineStr"/>
-    </row>
-    <row r="129" ht="26" customHeight="1">
-      <c r="A129" s="10" t="inlineStr">
-        <is>
-          <t>688392</t>
-        </is>
-      </c>
-      <c r="B129" s="11" t="inlineStr">
-        <is>
-          <t>骄成超声</t>
-        </is>
-      </c>
-      <c r="C129" s="10" t="inlineStr">
-        <is>
-          <t>算力/通信</t>
-        </is>
-      </c>
-      <c r="D129" s="10" t="inlineStr">
-        <is>
-          <t>2026-07-07</t>
-        </is>
-      </c>
-      <c r="E129" s="10" t="inlineStr">
-        <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="F129" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="G129" s="10" t="inlineStr">
-        <is>
-          <t>强势上攻</t>
-        </is>
-      </c>
-      <c r="H129" s="12" t="n">
-        <v>8.06</v>
-      </c>
-      <c r="I129" s="10" t="n">
-        <v>-17.67</v>
-      </c>
-      <c r="J129" s="10" t="n"/>
-      <c r="K129" s="10" t="inlineStr">
-        <is>
-          <t>正常</t>
-        </is>
-      </c>
-      <c r="L129" s="10" t="inlineStr"/>
-      <c r="M129" s="10" t="inlineStr"/>
+      <c r="M129" s="15" t="inlineStr"/>
     </row>
     <row r="130" ht="26" customHeight="1">
       <c r="A130" s="7" t="inlineStr">
         <is>
-          <t>603650</t>
+          <t>002600</t>
         </is>
       </c>
       <c r="B130" s="8" t="inlineStr">
         <is>
-          <t>彤程新材</t>
+          <t>领益智造</t>
         </is>
       </c>
       <c r="C130" s="7" t="inlineStr">
         <is>
-          <t>半导体/芯片</t>
+          <t>算力/通信</t>
         </is>
       </c>
       <c r="D130" s="7" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="E130" s="7" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="F130" s="7" t="n">
@@ -7138,14 +7126,12 @@
         </is>
       </c>
       <c r="H130" s="13" t="n">
-        <v>5.64</v>
+        <v>4.89</v>
       </c>
       <c r="I130" s="7" t="n">
-        <v>-17.61</v>
-      </c>
-      <c r="J130" s="7" t="n">
-        <v>0.84</v>
-      </c>
+        <v>-18.14</v>
+      </c>
+      <c r="J130" s="7" t="n"/>
       <c r="K130" s="7" t="inlineStr">
         <is>
           <t>正常</t>
@@ -7157,31 +7143,31 @@
     <row r="131" ht="26" customHeight="1">
       <c r="A131" s="10" t="inlineStr">
         <is>
-          <t>600520</t>
+          <t>688392</t>
         </is>
       </c>
       <c r="B131" s="11" t="inlineStr">
         <is>
-          <t>三佳科技</t>
+          <t>骄成超声</t>
         </is>
       </c>
       <c r="C131" s="10" t="inlineStr">
         <is>
-          <t>半导体/芯片</t>
+          <t>算力/通信</t>
         </is>
       </c>
       <c r="D131" s="10" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="E131" s="10" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="F131" s="10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G131" s="10" t="inlineStr">
         <is>
@@ -7189,10 +7175,10 @@
         </is>
       </c>
       <c r="H131" s="12" t="n">
-        <v>6.23</v>
+        <v>8.06</v>
       </c>
       <c r="I131" s="10" t="n">
-        <v>-17.61</v>
+        <v>-17.67</v>
       </c>
       <c r="J131" s="10" t="n"/>
       <c r="K131" s="10" t="inlineStr">
@@ -7206,12 +7192,12 @@
     <row r="132" ht="26" customHeight="1">
       <c r="A132" s="7" t="inlineStr">
         <is>
-          <t>688362</t>
+          <t>603650</t>
         </is>
       </c>
       <c r="B132" s="8" t="inlineStr">
         <is>
-          <t>甬矽电子</t>
+          <t>彤程新材</t>
         </is>
       </c>
       <c r="C132" s="7" t="inlineStr">
@@ -7221,16 +7207,16 @@
       </c>
       <c r="D132" s="7" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="E132" s="7" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="F132" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G132" s="7" t="inlineStr">
         <is>
@@ -7238,13 +7224,13 @@
         </is>
       </c>
       <c r="H132" s="13" t="n">
-        <v>17.14</v>
+        <v>5.64</v>
       </c>
       <c r="I132" s="7" t="n">
-        <v>-17.46</v>
+        <v>-17.61</v>
       </c>
       <c r="J132" s="7" t="n">
-        <v>1</v>
+        <v>0.84</v>
       </c>
       <c r="K132" s="7" t="inlineStr">
         <is>
@@ -7257,31 +7243,31 @@
     <row r="133" ht="26" customHeight="1">
       <c r="A133" s="10" t="inlineStr">
         <is>
-          <t>300720</t>
+          <t>600520</t>
         </is>
       </c>
       <c r="B133" s="11" t="inlineStr">
         <is>
-          <t>海川智能</t>
+          <t>三佳科技</t>
         </is>
       </c>
       <c r="C133" s="10" t="inlineStr">
         <is>
-          <t>机器人</t>
+          <t>半导体/芯片</t>
         </is>
       </c>
       <c r="D133" s="10" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="E133" s="10" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="F133" s="10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G133" s="10" t="inlineStr">
         <is>
@@ -7289,10 +7275,10 @@
         </is>
       </c>
       <c r="H133" s="12" t="n">
-        <v>4.93</v>
+        <v>6.23</v>
       </c>
       <c r="I133" s="10" t="n">
-        <v>-17.29</v>
+        <v>-17.61</v>
       </c>
       <c r="J133" s="10" t="n"/>
       <c r="K133" s="10" t="inlineStr">
@@ -7306,12 +7292,12 @@
     <row r="134" ht="26" customHeight="1">
       <c r="A134" s="7" t="inlineStr">
         <is>
-          <t>300671</t>
+          <t>688362</t>
         </is>
       </c>
       <c r="B134" s="8" t="inlineStr">
         <is>
-          <t>富满微</t>
+          <t>甬矽电子</t>
         </is>
       </c>
       <c r="C134" s="7" t="inlineStr">
@@ -7321,16 +7307,16 @@
       </c>
       <c r="D134" s="7" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="E134" s="7" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="F134" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G134" s="7" t="inlineStr">
         <is>
@@ -7338,12 +7324,14 @@
         </is>
       </c>
       <c r="H134" s="13" t="n">
-        <v>8.449999999999999</v>
+        <v>17.14</v>
       </c>
       <c r="I134" s="7" t="n">
-        <v>-17.2</v>
-      </c>
-      <c r="J134" s="7" t="n"/>
+        <v>-17.46</v>
+      </c>
+      <c r="J134" s="7" t="n">
+        <v>1</v>
+      </c>
       <c r="K134" s="7" t="inlineStr">
         <is>
           <t>正常</t>
@@ -7355,17 +7343,17 @@
     <row r="135" ht="26" customHeight="1">
       <c r="A135" s="10" t="inlineStr">
         <is>
-          <t>000733</t>
+          <t>300720</t>
         </is>
       </c>
       <c r="B135" s="11" t="inlineStr">
         <is>
-          <t>振华科技</t>
+          <t>海川智能</t>
         </is>
       </c>
       <c r="C135" s="10" t="inlineStr">
         <is>
-          <t>半导体/芯片</t>
+          <t>机器人</t>
         </is>
       </c>
       <c r="D135" s="10" t="inlineStr">
@@ -7375,11 +7363,11 @@
       </c>
       <c r="E135" s="10" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="F135" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G135" s="10" t="inlineStr">
         <is>
@@ -7387,10 +7375,10 @@
         </is>
       </c>
       <c r="H135" s="12" t="n">
-        <v>9.99</v>
+        <v>4.93</v>
       </c>
       <c r="I135" s="10" t="n">
-        <v>-16.76</v>
+        <v>-17.29</v>
       </c>
       <c r="J135" s="10" t="n"/>
       <c r="K135" s="10" t="inlineStr">
@@ -7404,31 +7392,31 @@
     <row r="136" ht="26" customHeight="1">
       <c r="A136" s="7" t="inlineStr">
         <is>
-          <t>300745</t>
+          <t>300671</t>
         </is>
       </c>
       <c r="B136" s="8" t="inlineStr">
         <is>
-          <t>欣锐科技</t>
+          <t>富满微</t>
         </is>
       </c>
       <c r="C136" s="7" t="inlineStr">
         <is>
-          <t>机器人</t>
+          <t>半导体/芯片</t>
         </is>
       </c>
       <c r="D136" s="7" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="E136" s="7" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="F136" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G136" s="7" t="inlineStr">
         <is>
@@ -7436,10 +7424,10 @@
         </is>
       </c>
       <c r="H136" s="13" t="n">
-        <v>12.72</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="I136" s="7" t="n">
-        <v>-16.52</v>
+        <v>-17.2</v>
       </c>
       <c r="J136" s="7" t="n"/>
       <c r="K136" s="7" t="inlineStr">
@@ -7453,12 +7441,12 @@
     <row r="137" ht="26" customHeight="1">
       <c r="A137" s="10" t="inlineStr">
         <is>
-          <t>300661</t>
+          <t>000733</t>
         </is>
       </c>
       <c r="B137" s="11" t="inlineStr">
         <is>
-          <t>圣邦股份</t>
+          <t>振华科技</t>
         </is>
       </c>
       <c r="C137" s="10" t="inlineStr">
@@ -7468,12 +7456,12 @@
       </c>
       <c r="D137" s="10" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="E137" s="10" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="F137" s="10" t="n">
@@ -7485,10 +7473,10 @@
         </is>
       </c>
       <c r="H137" s="12" t="n">
-        <v>3.49</v>
+        <v>9.99</v>
       </c>
       <c r="I137" s="10" t="n">
-        <v>-16.45</v>
+        <v>-16.76</v>
       </c>
       <c r="J137" s="10" t="n"/>
       <c r="K137" s="10" t="inlineStr">
@@ -7502,27 +7490,27 @@
     <row r="138" ht="26" customHeight="1">
       <c r="A138" s="7" t="inlineStr">
         <is>
-          <t>000551</t>
+          <t>300745</t>
         </is>
       </c>
       <c r="B138" s="8" t="inlineStr">
         <is>
-          <t>创元科技</t>
+          <t>欣锐科技</t>
         </is>
       </c>
       <c r="C138" s="7" t="inlineStr">
         <is>
-          <t>半导体/芯片</t>
+          <t>机器人</t>
         </is>
       </c>
       <c r="D138" s="7" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="E138" s="7" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="F138" s="7" t="n">
@@ -7534,17 +7522,15 @@
         </is>
       </c>
       <c r="H138" s="13" t="n">
-        <v>4.06</v>
+        <v>12.72</v>
       </c>
       <c r="I138" s="7" t="n">
-        <v>-16.3</v>
-      </c>
-      <c r="J138" s="7" t="n">
-        <v>1.21</v>
-      </c>
+        <v>-16.52</v>
+      </c>
+      <c r="J138" s="7" t="n"/>
       <c r="K138" s="7" t="inlineStr">
         <is>
-          <t>放量</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="L138" s="7" t="inlineStr"/>
@@ -7553,12 +7539,12 @@
     <row r="139" ht="26" customHeight="1">
       <c r="A139" s="10" t="inlineStr">
         <is>
-          <t>300540</t>
+          <t>300661</t>
         </is>
       </c>
       <c r="B139" s="11" t="inlineStr">
         <is>
-          <t>蜀道装备</t>
+          <t>圣邦股份</t>
         </is>
       </c>
       <c r="C139" s="10" t="inlineStr">
@@ -7568,16 +7554,16 @@
       </c>
       <c r="D139" s="10" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="E139" s="10" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="F139" s="10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G139" s="10" t="inlineStr">
         <is>
@@ -7585,10 +7571,10 @@
         </is>
       </c>
       <c r="H139" s="12" t="n">
-        <v>6.82</v>
+        <v>3.49</v>
       </c>
       <c r="I139" s="10" t="n">
-        <v>-15.45</v>
+        <v>-16.45</v>
       </c>
       <c r="J139" s="10" t="n"/>
       <c r="K139" s="10" t="inlineStr">
@@ -7600,74 +7586,70 @@
       <c r="M139" s="10" t="inlineStr"/>
     </row>
     <row r="140" ht="26" customHeight="1">
-      <c r="A140" s="15" t="inlineStr">
-        <is>
-          <t>300607</t>
-        </is>
-      </c>
-      <c r="B140" s="16" t="inlineStr">
-        <is>
-          <t>拓斯达</t>
-        </is>
-      </c>
-      <c r="C140" s="15" t="inlineStr">
-        <is>
-          <t>机器人</t>
-        </is>
-      </c>
-      <c r="D140" s="15" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="E140" s="15" t="inlineStr">
+      <c r="A140" s="7" t="inlineStr">
+        <is>
+          <t>000551</t>
+        </is>
+      </c>
+      <c r="B140" s="8" t="inlineStr">
+        <is>
+          <t>创元科技</t>
+        </is>
+      </c>
+      <c r="C140" s="7" t="inlineStr">
+        <is>
+          <t>半导体/芯片</t>
+        </is>
+      </c>
+      <c r="D140" s="7" t="inlineStr">
         <is>
           <t>2026-07-03</t>
         </is>
       </c>
-      <c r="F140" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="G140" s="17" t="inlineStr">
-        <is>
-          <t>强势上攻</t>
-        </is>
-      </c>
-      <c r="H140" s="19" t="n">
-        <v>13.55</v>
-      </c>
-      <c r="I140" s="15" t="n">
-        <v>-15.4</v>
-      </c>
-      <c r="J140" s="15" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="K140" s="15" t="inlineStr">
-        <is>
-          <t>缩量</t>
-        </is>
-      </c>
-      <c r="L140" s="15" t="inlineStr">
-        <is>
-          <t>首日涨幅&gt;20%</t>
-        </is>
-      </c>
-      <c r="M140" s="15" t="inlineStr"/>
+      <c r="E140" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="F140" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G140" s="7" t="inlineStr">
+        <is>
+          <t>强势上攻</t>
+        </is>
+      </c>
+      <c r="H140" s="13" t="n">
+        <v>4.06</v>
+      </c>
+      <c r="I140" s="7" t="n">
+        <v>-16.3</v>
+      </c>
+      <c r="J140" s="7" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="K140" s="7" t="inlineStr">
+        <is>
+          <t>放量</t>
+        </is>
+      </c>
+      <c r="L140" s="7" t="inlineStr"/>
+      <c r="M140" s="7" t="inlineStr"/>
     </row>
     <row r="141" ht="26" customHeight="1">
       <c r="A141" s="10" t="inlineStr">
         <is>
-          <t>688020</t>
+          <t>300540</t>
         </is>
       </c>
       <c r="B141" s="11" t="inlineStr">
         <is>
-          <t>方邦股份</t>
+          <t>蜀道装备</t>
         </is>
       </c>
       <c r="C141" s="10" t="inlineStr">
         <is>
-          <t>算力/通信</t>
+          <t>半导体/芯片</t>
         </is>
       </c>
       <c r="D141" s="10" t="inlineStr">
@@ -7677,11 +7659,11 @@
       </c>
       <c r="E141" s="10" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="F141" s="10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G141" s="10" t="inlineStr">
         <is>
@@ -7689,14 +7671,12 @@
         </is>
       </c>
       <c r="H141" s="12" t="n">
-        <v>8.210000000000001</v>
+        <v>6.82</v>
       </c>
       <c r="I141" s="10" t="n">
-        <v>-15.35</v>
-      </c>
-      <c r="J141" s="10" t="n">
-        <v>0.85</v>
-      </c>
+        <v>-15.45</v>
+      </c>
+      <c r="J141" s="10" t="n"/>
       <c r="K141" s="10" t="inlineStr">
         <is>
           <t>正常</t>
@@ -7706,125 +7686,125 @@
       <c r="M141" s="10" t="inlineStr"/>
     </row>
     <row r="142" ht="26" customHeight="1">
-      <c r="A142" s="7" t="inlineStr">
-        <is>
-          <t>600360</t>
-        </is>
-      </c>
-      <c r="B142" s="8" t="inlineStr">
-        <is>
-          <t>华微电子</t>
-        </is>
-      </c>
-      <c r="C142" s="7" t="inlineStr">
-        <is>
-          <t>半导体/芯片</t>
-        </is>
-      </c>
-      <c r="D142" s="7" t="inlineStr">
+      <c r="A142" s="15" t="inlineStr">
+        <is>
+          <t>300607</t>
+        </is>
+      </c>
+      <c r="B142" s="16" t="inlineStr">
+        <is>
+          <t>拓斯达</t>
+        </is>
+      </c>
+      <c r="C142" s="15" t="inlineStr">
+        <is>
+          <t>机器人</t>
+        </is>
+      </c>
+      <c r="D142" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="E142" s="15" t="inlineStr">
         <is>
           <t>2026-07-03</t>
         </is>
       </c>
-      <c r="E142" s="7" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="F142" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="G142" s="7" t="inlineStr">
-        <is>
-          <t>强势上攻</t>
-        </is>
-      </c>
-      <c r="H142" s="13" t="n">
-        <v>5</v>
-      </c>
-      <c r="I142" s="7" t="n">
-        <v>-14.12</v>
-      </c>
-      <c r="J142" s="7" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="K142" s="7" t="inlineStr">
-        <is>
-          <t>正常</t>
-        </is>
-      </c>
-      <c r="L142" s="7" t="inlineStr"/>
-      <c r="M142" s="7" t="inlineStr"/>
+      <c r="F142" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="G142" s="17" t="inlineStr">
+        <is>
+          <t>强势上攻</t>
+        </is>
+      </c>
+      <c r="H142" s="19" t="n">
+        <v>13.55</v>
+      </c>
+      <c r="I142" s="15" t="n">
+        <v>-15.4</v>
+      </c>
+      <c r="J142" s="15" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="K142" s="15" t="inlineStr">
+        <is>
+          <t>缩量</t>
+        </is>
+      </c>
+      <c r="L142" s="15" t="inlineStr">
+        <is>
+          <t>首日涨幅&gt;20%</t>
+        </is>
+      </c>
+      <c r="M142" s="15" t="inlineStr"/>
     </row>
     <row r="143" ht="26" customHeight="1">
-      <c r="A143" s="15" t="inlineStr">
-        <is>
-          <t>688571</t>
-        </is>
-      </c>
-      <c r="B143" s="16" t="inlineStr">
-        <is>
-          <t>杭华股份</t>
-        </is>
-      </c>
-      <c r="C143" s="15" t="inlineStr">
-        <is>
-          <t>半导体/芯片</t>
-        </is>
-      </c>
-      <c r="D143" s="15" t="inlineStr">
+      <c r="A143" s="10" t="inlineStr">
+        <is>
+          <t>688020</t>
+        </is>
+      </c>
+      <c r="B143" s="11" t="inlineStr">
+        <is>
+          <t>方邦股份</t>
+        </is>
+      </c>
+      <c r="C143" s="10" t="inlineStr">
+        <is>
+          <t>算力/通信</t>
+        </is>
+      </c>
+      <c r="D143" s="10" t="inlineStr">
         <is>
           <t>2026-07-01</t>
         </is>
       </c>
-      <c r="E143" s="15" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="F143" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="G143" s="17" t="inlineStr">
-        <is>
-          <t>强势上攻</t>
-        </is>
-      </c>
-      <c r="H143" s="19" t="n">
-        <v>5.33</v>
-      </c>
-      <c r="I143" s="15" t="n">
-        <v>-14.06</v>
-      </c>
-      <c r="J143" s="15" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="K143" s="15" t="inlineStr">
-        <is>
-          <t>正常</t>
-        </is>
-      </c>
-      <c r="L143" s="15" t="inlineStr">
-        <is>
-          <t>首日涨幅&gt;20%</t>
-        </is>
-      </c>
-      <c r="M143" s="15" t="inlineStr"/>
+      <c r="E143" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="F143" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G143" s="10" t="inlineStr">
+        <is>
+          <t>强势上攻</t>
+        </is>
+      </c>
+      <c r="H143" s="12" t="n">
+        <v>8.210000000000001</v>
+      </c>
+      <c r="I143" s="10" t="n">
+        <v>-15.35</v>
+      </c>
+      <c r="J143" s="10" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="K143" s="10" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="L143" s="10" t="inlineStr"/>
+      <c r="M143" s="10" t="inlineStr"/>
     </row>
     <row r="144" ht="26" customHeight="1">
       <c r="A144" s="7" t="inlineStr">
         <is>
-          <t>301067</t>
+          <t>600360</t>
         </is>
       </c>
       <c r="B144" s="8" t="inlineStr">
         <is>
-          <t>显盈科技</t>
+          <t>华微电子</t>
         </is>
       </c>
       <c r="C144" s="7" t="inlineStr">
         <is>
-          <t>算力/通信</t>
+          <t>半导体/芯片</t>
         </is>
       </c>
       <c r="D144" s="7" t="inlineStr">
@@ -7834,11 +7814,11 @@
       </c>
       <c r="E144" s="7" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="F144" s="7" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G144" s="7" t="inlineStr">
         <is>
@@ -7846,85 +7826,91 @@
         </is>
       </c>
       <c r="H144" s="13" t="n">
-        <v>6.93</v>
+        <v>5</v>
       </c>
       <c r="I144" s="7" t="n">
-        <v>-13.99</v>
+        <v>-14.12</v>
       </c>
       <c r="J144" s="7" t="n">
-        <v>0.42</v>
+        <v>1.05</v>
       </c>
       <c r="K144" s="7" t="inlineStr">
         <is>
-          <t>缩量</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="L144" s="7" t="inlineStr"/>
       <c r="M144" s="7" t="inlineStr"/>
     </row>
     <row r="145" ht="26" customHeight="1">
-      <c r="A145" s="10" t="inlineStr">
-        <is>
-          <t>603269</t>
-        </is>
-      </c>
-      <c r="B145" s="11" t="inlineStr">
-        <is>
-          <t>海鸥股份</t>
-        </is>
-      </c>
-      <c r="C145" s="10" t="inlineStr">
-        <is>
-          <t>算力/通信</t>
-        </is>
-      </c>
-      <c r="D145" s="10" t="inlineStr">
-        <is>
-          <t>2026-07-07</t>
-        </is>
-      </c>
-      <c r="E145" s="10" t="inlineStr">
-        <is>
-          <t>2026-07-07</t>
-        </is>
-      </c>
-      <c r="F145" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="G145" s="10" t="inlineStr">
-        <is>
-          <t>强势上攻</t>
-        </is>
-      </c>
-      <c r="H145" s="12" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="I145" s="10" t="n">
-        <v>-13.78</v>
-      </c>
-      <c r="J145" s="10" t="n"/>
-      <c r="K145" s="10" t="inlineStr">
-        <is>
-          <t>正常</t>
-        </is>
-      </c>
-      <c r="L145" s="10" t="inlineStr"/>
-      <c r="M145" s="10" t="inlineStr"/>
+      <c r="A145" s="15" t="inlineStr">
+        <is>
+          <t>688571</t>
+        </is>
+      </c>
+      <c r="B145" s="16" t="inlineStr">
+        <is>
+          <t>杭华股份</t>
+        </is>
+      </c>
+      <c r="C145" s="15" t="inlineStr">
+        <is>
+          <t>半导体/芯片</t>
+        </is>
+      </c>
+      <c r="D145" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="E145" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="F145" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="G145" s="17" t="inlineStr">
+        <is>
+          <t>强势上攻</t>
+        </is>
+      </c>
+      <c r="H145" s="19" t="n">
+        <v>5.33</v>
+      </c>
+      <c r="I145" s="15" t="n">
+        <v>-14.06</v>
+      </c>
+      <c r="J145" s="15" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="K145" s="15" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="L145" s="15" t="inlineStr">
+        <is>
+          <t>首日涨幅&gt;20%</t>
+        </is>
+      </c>
+      <c r="M145" s="15" t="inlineStr"/>
     </row>
     <row r="146" ht="26" customHeight="1">
       <c r="A146" s="7" t="inlineStr">
         <is>
-          <t>603662</t>
+          <t>301067</t>
         </is>
       </c>
       <c r="B146" s="8" t="inlineStr">
         <is>
-          <t>柯力传感</t>
+          <t>显盈科技</t>
         </is>
       </c>
       <c r="C146" s="7" t="inlineStr">
         <is>
-          <t>机器人</t>
+          <t>算力/通信</t>
         </is>
       </c>
       <c r="D146" s="7" t="inlineStr">
@@ -7946,13 +7932,13 @@
         </is>
       </c>
       <c r="H146" s="13" t="n">
-        <v>8.369999999999999</v>
+        <v>6.93</v>
       </c>
       <c r="I146" s="7" t="n">
-        <v>-13.76</v>
+        <v>-13.99</v>
       </c>
       <c r="J146" s="7" t="n">
-        <v>0.53</v>
+        <v>0.42</v>
       </c>
       <c r="K146" s="7" t="inlineStr">
         <is>
@@ -7965,27 +7951,27 @@
     <row r="147" ht="26" customHeight="1">
       <c r="A147" s="10" t="inlineStr">
         <is>
-          <t>001287</t>
+          <t>603269</t>
         </is>
       </c>
       <c r="B147" s="11" t="inlineStr">
         <is>
-          <t>中电港</t>
+          <t>海鸥股份</t>
         </is>
       </c>
       <c r="C147" s="10" t="inlineStr">
         <is>
-          <t>半导体/芯片</t>
+          <t>算力/通信</t>
         </is>
       </c>
       <c r="D147" s="10" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="E147" s="10" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="F147" s="10" t="n">
@@ -7997,10 +7983,10 @@
         </is>
       </c>
       <c r="H147" s="12" t="n">
-        <v>10</v>
+        <v>3.54</v>
       </c>
       <c r="I147" s="10" t="n">
-        <v>-13.48</v>
+        <v>-13.78</v>
       </c>
       <c r="J147" s="10" t="n"/>
       <c r="K147" s="10" t="inlineStr">
@@ -8014,12 +8000,12 @@
     <row r="148" ht="26" customHeight="1">
       <c r="A148" s="7" t="inlineStr">
         <is>
-          <t>603638</t>
+          <t>603662</t>
         </is>
       </c>
       <c r="B148" s="8" t="inlineStr">
         <is>
-          <t>艾迪精密</t>
+          <t>柯力传感</t>
         </is>
       </c>
       <c r="C148" s="7" t="inlineStr">
@@ -8034,11 +8020,11 @@
       </c>
       <c r="E148" s="7" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="F148" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G148" s="7" t="inlineStr">
         <is>
@@ -8046,13 +8032,13 @@
         </is>
       </c>
       <c r="H148" s="13" t="n">
-        <v>5.54</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="I148" s="7" t="n">
-        <v>-13.45</v>
+        <v>-13.76</v>
       </c>
       <c r="J148" s="7" t="n">
-        <v>0.51</v>
+        <v>0.53</v>
       </c>
       <c r="K148" s="7" t="inlineStr">
         <is>
@@ -8065,27 +8051,27 @@
     <row r="149" ht="26" customHeight="1">
       <c r="A149" s="10" t="inlineStr">
         <is>
-          <t>002916</t>
+          <t>001287</t>
         </is>
       </c>
       <c r="B149" s="11" t="inlineStr">
         <is>
-          <t>深南电路</t>
+          <t>中电港</t>
         </is>
       </c>
       <c r="C149" s="10" t="inlineStr">
         <is>
-          <t>算力/通信</t>
+          <t>半导体/芯片</t>
         </is>
       </c>
       <c r="D149" s="10" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="E149" s="10" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="F149" s="10" t="n">
@@ -8097,17 +8083,15 @@
         </is>
       </c>
       <c r="H149" s="12" t="n">
-        <v>7.42</v>
+        <v>10</v>
       </c>
       <c r="I149" s="10" t="n">
-        <v>-13.18</v>
-      </c>
-      <c r="J149" s="10" t="n">
-        <v>1.46</v>
-      </c>
+        <v>-13.48</v>
+      </c>
+      <c r="J149" s="10" t="n"/>
       <c r="K149" s="10" t="inlineStr">
         <is>
-          <t>放量</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="L149" s="10" t="inlineStr"/>
@@ -8116,12 +8100,12 @@
     <row r="150" ht="26" customHeight="1">
       <c r="A150" s="7" t="inlineStr">
         <is>
-          <t>688400</t>
+          <t>603638</t>
         </is>
       </c>
       <c r="B150" s="8" t="inlineStr">
         <is>
-          <t>凌云光</t>
+          <t>艾迪精密</t>
         </is>
       </c>
       <c r="C150" s="7" t="inlineStr">
@@ -8136,11 +8120,11 @@
       </c>
       <c r="E150" s="7" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="F150" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G150" s="7" t="inlineStr">
         <is>
@@ -8148,13 +8132,13 @@
         </is>
       </c>
       <c r="H150" s="13" t="n">
-        <v>9.02</v>
+        <v>5.54</v>
       </c>
       <c r="I150" s="7" t="n">
-        <v>-13.05</v>
+        <v>-13.45</v>
       </c>
       <c r="J150" s="7" t="n">
-        <v>0.67</v>
+        <v>0.51</v>
       </c>
       <c r="K150" s="7" t="inlineStr">
         <is>
@@ -8167,27 +8151,27 @@
     <row r="151" ht="26" customHeight="1">
       <c r="A151" s="10" t="inlineStr">
         <is>
-          <t>688596</t>
+          <t>002916</t>
         </is>
       </c>
       <c r="B151" s="11" t="inlineStr">
         <is>
-          <t>正帆科技</t>
+          <t>深南电路</t>
         </is>
       </c>
       <c r="C151" s="10" t="inlineStr">
         <is>
-          <t>半导体/芯片</t>
+          <t>算力/通信</t>
         </is>
       </c>
       <c r="D151" s="10" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="E151" s="10" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="F151" s="10" t="n">
@@ -8199,17 +8183,17 @@
         </is>
       </c>
       <c r="H151" s="12" t="n">
-        <v>5.82</v>
+        <v>7.42</v>
       </c>
       <c r="I151" s="10" t="n">
-        <v>-12.98</v>
+        <v>-13.18</v>
       </c>
       <c r="J151" s="10" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.46</v>
       </c>
       <c r="K151" s="10" t="inlineStr">
         <is>
-          <t>缩量</t>
+          <t>放量</t>
         </is>
       </c>
       <c r="L151" s="10" t="inlineStr"/>
@@ -8218,12 +8202,12 @@
     <row r="152" ht="26" customHeight="1">
       <c r="A152" s="7" t="inlineStr">
         <is>
-          <t>300005</t>
+          <t>688400</t>
         </is>
       </c>
       <c r="B152" s="8" t="inlineStr">
         <is>
-          <t>探路者</t>
+          <t>凌云光</t>
         </is>
       </c>
       <c r="C152" s="7" t="inlineStr">
@@ -8233,12 +8217,12 @@
       </c>
       <c r="D152" s="7" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="E152" s="7" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="F152" s="7" t="n">
@@ -8250,15 +8234,17 @@
         </is>
       </c>
       <c r="H152" s="13" t="n">
-        <v>8.1</v>
+        <v>9.02</v>
       </c>
       <c r="I152" s="7" t="n">
-        <v>-12.95</v>
-      </c>
-      <c r="J152" s="7" t="n"/>
+        <v>-13.05</v>
+      </c>
+      <c r="J152" s="7" t="n">
+        <v>0.67</v>
+      </c>
       <c r="K152" s="7" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>缩量</t>
         </is>
       </c>
       <c r="L152" s="7" t="inlineStr"/>
@@ -8267,31 +8253,31 @@
     <row r="153" ht="26" customHeight="1">
       <c r="A153" s="10" t="inlineStr">
         <is>
-          <t>301307</t>
+          <t>688596</t>
         </is>
       </c>
       <c r="B153" s="11" t="inlineStr">
         <is>
-          <t>美利信</t>
+          <t>正帆科技</t>
         </is>
       </c>
       <c r="C153" s="10" t="inlineStr">
         <is>
-          <t>算力/通信</t>
+          <t>半导体/芯片</t>
         </is>
       </c>
       <c r="D153" s="10" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="E153" s="10" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="F153" s="10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G153" s="10" t="inlineStr">
         <is>
@@ -8299,15 +8285,17 @@
         </is>
       </c>
       <c r="H153" s="12" t="n">
-        <v>13.21</v>
+        <v>5.82</v>
       </c>
       <c r="I153" s="10" t="n">
-        <v>-12.8</v>
-      </c>
-      <c r="J153" s="10" t="n"/>
+        <v>-12.98</v>
+      </c>
+      <c r="J153" s="10" t="n">
+        <v>0.6899999999999999</v>
+      </c>
       <c r="K153" s="10" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>缩量</t>
         </is>
       </c>
       <c r="L153" s="10" t="inlineStr"/>
@@ -8316,17 +8304,17 @@
     <row r="154" ht="26" customHeight="1">
       <c r="A154" s="7" t="inlineStr">
         <is>
-          <t>688766</t>
+          <t>300005</t>
         </is>
       </c>
       <c r="B154" s="8" t="inlineStr">
         <is>
-          <t>普冉股份</t>
+          <t>探路者</t>
         </is>
       </c>
       <c r="C154" s="7" t="inlineStr">
         <is>
-          <t>半导体/芯片</t>
+          <t>机器人</t>
         </is>
       </c>
       <c r="D154" s="7" t="inlineStr">
@@ -8348,14 +8336,12 @@
         </is>
       </c>
       <c r="H154" s="13" t="n">
-        <v>13.49</v>
+        <v>8.1</v>
       </c>
       <c r="I154" s="7" t="n">
-        <v>-12.46</v>
-      </c>
-      <c r="J154" s="7" t="n">
-        <v>0.96</v>
-      </c>
+        <v>-12.95</v>
+      </c>
+      <c r="J154" s="7" t="n"/>
       <c r="K154" s="7" t="inlineStr">
         <is>
           <t>正常</t>
@@ -8367,31 +8353,31 @@
     <row r="155" ht="26" customHeight="1">
       <c r="A155" s="10" t="inlineStr">
         <is>
-          <t>002056</t>
+          <t>301307</t>
         </is>
       </c>
       <c r="B155" s="11" t="inlineStr">
         <is>
-          <t>横店东磁</t>
+          <t>美利信</t>
         </is>
       </c>
       <c r="C155" s="10" t="inlineStr">
         <is>
-          <t>机器人</t>
+          <t>算力/通信</t>
         </is>
       </c>
       <c r="D155" s="10" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="E155" s="10" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="F155" s="10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G155" s="10" t="inlineStr">
         <is>
@@ -8399,14 +8385,12 @@
         </is>
       </c>
       <c r="H155" s="12" t="n">
-        <v>7.05</v>
+        <v>13.21</v>
       </c>
       <c r="I155" s="10" t="n">
-        <v>-12.34</v>
-      </c>
-      <c r="J155" s="10" t="n">
-        <v>0.96</v>
-      </c>
+        <v>-12.8</v>
+      </c>
+      <c r="J155" s="10" t="n"/>
       <c r="K155" s="10" t="inlineStr">
         <is>
           <t>正常</t>
@@ -8418,12 +8402,12 @@
     <row r="156" ht="26" customHeight="1">
       <c r="A156" s="7" t="inlineStr">
         <is>
-          <t>002559</t>
+          <t>688766</t>
         </is>
       </c>
       <c r="B156" s="8" t="inlineStr">
         <is>
-          <t>亚威股份</t>
+          <t>普冉股份</t>
         </is>
       </c>
       <c r="C156" s="7" t="inlineStr">
@@ -8438,11 +8422,11 @@
       </c>
       <c r="E156" s="7" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="F156" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G156" s="7" t="inlineStr">
         <is>
@@ -8450,12 +8434,14 @@
         </is>
       </c>
       <c r="H156" s="13" t="n">
-        <v>10.01</v>
+        <v>13.49</v>
       </c>
       <c r="I156" s="7" t="n">
-        <v>-12.33</v>
-      </c>
-      <c r="J156" s="7" t="n"/>
+        <v>-12.46</v>
+      </c>
+      <c r="J156" s="7" t="n">
+        <v>0.96</v>
+      </c>
       <c r="K156" s="7" t="inlineStr">
         <is>
           <t>正常</t>
@@ -8467,12 +8453,12 @@
     <row r="157" ht="26" customHeight="1">
       <c r="A157" s="10" t="inlineStr">
         <is>
-          <t>002354</t>
+          <t>002056</t>
         </is>
       </c>
       <c r="B157" s="11" t="inlineStr">
         <is>
-          <t>天娱数科</t>
+          <t>横店东磁</t>
         </is>
       </c>
       <c r="C157" s="10" t="inlineStr">
@@ -8487,11 +8473,11 @@
       </c>
       <c r="E157" s="10" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="F157" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G157" s="10" t="inlineStr">
         <is>
@@ -8499,12 +8485,14 @@
         </is>
       </c>
       <c r="H157" s="12" t="n">
-        <v>10</v>
+        <v>7.05</v>
       </c>
       <c r="I157" s="10" t="n">
-        <v>-11.74</v>
-      </c>
-      <c r="J157" s="10" t="n"/>
+        <v>-12.34</v>
+      </c>
+      <c r="J157" s="10" t="n">
+        <v>0.96</v>
+      </c>
       <c r="K157" s="10" t="inlineStr">
         <is>
           <t>正常</t>
@@ -8516,31 +8504,31 @@
     <row r="158" ht="26" customHeight="1">
       <c r="A158" s="7" t="inlineStr">
         <is>
-          <t>300420</t>
+          <t>002559</t>
         </is>
       </c>
       <c r="B158" s="8" t="inlineStr">
         <is>
-          <t>五洋自控</t>
+          <t>亚威股份</t>
         </is>
       </c>
       <c r="C158" s="7" t="inlineStr">
         <is>
-          <t>算力/通信</t>
+          <t>半导体/芯片</t>
         </is>
       </c>
       <c r="D158" s="7" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="E158" s="7" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="F158" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G158" s="7" t="inlineStr">
         <is>
@@ -8548,10 +8536,10 @@
         </is>
       </c>
       <c r="H158" s="13" t="n">
-        <v>4</v>
+        <v>10.01</v>
       </c>
       <c r="I158" s="7" t="n">
-        <v>-11.63</v>
+        <v>-12.33</v>
       </c>
       <c r="J158" s="7" t="n"/>
       <c r="K158" s="7" t="inlineStr">
@@ -8565,22 +8553,22 @@
     <row r="159" ht="26" customHeight="1">
       <c r="A159" s="10" t="inlineStr">
         <is>
-          <t>300938</t>
+          <t>002354</t>
         </is>
       </c>
       <c r="B159" s="11" t="inlineStr">
         <is>
-          <t>信测标准</t>
+          <t>天娱数科</t>
         </is>
       </c>
       <c r="C159" s="10" t="inlineStr">
         <is>
-          <t>半导体/芯片</t>
+          <t>机器人</t>
         </is>
       </c>
       <c r="D159" s="10" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="E159" s="10" t="inlineStr">
@@ -8589,7 +8577,7 @@
         </is>
       </c>
       <c r="F159" s="10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G159" s="10" t="inlineStr">
         <is>
@@ -8597,10 +8585,10 @@
         </is>
       </c>
       <c r="H159" s="12" t="n">
-        <v>3.29</v>
+        <v>10</v>
       </c>
       <c r="I159" s="10" t="n">
-        <v>-11.54</v>
+        <v>-11.74</v>
       </c>
       <c r="J159" s="10" t="n"/>
       <c r="K159" s="10" t="inlineStr">
@@ -8614,27 +8602,27 @@
     <row r="160" ht="26" customHeight="1">
       <c r="A160" s="7" t="inlineStr">
         <is>
-          <t>000566</t>
+          <t>300420</t>
         </is>
       </c>
       <c r="B160" s="8" t="inlineStr">
         <is>
-          <t>海南海药</t>
+          <t>五洋自控</t>
         </is>
       </c>
       <c r="C160" s="7" t="inlineStr">
         <is>
-          <t>创新药/CRO</t>
+          <t>算力/通信</t>
         </is>
       </c>
       <c r="D160" s="7" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="E160" s="7" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="F160" s="7" t="n">
@@ -8646,14 +8634,12 @@
         </is>
       </c>
       <c r="H160" s="13" t="n">
-        <v>4.72</v>
+        <v>4</v>
       </c>
       <c r="I160" s="7" t="n">
-        <v>-11.36</v>
-      </c>
-      <c r="J160" s="7" t="n">
-        <v>0.84</v>
-      </c>
+        <v>-11.63</v>
+      </c>
+      <c r="J160" s="7" t="n"/>
       <c r="K160" s="7" t="inlineStr">
         <is>
           <t>正常</t>
@@ -8663,88 +8649,82 @@
       <c r="M160" s="7" t="inlineStr"/>
     </row>
     <row r="161" ht="26" customHeight="1">
-      <c r="A161" s="15" t="inlineStr">
-        <is>
-          <t>688106</t>
-        </is>
-      </c>
-      <c r="B161" s="16" t="inlineStr">
-        <is>
-          <t>金宏气体</t>
-        </is>
-      </c>
-      <c r="C161" s="15" t="inlineStr">
+      <c r="A161" s="10" t="inlineStr">
+        <is>
+          <t>300938</t>
+        </is>
+      </c>
+      <c r="B161" s="11" t="inlineStr">
+        <is>
+          <t>信测标准</t>
+        </is>
+      </c>
+      <c r="C161" s="10" t="inlineStr">
         <is>
           <t>半导体/芯片</t>
         </is>
       </c>
-      <c r="D161" s="15" t="inlineStr">
+      <c r="D161" s="10" t="inlineStr">
         <is>
           <t>2026-07-01</t>
         </is>
       </c>
-      <c r="E161" s="15" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="F161" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G161" s="17" t="inlineStr">
-        <is>
-          <t>强势上攻</t>
-        </is>
-      </c>
-      <c r="H161" s="19" t="n">
-        <v>20.01</v>
-      </c>
-      <c r="I161" s="15" t="n">
-        <v>-10.86</v>
-      </c>
-      <c r="J161" s="15" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="K161" s="15" t="inlineStr">
-        <is>
-          <t>正常</t>
-        </is>
-      </c>
-      <c r="L161" s="15" t="inlineStr">
-        <is>
-          <t>首日涨幅&gt;20%</t>
-        </is>
-      </c>
-      <c r="M161" s="15" t="inlineStr"/>
+      <c r="E161" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="F161" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="G161" s="10" t="inlineStr">
+        <is>
+          <t>强势上攻</t>
+        </is>
+      </c>
+      <c r="H161" s="12" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="I161" s="10" t="n">
+        <v>-11.54</v>
+      </c>
+      <c r="J161" s="10" t="n"/>
+      <c r="K161" s="10" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="L161" s="10" t="inlineStr"/>
+      <c r="M161" s="10" t="inlineStr"/>
     </row>
     <row r="162" ht="26" customHeight="1">
       <c r="A162" s="7" t="inlineStr">
         <is>
-          <t>688112</t>
+          <t>000566</t>
         </is>
       </c>
       <c r="B162" s="8" t="inlineStr">
         <is>
-          <t>鼎阳科技</t>
+          <t>海南海药</t>
         </is>
       </c>
       <c r="C162" s="7" t="inlineStr">
         <is>
-          <t>算力/通信</t>
+          <t>创新药/CRO</t>
         </is>
       </c>
       <c r="D162" s="7" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="E162" s="7" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="F162" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G162" s="7" t="inlineStr">
         <is>
@@ -8752,101 +8732,105 @@
         </is>
       </c>
       <c r="H162" s="13" t="n">
-        <v>5.74</v>
+        <v>4.72</v>
       </c>
       <c r="I162" s="7" t="n">
-        <v>-10.67</v>
+        <v>-11.36</v>
       </c>
       <c r="J162" s="7" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.84</v>
       </c>
       <c r="K162" s="7" t="inlineStr">
         <is>
-          <t>缩量</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="L162" s="7" t="inlineStr"/>
       <c r="M162" s="7" t="inlineStr"/>
     </row>
     <row r="163" ht="26" customHeight="1">
-      <c r="A163" s="10" t="inlineStr">
-        <is>
-          <t>688305</t>
-        </is>
-      </c>
-      <c r="B163" s="11" t="inlineStr">
-        <is>
-          <t>科德数控</t>
-        </is>
-      </c>
-      <c r="C163" s="10" t="inlineStr">
-        <is>
-          <t>机器人</t>
-        </is>
-      </c>
-      <c r="D163" s="10" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="E163" s="10" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="F163" s="10" t="n">
+      <c r="A163" s="15" t="inlineStr">
+        <is>
+          <t>688106</t>
+        </is>
+      </c>
+      <c r="B163" s="16" t="inlineStr">
+        <is>
+          <t>金宏气体</t>
+        </is>
+      </c>
+      <c r="C163" s="15" t="inlineStr">
+        <is>
+          <t>半导体/芯片</t>
+        </is>
+      </c>
+      <c r="D163" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="E163" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="F163" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="G163" s="10" t="inlineStr">
-        <is>
-          <t>强势上攻</t>
-        </is>
-      </c>
-      <c r="H163" s="12" t="n">
-        <v>12.37</v>
-      </c>
-      <c r="I163" s="10" t="n">
-        <v>-10.66</v>
-      </c>
-      <c r="J163" s="10" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="K163" s="10" t="inlineStr">
-        <is>
-          <t>缩量</t>
-        </is>
-      </c>
-      <c r="L163" s="10" t="inlineStr"/>
-      <c r="M163" s="10" t="inlineStr"/>
+      <c r="G163" s="17" t="inlineStr">
+        <is>
+          <t>强势上攻</t>
+        </is>
+      </c>
+      <c r="H163" s="19" t="n">
+        <v>20.01</v>
+      </c>
+      <c r="I163" s="15" t="n">
+        <v>-10.86</v>
+      </c>
+      <c r="J163" s="15" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="K163" s="15" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="L163" s="15" t="inlineStr">
+        <is>
+          <t>首日涨幅&gt;20%</t>
+        </is>
+      </c>
+      <c r="M163" s="15" t="inlineStr"/>
     </row>
     <row r="164" ht="26" customHeight="1">
       <c r="A164" s="7" t="inlineStr">
         <is>
-          <t>688545</t>
+          <t>688112</t>
         </is>
       </c>
       <c r="B164" s="8" t="inlineStr">
         <is>
-          <t>兴福电子</t>
+          <t>鼎阳科技</t>
         </is>
       </c>
       <c r="C164" s="7" t="inlineStr">
         <is>
-          <t>半导体/芯片</t>
+          <t>算力/通信</t>
         </is>
       </c>
       <c r="D164" s="7" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="E164" s="7" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="F164" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G164" s="7" t="inlineStr">
         <is>
@@ -8854,17 +8838,17 @@
         </is>
       </c>
       <c r="H164" s="13" t="n">
-        <v>5.89</v>
+        <v>5.74</v>
       </c>
       <c r="I164" s="7" t="n">
-        <v>-10.53</v>
+        <v>-10.67</v>
       </c>
       <c r="J164" s="7" t="n">
-        <v>1.14</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="K164" s="7" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>缩量</t>
         </is>
       </c>
       <c r="L164" s="7" t="inlineStr"/>
@@ -8873,27 +8857,27 @@
     <row r="165" ht="26" customHeight="1">
       <c r="A165" s="10" t="inlineStr">
         <is>
-          <t>605289</t>
+          <t>688305</t>
         </is>
       </c>
       <c r="B165" s="11" t="inlineStr">
         <is>
-          <t>罗曼股份</t>
+          <t>科德数控</t>
         </is>
       </c>
       <c r="C165" s="10" t="inlineStr">
         <is>
-          <t>算力/通信</t>
+          <t>机器人</t>
         </is>
       </c>
       <c r="D165" s="10" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="E165" s="10" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="F165" s="10" t="n">
@@ -8905,17 +8889,17 @@
         </is>
       </c>
       <c r="H165" s="12" t="n">
-        <v>10</v>
+        <v>12.37</v>
       </c>
       <c r="I165" s="10" t="n">
-        <v>-10.43</v>
+        <v>-10.66</v>
       </c>
       <c r="J165" s="10" t="n">
-        <v>0.9</v>
+        <v>0.76</v>
       </c>
       <c r="K165" s="10" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>缩量</t>
         </is>
       </c>
       <c r="L165" s="10" t="inlineStr"/>
@@ -8924,27 +8908,27 @@
     <row r="166" ht="26" customHeight="1">
       <c r="A166" s="7" t="inlineStr">
         <is>
-          <t>688219</t>
+          <t>688545</t>
         </is>
       </c>
       <c r="B166" s="8" t="inlineStr">
         <is>
-          <t>会通股份</t>
+          <t>兴福电子</t>
         </is>
       </c>
       <c r="C166" s="7" t="inlineStr">
         <is>
-          <t>机器人</t>
+          <t>半导体/芯片</t>
         </is>
       </c>
       <c r="D166" s="7" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="E166" s="7" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="F166" s="7" t="n">
@@ -8956,17 +8940,17 @@
         </is>
       </c>
       <c r="H166" s="13" t="n">
-        <v>3.96</v>
+        <v>5.89</v>
       </c>
       <c r="I166" s="7" t="n">
-        <v>-10.42</v>
+        <v>-10.53</v>
       </c>
       <c r="J166" s="7" t="n">
-        <v>0.46</v>
+        <v>1.14</v>
       </c>
       <c r="K166" s="7" t="inlineStr">
         <is>
-          <t>缩量</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="L166" s="7" t="inlineStr"/>
@@ -8975,27 +8959,27 @@
     <row r="167" ht="26" customHeight="1">
       <c r="A167" s="10" t="inlineStr">
         <is>
-          <t>688322</t>
+          <t>605289</t>
         </is>
       </c>
       <c r="B167" s="11" t="inlineStr">
         <is>
-          <t>奥比中光</t>
+          <t>罗曼股份</t>
         </is>
       </c>
       <c r="C167" s="10" t="inlineStr">
         <is>
-          <t>机器人</t>
+          <t>算力/通信</t>
         </is>
       </c>
       <c r="D167" s="10" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="E167" s="10" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="F167" s="10" t="n">
@@ -9007,17 +8991,17 @@
         </is>
       </c>
       <c r="H167" s="12" t="n">
-        <v>13.32</v>
+        <v>10</v>
       </c>
       <c r="I167" s="10" t="n">
-        <v>-10.32</v>
+        <v>-10.43</v>
       </c>
       <c r="J167" s="10" t="n">
-        <v>0.64</v>
+        <v>0.9</v>
       </c>
       <c r="K167" s="10" t="inlineStr">
         <is>
-          <t>缩量</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="L167" s="10" t="inlineStr"/>
@@ -9026,17 +9010,17 @@
     <row r="168" ht="26" customHeight="1">
       <c r="A168" s="7" t="inlineStr">
         <is>
-          <t>301018</t>
+          <t>688219</t>
         </is>
       </c>
       <c r="B168" s="8" t="inlineStr">
         <is>
-          <t>申菱环境</t>
+          <t>会通股份</t>
         </is>
       </c>
       <c r="C168" s="7" t="inlineStr">
         <is>
-          <t>算力/通信</t>
+          <t>机器人</t>
         </is>
       </c>
       <c r="D168" s="7" t="inlineStr">
@@ -9046,11 +9030,11 @@
       </c>
       <c r="E168" s="7" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="F168" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G168" s="7" t="inlineStr">
         <is>
@@ -9058,15 +9042,17 @@
         </is>
       </c>
       <c r="H168" s="13" t="n">
-        <v>6.13</v>
+        <v>3.96</v>
       </c>
       <c r="I168" s="7" t="n">
-        <v>-10.11</v>
-      </c>
-      <c r="J168" s="7" t="n"/>
+        <v>-10.42</v>
+      </c>
+      <c r="J168" s="7" t="n">
+        <v>0.46</v>
+      </c>
       <c r="K168" s="7" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>缩量</t>
         </is>
       </c>
       <c r="L168" s="7" t="inlineStr"/>
@@ -9075,31 +9061,31 @@
     <row r="169" ht="26" customHeight="1">
       <c r="A169" s="10" t="inlineStr">
         <is>
-          <t>301607</t>
+          <t>688322</t>
         </is>
       </c>
       <c r="B169" s="11" t="inlineStr">
         <is>
-          <t>富特科技</t>
+          <t>奥比中光</t>
         </is>
       </c>
       <c r="C169" s="10" t="inlineStr">
         <is>
-          <t>半导体/芯片</t>
+          <t>机器人</t>
         </is>
       </c>
       <c r="D169" s="10" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="E169" s="10" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="F169" s="10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G169" s="10" t="inlineStr">
         <is>
@@ -9107,15 +9093,17 @@
         </is>
       </c>
       <c r="H169" s="12" t="n">
-        <v>20</v>
+        <v>13.32</v>
       </c>
       <c r="I169" s="10" t="n">
-        <v>-9.91</v>
-      </c>
-      <c r="J169" s="10" t="n"/>
+        <v>-10.32</v>
+      </c>
+      <c r="J169" s="10" t="n">
+        <v>0.64</v>
+      </c>
       <c r="K169" s="10" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>缩量</t>
         </is>
       </c>
       <c r="L169" s="10" t="inlineStr"/>
@@ -9124,22 +9112,22 @@
     <row r="170" ht="26" customHeight="1">
       <c r="A170" s="7" t="inlineStr">
         <is>
-          <t>001331</t>
+          <t>301018</t>
         </is>
       </c>
       <c r="B170" s="8" t="inlineStr">
         <is>
-          <t>胜通能源</t>
+          <t>申菱环境</t>
         </is>
       </c>
       <c r="C170" s="7" t="inlineStr">
         <is>
-          <t>机器人</t>
+          <t>算力/通信</t>
         </is>
       </c>
       <c r="D170" s="7" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="E170" s="7" t="inlineStr">
@@ -9148,7 +9136,7 @@
         </is>
       </c>
       <c r="F170" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G170" s="7" t="inlineStr">
         <is>
@@ -9156,10 +9144,10 @@
         </is>
       </c>
       <c r="H170" s="13" t="n">
-        <v>4.22</v>
+        <v>6.13</v>
       </c>
       <c r="I170" s="7" t="n">
-        <v>-9.31</v>
+        <v>-10.11</v>
       </c>
       <c r="J170" s="7" t="n"/>
       <c r="K170" s="7" t="inlineStr">
@@ -9173,12 +9161,12 @@
     <row r="171" ht="26" customHeight="1">
       <c r="A171" s="10" t="inlineStr">
         <is>
-          <t>688548</t>
+          <t>301607</t>
         </is>
       </c>
       <c r="B171" s="11" t="inlineStr">
         <is>
-          <t>广钢气体</t>
+          <t>富特科技</t>
         </is>
       </c>
       <c r="C171" s="10" t="inlineStr">
@@ -9188,16 +9176,16 @@
       </c>
       <c r="D171" s="10" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="E171" s="10" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="F171" s="10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G171" s="10" t="inlineStr">
         <is>
@@ -9205,14 +9193,12 @@
         </is>
       </c>
       <c r="H171" s="12" t="n">
-        <v>5.57</v>
+        <v>20</v>
       </c>
       <c r="I171" s="10" t="n">
-        <v>-9.1</v>
-      </c>
-      <c r="J171" s="10" t="n">
-        <v>0.88</v>
-      </c>
+        <v>-9.91</v>
+      </c>
+      <c r="J171" s="10" t="n"/>
       <c r="K171" s="10" t="inlineStr">
         <is>
           <t>正常</t>
@@ -9222,67 +9208,63 @@
       <c r="M171" s="10" t="inlineStr"/>
     </row>
     <row r="172" ht="26" customHeight="1">
-      <c r="A172" s="15" t="inlineStr">
-        <is>
-          <t>300604</t>
-        </is>
-      </c>
-      <c r="B172" s="16" t="inlineStr">
-        <is>
-          <t>长川科技</t>
-        </is>
-      </c>
-      <c r="C172" s="15" t="inlineStr">
-        <is>
-          <t>半导体/芯片</t>
-        </is>
-      </c>
-      <c r="D172" s="15" t="inlineStr">
-        <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="E172" s="15" t="inlineStr">
-        <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="F172" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G172" s="17" t="inlineStr">
-        <is>
-          <t>强势上攻</t>
-        </is>
-      </c>
-      <c r="H172" s="19" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="I172" s="15" t="n">
-        <v>-9.039999999999999</v>
-      </c>
-      <c r="J172" s="15" t="n"/>
-      <c r="K172" s="15" t="inlineStr">
-        <is>
-          <t>正常</t>
-        </is>
-      </c>
-      <c r="L172" s="15" t="inlineStr">
-        <is>
-          <t>首日涨幅&gt;18%</t>
-        </is>
-      </c>
-      <c r="M172" s="15" t="inlineStr"/>
+      <c r="A172" s="7" t="inlineStr">
+        <is>
+          <t>001331</t>
+        </is>
+      </c>
+      <c r="B172" s="8" t="inlineStr">
+        <is>
+          <t>胜通能源</t>
+        </is>
+      </c>
+      <c r="C172" s="7" t="inlineStr">
+        <is>
+          <t>机器人</t>
+        </is>
+      </c>
+      <c r="D172" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="E172" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="F172" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="G172" s="7" t="inlineStr">
+        <is>
+          <t>强势上攻</t>
+        </is>
+      </c>
+      <c r="H172" s="13" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="I172" s="7" t="n">
+        <v>-9.31</v>
+      </c>
+      <c r="J172" s="7" t="n"/>
+      <c r="K172" s="7" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="L172" s="7" t="inlineStr"/>
+      <c r="M172" s="7" t="inlineStr"/>
     </row>
     <row r="173" ht="26" customHeight="1">
       <c r="A173" s="10" t="inlineStr">
         <is>
-          <t>688653</t>
+          <t>688548</t>
         </is>
       </c>
       <c r="B173" s="11" t="inlineStr">
         <is>
-          <t>康希通信</t>
+          <t>广钢气体</t>
         </is>
       </c>
       <c r="C173" s="10" t="inlineStr">
@@ -9292,12 +9274,12 @@
       </c>
       <c r="D173" s="10" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="E173" s="10" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="F173" s="10" t="n">
@@ -9309,13 +9291,13 @@
         </is>
       </c>
       <c r="H173" s="12" t="n">
-        <v>5.96</v>
+        <v>5.57</v>
       </c>
       <c r="I173" s="10" t="n">
-        <v>-8.48</v>
+        <v>-9.1</v>
       </c>
       <c r="J173" s="10" t="n">
-        <v>0.99</v>
+        <v>0.88</v>
       </c>
       <c r="K173" s="10" t="inlineStr">
         <is>
@@ -9326,84 +9308,86 @@
       <c r="M173" s="10" t="inlineStr"/>
     </row>
     <row r="174" ht="26" customHeight="1">
-      <c r="A174" s="7" t="inlineStr">
-        <is>
-          <t>603726</t>
-        </is>
-      </c>
-      <c r="B174" s="8" t="inlineStr">
-        <is>
-          <t>朗迪集团</t>
-        </is>
-      </c>
-      <c r="C174" s="7" t="inlineStr">
+      <c r="A174" s="15" t="inlineStr">
+        <is>
+          <t>300604</t>
+        </is>
+      </c>
+      <c r="B174" s="16" t="inlineStr">
+        <is>
+          <t>长川科技</t>
+        </is>
+      </c>
+      <c r="C174" s="15" t="inlineStr">
         <is>
           <t>半导体/芯片</t>
         </is>
       </c>
-      <c r="D174" s="7" t="inlineStr">
-        <is>
-          <t>2026-07-03</t>
-        </is>
-      </c>
-      <c r="E174" s="7" t="inlineStr">
+      <c r="D174" s="15" t="inlineStr">
         <is>
           <t>2026-07-09</t>
         </is>
       </c>
-      <c r="F174" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="G174" s="7" t="inlineStr">
-        <is>
-          <t>强势上攻</t>
-        </is>
-      </c>
-      <c r="H174" s="13" t="n">
-        <v>10.02</v>
-      </c>
-      <c r="I174" s="7" t="n">
-        <v>-8.470000000000001</v>
-      </c>
-      <c r="J174" s="7" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="K174" s="7" t="inlineStr">
-        <is>
-          <t>正常</t>
-        </is>
-      </c>
-      <c r="L174" s="7" t="inlineStr"/>
-      <c r="M174" s="7" t="inlineStr"/>
+      <c r="E174" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="F174" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G174" s="17" t="inlineStr">
+        <is>
+          <t>强势上攻</t>
+        </is>
+      </c>
+      <c r="H174" s="19" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="I174" s="15" t="n">
+        <v>-9.039999999999999</v>
+      </c>
+      <c r="J174" s="15" t="n"/>
+      <c r="K174" s="15" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="L174" s="15" t="inlineStr">
+        <is>
+          <t>首日涨幅&gt;18%</t>
+        </is>
+      </c>
+      <c r="M174" s="15" t="inlineStr"/>
     </row>
     <row r="175" ht="26" customHeight="1">
       <c r="A175" s="10" t="inlineStr">
         <is>
-          <t>688319</t>
+          <t>688653</t>
         </is>
       </c>
       <c r="B175" s="11" t="inlineStr">
         <is>
-          <t>欧林生物</t>
+          <t>康希通信</t>
         </is>
       </c>
       <c r="C175" s="10" t="inlineStr">
         <is>
-          <t>创新药/CRO</t>
+          <t>半导体/芯片</t>
         </is>
       </c>
       <c r="D175" s="10" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="E175" s="10" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="F175" s="10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G175" s="10" t="inlineStr">
         <is>
@@ -9411,13 +9395,13 @@
         </is>
       </c>
       <c r="H175" s="12" t="n">
-        <v>11.54</v>
+        <v>5.96</v>
       </c>
       <c r="I175" s="10" t="n">
-        <v>-8.42</v>
+        <v>-8.48</v>
       </c>
       <c r="J175" s="10" t="n">
-        <v>0.82</v>
+        <v>0.99</v>
       </c>
       <c r="K175" s="10" t="inlineStr">
         <is>
@@ -9430,22 +9414,22 @@
     <row r="176" ht="26" customHeight="1">
       <c r="A176" s="7" t="inlineStr">
         <is>
-          <t>688448</t>
+          <t>603726</t>
         </is>
       </c>
       <c r="B176" s="8" t="inlineStr">
         <is>
-          <t>磁谷科技</t>
+          <t>朗迪集团</t>
         </is>
       </c>
       <c r="C176" s="7" t="inlineStr">
         <is>
-          <t>算力/通信</t>
+          <t>半导体/芯片</t>
         </is>
       </c>
       <c r="D176" s="7" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="E176" s="7" t="inlineStr">
@@ -9454,7 +9438,7 @@
         </is>
       </c>
       <c r="F176" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G176" s="7" t="inlineStr">
         <is>
@@ -9462,17 +9446,17 @@
         </is>
       </c>
       <c r="H176" s="13" t="n">
-        <v>3.81</v>
+        <v>10.02</v>
       </c>
       <c r="I176" s="7" t="n">
-        <v>-8.15</v>
+        <v>-8.470000000000001</v>
       </c>
       <c r="J176" s="7" t="n">
-        <v>0.45</v>
+        <v>0.93</v>
       </c>
       <c r="K176" s="7" t="inlineStr">
         <is>
-          <t>缩量</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="L176" s="7" t="inlineStr"/>
@@ -9481,17 +9465,17 @@
     <row r="177" ht="26" customHeight="1">
       <c r="A177" s="10" t="inlineStr">
         <is>
-          <t>002979</t>
+          <t>688319</t>
         </is>
       </c>
       <c r="B177" s="11" t="inlineStr">
         <is>
-          <t>雷赛智能</t>
+          <t>欧林生物</t>
         </is>
       </c>
       <c r="C177" s="10" t="inlineStr">
         <is>
-          <t>机器人</t>
+          <t>创新药/CRO</t>
         </is>
       </c>
       <c r="D177" s="10" t="inlineStr">
@@ -9501,11 +9485,11 @@
       </c>
       <c r="E177" s="10" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="F177" s="10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G177" s="10" t="inlineStr">
         <is>
@@ -9513,12 +9497,14 @@
         </is>
       </c>
       <c r="H177" s="12" t="n">
-        <v>5.35</v>
+        <v>11.54</v>
       </c>
       <c r="I177" s="10" t="n">
-        <v>-8.09</v>
-      </c>
-      <c r="J177" s="10" t="n"/>
+        <v>-8.42</v>
+      </c>
+      <c r="J177" s="10" t="n">
+        <v>0.82</v>
+      </c>
       <c r="K177" s="10" t="inlineStr">
         <is>
           <t>正常</t>
@@ -9530,31 +9516,31 @@
     <row r="178" ht="26" customHeight="1">
       <c r="A178" s="7" t="inlineStr">
         <is>
-          <t>688061</t>
+          <t>688448</t>
         </is>
       </c>
       <c r="B178" s="8" t="inlineStr">
         <is>
-          <t>灿瑞科技</t>
+          <t>磁谷科技</t>
         </is>
       </c>
       <c r="C178" s="7" t="inlineStr">
         <is>
-          <t>半导体/芯片</t>
+          <t>算力/通信</t>
         </is>
       </c>
       <c r="D178" s="7" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="E178" s="7" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="F178" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G178" s="7" t="inlineStr">
         <is>
@@ -9562,17 +9548,17 @@
         </is>
       </c>
       <c r="H178" s="13" t="n">
-        <v>7.34</v>
+        <v>3.81</v>
       </c>
       <c r="I178" s="7" t="n">
-        <v>-8</v>
+        <v>-8.15</v>
       </c>
       <c r="J178" s="7" t="n">
-        <v>0.97</v>
+        <v>0.45</v>
       </c>
       <c r="K178" s="7" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>缩量</t>
         </is>
       </c>
       <c r="L178" s="7" t="inlineStr"/>
@@ -9581,12 +9567,12 @@
     <row r="179" ht="26" customHeight="1">
       <c r="A179" s="10" t="inlineStr">
         <is>
-          <t>688057</t>
+          <t>002979</t>
         </is>
       </c>
       <c r="B179" s="11" t="inlineStr">
         <is>
-          <t>金达莱</t>
+          <t>雷赛智能</t>
         </is>
       </c>
       <c r="C179" s="10" t="inlineStr">
@@ -9596,16 +9582,16 @@
       </c>
       <c r="D179" s="10" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="E179" s="10" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="F179" s="10" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G179" s="10" t="inlineStr">
         <is>
@@ -9613,17 +9599,15 @@
         </is>
       </c>
       <c r="H179" s="12" t="n">
-        <v>13.54</v>
+        <v>5.35</v>
       </c>
       <c r="I179" s="10" t="n">
-        <v>-7.68</v>
-      </c>
-      <c r="J179" s="10" t="n">
-        <v>0.53</v>
-      </c>
+        <v>-8.09</v>
+      </c>
+      <c r="J179" s="10" t="n"/>
       <c r="K179" s="10" t="inlineStr">
         <is>
-          <t>缩量</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="L179" s="10" t="inlineStr"/>
@@ -9632,17 +9616,17 @@
     <row r="180" ht="26" customHeight="1">
       <c r="A180" s="7" t="inlineStr">
         <is>
-          <t>300553</t>
+          <t>688061</t>
         </is>
       </c>
       <c r="B180" s="8" t="inlineStr">
         <is>
-          <t>集智股份</t>
+          <t>灿瑞科技</t>
         </is>
       </c>
       <c r="C180" s="7" t="inlineStr">
         <is>
-          <t>机器人</t>
+          <t>半导体/芯片</t>
         </is>
       </c>
       <c r="D180" s="7" t="inlineStr">
@@ -9664,13 +9648,13 @@
         </is>
       </c>
       <c r="H180" s="13" t="n">
-        <v>8</v>
+        <v>7.34</v>
       </c>
       <c r="I180" s="7" t="n">
-        <v>-7.55</v>
+        <v>-8</v>
       </c>
       <c r="J180" s="7" t="n">
-        <v>0.86</v>
+        <v>0.97</v>
       </c>
       <c r="K180" s="7" t="inlineStr">
         <is>
@@ -9683,17 +9667,17 @@
     <row r="181" ht="26" customHeight="1">
       <c r="A181" s="10" t="inlineStr">
         <is>
-          <t>002409</t>
+          <t>688057</t>
         </is>
       </c>
       <c r="B181" s="11" t="inlineStr">
         <is>
-          <t>雅克科技</t>
+          <t>金达莱</t>
         </is>
       </c>
       <c r="C181" s="10" t="inlineStr">
         <is>
-          <t>半导体/芯片</t>
+          <t>机器人</t>
         </is>
       </c>
       <c r="D181" s="10" t="inlineStr">
@@ -9703,11 +9687,11 @@
       </c>
       <c r="E181" s="10" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="F181" s="10" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G181" s="10" t="inlineStr">
         <is>
@@ -9715,15 +9699,17 @@
         </is>
       </c>
       <c r="H181" s="12" t="n">
-        <v>5.16</v>
+        <v>13.54</v>
       </c>
       <c r="I181" s="10" t="n">
-        <v>-7.1</v>
-      </c>
-      <c r="J181" s="10" t="n"/>
+        <v>-7.68</v>
+      </c>
+      <c r="J181" s="10" t="n">
+        <v>0.53</v>
+      </c>
       <c r="K181" s="10" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>缩量</t>
         </is>
       </c>
       <c r="L181" s="10" t="inlineStr"/>
@@ -9732,17 +9718,17 @@
     <row r="182" ht="26" customHeight="1">
       <c r="A182" s="7" t="inlineStr">
         <is>
-          <t>002185</t>
+          <t>300553</t>
         </is>
       </c>
       <c r="B182" s="8" t="inlineStr">
         <is>
-          <t>华天科技</t>
+          <t>集智股份</t>
         </is>
       </c>
       <c r="C182" s="7" t="inlineStr">
         <is>
-          <t>半导体/芯片</t>
+          <t>机器人</t>
         </is>
       </c>
       <c r="D182" s="7" t="inlineStr">
@@ -9752,11 +9738,11 @@
       </c>
       <c r="E182" s="7" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="F182" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G182" s="7" t="inlineStr">
         <is>
@@ -9764,17 +9750,17 @@
         </is>
       </c>
       <c r="H182" s="13" t="n">
-        <v>6.42</v>
+        <v>8</v>
       </c>
       <c r="I182" s="7" t="n">
-        <v>-6.81</v>
+        <v>-7.55</v>
       </c>
       <c r="J182" s="7" t="n">
-        <v>1.4</v>
+        <v>0.86</v>
       </c>
       <c r="K182" s="7" t="inlineStr">
         <is>
-          <t>放量</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="L182" s="7" t="inlineStr"/>
@@ -9783,12 +9769,12 @@
     <row r="183" ht="26" customHeight="1">
       <c r="A183" s="10" t="inlineStr">
         <is>
-          <t>002371</t>
+          <t>002409</t>
         </is>
       </c>
       <c r="B183" s="11" t="inlineStr">
         <is>
-          <t>北方华创</t>
+          <t>雅克科技</t>
         </is>
       </c>
       <c r="C183" s="10" t="inlineStr">
@@ -9815,10 +9801,10 @@
         </is>
       </c>
       <c r="H183" s="12" t="n">
-        <v>5.74</v>
+        <v>5.16</v>
       </c>
       <c r="I183" s="10" t="n">
-        <v>-6.65</v>
+        <v>-7.1</v>
       </c>
       <c r="J183" s="10" t="n"/>
       <c r="K183" s="10" t="inlineStr">
@@ -9830,239 +9816,237 @@
       <c r="M183" s="10" t="inlineStr"/>
     </row>
     <row r="184" ht="26" customHeight="1">
-      <c r="A184" s="15" t="inlineStr">
+      <c r="A184" s="7" t="inlineStr">
+        <is>
+          <t>002185</t>
+        </is>
+      </c>
+      <c r="B184" s="8" t="inlineStr">
+        <is>
+          <t>华天科技</t>
+        </is>
+      </c>
+      <c r="C184" s="7" t="inlineStr">
+        <is>
+          <t>半导体/芯片</t>
+        </is>
+      </c>
+      <c r="D184" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="E184" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="F184" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G184" s="7" t="inlineStr">
+        <is>
+          <t>强势上攻</t>
+        </is>
+      </c>
+      <c r="H184" s="13" t="n">
+        <v>6.42</v>
+      </c>
+      <c r="I184" s="7" t="n">
+        <v>-6.81</v>
+      </c>
+      <c r="J184" s="7" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="K184" s="7" t="inlineStr">
+        <is>
+          <t>放量</t>
+        </is>
+      </c>
+      <c r="L184" s="7" t="inlineStr"/>
+      <c r="M184" s="7" t="inlineStr"/>
+    </row>
+    <row r="185" ht="26" customHeight="1">
+      <c r="A185" s="10" t="inlineStr">
+        <is>
+          <t>002371</t>
+        </is>
+      </c>
+      <c r="B185" s="11" t="inlineStr">
+        <is>
+          <t>北方华创</t>
+        </is>
+      </c>
+      <c r="C185" s="10" t="inlineStr">
+        <is>
+          <t>半导体/芯片</t>
+        </is>
+      </c>
+      <c r="D185" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="E185" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="F185" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G185" s="10" t="inlineStr">
+        <is>
+          <t>强势上攻</t>
+        </is>
+      </c>
+      <c r="H185" s="12" t="n">
+        <v>5.74</v>
+      </c>
+      <c r="I185" s="10" t="n">
+        <v>-6.65</v>
+      </c>
+      <c r="J185" s="10" t="n"/>
+      <c r="K185" s="10" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="L185" s="10" t="inlineStr"/>
+      <c r="M185" s="10" t="inlineStr"/>
+    </row>
+    <row r="186" ht="26" customHeight="1">
+      <c r="A186" s="15" t="inlineStr">
         <is>
           <t>688605</t>
         </is>
       </c>
-      <c r="B184" s="16" t="inlineStr">
+      <c r="B186" s="16" t="inlineStr">
         <is>
           <t>先锋精科</t>
         </is>
       </c>
-      <c r="C184" s="15" t="inlineStr">
+      <c r="C186" s="15" t="inlineStr">
         <is>
           <t>半导体/芯片</t>
         </is>
       </c>
-      <c r="D184" s="15" t="inlineStr">
+      <c r="D186" s="15" t="inlineStr">
         <is>
           <t>2026-07-07</t>
         </is>
       </c>
-      <c r="E184" s="15" t="inlineStr">
+      <c r="E186" s="15" t="inlineStr">
         <is>
           <t>2026-07-09</t>
         </is>
       </c>
-      <c r="F184" s="15" t="n">
+      <c r="F186" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="G184" s="17" t="inlineStr">
-        <is>
-          <t>强势上攻</t>
-        </is>
-      </c>
-      <c r="H184" s="19" t="n">
+      <c r="G186" s="17" t="inlineStr">
+        <is>
+          <t>强势上攻</t>
+        </is>
+      </c>
+      <c r="H186" s="19" t="n">
         <v>3.02</v>
       </c>
-      <c r="I184" s="15" t="n">
+      <c r="I186" s="15" t="n">
         <v>-6.48</v>
       </c>
-      <c r="J184" s="15" t="n">
+      <c r="J186" s="15" t="n">
         <v>0.74</v>
       </c>
-      <c r="K184" s="15" t="inlineStr">
+      <c r="K186" s="15" t="inlineStr">
         <is>
           <t>缩量</t>
         </is>
       </c>
-      <c r="L184" s="15" t="inlineStr">
+      <c r="L186" s="15" t="inlineStr">
         <is>
           <t>首日涨幅&gt;15%</t>
         </is>
       </c>
-      <c r="M184" s="15" t="inlineStr"/>
-    </row>
-    <row r="185" ht="26" customHeight="1">
-      <c r="A185" s="15" t="inlineStr">
+      <c r="M186" s="15" t="inlineStr"/>
+    </row>
+    <row r="187" ht="26" customHeight="1">
+      <c r="A187" s="15" t="inlineStr">
         <is>
           <t>301379</t>
         </is>
       </c>
-      <c r="B185" s="16" t="inlineStr">
+      <c r="B187" s="16" t="inlineStr">
         <is>
           <t>天山电子</t>
         </is>
       </c>
-      <c r="C185" s="15" t="inlineStr">
+      <c r="C187" s="15" t="inlineStr">
         <is>
           <t>半导体/芯片</t>
         </is>
       </c>
-      <c r="D185" s="15" t="inlineStr">
+      <c r="D187" s="15" t="inlineStr">
         <is>
           <t>2026-07-03</t>
         </is>
       </c>
-      <c r="E185" s="15" t="inlineStr">
+      <c r="E187" s="15" t="inlineStr">
         <is>
           <t>2026-07-09</t>
         </is>
       </c>
-      <c r="F185" s="15" t="n">
+      <c r="F187" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="G185" s="17" t="inlineStr">
-        <is>
-          <t>强势上攻</t>
-        </is>
-      </c>
-      <c r="H185" s="19" t="n">
+      <c r="G187" s="17" t="inlineStr">
+        <is>
+          <t>强势上攻</t>
+        </is>
+      </c>
+      <c r="H187" s="19" t="n">
         <v>19.99</v>
       </c>
-      <c r="I185" s="15" t="n">
+      <c r="I187" s="15" t="n">
         <v>-6.34</v>
       </c>
-      <c r="J185" s="15" t="n"/>
-      <c r="K185" s="15" t="inlineStr">
-        <is>
-          <t>正常</t>
-        </is>
-      </c>
-      <c r="L185" s="15" t="inlineStr">
+      <c r="J187" s="15" t="n"/>
+      <c r="K187" s="15" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="L187" s="15" t="inlineStr">
         <is>
           <t>首日涨幅&gt;20%</t>
         </is>
       </c>
-      <c r="M185" s="15" t="inlineStr"/>
-    </row>
-    <row r="186" ht="26" customHeight="1">
-      <c r="A186" s="7" t="inlineStr">
-        <is>
-          <t>688163</t>
-        </is>
-      </c>
-      <c r="B186" s="8" t="inlineStr">
-        <is>
-          <t>赛伦生物</t>
-        </is>
-      </c>
-      <c r="C186" s="7" t="inlineStr">
-        <is>
-          <t>创新药/CRO</t>
-        </is>
-      </c>
-      <c r="D186" s="7" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="E186" s="7" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="F186" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G186" s="7" t="inlineStr">
-        <is>
-          <t>强势上攻</t>
-        </is>
-      </c>
-      <c r="H186" s="13" t="n">
-        <v>4.54</v>
-      </c>
-      <c r="I186" s="7" t="n">
-        <v>-6.12</v>
-      </c>
-      <c r="J186" s="7" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="K186" s="7" t="inlineStr">
-        <is>
-          <t>正常</t>
-        </is>
-      </c>
-      <c r="L186" s="7" t="inlineStr"/>
-      <c r="M186" s="7" t="inlineStr"/>
-    </row>
-    <row r="187" ht="26" customHeight="1">
-      <c r="A187" s="10" t="inlineStr">
-        <is>
-          <t>688729</t>
-        </is>
-      </c>
-      <c r="B187" s="11" t="inlineStr">
-        <is>
-          <t>屹唐股份</t>
-        </is>
-      </c>
-      <c r="C187" s="10" t="inlineStr">
-        <is>
-          <t>半导体/芯片</t>
-        </is>
-      </c>
-      <c r="D187" s="10" t="inlineStr">
-        <is>
-          <t>2026-07-03</t>
-        </is>
-      </c>
-      <c r="E187" s="10" t="inlineStr">
-        <is>
-          <t>2026-07-03</t>
-        </is>
-      </c>
-      <c r="F187" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="G187" s="10" t="inlineStr">
-        <is>
-          <t>强势上攻</t>
-        </is>
-      </c>
-      <c r="H187" s="12" t="n">
-        <v>5.81</v>
-      </c>
-      <c r="I187" s="10" t="n">
-        <v>-6.03</v>
-      </c>
-      <c r="J187" s="10" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="K187" s="10" t="inlineStr">
-        <is>
-          <t>正常</t>
-        </is>
-      </c>
-      <c r="L187" s="10" t="inlineStr"/>
-      <c r="M187" s="10" t="inlineStr"/>
+      <c r="M187" s="15" t="inlineStr"/>
     </row>
     <row r="188" ht="26" customHeight="1">
       <c r="A188" s="7" t="inlineStr">
         <is>
-          <t>688652</t>
+          <t>688163</t>
         </is>
       </c>
       <c r="B188" s="8" t="inlineStr">
         <is>
-          <t>京仪装备</t>
+          <t>赛伦生物</t>
         </is>
       </c>
       <c r="C188" s="7" t="inlineStr">
         <is>
-          <t>半导体/芯片</t>
+          <t>创新药/CRO</t>
         </is>
       </c>
       <c r="D188" s="7" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="E188" s="7" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="F188" s="7" t="n">
@@ -10074,17 +10058,17 @@
         </is>
       </c>
       <c r="H188" s="13" t="n">
-        <v>12.4</v>
+        <v>4.54</v>
       </c>
       <c r="I188" s="7" t="n">
-        <v>-5.94</v>
+        <v>-6.12</v>
       </c>
       <c r="J188" s="7" t="n">
-        <v>0.68</v>
+        <v>0.96</v>
       </c>
       <c r="K188" s="7" t="inlineStr">
         <is>
-          <t>缩量</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="L188" s="7" t="inlineStr"/>
@@ -10093,22 +10077,22 @@
     <row r="189" ht="26" customHeight="1">
       <c r="A189" s="10" t="inlineStr">
         <is>
-          <t>301603</t>
+          <t>688729</t>
         </is>
       </c>
       <c r="B189" s="11" t="inlineStr">
         <is>
-          <t>乔锋智能</t>
+          <t>屹唐股份</t>
         </is>
       </c>
       <c r="C189" s="10" t="inlineStr">
         <is>
-          <t>机器人</t>
+          <t>半导体/芯片</t>
         </is>
       </c>
       <c r="D189" s="10" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="E189" s="10" t="inlineStr">
@@ -10117,7 +10101,7 @@
         </is>
       </c>
       <c r="F189" s="10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G189" s="10" t="inlineStr">
         <is>
@@ -10125,17 +10109,17 @@
         </is>
       </c>
       <c r="H189" s="12" t="n">
-        <v>10.54</v>
+        <v>5.81</v>
       </c>
       <c r="I189" s="10" t="n">
-        <v>-4.93</v>
+        <v>-6.03</v>
       </c>
       <c r="J189" s="10" t="n">
-        <v>0.57</v>
+        <v>0.8</v>
       </c>
       <c r="K189" s="10" t="inlineStr">
         <is>
-          <t>缩量</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="L189" s="10" t="inlineStr"/>
@@ -10144,12 +10128,12 @@
     <row r="190" ht="26" customHeight="1">
       <c r="A190" s="7" t="inlineStr">
         <is>
-          <t>688262</t>
+          <t>688652</t>
         </is>
       </c>
       <c r="B190" s="8" t="inlineStr">
         <is>
-          <t>国芯科技</t>
+          <t>京仪装备</t>
         </is>
       </c>
       <c r="C190" s="7" t="inlineStr">
@@ -10159,12 +10143,12 @@
       </c>
       <c r="D190" s="7" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="E190" s="7" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="F190" s="7" t="n">
@@ -10176,17 +10160,17 @@
         </is>
       </c>
       <c r="H190" s="13" t="n">
-        <v>10.74</v>
+        <v>12.4</v>
       </c>
       <c r="I190" s="7" t="n">
-        <v>-3.61</v>
+        <v>-5.94</v>
       </c>
       <c r="J190" s="7" t="n">
-        <v>0.83</v>
+        <v>0.68</v>
       </c>
       <c r="K190" s="7" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>缩量</t>
         </is>
       </c>
       <c r="L190" s="7" t="inlineStr"/>
@@ -10195,27 +10179,27 @@
     <row r="191" ht="26" customHeight="1">
       <c r="A191" s="10" t="inlineStr">
         <is>
-          <t>688002</t>
+          <t>301603</t>
         </is>
       </c>
       <c r="B191" s="11" t="inlineStr">
         <is>
-          <t>睿创微纳</t>
+          <t>乔锋智能</t>
         </is>
       </c>
       <c r="C191" s="10" t="inlineStr">
         <is>
-          <t>半导体/芯片</t>
+          <t>机器人</t>
         </is>
       </c>
       <c r="D191" s="10" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="E191" s="10" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="F191" s="10" t="n">
@@ -10227,13 +10211,13 @@
         </is>
       </c>
       <c r="H191" s="12" t="n">
-        <v>6.29</v>
+        <v>10.54</v>
       </c>
       <c r="I191" s="10" t="n">
-        <v>-3.56</v>
+        <v>-4.93</v>
       </c>
       <c r="J191" s="10" t="n">
-        <v>0.76</v>
+        <v>0.57</v>
       </c>
       <c r="K191" s="10" t="inlineStr">
         <is>
@@ -10246,12 +10230,12 @@
     <row r="192" ht="26" customHeight="1">
       <c r="A192" s="7" t="inlineStr">
         <is>
-          <t>605178</t>
+          <t>688262</t>
         </is>
       </c>
       <c r="B192" s="8" t="inlineStr">
         <is>
-          <t>时空科技</t>
+          <t>国芯科技</t>
         </is>
       </c>
       <c r="C192" s="7" t="inlineStr">
@@ -10261,16 +10245,16 @@
       </c>
       <c r="D192" s="7" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="E192" s="7" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="F192" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G192" s="7" t="inlineStr">
         <is>
@@ -10278,13 +10262,13 @@
         </is>
       </c>
       <c r="H192" s="13" t="n">
-        <v>6.93</v>
+        <v>10.74</v>
       </c>
       <c r="I192" s="7" t="n">
-        <v>-3.27</v>
+        <v>-3.61</v>
       </c>
       <c r="J192" s="7" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.83</v>
       </c>
       <c r="K192" s="7" t="inlineStr">
         <is>
@@ -10297,31 +10281,31 @@
     <row r="193" ht="26" customHeight="1">
       <c r="A193" s="10" t="inlineStr">
         <is>
-          <t>603380</t>
+          <t>688002</t>
         </is>
       </c>
       <c r="B193" s="11" t="inlineStr">
         <is>
-          <t>易德龙</t>
+          <t>睿创微纳</t>
         </is>
       </c>
       <c r="C193" s="10" t="inlineStr">
         <is>
-          <t>机器人</t>
+          <t>半导体/芯片</t>
         </is>
       </c>
       <c r="D193" s="10" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="E193" s="10" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="F193" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G193" s="10" t="inlineStr">
         <is>
@@ -10329,13 +10313,13 @@
         </is>
       </c>
       <c r="H193" s="12" t="n">
-        <v>6.47</v>
-      </c>
-      <c r="I193" s="14" t="n">
-        <v>-2.79</v>
+        <v>6.29</v>
+      </c>
+      <c r="I193" s="10" t="n">
+        <v>-3.56</v>
       </c>
       <c r="J193" s="10" t="n">
-        <v>0.7</v>
+        <v>0.76</v>
       </c>
       <c r="K193" s="10" t="inlineStr">
         <is>
@@ -10348,12 +10332,12 @@
     <row r="194" ht="26" customHeight="1">
       <c r="A194" s="7" t="inlineStr">
         <is>
-          <t>603928</t>
+          <t>605178</t>
         </is>
       </c>
       <c r="B194" s="8" t="inlineStr">
         <is>
-          <t>兴业股份</t>
+          <t>时空科技</t>
         </is>
       </c>
       <c r="C194" s="7" t="inlineStr">
@@ -10363,16 +10347,16 @@
       </c>
       <c r="D194" s="7" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="E194" s="7" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="F194" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G194" s="7" t="inlineStr">
         <is>
@@ -10380,17 +10364,17 @@
         </is>
       </c>
       <c r="H194" s="13" t="n">
-        <v>10.02</v>
-      </c>
-      <c r="I194" s="9" t="n">
-        <v>-2.75</v>
+        <v>6.93</v>
+      </c>
+      <c r="I194" s="7" t="n">
+        <v>-3.27</v>
       </c>
       <c r="J194" s="7" t="n">
-        <v>0.78</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="K194" s="7" t="inlineStr">
         <is>
-          <t>缩量</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="L194" s="7" t="inlineStr"/>
@@ -10399,27 +10383,27 @@
     <row r="195" ht="26" customHeight="1">
       <c r="A195" s="10" t="inlineStr">
         <is>
-          <t>300558</t>
+          <t>603380</t>
         </is>
       </c>
       <c r="B195" s="11" t="inlineStr">
         <is>
-          <t>贝达药业</t>
+          <t>易德龙</t>
         </is>
       </c>
       <c r="C195" s="10" t="inlineStr">
         <is>
-          <t>创新药/CRO</t>
+          <t>机器人</t>
         </is>
       </c>
       <c r="D195" s="10" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="E195" s="10" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="F195" s="10" t="n">
@@ -10431,15 +10415,17 @@
         </is>
       </c>
       <c r="H195" s="12" t="n">
-        <v>8.48</v>
+        <v>6.47</v>
       </c>
       <c r="I195" s="14" t="n">
-        <v>-2.27</v>
-      </c>
-      <c r="J195" s="10" t="n"/>
+        <v>-2.79</v>
+      </c>
+      <c r="J195" s="10" t="n">
+        <v>0.7</v>
+      </c>
       <c r="K195" s="10" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>缩量</t>
         </is>
       </c>
       <c r="L195" s="10" t="inlineStr"/>
@@ -10448,12 +10434,12 @@
     <row r="196" ht="26" customHeight="1">
       <c r="A196" s="7" t="inlineStr">
         <is>
-          <t>001229</t>
+          <t>603928</t>
         </is>
       </c>
       <c r="B196" s="8" t="inlineStr">
         <is>
-          <t>魅视科技</t>
+          <t>兴业股份</t>
         </is>
       </c>
       <c r="C196" s="7" t="inlineStr">
@@ -10468,11 +10454,11 @@
       </c>
       <c r="E196" s="7" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="F196" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G196" s="7" t="inlineStr">
         <is>
@@ -10480,17 +10466,17 @@
         </is>
       </c>
       <c r="H196" s="13" t="n">
-        <v>4.6</v>
+        <v>10.02</v>
       </c>
       <c r="I196" s="9" t="n">
-        <v>-1.87</v>
+        <v>-2.75</v>
       </c>
       <c r="J196" s="7" t="n">
-        <v>1.1</v>
+        <v>0.78</v>
       </c>
       <c r="K196" s="7" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>缩量</t>
         </is>
       </c>
       <c r="L196" s="7" t="inlineStr"/>
@@ -10499,31 +10485,31 @@
     <row r="197" ht="26" customHeight="1">
       <c r="A197" s="10" t="inlineStr">
         <is>
-          <t>002965</t>
+          <t>300558</t>
         </is>
       </c>
       <c r="B197" s="11" t="inlineStr">
         <is>
-          <t>祥鑫科技</t>
+          <t>贝达药业</t>
         </is>
       </c>
       <c r="C197" s="10" t="inlineStr">
         <is>
-          <t>算力/通信</t>
+          <t>创新药/CRO</t>
         </is>
       </c>
       <c r="D197" s="10" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="E197" s="10" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="F197" s="10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G197" s="10" t="inlineStr">
         <is>
@@ -10531,10 +10517,10 @@
         </is>
       </c>
       <c r="H197" s="12" t="n">
-        <v>3.25</v>
+        <v>8.48</v>
       </c>
       <c r="I197" s="14" t="n">
-        <v>-1.37</v>
+        <v>-2.27</v>
       </c>
       <c r="J197" s="10" t="n"/>
       <c r="K197" s="10" t="inlineStr">
@@ -10548,31 +10534,31 @@
     <row r="198" ht="26" customHeight="1">
       <c r="A198" s="7" t="inlineStr">
         <is>
-          <t>300966</t>
+          <t>001229</t>
         </is>
       </c>
       <c r="B198" s="8" t="inlineStr">
         <is>
-          <t>共同药业</t>
+          <t>魅视科技</t>
         </is>
       </c>
       <c r="C198" s="7" t="inlineStr">
         <is>
-          <t>创新药/CRO</t>
+          <t>半导体/芯片</t>
         </is>
       </c>
       <c r="D198" s="7" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="E198" s="7" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="F198" s="7" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G198" s="7" t="inlineStr">
         <is>
@@ -10580,17 +10566,17 @@
         </is>
       </c>
       <c r="H198" s="13" t="n">
-        <v>8.029999999999999</v>
+        <v>4.6</v>
       </c>
       <c r="I198" s="9" t="n">
-        <v>-0.48</v>
+        <v>-1.87</v>
       </c>
       <c r="J198" s="7" t="n">
-        <v>0.73</v>
+        <v>1.1</v>
       </c>
       <c r="K198" s="7" t="inlineStr">
         <is>
-          <t>缩量</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="L198" s="7" t="inlineStr"/>
@@ -10599,31 +10585,31 @@
     <row r="199" ht="26" customHeight="1">
       <c r="A199" s="10" t="inlineStr">
         <is>
-          <t>300199</t>
+          <t>002965</t>
         </is>
       </c>
       <c r="B199" s="11" t="inlineStr">
         <is>
-          <t>翰宇药业</t>
+          <t>祥鑫科技</t>
         </is>
       </c>
       <c r="C199" s="10" t="inlineStr">
         <is>
-          <t>创新药/CRO</t>
+          <t>算力/通信</t>
         </is>
       </c>
       <c r="D199" s="10" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="E199" s="10" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="F199" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G199" s="10" t="inlineStr">
         <is>
@@ -10631,17 +10617,15 @@
         </is>
       </c>
       <c r="H199" s="12" t="n">
-        <v>6.94</v>
+        <v>3.25</v>
       </c>
       <c r="I199" s="14" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="J199" s="10" t="n">
-        <v>0.74</v>
-      </c>
+        <v>-1.37</v>
+      </c>
+      <c r="J199" s="10" t="n"/>
       <c r="K199" s="10" t="inlineStr">
         <is>
-          <t>缩量</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="L199" s="10" t="inlineStr"/>
@@ -10650,31 +10634,31 @@
     <row r="200" ht="26" customHeight="1">
       <c r="A200" s="7" t="inlineStr">
         <is>
-          <t>002747</t>
+          <t>300966</t>
         </is>
       </c>
       <c r="B200" s="8" t="inlineStr">
         <is>
-          <t>埃斯顿</t>
+          <t>共同药业</t>
         </is>
       </c>
       <c r="C200" s="7" t="inlineStr">
         <is>
-          <t>机器人</t>
+          <t>创新药/CRO</t>
         </is>
       </c>
       <c r="D200" s="7" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="E200" s="7" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="F200" s="7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G200" s="7" t="inlineStr">
         <is>
@@ -10682,15 +10666,17 @@
         </is>
       </c>
       <c r="H200" s="13" t="n">
-        <v>6.45</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="I200" s="9" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="J200" s="7" t="n"/>
+        <v>-0.48</v>
+      </c>
+      <c r="J200" s="7" t="n">
+        <v>0.73</v>
+      </c>
       <c r="K200" s="7" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>缩量</t>
         </is>
       </c>
       <c r="L200" s="7" t="inlineStr"/>
@@ -10699,31 +10685,31 @@
     <row r="201" ht="26" customHeight="1">
       <c r="A201" s="10" t="inlineStr">
         <is>
-          <t>603991</t>
+          <t>300199</t>
         </is>
       </c>
       <c r="B201" s="11" t="inlineStr">
         <is>
-          <t>领先股份</t>
+          <t>翰宇药业</t>
         </is>
       </c>
       <c r="C201" s="10" t="inlineStr">
         <is>
-          <t>半导体/芯片</t>
+          <t>创新药/CRO</t>
         </is>
       </c>
       <c r="D201" s="10" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="E201" s="10" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="F201" s="10" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G201" s="10" t="inlineStr">
         <is>
@@ -10731,17 +10717,17 @@
         </is>
       </c>
       <c r="H201" s="12" t="n">
-        <v>10</v>
+        <v>6.94</v>
       </c>
       <c r="I201" s="14" t="n">
-        <v>1.07</v>
+        <v>0.21</v>
       </c>
       <c r="J201" s="10" t="n">
-        <v>1.05</v>
+        <v>0.74</v>
       </c>
       <c r="K201" s="10" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>缩量</t>
         </is>
       </c>
       <c r="L201" s="10" t="inlineStr"/>
@@ -10750,12 +10736,12 @@
     <row r="202" ht="26" customHeight="1">
       <c r="A202" s="7" t="inlineStr">
         <is>
-          <t>603211</t>
+          <t>002747</t>
         </is>
       </c>
       <c r="B202" s="8" t="inlineStr">
         <is>
-          <t>晋拓股份</t>
+          <t>埃斯顿</t>
         </is>
       </c>
       <c r="C202" s="7" t="inlineStr">
@@ -10765,16 +10751,16 @@
       </c>
       <c r="D202" s="7" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="E202" s="7" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="F202" s="7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G202" s="7" t="inlineStr">
         <is>
@@ -10782,10 +10768,10 @@
         </is>
       </c>
       <c r="H202" s="13" t="n">
-        <v>9.99</v>
+        <v>6.45</v>
       </c>
       <c r="I202" s="9" t="n">
-        <v>1.26</v>
+        <v>0.74</v>
       </c>
       <c r="J202" s="7" t="n"/>
       <c r="K202" s="7" t="inlineStr">
@@ -10797,88 +10783,84 @@
       <c r="M202" s="7" t="inlineStr"/>
     </row>
     <row r="203" ht="26" customHeight="1">
-      <c r="A203" s="15" t="inlineStr">
-        <is>
-          <t>688720</t>
-        </is>
-      </c>
-      <c r="B203" s="16" t="inlineStr">
-        <is>
-          <t>艾森股份</t>
-        </is>
-      </c>
-      <c r="C203" s="15" t="inlineStr">
+      <c r="A203" s="10" t="inlineStr">
+        <is>
+          <t>603991</t>
+        </is>
+      </c>
+      <c r="B203" s="11" t="inlineStr">
+        <is>
+          <t>领先股份</t>
+        </is>
+      </c>
+      <c r="C203" s="10" t="inlineStr">
         <is>
           <t>半导体/芯片</t>
         </is>
       </c>
-      <c r="D203" s="15" t="inlineStr">
+      <c r="D203" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="E203" s="10" t="inlineStr">
         <is>
           <t>2026-07-09</t>
         </is>
       </c>
-      <c r="E203" s="15" t="inlineStr">
-        <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="F203" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G203" s="17" t="inlineStr">
-        <is>
-          <t>强势上攻</t>
-        </is>
-      </c>
-      <c r="H203" s="19" t="n">
-        <v>20</v>
-      </c>
-      <c r="I203" s="18" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="J203" s="15" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="K203" s="15" t="inlineStr">
-        <is>
-          <t>正常</t>
-        </is>
-      </c>
-      <c r="L203" s="15" t="inlineStr">
-        <is>
-          <t>首日涨幅&gt;20%</t>
-        </is>
-      </c>
-      <c r="M203" s="15" t="inlineStr"/>
+      <c r="F203" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="G203" s="10" t="inlineStr">
+        <is>
+          <t>强势上攻</t>
+        </is>
+      </c>
+      <c r="H203" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="I203" s="14" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="J203" s="10" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="K203" s="10" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="L203" s="10" t="inlineStr"/>
+      <c r="M203" s="10" t="inlineStr"/>
     </row>
     <row r="204" ht="26" customHeight="1">
       <c r="A204" s="7" t="inlineStr">
         <is>
-          <t>301151</t>
+          <t>603211</t>
         </is>
       </c>
       <c r="B204" s="8" t="inlineStr">
         <is>
-          <t>冠龙节能</t>
+          <t>晋拓股份</t>
         </is>
       </c>
       <c r="C204" s="7" t="inlineStr">
         <is>
-          <t>算力/通信</t>
+          <t>机器人</t>
         </is>
       </c>
       <c r="D204" s="7" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="E204" s="7" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="F204" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G204" s="7" t="inlineStr">
         <is>
@@ -10886,309 +10868,311 @@
         </is>
       </c>
       <c r="H204" s="13" t="n">
-        <v>7.33</v>
+        <v>9.99</v>
       </c>
       <c r="I204" s="9" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="J204" s="7" t="n">
-        <v>0.68</v>
-      </c>
+        <v>1.26</v>
+      </c>
+      <c r="J204" s="7" t="n"/>
       <c r="K204" s="7" t="inlineStr">
         <is>
-          <t>缩量</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="L204" s="7" t="inlineStr"/>
       <c r="M204" s="7" t="inlineStr"/>
     </row>
     <row r="205" ht="26" customHeight="1">
-      <c r="A205" s="10" t="inlineStr">
+      <c r="A205" s="15" t="inlineStr">
+        <is>
+          <t>688720</t>
+        </is>
+      </c>
+      <c r="B205" s="16" t="inlineStr">
+        <is>
+          <t>艾森股份</t>
+        </is>
+      </c>
+      <c r="C205" s="15" t="inlineStr">
+        <is>
+          <t>半导体/芯片</t>
+        </is>
+      </c>
+      <c r="D205" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="E205" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="F205" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G205" s="17" t="inlineStr">
+        <is>
+          <t>强势上攻</t>
+        </is>
+      </c>
+      <c r="H205" s="19" t="n">
+        <v>20</v>
+      </c>
+      <c r="I205" s="18" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="J205" s="15" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="K205" s="15" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="L205" s="15" t="inlineStr">
+        <is>
+          <t>首日涨幅&gt;20%</t>
+        </is>
+      </c>
+      <c r="M205" s="15" t="inlineStr"/>
+    </row>
+    <row r="206" ht="26" customHeight="1">
+      <c r="A206" s="7" t="inlineStr">
+        <is>
+          <t>301151</t>
+        </is>
+      </c>
+      <c r="B206" s="8" t="inlineStr">
+        <is>
+          <t>冠龙节能</t>
+        </is>
+      </c>
+      <c r="C206" s="7" t="inlineStr">
+        <is>
+          <t>算力/通信</t>
+        </is>
+      </c>
+      <c r="D206" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="E206" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="F206" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="G206" s="7" t="inlineStr">
+        <is>
+          <t>强势上攻</t>
+        </is>
+      </c>
+      <c r="H206" s="13" t="n">
+        <v>7.33</v>
+      </c>
+      <c r="I206" s="9" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="J206" s="7" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="K206" s="7" t="inlineStr">
+        <is>
+          <t>缩量</t>
+        </is>
+      </c>
+      <c r="L206" s="7" t="inlineStr"/>
+      <c r="M206" s="7" t="inlineStr"/>
+    </row>
+    <row r="207" ht="26" customHeight="1">
+      <c r="A207" s="10" t="inlineStr">
         <is>
           <t>688359</t>
         </is>
       </c>
-      <c r="B205" s="11" t="inlineStr">
+      <c r="B207" s="11" t="inlineStr">
         <is>
           <t>三孚新科</t>
         </is>
       </c>
-      <c r="C205" s="10" t="inlineStr">
+      <c r="C207" s="10" t="inlineStr">
         <is>
           <t>半导体/芯片</t>
         </is>
       </c>
-      <c r="D205" s="10" t="inlineStr">
+      <c r="D207" s="10" t="inlineStr">
         <is>
           <t>2026-07-01</t>
         </is>
       </c>
-      <c r="E205" s="10" t="inlineStr">
+      <c r="E207" s="10" t="inlineStr">
         <is>
           <t>2026-07-01</t>
         </is>
       </c>
-      <c r="F205" s="10" t="n">
+      <c r="F207" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="G205" s="10" t="inlineStr">
-        <is>
-          <t>强势上攻</t>
-        </is>
-      </c>
-      <c r="H205" s="12" t="n">
+      <c r="G207" s="10" t="inlineStr">
+        <is>
+          <t>强势上攻</t>
+        </is>
+      </c>
+      <c r="H207" s="12" t="n">
         <v>7.59</v>
       </c>
-      <c r="I205" s="14" t="n">
+      <c r="I207" s="14" t="n">
         <v>2.6</v>
       </c>
-      <c r="J205" s="10" t="n">
+      <c r="J207" s="10" t="n">
         <v>1.04</v>
       </c>
-      <c r="K205" s="10" t="inlineStr">
-        <is>
-          <t>正常</t>
-        </is>
-      </c>
-      <c r="L205" s="10" t="inlineStr"/>
-      <c r="M205" s="10" t="inlineStr"/>
-    </row>
-    <row r="206" ht="26" customHeight="1">
-      <c r="A206" s="15" t="inlineStr">
+      <c r="K207" s="10" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="L207" s="10" t="inlineStr"/>
+      <c r="M207" s="10" t="inlineStr"/>
+    </row>
+    <row r="208" ht="26" customHeight="1">
+      <c r="A208" s="15" t="inlineStr">
         <is>
           <t>688216</t>
         </is>
       </c>
-      <c r="B206" s="16" t="inlineStr">
+      <c r="B208" s="16" t="inlineStr">
         <is>
           <t>气派科技</t>
         </is>
       </c>
-      <c r="C206" s="15" t="inlineStr">
+      <c r="C208" s="15" t="inlineStr">
         <is>
           <t>半导体/芯片</t>
         </is>
       </c>
-      <c r="D206" s="15" t="inlineStr">
+      <c r="D208" s="15" t="inlineStr">
         <is>
           <t>2026-07-02</t>
         </is>
       </c>
-      <c r="E206" s="15" t="inlineStr">
+      <c r="E208" s="15" t="inlineStr">
         <is>
           <t>2026-07-02</t>
         </is>
       </c>
-      <c r="F206" s="15" t="n">
+      <c r="F208" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="G206" s="17" t="inlineStr">
-        <is>
-          <t>强势上攻</t>
-        </is>
-      </c>
-      <c r="H206" s="19" t="n">
+      <c r="G208" s="17" t="inlineStr">
+        <is>
+          <t>强势上攻</t>
+        </is>
+      </c>
+      <c r="H208" s="19" t="n">
         <v>20</v>
       </c>
-      <c r="I206" s="15" t="n">
+      <c r="I208" s="15" t="n">
         <v>3.99</v>
       </c>
-      <c r="J206" s="15" t="n">
+      <c r="J208" s="15" t="n">
         <v>1.63</v>
       </c>
-      <c r="K206" s="15" t="inlineStr">
+      <c r="K208" s="15" t="inlineStr">
         <is>
           <t>放量</t>
         </is>
       </c>
-      <c r="L206" s="15" t="inlineStr">
+      <c r="L208" s="15" t="inlineStr">
         <is>
           <t>首日涨幅&gt;20%</t>
         </is>
       </c>
-      <c r="M206" s="15" t="inlineStr"/>
-    </row>
-    <row r="207" ht="26" customHeight="1">
-      <c r="A207" s="15" t="inlineStr">
+      <c r="M208" s="15" t="inlineStr"/>
+    </row>
+    <row r="209" ht="26" customHeight="1">
+      <c r="A209" s="15" t="inlineStr">
         <is>
           <t>301092</t>
         </is>
       </c>
-      <c r="B207" s="16" t="inlineStr">
+      <c r="B209" s="16" t="inlineStr">
         <is>
           <t>争光股份</t>
         </is>
       </c>
-      <c r="C207" s="15" t="inlineStr">
+      <c r="C209" s="15" t="inlineStr">
         <is>
           <t>算力/通信</t>
         </is>
       </c>
-      <c r="D207" s="15" t="inlineStr">
+      <c r="D209" s="15" t="inlineStr">
         <is>
           <t>2026-07-02</t>
         </is>
       </c>
-      <c r="E207" s="15" t="inlineStr">
+      <c r="E209" s="15" t="inlineStr">
         <is>
           <t>2026-07-17</t>
         </is>
       </c>
-      <c r="F207" s="15" t="n">
+      <c r="F209" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="G207" s="17" t="inlineStr">
-        <is>
-          <t>强势上攻</t>
-        </is>
-      </c>
-      <c r="H207" s="19" t="n">
+      <c r="G209" s="17" t="inlineStr">
+        <is>
+          <t>强势上攻</t>
+        </is>
+      </c>
+      <c r="H209" s="19" t="n">
         <v>11.13</v>
       </c>
-      <c r="I207" s="15" t="n">
+      <c r="I209" s="15" t="n">
         <v>4.04</v>
       </c>
-      <c r="J207" s="15" t="n">
+      <c r="J209" s="15" t="n">
         <v>1.14</v>
       </c>
-      <c r="K207" s="15" t="inlineStr">
-        <is>
-          <t>正常</t>
-        </is>
-      </c>
-      <c r="L207" s="15" t="inlineStr">
+      <c r="K209" s="15" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="L209" s="15" t="inlineStr">
         <is>
           <t>首日涨幅&gt;20%</t>
         </is>
       </c>
-      <c r="M207" s="15" t="inlineStr"/>
-    </row>
-    <row r="208" ht="26" customHeight="1">
-      <c r="A208" s="7" t="inlineStr">
-        <is>
-          <t>300990</t>
-        </is>
-      </c>
-      <c r="B208" s="8" t="inlineStr">
-        <is>
-          <t>同飞股份</t>
-        </is>
-      </c>
-      <c r="C208" s="7" t="inlineStr">
-        <is>
-          <t>算力/通信</t>
-        </is>
-      </c>
-      <c r="D208" s="7" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="E208" s="7" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="F208" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G208" s="7" t="inlineStr">
-        <is>
-          <t>强势上攻</t>
-        </is>
-      </c>
-      <c r="H208" s="13" t="n">
-        <v>14.69</v>
-      </c>
-      <c r="I208" s="7" t="n">
-        <v>4.29</v>
-      </c>
-      <c r="J208" s="7" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="K208" s="7" t="inlineStr">
-        <is>
-          <t>放量</t>
-        </is>
-      </c>
-      <c r="L208" s="7" t="inlineStr"/>
-      <c r="M208" s="7" t="inlineStr"/>
-    </row>
-    <row r="209" ht="26" customHeight="1">
-      <c r="A209" s="10" t="inlineStr">
-        <is>
-          <t>300878</t>
-        </is>
-      </c>
-      <c r="B209" s="11" t="inlineStr">
-        <is>
-          <t>维康药业</t>
-        </is>
-      </c>
-      <c r="C209" s="10" t="inlineStr">
-        <is>
-          <t>创新药/CRO</t>
-        </is>
-      </c>
-      <c r="D209" s="10" t="inlineStr">
-        <is>
-          <t>2026-07-03</t>
-        </is>
-      </c>
-      <c r="E209" s="10" t="inlineStr">
-        <is>
-          <t>2026-07-03</t>
-        </is>
-      </c>
-      <c r="F209" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="G209" s="10" t="inlineStr">
-        <is>
-          <t>强势上攻</t>
-        </is>
-      </c>
-      <c r="H209" s="12" t="n">
-        <v>10.66</v>
-      </c>
-      <c r="I209" s="10" t="n">
-        <v>4.77</v>
-      </c>
-      <c r="J209" s="10" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="K209" s="10" t="inlineStr">
-        <is>
-          <t>正常</t>
-        </is>
-      </c>
-      <c r="L209" s="10" t="inlineStr"/>
-      <c r="M209" s="10" t="inlineStr"/>
+      <c r="M209" s="15" t="inlineStr"/>
     </row>
     <row r="210" ht="26" customHeight="1">
       <c r="A210" s="7" t="inlineStr">
         <is>
-          <t>688981</t>
+          <t>300990</t>
         </is>
       </c>
       <c r="B210" s="8" t="inlineStr">
         <is>
-          <t>中芯国际</t>
+          <t>同飞股份</t>
         </is>
       </c>
       <c r="C210" s="7" t="inlineStr">
         <is>
-          <t>半导体/芯片</t>
+          <t>算力/通信</t>
         </is>
       </c>
       <c r="D210" s="7" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="E210" s="7" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="F210" s="7" t="n">
@@ -11200,17 +11184,17 @@
         </is>
       </c>
       <c r="H210" s="13" t="n">
-        <v>13.74</v>
+        <v>14.69</v>
       </c>
       <c r="I210" s="7" t="n">
-        <v>5.11</v>
+        <v>4.29</v>
       </c>
       <c r="J210" s="7" t="n">
-        <v>1.09</v>
+        <v>2.06</v>
       </c>
       <c r="K210" s="7" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>放量</t>
         </is>
       </c>
       <c r="L210" s="7" t="inlineStr"/>
@@ -11219,12 +11203,12 @@
     <row r="211" ht="26" customHeight="1">
       <c r="A211" s="10" t="inlineStr">
         <is>
-          <t>002317</t>
+          <t>300878</t>
         </is>
       </c>
       <c r="B211" s="11" t="inlineStr">
         <is>
-          <t>众生药业</t>
+          <t>维康药业</t>
         </is>
       </c>
       <c r="C211" s="10" t="inlineStr">
@@ -11234,16 +11218,16 @@
       </c>
       <c r="D211" s="10" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="E211" s="10" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="F211" s="10" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G211" s="10" t="inlineStr">
         <is>
@@ -11251,17 +11235,17 @@
         </is>
       </c>
       <c r="H211" s="12" t="n">
-        <v>6.87</v>
+        <v>10.66</v>
       </c>
       <c r="I211" s="10" t="n">
-        <v>5.44</v>
+        <v>4.77</v>
       </c>
       <c r="J211" s="10" t="n">
-        <v>1.33</v>
+        <v>1.19</v>
       </c>
       <c r="K211" s="10" t="inlineStr">
         <is>
-          <t>放量</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="L211" s="10" t="inlineStr"/>
@@ -11270,27 +11254,27 @@
     <row r="212" ht="26" customHeight="1">
       <c r="A212" s="7" t="inlineStr">
         <is>
-          <t>603757</t>
+          <t>688981</t>
         </is>
       </c>
       <c r="B212" s="8" t="inlineStr">
         <is>
-          <t>大元泵业</t>
+          <t>中芯国际</t>
         </is>
       </c>
       <c r="C212" s="7" t="inlineStr">
         <is>
-          <t>算力/通信</t>
+          <t>半导体/芯片</t>
         </is>
       </c>
       <c r="D212" s="7" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="E212" s="7" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="F212" s="7" t="n">
@@ -11302,13 +11286,13 @@
         </is>
       </c>
       <c r="H212" s="13" t="n">
-        <v>10</v>
+        <v>13.74</v>
       </c>
       <c r="I212" s="7" t="n">
-        <v>5.88</v>
+        <v>5.11</v>
       </c>
       <c r="J212" s="7" t="n">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="K212" s="7" t="inlineStr">
         <is>
@@ -11321,31 +11305,31 @@
     <row r="213" ht="26" customHeight="1">
       <c r="A213" s="10" t="inlineStr">
         <is>
-          <t>688103</t>
+          <t>002317</t>
         </is>
       </c>
       <c r="B213" s="11" t="inlineStr">
         <is>
-          <t>国力电子</t>
+          <t>众生药业</t>
         </is>
       </c>
       <c r="C213" s="10" t="inlineStr">
         <is>
-          <t>半导体/芯片</t>
+          <t>创新药/CRO</t>
         </is>
       </c>
       <c r="D213" s="10" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="E213" s="10" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="F213" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G213" s="10" t="inlineStr">
         <is>
@@ -11353,17 +11337,17 @@
         </is>
       </c>
       <c r="H213" s="12" t="n">
-        <v>15.13</v>
+        <v>6.87</v>
       </c>
       <c r="I213" s="10" t="n">
-        <v>5.89</v>
+        <v>5.44</v>
       </c>
       <c r="J213" s="10" t="n">
-        <v>0.84</v>
+        <v>1.33</v>
       </c>
       <c r="K213" s="10" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>放量</t>
         </is>
       </c>
       <c r="L213" s="10" t="inlineStr"/>
@@ -11372,27 +11356,27 @@
     <row r="214" ht="26" customHeight="1">
       <c r="A214" s="7" t="inlineStr">
         <is>
-          <t>688202</t>
+          <t>603757</t>
         </is>
       </c>
       <c r="B214" s="8" t="inlineStr">
         <is>
-          <t>美迪西</t>
+          <t>大元泵业</t>
         </is>
       </c>
       <c r="C214" s="7" t="inlineStr">
         <is>
-          <t>创新药/CRO</t>
+          <t>算力/通信</t>
         </is>
       </c>
       <c r="D214" s="7" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="E214" s="7" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="F214" s="7" t="n">
@@ -11404,17 +11388,17 @@
         </is>
       </c>
       <c r="H214" s="13" t="n">
-        <v>12.77</v>
+        <v>10</v>
       </c>
       <c r="I214" s="7" t="n">
-        <v>6.29</v>
+        <v>5.88</v>
       </c>
       <c r="J214" s="7" t="n">
-        <v>1.27</v>
+        <v>1.15</v>
       </c>
       <c r="K214" s="7" t="inlineStr">
         <is>
-          <t>放量</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="L214" s="7" t="inlineStr"/>
@@ -11423,12 +11407,12 @@
     <row r="215" ht="26" customHeight="1">
       <c r="A215" s="10" t="inlineStr">
         <is>
-          <t>688206</t>
+          <t>688103</t>
         </is>
       </c>
       <c r="B215" s="11" t="inlineStr">
         <is>
-          <t>概伦电子</t>
+          <t>国力电子</t>
         </is>
       </c>
       <c r="C215" s="10" t="inlineStr">
@@ -11438,12 +11422,12 @@
       </c>
       <c r="D215" s="10" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="E215" s="10" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="F215" s="10" t="n">
@@ -11455,13 +11439,13 @@
         </is>
       </c>
       <c r="H215" s="12" t="n">
-        <v>10.07</v>
+        <v>15.13</v>
       </c>
       <c r="I215" s="10" t="n">
-        <v>7.21</v>
+        <v>5.89</v>
       </c>
       <c r="J215" s="10" t="n">
-        <v>0.8</v>
+        <v>0.84</v>
       </c>
       <c r="K215" s="10" t="inlineStr">
         <is>
@@ -11474,27 +11458,27 @@
     <row r="216" ht="26" customHeight="1">
       <c r="A216" s="7" t="inlineStr">
         <is>
-          <t>688138</t>
+          <t>688202</t>
         </is>
       </c>
       <c r="B216" s="8" t="inlineStr">
         <is>
-          <t>清溢光电</t>
+          <t>美迪西</t>
         </is>
       </c>
       <c r="C216" s="7" t="inlineStr">
         <is>
-          <t>半导体/芯片</t>
+          <t>创新药/CRO</t>
         </is>
       </c>
       <c r="D216" s="7" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="E216" s="7" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="F216" s="7" t="n">
@@ -11506,13 +11490,13 @@
         </is>
       </c>
       <c r="H216" s="13" t="n">
-        <v>7.21</v>
+        <v>12.77</v>
       </c>
       <c r="I216" s="7" t="n">
-        <v>7.74</v>
+        <v>6.29</v>
       </c>
       <c r="J216" s="7" t="n">
-        <v>1.44</v>
+        <v>1.27</v>
       </c>
       <c r="K216" s="7" t="inlineStr">
         <is>
@@ -11525,31 +11509,31 @@
     <row r="217" ht="26" customHeight="1">
       <c r="A217" s="10" t="inlineStr">
         <is>
-          <t>002821</t>
+          <t>688206</t>
         </is>
       </c>
       <c r="B217" s="11" t="inlineStr">
         <is>
-          <t>凯莱英</t>
+          <t>概伦电子</t>
         </is>
       </c>
       <c r="C217" s="10" t="inlineStr">
         <is>
-          <t>创新药/CRO</t>
+          <t>半导体/芯片</t>
         </is>
       </c>
       <c r="D217" s="10" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="E217" s="10" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="F217" s="10" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G217" s="10" t="inlineStr">
         <is>
@@ -11557,13 +11541,13 @@
         </is>
       </c>
       <c r="H217" s="12" t="n">
-        <v>10</v>
+        <v>10.07</v>
       </c>
       <c r="I217" s="10" t="n">
-        <v>8.52</v>
+        <v>7.21</v>
       </c>
       <c r="J217" s="10" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="K217" s="10" t="inlineStr">
         <is>
@@ -11576,27 +11560,27 @@
     <row r="218" ht="26" customHeight="1">
       <c r="A218" s="7" t="inlineStr">
         <is>
-          <t>688321</t>
+          <t>688138</t>
         </is>
       </c>
       <c r="B218" s="8" t="inlineStr">
         <is>
-          <t>微芯生物</t>
+          <t>清溢光电</t>
         </is>
       </c>
       <c r="C218" s="7" t="inlineStr">
         <is>
-          <t>创新药/CRO</t>
+          <t>半导体/芯片</t>
         </is>
       </c>
       <c r="D218" s="7" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="E218" s="7" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="F218" s="7" t="n">
@@ -11608,15 +11592,17 @@
         </is>
       </c>
       <c r="H218" s="13" t="n">
-        <v>12.58</v>
+        <v>7.21</v>
       </c>
       <c r="I218" s="7" t="n">
-        <v>8.58</v>
-      </c>
-      <c r="J218" s="7" t="n"/>
+        <v>7.74</v>
+      </c>
+      <c r="J218" s="7" t="n">
+        <v>1.44</v>
+      </c>
       <c r="K218" s="7" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>放量</t>
         </is>
       </c>
       <c r="L218" s="7" t="inlineStr"/>
@@ -11625,31 +11611,31 @@
     <row r="219" ht="26" customHeight="1">
       <c r="A219" s="10" t="inlineStr">
         <is>
-          <t>688432</t>
+          <t>002821</t>
         </is>
       </c>
       <c r="B219" s="11" t="inlineStr">
         <is>
-          <t>有研硅</t>
+          <t>凯莱英</t>
         </is>
       </c>
       <c r="C219" s="10" t="inlineStr">
         <is>
-          <t>半导体/芯片</t>
+          <t>创新药/CRO</t>
         </is>
       </c>
       <c r="D219" s="10" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="E219" s="10" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="F219" s="10" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G219" s="10" t="inlineStr">
         <is>
@@ -11657,17 +11643,17 @@
         </is>
       </c>
       <c r="H219" s="12" t="n">
-        <v>5.26</v>
+        <v>10</v>
       </c>
       <c r="I219" s="10" t="n">
-        <v>8.609999999999999</v>
+        <v>8.52</v>
       </c>
       <c r="J219" s="10" t="n">
-        <v>0.74</v>
+        <v>1.2</v>
       </c>
       <c r="K219" s="10" t="inlineStr">
         <is>
-          <t>缩量</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="L219" s="10" t="inlineStr"/>
@@ -11676,12 +11662,12 @@
     <row r="220" ht="26" customHeight="1">
       <c r="A220" s="7" t="inlineStr">
         <is>
-          <t>688266</t>
+          <t>688321</t>
         </is>
       </c>
       <c r="B220" s="8" t="inlineStr">
         <is>
-          <t>泽璟制药</t>
+          <t>微芯生物</t>
         </is>
       </c>
       <c r="C220" s="7" t="inlineStr">
@@ -11691,16 +11677,16 @@
       </c>
       <c r="D220" s="7" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="E220" s="7" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="F220" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G220" s="7" t="inlineStr">
         <is>
@@ -11708,17 +11694,15 @@
         </is>
       </c>
       <c r="H220" s="13" t="n">
-        <v>4.91</v>
+        <v>12.58</v>
       </c>
       <c r="I220" s="7" t="n">
-        <v>10.06</v>
-      </c>
-      <c r="J220" s="7" t="n">
-        <v>0.77</v>
-      </c>
+        <v>8.58</v>
+      </c>
+      <c r="J220" s="7" t="n"/>
       <c r="K220" s="7" t="inlineStr">
         <is>
-          <t>缩量</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="L220" s="7" t="inlineStr"/>
@@ -11727,17 +11711,17 @@
     <row r="221" ht="26" customHeight="1">
       <c r="A221" s="10" t="inlineStr">
         <is>
-          <t>002422</t>
+          <t>688432</t>
         </is>
       </c>
       <c r="B221" s="11" t="inlineStr">
         <is>
-          <t>科伦药业</t>
+          <t>有研硅</t>
         </is>
       </c>
       <c r="C221" s="10" t="inlineStr">
         <is>
-          <t>创新药/CRO</t>
+          <t>半导体/芯片</t>
         </is>
       </c>
       <c r="D221" s="10" t="inlineStr">
@@ -11747,11 +11731,11 @@
       </c>
       <c r="E221" s="10" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="F221" s="10" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G221" s="10" t="inlineStr">
         <is>
@@ -11759,17 +11743,17 @@
         </is>
       </c>
       <c r="H221" s="12" t="n">
-        <v>7.22</v>
+        <v>5.26</v>
       </c>
       <c r="I221" s="10" t="n">
-        <v>10.78</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="J221" s="10" t="n">
-        <v>1.22</v>
+        <v>0.74</v>
       </c>
       <c r="K221" s="10" t="inlineStr">
         <is>
-          <t>放量</t>
+          <t>缩量</t>
         </is>
       </c>
       <c r="L221" s="10" t="inlineStr"/>
@@ -11778,12 +11762,12 @@
     <row r="222" ht="26" customHeight="1">
       <c r="A222" s="7" t="inlineStr">
         <is>
-          <t>603669</t>
+          <t>688266</t>
         </is>
       </c>
       <c r="B222" s="8" t="inlineStr">
         <is>
-          <t>灵康药业</t>
+          <t>泽璟制药</t>
         </is>
       </c>
       <c r="C222" s="7" t="inlineStr">
@@ -11793,16 +11777,16 @@
       </c>
       <c r="D222" s="7" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="E222" s="7" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="F222" s="7" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G222" s="7" t="inlineStr">
         <is>
@@ -11810,17 +11794,17 @@
         </is>
       </c>
       <c r="H222" s="13" t="n">
-        <v>9.59</v>
+        <v>4.91</v>
       </c>
       <c r="I222" s="7" t="n">
-        <v>13.41</v>
+        <v>10.06</v>
       </c>
       <c r="J222" s="7" t="n">
-        <v>2.57</v>
+        <v>0.77</v>
       </c>
       <c r="K222" s="7" t="inlineStr">
         <is>
-          <t>放量</t>
+          <t>缩量</t>
         </is>
       </c>
       <c r="L222" s="7" t="inlineStr"/>
@@ -11829,12 +11813,12 @@
     <row r="223" ht="26" customHeight="1">
       <c r="A223" s="10" t="inlineStr">
         <is>
-          <t>688758</t>
+          <t>002422</t>
         </is>
       </c>
       <c r="B223" s="11" t="inlineStr">
         <is>
-          <t>赛分科技</t>
+          <t>科伦药业</t>
         </is>
       </c>
       <c r="C223" s="10" t="inlineStr">
@@ -11844,16 +11828,16 @@
       </c>
       <c r="D223" s="10" t="inlineStr">
         <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="E223" s="10" t="inlineStr">
+        <is>
           <t>2026-07-03</t>
         </is>
       </c>
-      <c r="E223" s="10" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
       <c r="F223" s="10" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G223" s="10" t="inlineStr">
         <is>
@@ -11861,13 +11845,13 @@
         </is>
       </c>
       <c r="H223" s="12" t="n">
-        <v>3.66</v>
+        <v>7.22</v>
       </c>
       <c r="I223" s="10" t="n">
-        <v>13.71</v>
+        <v>10.78</v>
       </c>
       <c r="J223" s="10" t="n">
-        <v>1.86</v>
+        <v>1.22</v>
       </c>
       <c r="K223" s="10" t="inlineStr">
         <is>
@@ -11880,31 +11864,31 @@
     <row r="224" ht="26" customHeight="1">
       <c r="A224" s="7" t="inlineStr">
         <is>
-          <t>688702</t>
+          <t>603669</t>
         </is>
       </c>
       <c r="B224" s="8" t="inlineStr">
         <is>
-          <t>盛科通信</t>
+          <t>灵康药业</t>
         </is>
       </c>
       <c r="C224" s="7" t="inlineStr">
         <is>
-          <t>算力/通信</t>
+          <t>创新药/CRO</t>
         </is>
       </c>
       <c r="D224" s="7" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="E224" s="7" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="F224" s="7" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G224" s="7" t="inlineStr">
         <is>
@@ -11912,13 +11896,13 @@
         </is>
       </c>
       <c r="H224" s="13" t="n">
-        <v>8.890000000000001</v>
+        <v>9.59</v>
       </c>
       <c r="I224" s="7" t="n">
-        <v>13.92</v>
+        <v>13.41</v>
       </c>
       <c r="J224" s="7" t="n">
-        <v>1.31</v>
+        <v>2.57</v>
       </c>
       <c r="K224" s="7" t="inlineStr">
         <is>
@@ -11931,31 +11915,31 @@
     <row r="225" ht="26" customHeight="1">
       <c r="A225" s="10" t="inlineStr">
         <is>
-          <t>688584</t>
+          <t>688758</t>
         </is>
       </c>
       <c r="B225" s="11" t="inlineStr">
         <is>
-          <t>上海合晶</t>
+          <t>赛分科技</t>
         </is>
       </c>
       <c r="C225" s="10" t="inlineStr">
         <is>
-          <t>半导体/芯片</t>
+          <t>创新药/CRO</t>
         </is>
       </c>
       <c r="D225" s="10" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="E225" s="10" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="F225" s="10" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G225" s="10" t="inlineStr">
         <is>
@@ -11963,17 +11947,17 @@
         </is>
       </c>
       <c r="H225" s="12" t="n">
-        <v>5.98</v>
+        <v>3.66</v>
       </c>
       <c r="I225" s="10" t="n">
-        <v>13.95</v>
+        <v>13.71</v>
       </c>
       <c r="J225" s="10" t="n">
-        <v>1.09</v>
+        <v>1.86</v>
       </c>
       <c r="K225" s="10" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>放量</t>
         </is>
       </c>
       <c r="L225" s="10" t="inlineStr"/>
@@ -11982,17 +11966,17 @@
     <row r="226" ht="26" customHeight="1">
       <c r="A226" s="7" t="inlineStr">
         <is>
-          <t>300759</t>
+          <t>688702</t>
         </is>
       </c>
       <c r="B226" s="8" t="inlineStr">
         <is>
-          <t>康龙化成</t>
+          <t>盛科通信</t>
         </is>
       </c>
       <c r="C226" s="7" t="inlineStr">
         <is>
-          <t>创新药/CRO</t>
+          <t>算力/通信</t>
         </is>
       </c>
       <c r="D226" s="7" t="inlineStr">
@@ -12002,11 +11986,11 @@
       </c>
       <c r="E226" s="7" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="F226" s="7" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G226" s="7" t="inlineStr">
         <is>
@@ -12014,13 +11998,13 @@
         </is>
       </c>
       <c r="H226" s="13" t="n">
-        <v>5.58</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="I226" s="7" t="n">
-        <v>14.26</v>
+        <v>13.92</v>
       </c>
       <c r="J226" s="7" t="n">
-        <v>1.57</v>
+        <v>1.31</v>
       </c>
       <c r="K226" s="7" t="inlineStr">
         <is>
@@ -12031,88 +12015,84 @@
       <c r="M226" s="7" t="inlineStr"/>
     </row>
     <row r="227" ht="26" customHeight="1">
-      <c r="A227" s="15" t="inlineStr">
-        <is>
-          <t>688328</t>
-        </is>
-      </c>
-      <c r="B227" s="16" t="inlineStr">
-        <is>
-          <t>深科达</t>
-        </is>
-      </c>
-      <c r="C227" s="15" t="inlineStr">
+      <c r="A227" s="10" t="inlineStr">
+        <is>
+          <t>688584</t>
+        </is>
+      </c>
+      <c r="B227" s="11" t="inlineStr">
+        <is>
+          <t>上海合晶</t>
+        </is>
+      </c>
+      <c r="C227" s="10" t="inlineStr">
         <is>
           <t>半导体/芯片</t>
         </is>
       </c>
-      <c r="D227" s="15" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="E227" s="15" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="F227" s="15" t="n">
+      <c r="D227" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="E227" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="F227" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="G227" s="17" t="inlineStr">
-        <is>
-          <t>强势上攻</t>
-        </is>
-      </c>
-      <c r="H227" s="19" t="n">
-        <v>15.89</v>
-      </c>
-      <c r="I227" s="15" t="n">
-        <v>15.46</v>
-      </c>
-      <c r="J227" s="15" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="K227" s="15" t="inlineStr">
-        <is>
-          <t>正常</t>
-        </is>
-      </c>
-      <c r="L227" s="15" t="inlineStr">
-        <is>
-          <t>首日涨幅&gt;16%</t>
-        </is>
-      </c>
-      <c r="M227" s="15" t="inlineStr"/>
+      <c r="G227" s="10" t="inlineStr">
+        <is>
+          <t>强势上攻</t>
+        </is>
+      </c>
+      <c r="H227" s="12" t="n">
+        <v>5.98</v>
+      </c>
+      <c r="I227" s="10" t="n">
+        <v>13.95</v>
+      </c>
+      <c r="J227" s="10" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="K227" s="10" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="L227" s="10" t="inlineStr"/>
+      <c r="M227" s="10" t="inlineStr"/>
     </row>
     <row r="228" ht="26" customHeight="1">
       <c r="A228" s="7" t="inlineStr">
         <is>
-          <t>603065</t>
+          <t>300759</t>
         </is>
       </c>
       <c r="B228" s="8" t="inlineStr">
         <is>
-          <t>宿迁联盛</t>
+          <t>康龙化成</t>
         </is>
       </c>
       <c r="C228" s="7" t="inlineStr">
         <is>
-          <t>半导体/芯片</t>
+          <t>创新药/CRO</t>
         </is>
       </c>
       <c r="D228" s="7" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="E228" s="7" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="F228" s="7" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G228" s="7" t="inlineStr">
         <is>
@@ -12120,99 +12100,105 @@
         </is>
       </c>
       <c r="H228" s="13" t="n">
-        <v>10</v>
+        <v>5.58</v>
       </c>
       <c r="I228" s="7" t="n">
-        <v>15.51</v>
+        <v>14.26</v>
       </c>
       <c r="J228" s="7" t="n">
-        <v>0.9</v>
+        <v>1.57</v>
       </c>
       <c r="K228" s="7" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>放量</t>
         </is>
       </c>
       <c r="L228" s="7" t="inlineStr"/>
       <c r="M228" s="7" t="inlineStr"/>
     </row>
     <row r="229" ht="26" customHeight="1">
-      <c r="A229" s="10" t="inlineStr">
-        <is>
-          <t>688293</t>
-        </is>
-      </c>
-      <c r="B229" s="11" t="inlineStr">
-        <is>
-          <t>奥浦迈</t>
-        </is>
-      </c>
-      <c r="C229" s="10" t="inlineStr">
-        <is>
-          <t>创新药/CRO</t>
-        </is>
-      </c>
-      <c r="D229" s="10" t="inlineStr">
-        <is>
-          <t>2026-07-21</t>
-        </is>
-      </c>
-      <c r="E229" s="10" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="F229" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="G229" s="10" t="inlineStr">
-        <is>
-          <t>强势上攻</t>
-        </is>
-      </c>
-      <c r="H229" s="12" t="n">
-        <v>5.73</v>
-      </c>
-      <c r="I229" s="10" t="n">
-        <v>15.71</v>
-      </c>
-      <c r="J229" s="10" t="n"/>
-      <c r="K229" s="10" t="inlineStr">
-        <is>
-          <t>正常</t>
-        </is>
-      </c>
-      <c r="L229" s="10" t="inlineStr"/>
-      <c r="M229" s="10" t="inlineStr"/>
+      <c r="A229" s="15" t="inlineStr">
+        <is>
+          <t>688328</t>
+        </is>
+      </c>
+      <c r="B229" s="16" t="inlineStr">
+        <is>
+          <t>深科达</t>
+        </is>
+      </c>
+      <c r="C229" s="15" t="inlineStr">
+        <is>
+          <t>半导体/芯片</t>
+        </is>
+      </c>
+      <c r="D229" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="E229" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="F229" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G229" s="17" t="inlineStr">
+        <is>
+          <t>强势上攻</t>
+        </is>
+      </c>
+      <c r="H229" s="19" t="n">
+        <v>15.89</v>
+      </c>
+      <c r="I229" s="15" t="n">
+        <v>15.46</v>
+      </c>
+      <c r="J229" s="15" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="K229" s="15" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="L229" s="15" t="inlineStr">
+        <is>
+          <t>首日涨幅&gt;16%</t>
+        </is>
+      </c>
+      <c r="M229" s="15" t="inlineStr"/>
     </row>
     <row r="230" ht="26" customHeight="1">
       <c r="A230" s="7" t="inlineStr">
         <is>
-          <t>002396</t>
+          <t>603065</t>
         </is>
       </c>
       <c r="B230" s="8" t="inlineStr">
         <is>
-          <t>星网锐捷</t>
+          <t>宿迁联盛</t>
         </is>
       </c>
       <c r="C230" s="7" t="inlineStr">
         <is>
-          <t>算力/通信</t>
+          <t>半导体/芯片</t>
         </is>
       </c>
       <c r="D230" s="7" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="E230" s="7" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="F230" s="7" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G230" s="7" t="inlineStr">
         <is>
@@ -12220,13 +12206,13 @@
         </is>
       </c>
       <c r="H230" s="13" t="n">
-        <v>9.43</v>
+        <v>10</v>
       </c>
       <c r="I230" s="7" t="n">
-        <v>19.51</v>
+        <v>15.51</v>
       </c>
       <c r="J230" s="7" t="n">
-        <v>1.16</v>
+        <v>0.9</v>
       </c>
       <c r="K230" s="7" t="inlineStr">
         <is>
@@ -12239,22 +12225,22 @@
     <row r="231" ht="26" customHeight="1">
       <c r="A231" s="10" t="inlineStr">
         <is>
-          <t>000938</t>
+          <t>688293</t>
         </is>
       </c>
       <c r="B231" s="11" t="inlineStr">
         <is>
-          <t>紫光股份</t>
+          <t>奥浦迈</t>
         </is>
       </c>
       <c r="C231" s="10" t="inlineStr">
         <is>
-          <t>算力/通信</t>
+          <t>创新药/CRO</t>
         </is>
       </c>
       <c r="D231" s="10" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="E231" s="10" t="inlineStr">
@@ -12263,7 +12249,7 @@
         </is>
       </c>
       <c r="F231" s="10" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G231" s="10" t="inlineStr">
         <is>
@@ -12271,17 +12257,15 @@
         </is>
       </c>
       <c r="H231" s="12" t="n">
-        <v>8.300000000000001</v>
+        <v>5.73</v>
       </c>
       <c r="I231" s="10" t="n">
-        <v>21.31</v>
-      </c>
-      <c r="J231" s="10" t="n">
-        <v>1.23</v>
-      </c>
+        <v>15.71</v>
+      </c>
+      <c r="J231" s="10" t="n"/>
       <c r="K231" s="10" t="inlineStr">
         <is>
-          <t>放量</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="L231" s="10" t="inlineStr"/>
@@ -12290,31 +12274,31 @@
     <row r="232" ht="26" customHeight="1">
       <c r="A232" s="7" t="inlineStr">
         <is>
-          <t>002841</t>
+          <t>002396</t>
         </is>
       </c>
       <c r="B232" s="8" t="inlineStr">
         <is>
-          <t>视源股份</t>
+          <t>星网锐捷</t>
         </is>
       </c>
       <c r="C232" s="7" t="inlineStr">
         <is>
-          <t>机器人</t>
+          <t>算力/通信</t>
         </is>
       </c>
       <c r="D232" s="7" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="E232" s="7" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="F232" s="7" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G232" s="7" t="inlineStr">
         <is>
@@ -12322,13 +12306,13 @@
         </is>
       </c>
       <c r="H232" s="13" t="n">
-        <v>10</v>
+        <v>9.43</v>
       </c>
       <c r="I232" s="7" t="n">
-        <v>22.83</v>
+        <v>19.51</v>
       </c>
       <c r="J232" s="7" t="n">
-        <v>0.9</v>
+        <v>1.16</v>
       </c>
       <c r="K232" s="7" t="inlineStr">
         <is>
@@ -12341,31 +12325,31 @@
     <row r="233" ht="26" customHeight="1">
       <c r="A233" s="10" t="inlineStr">
         <is>
-          <t>603127</t>
+          <t>000938</t>
         </is>
       </c>
       <c r="B233" s="11" t="inlineStr">
         <is>
-          <t>昭衍新药</t>
+          <t>紫光股份</t>
         </is>
       </c>
       <c r="C233" s="10" t="inlineStr">
         <is>
-          <t>创新药/CRO</t>
+          <t>算力/通信</t>
         </is>
       </c>
       <c r="D233" s="10" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="E233" s="10" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="F233" s="10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G233" s="10" t="inlineStr">
         <is>
@@ -12373,13 +12357,13 @@
         </is>
       </c>
       <c r="H233" s="12" t="n">
-        <v>5.2</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I233" s="10" t="n">
-        <v>25.15</v>
+        <v>21.31</v>
       </c>
       <c r="J233" s="10" t="n">
-        <v>1.62</v>
+        <v>1.23</v>
       </c>
       <c r="K233" s="10" t="inlineStr">
         <is>
@@ -12390,241 +12374,243 @@
       <c r="M233" s="10" t="inlineStr"/>
     </row>
     <row r="234" ht="26" customHeight="1">
-      <c r="A234" s="15" t="inlineStr">
+      <c r="A234" s="7" t="inlineStr">
+        <is>
+          <t>002841</t>
+        </is>
+      </c>
+      <c r="B234" s="8" t="inlineStr">
+        <is>
+          <t>视源股份</t>
+        </is>
+      </c>
+      <c r="C234" s="7" t="inlineStr">
+        <is>
+          <t>机器人</t>
+        </is>
+      </c>
+      <c r="D234" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="E234" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="F234" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="G234" s="7" t="inlineStr">
+        <is>
+          <t>强势上攻</t>
+        </is>
+      </c>
+      <c r="H234" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="I234" s="7" t="n">
+        <v>22.83</v>
+      </c>
+      <c r="J234" s="7" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="K234" s="7" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="L234" s="7" t="inlineStr"/>
+      <c r="M234" s="7" t="inlineStr"/>
+    </row>
+    <row r="235" ht="26" customHeight="1">
+      <c r="A235" s="10" t="inlineStr">
+        <is>
+          <t>603127</t>
+        </is>
+      </c>
+      <c r="B235" s="11" t="inlineStr">
+        <is>
+          <t>昭衍新药</t>
+        </is>
+      </c>
+      <c r="C235" s="10" t="inlineStr">
+        <is>
+          <t>创新药/CRO</t>
+        </is>
+      </c>
+      <c r="D235" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="E235" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="F235" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="G235" s="10" t="inlineStr">
+        <is>
+          <t>强势上攻</t>
+        </is>
+      </c>
+      <c r="H235" s="12" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="I235" s="10" t="n">
+        <v>25.15</v>
+      </c>
+      <c r="J235" s="10" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="K235" s="10" t="inlineStr">
+        <is>
+          <t>放量</t>
+        </is>
+      </c>
+      <c r="L235" s="10" t="inlineStr"/>
+      <c r="M235" s="10" t="inlineStr"/>
+    </row>
+    <row r="236" ht="26" customHeight="1">
+      <c r="A236" s="15" t="inlineStr">
         <is>
           <t>688192</t>
         </is>
       </c>
-      <c r="B234" s="16" t="inlineStr">
+      <c r="B236" s="16" t="inlineStr">
         <is>
           <t>迪哲医药</t>
         </is>
       </c>
-      <c r="C234" s="15" t="inlineStr">
+      <c r="C236" s="15" t="inlineStr">
         <is>
           <t>创新药/CRO</t>
         </is>
       </c>
-      <c r="D234" s="15" t="inlineStr">
+      <c r="D236" s="15" t="inlineStr">
         <is>
           <t>2026-07-15</t>
         </is>
       </c>
-      <c r="E234" s="15" t="inlineStr">
+      <c r="E236" s="15" t="inlineStr">
         <is>
           <t>2026-07-15</t>
         </is>
       </c>
-      <c r="F234" s="15" t="n">
+      <c r="F236" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="G234" s="17" t="inlineStr">
-        <is>
-          <t>强势上攻</t>
-        </is>
-      </c>
-      <c r="H234" s="19" t="n">
+      <c r="G236" s="17" t="inlineStr">
+        <is>
+          <t>强势上攻</t>
+        </is>
+      </c>
+      <c r="H236" s="19" t="n">
         <v>20.01</v>
       </c>
-      <c r="I234" s="15" t="n">
+      <c r="I236" s="15" t="n">
         <v>29.06</v>
       </c>
-      <c r="J234" s="15" t="n"/>
-      <c r="K234" s="15" t="inlineStr">
-        <is>
-          <t>正常</t>
-        </is>
-      </c>
-      <c r="L234" s="15" t="inlineStr">
+      <c r="J236" s="15" t="n"/>
+      <c r="K236" s="15" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="L236" s="15" t="inlineStr">
         <is>
           <t>首日涨幅&gt;20%</t>
         </is>
       </c>
-      <c r="M234" s="15" t="inlineStr"/>
-    </row>
-    <row r="235" ht="26" customHeight="1">
-      <c r="A235" s="15" t="inlineStr">
+      <c r="M236" s="15" t="inlineStr"/>
+    </row>
+    <row r="237" ht="26" customHeight="1">
+      <c r="A237" s="15" t="inlineStr">
         <is>
           <t>300214</t>
         </is>
       </c>
-      <c r="B235" s="16" t="inlineStr">
+      <c r="B237" s="16" t="inlineStr">
         <is>
           <t>日科化学</t>
         </is>
       </c>
-      <c r="C235" s="15" t="inlineStr">
+      <c r="C237" s="15" t="inlineStr">
         <is>
           <t>算力/通信</t>
         </is>
       </c>
-      <c r="D235" s="15" t="inlineStr">
+      <c r="D237" s="15" t="inlineStr">
         <is>
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="E235" s="15" t="inlineStr">
+      <c r="E237" s="15" t="inlineStr">
         <is>
           <t>2026-07-27</t>
         </is>
       </c>
-      <c r="F235" s="15" t="n">
+      <c r="F237" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="G235" s="17" t="inlineStr">
-        <is>
-          <t>强势上攻</t>
-        </is>
-      </c>
-      <c r="H235" s="19" t="n">
+      <c r="G237" s="17" t="inlineStr">
+        <is>
+          <t>强势上攻</t>
+        </is>
+      </c>
+      <c r="H237" s="19" t="n">
         <v>19.98</v>
       </c>
-      <c r="I235" s="15" t="n">
+      <c r="I237" s="15" t="n">
         <v>32.25</v>
       </c>
-      <c r="J235" s="15" t="n">
+      <c r="J237" s="15" t="n">
         <v>1.51</v>
       </c>
-      <c r="K235" s="15" t="inlineStr">
+      <c r="K237" s="15" t="inlineStr">
         <is>
           <t>放量</t>
         </is>
       </c>
-      <c r="L235" s="15" t="inlineStr">
+      <c r="L237" s="15" t="inlineStr">
         <is>
           <t>首日涨幅&gt;20%</t>
         </is>
       </c>
-      <c r="M235" s="15" t="inlineStr"/>
-    </row>
-    <row r="236" ht="26" customHeight="1">
-      <c r="A236" s="7" t="inlineStr">
-        <is>
-          <t>603137</t>
-        </is>
-      </c>
-      <c r="B236" s="8" t="inlineStr">
-        <is>
-          <t>恒尚节能</t>
-        </is>
-      </c>
-      <c r="C236" s="7" t="inlineStr">
-        <is>
-          <t>半导体/芯片</t>
-        </is>
-      </c>
-      <c r="D236" s="7" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="E236" s="7" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-      <c r="F236" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="G236" s="7" t="inlineStr">
-        <is>
-          <t>强势上攻</t>
-        </is>
-      </c>
-      <c r="H236" s="13" t="n">
-        <v>10.01</v>
-      </c>
-      <c r="I236" s="7" t="n">
-        <v>37</v>
-      </c>
-      <c r="J236" s="7" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="K236" s="7" t="inlineStr">
-        <is>
-          <t>放量</t>
-        </is>
-      </c>
-      <c r="L236" s="7" t="inlineStr"/>
-      <c r="M236" s="7" t="inlineStr"/>
-    </row>
-    <row r="237" ht="26" customHeight="1">
-      <c r="A237" s="10" t="inlineStr">
-        <is>
-          <t>300534</t>
-        </is>
-      </c>
-      <c r="B237" s="11" t="inlineStr">
-        <is>
-          <t>陇神戎发</t>
-        </is>
-      </c>
-      <c r="C237" s="10" t="inlineStr">
-        <is>
-          <t>创新药/CRO</t>
-        </is>
-      </c>
-      <c r="D237" s="10" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="E237" s="10" t="inlineStr">
-        <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="F237" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="G237" s="10" t="inlineStr">
-        <is>
-          <t>强势上攻</t>
-        </is>
-      </c>
-      <c r="H237" s="12" t="n">
-        <v>20.04</v>
-      </c>
-      <c r="I237" s="10" t="n">
-        <v>46.22</v>
-      </c>
-      <c r="J237" s="10" t="n"/>
-      <c r="K237" s="10" t="inlineStr">
-        <is>
-          <t>正常</t>
-        </is>
-      </c>
-      <c r="L237" s="10" t="inlineStr"/>
-      <c r="M237" s="10" t="inlineStr"/>
+      <c r="M237" s="15" t="inlineStr"/>
     </row>
     <row r="238" ht="26" customHeight="1">
       <c r="A238" s="7" t="inlineStr">
         <is>
-          <t>301520</t>
+          <t>603137</t>
         </is>
       </c>
       <c r="B238" s="8" t="inlineStr">
         <is>
-          <t>万邦医药</t>
+          <t>恒尚节能</t>
         </is>
       </c>
       <c r="C238" s="7" t="inlineStr">
         <is>
-          <t>创新药/CRO</t>
+          <t>半导体/芯片</t>
         </is>
       </c>
       <c r="D238" s="7" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="E238" s="7" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="F238" s="7" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G238" s="7" t="inlineStr">
         <is>
@@ -12632,96 +12618,90 @@
         </is>
       </c>
       <c r="H238" s="13" t="n">
-        <v>13.37</v>
+        <v>10.01</v>
       </c>
       <c r="I238" s="7" t="n">
-        <v>53.52</v>
+        <v>37</v>
       </c>
       <c r="J238" s="7" t="n">
-        <v>1.08</v>
+        <v>1.45</v>
       </c>
       <c r="K238" s="7" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>放量</t>
         </is>
       </c>
       <c r="L238" s="7" t="inlineStr"/>
       <c r="M238" s="7" t="inlineStr"/>
     </row>
     <row r="239" ht="26" customHeight="1">
-      <c r="A239" s="15" t="inlineStr">
-        <is>
-          <t>301234</t>
-        </is>
-      </c>
-      <c r="B239" s="16" t="inlineStr">
-        <is>
-          <t>五洲医疗</t>
-        </is>
-      </c>
-      <c r="C239" s="15" t="inlineStr">
+      <c r="A239" s="10" t="inlineStr">
+        <is>
+          <t>300534</t>
+        </is>
+      </c>
+      <c r="B239" s="11" t="inlineStr">
+        <is>
+          <t>陇神戎发</t>
+        </is>
+      </c>
+      <c r="C239" s="10" t="inlineStr">
         <is>
           <t>创新药/CRO</t>
         </is>
       </c>
-      <c r="D239" s="15" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="E239" s="15" t="inlineStr">
+      <c r="D239" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="E239" s="10" t="inlineStr">
         <is>
           <t>2026-07-27</t>
         </is>
       </c>
-      <c r="F239" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="G239" s="17" t="inlineStr">
-        <is>
-          <t>强势上攻</t>
-        </is>
-      </c>
-      <c r="H239" s="19" t="n">
-        <v>20</v>
-      </c>
-      <c r="I239" s="15" t="n">
-        <v>73.03</v>
-      </c>
-      <c r="J239" s="15" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="K239" s="15" t="inlineStr">
-        <is>
-          <t>放量</t>
-        </is>
-      </c>
-      <c r="L239" s="15" t="inlineStr">
-        <is>
-          <t>首日涨幅&gt;20%</t>
-        </is>
-      </c>
-      <c r="M239" s="15" t="inlineStr"/>
+      <c r="F239" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="G239" s="10" t="inlineStr">
+        <is>
+          <t>强势上攻</t>
+        </is>
+      </c>
+      <c r="H239" s="12" t="n">
+        <v>20.04</v>
+      </c>
+      <c r="I239" s="10" t="n">
+        <v>46.22</v>
+      </c>
+      <c r="J239" s="10" t="n"/>
+      <c r="K239" s="10" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="L239" s="10" t="inlineStr"/>
+      <c r="M239" s="10" t="inlineStr"/>
     </row>
     <row r="240" ht="26" customHeight="1">
       <c r="A240" s="7" t="inlineStr">
         <is>
-          <t>002141</t>
+          <t>301520</t>
         </is>
       </c>
       <c r="B240" s="8" t="inlineStr">
         <is>
-          <t>贤丰控股</t>
+          <t>万邦医药</t>
         </is>
       </c>
       <c r="C240" s="7" t="inlineStr">
         <is>
-          <t>算力/通信</t>
+          <t>创新药/CRO</t>
         </is>
       </c>
       <c r="D240" s="7" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="E240" s="7" t="inlineStr">
@@ -12730,7 +12710,7 @@
         </is>
       </c>
       <c r="F240" s="7" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G240" s="7" t="inlineStr">
         <is>
@@ -12738,91 +12718,105 @@
         </is>
       </c>
       <c r="H240" s="13" t="n">
-        <v>5.35</v>
-      </c>
-      <c r="I240" s="7" t="n"/>
-      <c r="J240" s="7" t="n"/>
-      <c r="K240" s="7" t="inlineStr"/>
+        <v>13.37</v>
+      </c>
+      <c r="I240" s="7" t="n">
+        <v>53.52</v>
+      </c>
+      <c r="J240" s="7" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="K240" s="7" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
       <c r="L240" s="7" t="inlineStr"/>
       <c r="M240" s="7" t="inlineStr"/>
     </row>
     <row r="241" ht="26" customHeight="1">
-      <c r="A241" s="10" t="inlineStr">
-        <is>
-          <t>301191</t>
-        </is>
-      </c>
-      <c r="B241" s="11" t="inlineStr">
-        <is>
-          <t>菲菱科思</t>
-        </is>
-      </c>
-      <c r="C241" s="10" t="inlineStr">
-        <is>
-          <t>算力/通信</t>
-        </is>
-      </c>
-      <c r="D241" s="10" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="E241" s="10" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="F241" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="G241" s="10" t="inlineStr">
-        <is>
-          <t>强势上攻</t>
-        </is>
-      </c>
-      <c r="H241" s="12" t="n">
-        <v>5.09</v>
-      </c>
-      <c r="I241" s="10" t="n"/>
-      <c r="J241" s="10" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="K241" s="10" t="inlineStr">
-        <is>
-          <t>正常</t>
-        </is>
-      </c>
-      <c r="L241" s="10" t="inlineStr"/>
-      <c r="M241" s="10" t="inlineStr"/>
+      <c r="A241" s="15" t="inlineStr">
+        <is>
+          <t>301234</t>
+        </is>
+      </c>
+      <c r="B241" s="16" t="inlineStr">
+        <is>
+          <t>五洲医疗</t>
+        </is>
+      </c>
+      <c r="C241" s="15" t="inlineStr">
+        <is>
+          <t>创新药/CRO</t>
+        </is>
+      </c>
+      <c r="D241" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="E241" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="F241" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="G241" s="17" t="inlineStr">
+        <is>
+          <t>强势上攻</t>
+        </is>
+      </c>
+      <c r="H241" s="19" t="n">
+        <v>20</v>
+      </c>
+      <c r="I241" s="15" t="n">
+        <v>73.03</v>
+      </c>
+      <c r="J241" s="15" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="K241" s="15" t="inlineStr">
+        <is>
+          <t>放量</t>
+        </is>
+      </c>
+      <c r="L241" s="15" t="inlineStr">
+        <is>
+          <t>首日涨幅&gt;20%</t>
+        </is>
+      </c>
+      <c r="M241" s="15" t="inlineStr"/>
     </row>
     <row r="242" ht="26" customHeight="1">
       <c r="A242" s="7" t="inlineStr">
         <is>
-          <t>000739</t>
+          <t>002141</t>
         </is>
       </c>
       <c r="B242" s="8" t="inlineStr">
         <is>
-          <t>普洛药业</t>
+          <t>贤丰控股</t>
         </is>
       </c>
       <c r="C242" s="7" t="inlineStr">
         <is>
-          <t>创新药/CRO</t>
+          <t>算力/通信</t>
         </is>
       </c>
       <c r="D242" s="7" t="inlineStr">
         <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="E242" s="7" t="inlineStr">
+        <is>
           <t>2026-07-16</t>
         </is>
       </c>
-      <c r="E242" s="7" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
       <c r="F242" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G242" s="7" t="inlineStr">
         <is>
@@ -12830,7 +12824,7 @@
         </is>
       </c>
       <c r="H242" s="13" t="n">
-        <v>3.53</v>
+        <v>5.35</v>
       </c>
       <c r="I242" s="7" t="n"/>
       <c r="J242" s="7" t="n"/>
@@ -12841,27 +12835,27 @@
     <row r="243" ht="26" customHeight="1">
       <c r="A243" s="10" t="inlineStr">
         <is>
-          <t>600881</t>
+          <t>301191</t>
         </is>
       </c>
       <c r="B243" s="11" t="inlineStr">
         <is>
-          <t>亚泰集团</t>
+          <t>菲菱科思</t>
         </is>
       </c>
       <c r="C243" s="10" t="inlineStr">
         <is>
-          <t>创新药/CRO</t>
+          <t>算力/通信</t>
         </is>
       </c>
       <c r="D243" s="10" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="E243" s="10" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="F243" s="10" t="n">
@@ -12873,23 +12867,29 @@
         </is>
       </c>
       <c r="H243" s="12" t="n">
-        <v>10.06</v>
+        <v>5.09</v>
       </c>
       <c r="I243" s="10" t="n"/>
-      <c r="J243" s="10" t="n"/>
-      <c r="K243" s="10" t="inlineStr"/>
+      <c r="J243" s="10" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="K243" s="10" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
       <c r="L243" s="10" t="inlineStr"/>
       <c r="M243" s="10" t="inlineStr"/>
     </row>
     <row r="244" ht="26" customHeight="1">
       <c r="A244" s="7" t="inlineStr">
         <is>
-          <t>002412</t>
+          <t>000739</t>
         </is>
       </c>
       <c r="B244" s="8" t="inlineStr">
         <is>
-          <t>汉森制药</t>
+          <t>普洛药业</t>
         </is>
       </c>
       <c r="C244" s="7" t="inlineStr">
@@ -12899,16 +12899,16 @@
       </c>
       <c r="D244" s="7" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="E244" s="7" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="F244" s="7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G244" s="7" t="inlineStr">
         <is>
@@ -12916,7 +12916,7 @@
         </is>
       </c>
       <c r="H244" s="13" t="n">
-        <v>9.99</v>
+        <v>3.53</v>
       </c>
       <c r="I244" s="7" t="n"/>
       <c r="J244" s="7" t="n"/>
@@ -12925,62 +12925,148 @@
       <c r="M244" s="7" t="inlineStr"/>
     </row>
     <row r="245" ht="26" customHeight="1">
-      <c r="A245" s="15" t="inlineStr">
+      <c r="A245" s="10" t="inlineStr">
+        <is>
+          <t>600881</t>
+        </is>
+      </c>
+      <c r="B245" s="11" t="inlineStr">
+        <is>
+          <t>亚泰集团</t>
+        </is>
+      </c>
+      <c r="C245" s="10" t="inlineStr">
+        <is>
+          <t>创新药/CRO</t>
+        </is>
+      </c>
+      <c r="D245" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="E245" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="F245" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G245" s="10" t="inlineStr">
+        <is>
+          <t>强势上攻</t>
+        </is>
+      </c>
+      <c r="H245" s="12" t="n">
+        <v>10.06</v>
+      </c>
+      <c r="I245" s="10" t="n"/>
+      <c r="J245" s="10" t="n"/>
+      <c r="K245" s="10" t="inlineStr"/>
+      <c r="L245" s="10" t="inlineStr"/>
+      <c r="M245" s="10" t="inlineStr"/>
+    </row>
+    <row r="246" ht="26" customHeight="1">
+      <c r="A246" s="7" t="inlineStr">
+        <is>
+          <t>002412</t>
+        </is>
+      </c>
+      <c r="B246" s="8" t="inlineStr">
+        <is>
+          <t>汉森制药</t>
+        </is>
+      </c>
+      <c r="C246" s="7" t="inlineStr">
+        <is>
+          <t>创新药/CRO</t>
+        </is>
+      </c>
+      <c r="D246" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="E246" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="F246" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G246" s="7" t="inlineStr">
+        <is>
+          <t>强势上攻</t>
+        </is>
+      </c>
+      <c r="H246" s="13" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="I246" s="7" t="n"/>
+      <c r="J246" s="7" t="n"/>
+      <c r="K246" s="7" t="inlineStr"/>
+      <c r="L246" s="7" t="inlineStr"/>
+      <c r="M246" s="7" t="inlineStr"/>
+    </row>
+    <row r="247" ht="26" customHeight="1">
+      <c r="A247" s="15" t="inlineStr">
         <is>
           <t>688710</t>
         </is>
       </c>
-      <c r="B245" s="16" t="inlineStr">
+      <c r="B247" s="16" t="inlineStr">
         <is>
           <t>益诺思</t>
         </is>
       </c>
-      <c r="C245" s="15" t="inlineStr">
+      <c r="C247" s="15" t="inlineStr">
         <is>
           <t>创新药/CRO</t>
         </is>
       </c>
-      <c r="D245" s="15" t="inlineStr">
+      <c r="D247" s="15" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
-      <c r="E245" s="15" t="inlineStr">
+      <c r="E247" s="15" t="inlineStr">
         <is>
           <t>2026-07-14</t>
         </is>
       </c>
-      <c r="F245" s="15" t="n">
+      <c r="F247" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="G245" s="19" t="inlineStr">
+      <c r="G247" s="19" t="inlineStr">
         <is>
           <t>放量下跌</t>
         </is>
       </c>
-      <c r="H245" s="18" t="n">
+      <c r="H247" s="18" t="n">
         <v>-3.5</v>
       </c>
-      <c r="I245" s="15" t="n">
+      <c r="I247" s="15" t="n">
         <v>17.48</v>
       </c>
-      <c r="J245" s="15" t="n">
+      <c r="J247" s="15" t="n">
         <v>1.3</v>
       </c>
-      <c r="K245" s="15" t="inlineStr">
+      <c r="K247" s="15" t="inlineStr">
         <is>
           <t>放量</t>
         </is>
       </c>
-      <c r="L245" s="15" t="inlineStr">
+      <c r="L247" s="15" t="inlineStr">
         <is>
           <t>首日涨幅&gt;20%</t>
         </is>
       </c>
-      <c r="M245" s="15" t="inlineStr"/>
+      <c r="M247" s="15" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:N245"/>
+  <autoFilter ref="A3:N247"/>
   <mergeCells count="1">
     <mergeCell ref="A1:N1"/>
   </mergeCells>
@@ -13012,7 +13098,7 @@
     <row r="1">
       <c r="A1" s="20" t="inlineStr">
         <is>
-          <t>狙击池 2026-07-27</t>
+          <t>狙击池 2026-07-29</t>
         </is>
       </c>
     </row>
@@ -13106,7 +13192,7 @@
     <row r="1">
       <c r="A1" s="22" t="inlineStr">
         <is>
-          <t>后备池 2026-07-27</t>
+          <t>后备池 2026-07-29</t>
         </is>
       </c>
     </row>
@@ -14396,7 +14482,7 @@
     <row r="1">
       <c r="A1" s="24" t="inlineStr">
         <is>
-          <t>持仓预警 2026-07-27</t>
+          <t>持仓预警 2026-07-29</t>
         </is>
       </c>
     </row>
@@ -14473,7 +14559,7 @@
     <row r="1" ht="36" customHeight="1">
       <c r="A1" s="25" t="inlineStr">
         <is>
-          <t>回踩狙击榜 2026-07-27 (10只·按综合分排序)</t>
+          <t>回踩狙击榜 2026-07-29 (10只·按综合分排序)</t>
         </is>
       </c>
     </row>
@@ -14560,7 +14646,7 @@
         <v>76</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
@@ -14600,10 +14686,10 @@
         </is>
       </c>
       <c r="F5" s="10" t="n">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="G5" s="10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H5" s="10" t="inlineStr">
         <is>
@@ -14625,16 +14711,16 @@
     <row r="6" ht="26" customHeight="1">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>601607</t>
+          <t>301393</t>
         </is>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>上海医药 NEW</t>
-        </is>
-      </c>
-      <c r="C6" s="7" t="n">
-        <v>1.52</v>
+          <t>昊帆生物</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="n">
+        <v>0.46</v>
       </c>
       <c r="D6" s="7" t="n"/>
       <c r="E6" s="7" t="inlineStr">
@@ -14643,41 +14729,41 @@
         </is>
       </c>
       <c r="F6" s="7" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>0.49</v>
+        <v>-1.27</v>
       </c>
       <c r="J6" s="7" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K6" s="7" t="inlineStr">
         <is>
-          <t>疑似出货</t>
+          <t>★极近均线</t>
         </is>
       </c>
     </row>
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="10" t="inlineStr">
         <is>
-          <t>301393</t>
+          <t>601607</t>
         </is>
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>昊帆生物</t>
-        </is>
-      </c>
-      <c r="C7" s="14" t="n">
-        <v>0.46</v>
+          <t>上海医药</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="n">
+        <v>1.52</v>
       </c>
       <c r="D7" s="10" t="n"/>
       <c r="E7" s="10" t="inlineStr">
@@ -14686,25 +14772,25 @@
         </is>
       </c>
       <c r="F7" s="10" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G7" s="10" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="H7" s="10" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="I7" s="10" t="n">
-        <v>-1.27</v>
+        <v>0.49</v>
       </c>
       <c r="J7" s="10" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K7" s="10" t="inlineStr">
         <is>
-          <t>★极近均线</t>
+          <t>疑似出货</t>
         </is>
       </c>
     </row>
@@ -14731,10 +14817,10 @@
         </is>
       </c>
       <c r="F8" s="7" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
@@ -14772,10 +14858,10 @@
         </is>
       </c>
       <c r="F9" s="10" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="G9" s="10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H9" s="10" t="inlineStr">
         <is>
@@ -14786,7 +14872,7 @@
         <v>0.85</v>
       </c>
       <c r="J9" s="10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K9" s="10" t="inlineStr">
         <is>
@@ -14820,7 +14906,7 @@
         <v>33</v>
       </c>
       <c r="G10" s="7" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
@@ -14831,7 +14917,7 @@
         <v>-1.92</v>
       </c>
       <c r="J10" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K10" s="7" t="inlineStr"/>
     </row>
@@ -14861,7 +14947,7 @@
         <v>30</v>
       </c>
       <c r="G11" s="10" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H11" s="10" t="inlineStr">
         <is>
@@ -14872,7 +14958,7 @@
         <v>0.05</v>
       </c>
       <c r="J11" s="10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K11" s="10" t="inlineStr"/>
     </row>
@@ -14902,7 +14988,7 @@
         <v>20</v>
       </c>
       <c r="G12" s="7" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
@@ -14940,10 +15026,10 @@
         </is>
       </c>
       <c r="F13" s="10" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G13" s="10" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H13" s="10" t="inlineStr">
         <is>
@@ -15019,7 +15105,7 @@
       </c>
       <c r="B5" s="28" t="inlineStr">
         <is>
-          <t>医药(3), 通信(1), 芯片(1)</t>
+          <t>AI(1), 机器人(1), 通信(1)</t>
         </is>
       </c>
     </row>
